--- a/Manga.Manhwua/Updated manhwua.xlsx
+++ b/Manga.Manhwua/Updated manhwua.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Manga\Manga.Manhwua\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C3AD8D-37DA-49C8-B37E-25FDCA5301BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88ABB921-EB00-49FA-9395-2BA3CD4B9121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="386">
   <si>
     <t>Title</t>
   </si>
@@ -1210,18 +1210,28 @@
   <si>
     <t>The Genius Martial Artist Who Remembers Everything</t>
   </si>
+  <si>
+    <t>The Dark Mage’s Return to Enlistment</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1312,7 +1322,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1332,17 +1342,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1377,23 +1407,6 @@
         </right>
         <top/>
         <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
       </border>
     </dxf>
   </dxfs>
@@ -1478,11 +1491,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A9821095-33AF-4937-9131-C6EA9C68C3CC}" name="Table2" displayName="Table2" ref="A1:B1048576" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="2" tableBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A9821095-33AF-4937-9131-C6EA9C68C3CC}" name="Table2" displayName="Table2" ref="A1:B1048576" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="2" tableBorderDxfId="1">
   <autoFilter ref="A1:B1048576" xr:uid="{A9821095-33AF-4937-9131-C6EA9C68C3CC}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{678D9D41-282A-4DD7-BC85-778E9EDE1B90}" name="Title"/>
-    <tableColumn id="2" xr3:uid="{350740A5-DA27-48C1-843B-6CB73278A439}" name="Episodes" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{350740A5-DA27-48C1-843B-6CB73278A439}" name="Episodes" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1667,7 +1680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B385"/>
+  <dimension ref="A1:B386"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="169" customWidth="1"/>
@@ -4754,11 +4767,19 @@
         <v>6</v>
       </c>
     </row>
+    <row r="386" spans="1:2">
+      <c r="A386" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="B386" s="1">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Manga.Manhwua/Updated manhwua.xlsx
+++ b/Manga.Manhwua/Updated manhwua.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="385">
   <si>
     <t xml:space="preserve">Title</t>
   </si>
@@ -1201,6 +1201,9 @@
   </si>
   <si>
     <t xml:space="preserve">The Genius Martial Artist Who Remembers Everything</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Shepherd Wizard</t>
   </si>
 </sst>
 </file>
@@ -1337,7 +1340,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1372,6 +1375,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -4732,9 +4739,13 @@
         <v>26</v>
       </c>
     </row>
-    <row r="385" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A385" s="0"/>
-      <c r="B385" s="0"/>
+    <row r="385" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A385" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="B385" s="9" t="n">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Manga.Manhwua/Updated manhwua.xlsx
+++ b/Manga.Manhwua/Updated manhwua.xlsx
@@ -1,22 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Manga\Manga.Manhwua\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{0DF4870B-27D9-410B-B860-D791AECF0B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -28,511 +22,511 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="386">
   <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Episodes</t>
-  </si>
-  <si>
-    <t>Kingdom</t>
-  </si>
-  <si>
-    <t>Vagabond</t>
-  </si>
-  <si>
-    <t>My Dragon System</t>
-  </si>
-  <si>
-    <t>The Knight King Who Returned With A God</t>
-  </si>
-  <si>
-    <t>The Player Hides His Past</t>
-  </si>
-  <si>
-    <t>Disastrous Necromancer</t>
-  </si>
-  <si>
-    <t>The Priest of Corruption</t>
-  </si>
-  <si>
-    <t>Dragon Emperor Martial God</t>
-  </si>
-  <si>
-    <t>Mookhyang - Dark Lady</t>
-  </si>
-  <si>
-    <t>Leveling Up By Hoarding</t>
-  </si>
-  <si>
-    <t>Master Of The Martial Arts Library</t>
-  </si>
-  <si>
-    <t>Absolute Necromancer</t>
-  </si>
-  <si>
-    <t>Tales Of A Shinning Sword</t>
-  </si>
-  <si>
-    <t>Kyushu Chronicles Of Immortals And Demons</t>
-  </si>
-  <si>
-    <t>Level 1 Player</t>
-  </si>
-  <si>
-    <t>Logging 10,000 Years into the Future</t>
-  </si>
-  <si>
-    <t>Swordmaster’S Youngest Son</t>
-  </si>
-  <si>
-    <t>World’S Greatest Senior Disciple</t>
-  </si>
-  <si>
-    <t>Dragon Master</t>
-  </si>
-  <si>
-    <t>The Return Of The Disaster-Class Hero</t>
-  </si>
-  <si>
-    <t>Solo Farming In The Tower</t>
-  </si>
-  <si>
-    <t>Chronicles Of The Demon Faction</t>
-  </si>
-  <si>
-    <t>Demonic Master Of Mount Kunlun</t>
-  </si>
-  <si>
-    <t>Necromancer's Evolutionary Traits</t>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Episodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vagabond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Dragon System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Knight King Who Returned With A God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Player Hides His Past</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disastrous Necromancer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Priest of Corruption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragon Emperor Martial God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mookhyang - Dark Lady</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leveling Up By Hoarding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master Of The Martial Arts Library</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Absolute Necromancer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tales Of A Shinning Sword</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyushu Chronicles Of Immortals And Demons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level 1 Player</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logging 10,000 Years into the Future</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swordmaster’S Youngest Son</t>
+  </si>
+  <si>
+    <t xml:space="preserve">World’S Greatest Senior Disciple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragon Master</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Return Of The Disaster-Class Hero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo Farming In The Tower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chronicles Of The Demon Faction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demonic Master Of Mount Kunlun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Necromancer's Evolutionary Traits</t>
   </si>
   <si>
     <t xml:space="preserve">Samurai In Another World </t>
   </si>
   <si>
-    <t>Peerless Quest – The Cheat Skill Only I Can Use</t>
-  </si>
-  <si>
-    <t>Isekai De Haishin Katsudou Wo Shitara Tairyou No Yandere Shinja Wo Umidashite Shimatta Ken</t>
-  </si>
-  <si>
-    <t>Boundless Necromancer</t>
-  </si>
-  <si>
-    <t>Academy’S Genius Swordsman</t>
-  </si>
-  <si>
-    <t>Demon Evolution</t>
-  </si>
-  <si>
-    <t>The Iron-Blooded Necromancer Has Returned</t>
-  </si>
-  <si>
-    <t>Infinite Mage</t>
-  </si>
-  <si>
-    <t>Star Instructor  Master Baek</t>
-  </si>
-  <si>
-    <t>The Story Of Thorny Spear</t>
-  </si>
-  <si>
-    <t>Blade debt</t>
-  </si>
-  <si>
-    <t>Martial God Regressed To Level 2</t>
-  </si>
-  <si>
-    <t>What, You Dare Pretend In Front Of Me, The Strongest In The Immortal World?</t>
-  </si>
-  <si>
-    <t>Terminally-Ill Genius Dark Knight</t>
-  </si>
-  <si>
-    <t>Heavenly Inquisition Sword</t>
-  </si>
-  <si>
-    <t>Tsuki Ga Michibiku Isekai Douchuu</t>
-  </si>
-  <si>
-    <t>The Emperor’s Sword</t>
-  </si>
-  <si>
-    <t>The Constellations Are My Disciples</t>
-  </si>
-  <si>
-    <t>Revenge of the Iron-Blooded Sword Hound</t>
-  </si>
-  <si>
-    <t>Mr. Zombie</t>
-  </si>
-  <si>
-    <t>Master: This Villainous Disciple Is Not The Holy Child</t>
-  </si>
-  <si>
-    <t>Solo Max-Level Newbie</t>
-  </si>
-  <si>
-    <t>Murim Login</t>
-  </si>
-  <si>
-    <t>The Great Villain Who Threatened to Kill Himself</t>
-  </si>
-  <si>
-    <t>Weapon Maker</t>
-  </si>
-  <si>
-    <t>The Reincarnated Assassin is a Genius Swordsman</t>
-  </si>
-  <si>
-    <t>I was more overpowered than the hero, so I hid my power!</t>
-  </si>
-  <si>
-    <t>Million Times Attack Speed</t>
-  </si>
-  <si>
-    <t>I am the descendant of the Divine Dragon</t>
-  </si>
-  <si>
-    <t>Hero X Demon Queen</t>
-  </si>
-  <si>
-    <t>Records Of The Demonic Path’S Return</t>
-  </si>
-  <si>
-    <t>Five-Dimensional Zone</t>
-  </si>
-  <si>
-    <t>Legendary Youngest Son Of The Marquis House</t>
-  </si>
-  <si>
-    <t>I am fated villain</t>
-  </si>
-  <si>
-    <t>Return Of The Mount Hua Sect</t>
-  </si>
-  <si>
-    <t>Beyond Myriad Peoples</t>
-  </si>
-  <si>
-    <t>Nano Machine</t>
-  </si>
-  <si>
-    <t>Tensei Shitara Dai Nana Ouji Dattanode, Kimamani Majutsu O Kiwamemasu</t>
-  </si>
-  <si>
-    <t>Scoring the Sacred Body of the Ancients from the Get-go</t>
-  </si>
-  <si>
-    <t>Magic Emperor</t>
-  </si>
-  <si>
-    <t>Martial Peak</t>
-  </si>
-  <si>
-    <t>The Self-Disciplined Me Is Practically Invincible</t>
-  </si>
-  <si>
-    <t>Global Power: I Can Control All The Elements</t>
-  </si>
-  <si>
-    <t>Moon Slayer</t>
-  </si>
-  <si>
-    <t>Lightning Degree</t>
-  </si>
-  <si>
-    <t>The World's Best Sect Of Dependency</t>
-  </si>
-  <si>
-    <t>The Return Of Apocalypses Tyrant</t>
-  </si>
-  <si>
-    <t>What Do You Do When You Suddenly Become An Immortal?</t>
-  </si>
-  <si>
-    <t>Tales Of Demons And Gods</t>
-  </si>
-  <si>
-    <t>The Kingdoms Of Ruin</t>
-  </si>
-  <si>
-    <t>Necromancer Academy And The Genius Summoner</t>
-  </si>
-  <si>
-    <t>Yuan Zun</t>
-  </si>
-  <si>
-    <t>The Greatest Estate Designer</t>
-  </si>
-  <si>
-    <t>Conqueror of modern martial arts Kang Haejin</t>
-  </si>
-  <si>
-    <t>Records Of The Swordsman Scholar</t>
-  </si>
-  <si>
-    <t>The Scholar's Reincarnation</t>
-  </si>
-  <si>
-    <t>Tale of a Scribe Who Retires To The Countryside</t>
-  </si>
-  <si>
-    <t>Return Of The Bachelor</t>
-  </si>
-  <si>
-    <t>Reincarnation Of The Murim Clan's Former Ranker</t>
-  </si>
-  <si>
-    <t>Regressing with the King’s Power</t>
-  </si>
-  <si>
-    <t>The Last Cultivator</t>
-  </si>
-  <si>
-    <t>HEAVENLY MOON</t>
-  </si>
-  <si>
-    <t>Infinite Leveling: Murim</t>
-  </si>
-  <si>
-    <t>Volcanic Age</t>
-  </si>
-  <si>
-    <t>Chronicles Of A Returner</t>
-  </si>
-  <si>
-    <t>The Undefeatable Swordsman</t>
-  </si>
-  <si>
-    <t>Second Life of Dongfang Bubai</t>
-  </si>
-  <si>
-    <t>Job Change: I Became The Undead Monarch</t>
-  </si>
-  <si>
-    <t>Relife Player</t>
-  </si>
-  <si>
-    <t>My Lucky Encounter From The Game Turned Into Reality</t>
-  </si>
-  <si>
-    <t>I Killed an Academy Player</t>
-  </si>
-  <si>
-    <t>Bloodhound’s Regression Instinct</t>
-  </si>
-  <si>
-    <t>I Raised the Yandere Villain Empress</t>
-  </si>
-  <si>
-    <t>The Max-Level Player’s 100th Regression</t>
-  </si>
-  <si>
-    <t>The Heavenly Demon Can't Live A Normal Life</t>
-  </si>
-  <si>
-    <t>The Player That Can't Level Up</t>
-  </si>
-  <si>
-    <t>Reborn As The Enemy Prince</t>
-  </si>
-  <si>
-    <t>The Archmage's Restaurant</t>
-  </si>
-  <si>
-    <t>I Rely on My Invincibility to Deal Tons of Damage Passively!</t>
-  </si>
-  <si>
-    <t>Wild West Murim</t>
-  </si>
-  <si>
-    <t>Monster Pet Evolution</t>
-  </si>
-  <si>
-    <t>The Strongest Sect Of All Times</t>
-  </si>
-  <si>
-    <t>Youngest Scion Of The Mages</t>
-  </si>
-  <si>
-    <t>I Will Do Whatever I Want In Ten Thousand Years</t>
-  </si>
-  <si>
-    <t>Genkai Level 1 Kara No Nariagari: Saijaku Level No Ore Ga Isekai Saikyou Ni Naru Made</t>
-  </si>
-  <si>
-    <t>How to Live at the Max Level</t>
-  </si>
-  <si>
-    <t>The All-Knowing Cultivator</t>
-  </si>
-  <si>
-    <t>Kurasu ≪Mushoku≫ No Eiyuu-Tan ~Koushaku-Ka O Tsuihou Sareta Ga, Jitsu Wa Nagutta Dake De Sukiru O Kakutoku Dekiru To Wakari, Tairiku Ichi No Eiyuu Ni Nobori Tsumeru</t>
-  </si>
-  <si>
-    <t>Villager A Wants To Save The Villainess No Matter What!</t>
-  </si>
-  <si>
-    <t>Savage Hero</t>
-  </si>
-  <si>
-    <t>Genkai Koe No Tenpu wa, Tensei-sha ni Shika Atsukaenai Overlimit Skill Holders</t>
-  </si>
-  <si>
-    <t>Maken Tsukai No Moto Shounen Hei Wa, Moto Teki Kanbu No Onee-San To Issho Ni Ikitai</t>
-  </si>
-  <si>
-    <t>Mannen D-Rank No Chuunen Boukensha, Yotta Ikioi De Densetsu No Ken Wo Hikkonuku</t>
-  </si>
-  <si>
-    <t>Dungeon Sherpa: Meikyuu Michisaki Annainin</t>
-  </si>
-  <si>
-    <t>A Sword Master Childhood Friend Power Harassed Me Harshly, So I Broke Off Our Relationship And Made A Fresh Start At The Frontier As A Magic Swordsman</t>
-  </si>
-  <si>
-    <t>I Summoned The Devil To Grant Me A Wish, But I Married Her Instead Since She Was Adorable ~My New Devil Wife~</t>
-  </si>
-  <si>
-    <t>A Story About A Dragon And The Rising Of An Adventurer</t>
-  </si>
-  <si>
-    <t>After Being Called A Hero: The Unrivaled Man Starts A Family</t>
-  </si>
-  <si>
-    <t>A Warrior Exiled By The Hero And His Lover</t>
-  </si>
-  <si>
-    <t>Nimotsu Mochi No Nousuji Musou</t>
-  </si>
-  <si>
-    <t>The Strongest Dull Prince’s Secret Battle for the Throne</t>
-  </si>
-  <si>
-    <t>The Sword of Princess Gluttony</t>
-  </si>
-  <si>
-    <t>Wistoria's Wand And Sword</t>
-  </si>
-  <si>
-    <t>The Crafty Mage: Frontier Settling Made Easy</t>
-  </si>
-  <si>
-    <t>Delivery Man From Murim</t>
-  </si>
-  <si>
-    <t>Henkyou Gurashi No Maou, Tensei Shite Saikyou No Majutsushi Ni Naru</t>
-  </si>
-  <si>
-    <t>The Executed Sage Is Reincarnated As A Lich And Starts An All-Out War</t>
-  </si>
-  <si>
-    <t>Dungeon Ni Hisomu Yandere Na Kanojo Ni Ore Wa Nando Mo Korosareru</t>
-  </si>
-  <si>
-    <t>I Became A Big-Shot On The Heavenly Leaderboard</t>
-  </si>
-  <si>
-    <t>The Dark Magician Transmigrates After 66666 Years</t>
-  </si>
-  <si>
-    <t>Reaper Of The Drifting Moon</t>
-  </si>
-  <si>
-    <t>The Unbeatable Dungeon's Lazy Boss Monster</t>
-  </si>
-  <si>
-    <t>All My Abilities Are Forbidden Spells</t>
-  </si>
-  <si>
-    <t>How To Survive As A Dragon With Time-Limit</t>
-  </si>
-  <si>
-    <t>Myst, Might, Mayhem</t>
-  </si>
-  <si>
-    <t>Dark And Light Martial Emperor</t>
-  </si>
-  <si>
-    <t>The doomsday ruthless man: hoarding trillions of supplies at the beginning</t>
-  </si>
-  <si>
-    <t>Becoming the Swordmaster Rank Young Lord of the Sichuan Tang Family</t>
-  </si>
-  <si>
-    <t>This Account Is Ridiculous</t>
-  </si>
-  <si>
-    <t>The Mysterious World’s Greatest Martial Artist Little Prince</t>
-  </si>
-  <si>
-    <t>The Reborn Young Lord Is An Assassin</t>
-  </si>
-  <si>
-    <t>God-Slaying Copycat</t>
-  </si>
-  <si>
-    <t>The Great Mage Of The Hero’S Party Reincarnates</t>
-  </si>
-  <si>
-    <t>My Brother Is The Chosen One</t>
-  </si>
-  <si>
-    <t>The Max Level Hero Strikes Back</t>
-  </si>
-  <si>
-    <t>Overlord of Insects</t>
-  </si>
-  <si>
-    <t>Game Of Familia: Kazoku Senki</t>
-  </si>
-  <si>
-    <t>Grand General</t>
-  </si>
-  <si>
-    <t>The Legendary Spearman Returns</t>
-  </si>
-  <si>
-    <t>Ice lord</t>
-  </si>
-  <si>
-    <t>My Inventory is Abnormal</t>
-  </si>
-  <si>
-    <t>Escort Agency Of The Apocalypse</t>
-  </si>
-  <si>
-    <t>The Heavenly Demon Will Give You a Massage</t>
-  </si>
-  <si>
-    <t>The Twin Swords Of The Sima</t>
-  </si>
-  <si>
-    <t>Versatile Sword Cultivator</t>
-  </si>
-  <si>
-    <t>Asura</t>
-  </si>
-  <si>
-    <t>Magic Academy’s Genius Blinker</t>
-  </si>
-  <si>
-    <t>Worthless Profession: Dragon Tamer</t>
-  </si>
-  <si>
-    <t>Expelled Hero Is Too Strong</t>
-  </si>
-  <si>
-    <t>The Ten Thousand Clans Invasion: Guardian Of The Rear</t>
-  </si>
-  <si>
-    <t>My Disciple Became the Great Demon Empress?!</t>
-  </si>
-  <si>
-    <t>The Greatest In The World</t>
-  </si>
-  <si>
-    <t>Drawing: The Greatest Mangaka Becomes A Skilled “Martial Artist” In Another World</t>
+    <t xml:space="preserve">Peerless Quest – The Cheat Skill Only I Can Use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isekai De Haishin Katsudou Wo Shitara Tairyou No Yandere Shinja Wo Umidashite Shimatta Ken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boundless Necromancer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Academy’S Genius Swordsman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demon Evolution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Iron-Blooded Necromancer Has Returned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infinite Mage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Star Instructor  Master Baek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Story Of Thorny Spear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blade debt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martial God Regressed To Level 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What, You Dare Pretend In Front Of Me, The Strongest In The Immortal World?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminally-Ill Genius Dark Knight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heavenly Inquisition Sword</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tsuki Ga Michibiku Isekai Douchuu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Emperor’s Sword</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Constellations Are My Disciples</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenge of the Iron-Blooded Sword Hound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Zombie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master: This Villainous Disciple Is Not The Holy Child</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo Max-Level Newbie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murim Login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Great Villain Who Threatened to Kill Himself</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon Maker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Reincarnated Assassin is a Genius Swordsman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I was more overpowered than the hero, so I hid my power!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Million Times Attack Speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I am the descendant of the Divine Dragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hero X Demon Queen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Records Of The Demonic Path’S Return</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Five-Dimensional Zone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legendary Youngest Son Of The Marquis House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I am fated villain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return Of The Mount Hua Sect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beyond Myriad Peoples</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nano Machine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tensei Shitara Dai Nana Ouji Dattanode, Kimamani Majutsu O Kiwamemasu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scoring the Sacred Body of the Ancients from the Get-go</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magic Emperor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martial Peak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Self-Disciplined Me Is Practically Invincible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Power: I Can Control All The Elements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Slayer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightning Degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The World's Best Sect Of Dependency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Return Of Apocalypses Tyrant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What Do You Do When You Suddenly Become An Immortal?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tales Of Demons And Gods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Kingdoms Of Ruin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Necromancer Academy And The Genius Summoner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yuan Zun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Greatest Estate Designer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conqueror of modern martial arts Kang Haejin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Records Of The Swordsman Scholar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Scholar's Reincarnation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tale of a Scribe Who Retires To The Countryside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return Of The Bachelor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnation Of The Murim Clan's Former Ranker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regressing with the King’s Power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Last Cultivator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEAVENLY MOON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infinite Leveling: Murim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volcanic Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chronicles Of A Returner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Undefeatable Swordsman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Second Life of Dongfang Bubai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job Change: I Became The Undead Monarch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relife Player</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Lucky Encounter From The Game Turned Into Reality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Killed an Academy Player</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bloodhound’s Regression Instinct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Raised the Yandere Villain Empress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Max-Level Player’s 100th Regression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Heavenly Demon Can't Live A Normal Life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Player That Can't Level Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reborn As The Enemy Prince</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Archmage's Restaurant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Rely on My Invincibility to Deal Tons of Damage Passively!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wild West Murim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster Pet Evolution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Strongest Sect Of All Times</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Youngest Scion Of The Mages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Will Do Whatever I Want In Ten Thousand Years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genkai Level 1 Kara No Nariagari: Saijaku Level No Ore Ga Isekai Saikyou Ni Naru Made</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How to Live at the Max Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The All-Knowing Cultivator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurasu ≪Mushoku≫ No Eiyuu-Tan ~Koushaku-Ka O Tsuihou Sareta Ga, Jitsu Wa Nagutta Dake De Sukiru O Kakutoku Dekiru To Wakari, Tairiku Ichi No Eiyuu Ni Nobori Tsumeru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villager A Wants To Save The Villainess No Matter What!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Savage Hero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genkai Koe No Tenpu wa, Tensei-sha ni Shika Atsukaenai Overlimit Skill Holders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maken Tsukai No Moto Shounen Hei Wa, Moto Teki Kanbu No Onee-San To Issho Ni Ikitai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mannen D-Rank No Chuunen Boukensha, Yotta Ikioi De Densetsu No Ken Wo Hikkonuku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dungeon Sherpa: Meikyuu Michisaki Annainin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Sword Master Childhood Friend Power Harassed Me Harshly, So I Broke Off Our Relationship And Made A Fresh Start At The Frontier As A Magic Swordsman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Summoned The Devil To Grant Me A Wish, But I Married Her Instead Since She Was Adorable ~My New Devil Wife~</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Story About A Dragon And The Rising Of An Adventurer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After Being Called A Hero: The Unrivaled Man Starts A Family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Warrior Exiled By The Hero And His Lover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimotsu Mochi No Nousuji Musou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Strongest Dull Prince’s Secret Battle for the Throne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Sword of Princess Gluttony</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wistoria's Wand And Sword</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Crafty Mage: Frontier Settling Made Easy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delivery Man From Murim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Henkyou Gurashi No Maou, Tensei Shite Saikyou No Majutsushi Ni Naru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Executed Sage Is Reincarnated As A Lich And Starts An All-Out War</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dungeon Ni Hisomu Yandere Na Kanojo Ni Ore Wa Nando Mo Korosareru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Became A Big-Shot On The Heavenly Leaderboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Dark Magician Transmigrates After 66666 Years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reaper Of The Drifting Moon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Unbeatable Dungeon's Lazy Boss Monster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All My Abilities Are Forbidden Spells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How To Survive As A Dragon With Time-Limit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myst, Might, Mayhem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark And Light Martial Emperor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The doomsday ruthless man: hoarding trillions of supplies at the beginning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Becoming the Swordmaster Rank Young Lord of the Sichuan Tang Family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This Account Is Ridiculous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Mysterious World’s Greatest Martial Artist Little Prince</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Reborn Young Lord Is An Assassin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">God-Slaying Copycat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Great Mage Of The Hero’S Party Reincarnates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Brother Is The Chosen One</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Max Level Hero Strikes Back</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overlord of Insects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Game Of Familia: Kazoku Senki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grand General</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Legendary Spearman Returns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ice lord</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Inventory is Abnormal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escort Agency Of The Apocalypse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Heavenly Demon Will Give You a Massage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Twin Swords Of The Sima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Versatile Sword Cultivator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magic Academy’s Genius Blinker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worthless Profession: Dragon Tamer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expelled Hero Is Too Strong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Ten Thousand Clans Invasion: Guardian Of The Rear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Disciple Became the Great Demon Empress?!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Greatest In The World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drawing: The Greatest Mangaka Becomes A Skilled “Martial Artist” In Another World</t>
   </si>
   <si>
     <r>
@@ -553,7 +547,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t>～</t>
+      <t xml:space="preserve">～</t>
     </r>
     <r>
       <rPr>
@@ -563,663 +557,666 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t>I Returned To The Past To Rewrite It As The World's Strongest</t>
+      <t xml:space="preserve">I Returned To The Past To Rewrite It As The World's Strongest</t>
     </r>
   </si>
   <si>
-    <t>Hundreds of Invincible Strikes</t>
-  </si>
-  <si>
-    <t>arctic cold war</t>
-  </si>
-  <si>
-    <t>Apocalyptic Super Farm</t>
-  </si>
-  <si>
-    <t>Sword Sheath's Child</t>
-  </si>
-  <si>
-    <t>Reincarnator</t>
-  </si>
-  <si>
-    <t>Hunter Academy’S Strongest Battle God</t>
-  </si>
-  <si>
-    <t>Childhood Friend of the Zenith</t>
-  </si>
-  <si>
-    <t>Absolute Regression</t>
-  </si>
-  <si>
-    <t>Warrior Grandpa And Supreme Granddaughter</t>
-  </si>
-  <si>
-    <t>I Scared the Divine Lord as I Handed over the Ancient Immortal Pill</t>
-  </si>
-  <si>
-    <t>I Become a Legendary Arch Mage by Reading a Book</t>
-  </si>
-  <si>
-    <t>Hiding a logistics center in the apocalypse</t>
-  </si>
-  <si>
-    <t>The Hated Black Mage Returns</t>
-  </si>
-  <si>
-    <t>The Masters Are Subscribing To Me</t>
-  </si>
-  <si>
-    <t>A Ranker's Guide To The Good Life</t>
-  </si>
-  <si>
-    <t>Black Serpent</t>
-  </si>
-  <si>
-    <t>Conquering the Academy with Just a Sashimi Knife</t>
-  </si>
-  <si>
-    <t>The Magic Genius Of The Marquis House</t>
-  </si>
-  <si>
-    <t>The Reversal Of My Life As A Side Character</t>
-  </si>
-  <si>
-    <t>Absolute Dominion</t>
-  </si>
-  <si>
-    <t>Fatal Reset</t>
-  </si>
-  <si>
-    <t>The Necromancer Family’s Young Heir</t>
-  </si>
-  <si>
-    <t>Starting As A Master Of Female Disciples' Leisure Skills</t>
-  </si>
-  <si>
-    <t>Song Baek</t>
-  </si>
-  <si>
-    <t>Surviving as a Genius on Borrowed Time</t>
-  </si>
-  <si>
-    <t>The Regressed Mercenary’s Machinations</t>
-  </si>
-  <si>
-    <t>Traveling Through Time And Space To Become An Unlucky Npc: I Have A Wife To Protect Me</t>
-  </si>
-  <si>
-    <t>Cultivation: The Heaven's Fated Useless Genius</t>
-  </si>
-  <si>
-    <t>The Edgeless Sword From The Village</t>
-  </si>
-  <si>
-    <t>Levelling Up In An Exclusive Dungeon</t>
-  </si>
-  <si>
-    <t>Reincarnated As A Genius Prodigy Of A Prestigious Family</t>
-  </si>
-  <si>
-    <t>From Goblin To Goblin God</t>
-  </si>
-  <si>
-    <t>Margrave’S Bastard Son Was The Emperor</t>
-  </si>
-  <si>
-    <t>The Second Eunuch Regains His Manhood</t>
-  </si>
-  <si>
-    <t>Return Of The Runebound Professor</t>
-  </si>
-  <si>
-    <t>Regressing as the Reincarnated Bastard of the Sword Clan</t>
-  </si>
-  <si>
-    <t>I, The Demon Lord, Am Being Targeted By My Female Disciples!</t>
-  </si>
-  <si>
-    <t>Fated to Be Loved by Villains</t>
-  </si>
-  <si>
-    <t>The Chaebeol’s Youngest Son</t>
-  </si>
-  <si>
-    <t>Heavenly Demon Wants To Be A Chef</t>
-  </si>
-  <si>
-    <t>Entomologist In Sichuan Tang Clan</t>
-  </si>
-  <si>
-    <t>Last Word of the World</t>
-  </si>
-  <si>
-    <t>Cosmic Heavenly Demon 3077</t>
-  </si>
-  <si>
-    <t>Solo Resurrection</t>
-  </si>
-  <si>
-    <t>Dao of the Bizarre Immortal</t>
-  </si>
-  <si>
-    <t>Tenkaichi: Nihon Saikyou Bugeisha Ketteisen</t>
-  </si>
-  <si>
-    <t>Reincarnation Of The Heavenly Demon</t>
-  </si>
-  <si>
-    <t>Black Corporation: Joseon</t>
-  </si>
-  <si>
-    <t>Perhaps Invincible</t>
-  </si>
-  <si>
-    <t>The mad gate</t>
-  </si>
-  <si>
-    <t>Surviving the Apocalypse</t>
-  </si>
-  <si>
-    <t>Genius Prismatic Mage</t>
-  </si>
-  <si>
-    <t>Becoming a God, Starting as water monkey</t>
-  </si>
-  <si>
-    <t>I Became the Successor of the Martial God</t>
-  </si>
-  <si>
-    <t>Regression of the Yong Clan Heir</t>
-  </si>
-  <si>
-    <t>Chronicles of the Reincarnated Demon God</t>
-  </si>
-  <si>
-    <t>Revenge Of the Bloom Flower</t>
-  </si>
-  <si>
-    <t>The Heavenly Demon Wants a Quiet Life</t>
-  </si>
-  <si>
-    <t>Monster General Recorded Legacy</t>
-  </si>
-  <si>
-    <t>Using My Cooking Skills in a Murim World</t>
-  </si>
-  <si>
-    <t>I’m a Martial Art Villainess, but I’m the Strongest!</t>
-  </si>
-  <si>
-    <t>Metcha Shoukan Sareta Ken</t>
-  </si>
-  <si>
-    <t>Mount Hua Sect's Genius Phantom Swordsman</t>
-  </si>
-  <si>
-    <t>I'm going to destroy this country</t>
-  </si>
-  <si>
-    <t>The New Beggars' Sect</t>
-  </si>
-  <si>
-    <t>Overgeared</t>
-  </si>
-  <si>
-    <t>Regressed life of the Sword Clan’s Ignoble Reincarnator</t>
-  </si>
-  <si>
-    <t>Black Fox: Sword Master Of Mount Kunlun</t>
-  </si>
-  <si>
-    <t>God-level Assassin, I’m the Shadow</t>
-  </si>
-  <si>
-    <t>War Of The Corpses</t>
-  </si>
-  <si>
-    <t>The Illegitimate Who Devours Weapons</t>
-  </si>
-  <si>
-    <t>The Great Sage of the Namgung Clan</t>
-  </si>
-  <si>
-    <t>Limitless Ascension: Strength Amid Adversity</t>
-  </si>
-  <si>
-    <t>Apocalypse: Cockroaches Gives Me Buff</t>
-  </si>
-  <si>
-    <t>The Legendary Hero is an Academy Honors Student</t>
-  </si>
-  <si>
-    <t>Like a Fiery Flame</t>
-  </si>
-  <si>
-    <t>The Magic Tower's Problem Child</t>
-  </si>
-  <si>
-    <t>I Became the Husband of the Cult Leader of the Demonic Sect</t>
-  </si>
-  <si>
-    <t>The Apocalypse is Here</t>
-  </si>
-  <si>
-    <t>If I Don’t Die Soon, I Will Rule The Demon Realm</t>
-  </si>
-  <si>
-    <t>I Will Raise This Family to Greatness</t>
-  </si>
-  <si>
-    <t>The Villain Wants to Live</t>
-  </si>
-  <si>
-    <t>Genius Archer’s Livestreaming</t>
-  </si>
-  <si>
-    <t>After Ten Millennia in Hell</t>
-  </si>
-  <si>
-    <t>Heavenly Grand Archive's Young Master</t>
-  </si>
-  <si>
-    <t>Space Cheon-ma 3077</t>
-  </si>
-  <si>
-    <t>Iljin Romance</t>
-  </si>
-  <si>
-    <t>Shut Up, Evil Dragon! I Don't Want to Raise a Child With You Anymore</t>
-  </si>
-  <si>
-    <t>On the Way to Meet Mom</t>
-  </si>
-  <si>
-    <t>Ultimate Shut-in</t>
-  </si>
-  <si>
-    <t>The beginning after the end</t>
-  </si>
-  <si>
-    <t>Reborn in a Cyber Cultivation World, I Fight My Way to the Top</t>
-  </si>
-  <si>
-    <t>Level 999 Goblin</t>
-  </si>
-  <si>
-    <t>Dominating the Wasteland: I Control an Immortal Sect in the Apocalypse</t>
-  </si>
-  <si>
-    <t>Starting As The God Of Wealth, Taming Billions Of Divine Pets!</t>
-  </si>
-  <si>
-    <t>Martial Evolution: Start by Awakening the King of Monsters</t>
-  </si>
-  <si>
-    <t>The Girl from Random Chatting</t>
-  </si>
-  <si>
-    <t>Return of the Legend</t>
-  </si>
-  <si>
-    <t>Elven Queen</t>
-  </si>
-  <si>
-    <t>Emperor of Solo Play</t>
-  </si>
-  <si>
-    <t>The Fox-Eyed Villain of the Demon Academy</t>
-  </si>
-  <si>
-    <t>The Awakening Contract</t>
-  </si>
-  <si>
-    <t>The Sword God From a Fallen World</t>
-  </si>
-  <si>
-    <t>I Awakened to the Ex Skill "Fixed Damage" and Became Invincible</t>
-  </si>
-  <si>
-    <t>Warrior of the Mind Sword</t>
-  </si>
-  <si>
-    <t>Ninja Reincarnation: Fuuma Kotarou’s Quest to Reclaim His Humanity</t>
-  </si>
-  <si>
-    <t>Empress Maria</t>
-  </si>
-  <si>
-    <t>Reincarnation of the Fist King</t>
-  </si>
-  <si>
-    <t>There Are No Bad Warriors in the World</t>
-  </si>
-  <si>
-    <t>Return From The Depth</t>
-  </si>
-  <si>
-    <t>Return of the Apocalypse-Class Death Knight</t>
-  </si>
-  <si>
-    <t>Oversummoned, Overpowered, and Over It!</t>
-  </si>
-  <si>
-    <t>A Rogue Guard in a Medieval Fantasy</t>
-  </si>
-  <si>
-    <t>Chronicles of the Lazy Sovereign</t>
-  </si>
-  <si>
-    <t>I Was the Final Boss</t>
-  </si>
-  <si>
-    <t>Tang Clan Legend</t>
-  </si>
-  <si>
-    <t>The Demon-Slaying Madman—reborn as a demon</t>
-  </si>
-  <si>
-    <t>Urek Mazino</t>
-  </si>
-  <si>
-    <t>Demonic Sect Frontline: Thirteen Flying Dragons</t>
-  </si>
-  <si>
-    <t>Goddess of Abundance and the Genius Rogue Apostle</t>
-  </si>
-  <si>
-    <t>New Goguryeo Chronicles</t>
-  </si>
-  <si>
-    <t>Devil Summoner, I am the Abyss Lord</t>
-  </si>
-  <si>
-    <t>Legend of Dangun</t>
-  </si>
-  <si>
-    <t>The Tale of the Skeleton Messenger</t>
-  </si>
-  <si>
-    <t>The Great Heavenly Demon Sovereign</t>
-  </si>
-  <si>
-    <t>A Regressor's Tale of Cultivation</t>
-  </si>
-  <si>
-    <t>Jade of the Eight Gates</t>
-  </si>
-  <si>
-    <t>Disciple of the Three Kings</t>
-  </si>
-  <si>
-    <t>After the School Belle Dumped Me, I Became a Martial Arts God</t>
-  </si>
-  <si>
-    <t>Dead Mansion</t>
-  </si>
-  <si>
-    <t>Return of the King of Hell</t>
-  </si>
-  <si>
-    <t>Plaything</t>
-  </si>
-  <si>
-    <t>The Regressor Protects Only Me</t>
-  </si>
-  <si>
-    <t>Full-Time Awakening</t>
-  </si>
-  <si>
-    <t>Rebirth of the Divine Demon</t>
-  </si>
-  <si>
-    <t>Return of the First Patriarch: The Strongest Reincarnates into His Descendant 1000 Years Later</t>
-  </si>
-  <si>
-    <t>Lv. 99 Princess of Black Flame</t>
-  </si>
-  <si>
-    <t>Battle of the Martial Masters</t>
-  </si>
-  <si>
-    <t>The Yellow-haired Villain in Female Main Character's Novel wants Happiness</t>
-  </si>
-  <si>
-    <t>From Six to Sovereignty: The Girl Who Ruled</t>
-  </si>
-  <si>
-    <t>Eat and Go</t>
-  </si>
-  <si>
-    <t>I Shall Seal the Heavens</t>
-  </si>
-  <si>
-    <t>The Executed Sage Who Was Reincarnated as a Lich and Started an All-Out War</t>
-  </si>
-  <si>
-    <t>Demon Instructor's Return</t>
-  </si>
-  <si>
-    <t>The Archduke's Bride Is a Hell Warrior</t>
-  </si>
-  <si>
-    <t>Solo Leveling: Ragnarok</t>
-  </si>
-  <si>
-    <t>I Became a Patron of Villains</t>
-  </si>
-  <si>
-    <t>Black Crow</t>
-  </si>
-  <si>
-    <t>The Marquis Is the Marital Archduke</t>
-  </si>
-  <si>
-    <t>Dukedom's Legendary Prodigy</t>
-  </si>
-  <si>
-    <t>Reincarnated as the Crazed Heir</t>
-  </si>
-  <si>
-    <t>Lord of the Apocalypse</t>
-  </si>
-  <si>
-    <t>Don't Tell Me You Think Cultivating Immortality Is Difficult?</t>
-  </si>
-  <si>
-    <t>Immortal Fairy, Please Listen to My Explanation</t>
-  </si>
-  <si>
-    <t>Maplestory: The Last Adventurer</t>
-  </si>
-  <si>
-    <t>The Steel Emperor</t>
-  </si>
-  <si>
-    <t>The Luoyang Branch of the Heavenly Demon Cult</t>
-  </si>
-  <si>
-    <t>Spirit Hunter</t>
-  </si>
-  <si>
-    <t>Player of the Fallen Family</t>
-  </si>
-  <si>
-    <t>Unrivaled Spear Ghost</t>
-  </si>
-  <si>
-    <t>Reincarnation of the Martial God</t>
-  </si>
-  <si>
-    <t>After Rebirth, I Used Mirror Reversal For Vengeance</t>
-  </si>
-  <si>
-    <t>Death Attribute Magician</t>
-  </si>
-  <si>
-    <t>The Great Emperor Shinmadae</t>
-  </si>
-  <si>
-    <t>Revenger: Apocalypse of Vengeance</t>
-  </si>
-  <si>
-    <t>Hiding Out in an Apocalypse</t>
-  </si>
-  <si>
-    <t>Bad Born Blood</t>
-  </si>
-  <si>
-    <t>KaguRai: Kagura to Raito</t>
-  </si>
-  <si>
-    <t>Reincarnated as the Lazy and Villainous Noble, I Broke the Scenario and Became the Most Formidable With Extraordinary Magic</t>
-  </si>
-  <si>
-    <t>Star Armor꞉ I’ll Slaughter Through the Chaos with Star Soul Generals</t>
-  </si>
-  <si>
-    <t>The Demon King Overrun by Heroes</t>
-  </si>
-  <si>
-    <t>The Monkey King’s Journey to the Murim</t>
-  </si>
-  <si>
-    <t>The Sage who returned from another world wants to live quietly</t>
-  </si>
-  <si>
-    <t>Returned from Another World, Earth Turned Out to Be Quite the Fantasy Too. Also, Losing Heroines, Stop Looking This Way</t>
-  </si>
-  <si>
-    <t>Embodiment of the Assassin in the Murim World</t>
-  </si>
-  <si>
-    <t>Märchen - The Embodiment of Tales</t>
-  </si>
-  <si>
-    <t>Sichuan’s Supreme King</t>
-  </si>
-  <si>
-    <t>The Cold-Blooded Warrior</t>
-  </si>
-  <si>
-    <t>Everyone Loves Her</t>
-  </si>
-  <si>
-    <t>Paper Tiger</t>
-  </si>
-  <si>
-    <t>The Sword-Eating Swordmaster</t>
-  </si>
-  <si>
-    <t>The World's Best Kunlun Tavern</t>
-  </si>
-  <si>
-    <t>Defense Breaker</t>
-  </si>
-  <si>
-    <t>Worlds Best Assassin</t>
-  </si>
-  <si>
-    <t>The World's Best Martial Arts Instructor</t>
-  </si>
-  <si>
-    <t>How a Realist Hero Rebuilt the Kingdom</t>
-  </si>
-  <si>
-    <t>Sleepy Princess in the Demon Castle</t>
-  </si>
-  <si>
-    <t>To Hell With The Status Window</t>
-  </si>
-  <si>
-    <t>Becoming a Cheat-Level Skill Thief</t>
-  </si>
-  <si>
-    <t>Sichuan's Supreme King</t>
-  </si>
-  <si>
-    <t>Reborn After the Eight Empresses Betrayed Me, Now I’ll Make Them Regret It</t>
-  </si>
-  <si>
-    <t>Rebirth of the Demon Lord: the Slave who Conquered Fate</t>
-  </si>
-  <si>
-    <t>I, The Demon Lord am being targeted by my female Disciples!</t>
-  </si>
-  <si>
-    <t>The Strongest Wizard Becomes a Countryside Guard After Taking an Arrow to the Knee</t>
-  </si>
-  <si>
-    <t>The Secret Martial Artist of Demonic Blood</t>
-  </si>
-  <si>
-    <t>The Strongest Hero Who Longs For Revenge Will Peerlessly Annihilate With The Power Of Darkness</t>
-  </si>
-  <si>
-    <t>I Became the Scoundrel of the Cheon Family</t>
-  </si>
-  <si>
-    <t>Supreme Demon of Hyungsan</t>
-  </si>
-  <si>
-    <t>Orc Hero Story - Discovery Chronicles</t>
-  </si>
-  <si>
-    <t>Boukun Meika no Hangyakusha -Aster</t>
-  </si>
-  <si>
-    <t>Jakdu</t>
-  </si>
-  <si>
-    <t>Secretly Cultivating by the Demon Cult Leader's Side</t>
-  </si>
-  <si>
-    <t>The Old Prisoner Lives in Solitude</t>
-  </si>
-  <si>
-    <t>Revenge of Young Master Peng</t>
-  </si>
-  <si>
-    <t>Murim’s Dept King</t>
-  </si>
-  <si>
-    <t>My Girlfriend's Friend</t>
-  </si>
-  <si>
-    <t>Teto X Egen</t>
-  </si>
-  <si>
-    <t>Gokusotsu Kraken</t>
-  </si>
-  <si>
-    <t>The Masters of Heaven and Earth</t>
-  </si>
-  <si>
-    <t>Red Storm</t>
-  </si>
-  <si>
-    <t>A Dragon Lives in Kunlun</t>
-  </si>
-  <si>
-    <t>Friend of the Demon King</t>
-  </si>
-  <si>
-    <t>High Martial Arts: Sweeping Through Three Thousand Emperors with One Hand!</t>
-  </si>
-  <si>
-    <t>The Genius Martial Artist Who Remembers Everything</t>
-  </si>
-  <si>
-    <t>The Shepherd Wizard</t>
-  </si>
-  <si>
-    <t>Sovereign of a Hundred Blades: Heir to the Strongest Style</t>
+    <t xml:space="preserve">Hundreds of Invincible Strikes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">arctic cold war</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apocalyptic Super Farm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sword Sheath's Child</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunter Academy’S Strongest Battle God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Childhood Friend of the Zenith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Absolute Regression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warrior Grandpa And Supreme Granddaughter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Scared the Divine Lord as I Handed over the Ancient Immortal Pill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Become a Legendary Arch Mage by Reading a Book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hiding a logistics center in the apocalypse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Hated Black Mage Returns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Masters Are Subscribing To Me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Ranker's Guide To The Good Life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Serpent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conquering the Academy with Just a Sashimi Knife</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Magic Genius Of The Marquis House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Reversal Of My Life As A Side Character</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Absolute Dominion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fatal Reset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Necromancer Family’s Young Heir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starting As A Master Of Female Disciples' Leisure Skills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Song Baek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surviving as a Genius on Borrowed Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Regressed Mercenary’s Machinations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traveling Through Time And Space To Become An Unlucky Npc: I Have A Wife To Protect Me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cultivation: The Heaven's Fated Useless Genius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Edgeless Sword From The Village</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Levelling Up In An Exclusive Dungeon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnated As A Genius Prodigy Of A Prestigious Family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From Goblin To Goblin God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margrave’S Bastard Son Was The Emperor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Second Eunuch Regains His Manhood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return Of The Runebound Professor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regressing as the Reincarnated Bastard of the Sword Clan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I, The Demon Lord, Am Being Targeted By My Female Disciples!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fated to Be Loved by Villains</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Chaebeol’s Youngest Son</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heavenly Demon Wants To Be A Chef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entomologist In Sichuan Tang Clan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last Word of the World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cosmic Heavenly Demon 3077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo Resurrection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dao of the Bizarre Immortal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tenkaichi: Nihon Saikyou Bugeisha Ketteisen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnation Of The Heavenly Demon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Corporation: Joseon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perhaps Invincible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The mad gate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surviving the Apocalypse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genius Prismatic Mage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Becoming a God, Starting as water monkey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Became the Successor of the Martial God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regression of the Yong Clan Heir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chronicles of the Reincarnated Demon God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenge Of the Bloom Flower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Heavenly Demon Wants a Quiet Life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster General Recorded Legacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Using My Cooking Skills in a Murim World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I’m a Martial Art Villainess, but I’m the Strongest!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metcha Shoukan Sareta Ken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mount Hua Sect's Genius Phantom Swordsman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I'm going to destroy this country</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The New Beggars' Sect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overgeared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regressed life of the Sword Clan’s Ignoble Reincarnator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Fox: Sword Master Of Mount Kunlun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">God-level Assassin, I’m the Shadow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">War Of The Corpses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Illegitimate Who Devours Weapons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Great Sage of the Namgung Clan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limitless Ascension: Strength Amid Adversity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apocalypse: Cockroaches Gives Me Buff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Legendary Hero is an Academy Honors Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Like a Fiery Flame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Magic Tower's Problem Child</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Became the Husband of the Cult Leader of the Demonic Sect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Apocalypse is Here</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If I Don’t Die Soon, I Will Rule The Demon Realm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Will Raise This Family to Greatness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Villain Wants to Live</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genius Archer’s Livestreaming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After Ten Millennia in Hell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heavenly Grand Archive's Young Master</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Space Cheon-ma 3077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iljin Romance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shut Up, Evil Dragon! I Don't Want to Raise a Child With You Anymore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On the Way to Meet Mom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultimate Shut-in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The beginning after the end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reborn in a Cyber Cultivation World, I Fight My Way to the Top</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level 999 Goblin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominating the Wasteland: I Control an Immortal Sect in the Apocalypse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starting As The God Of Wealth, Taming Billions Of Divine Pets!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martial Evolution: Start by Awakening the King of Monsters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Girl from Random Chatting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return of the Legend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elven Queen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emperor of Solo Play</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Fox-Eyed Villain of the Demon Academy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Awakening Contract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Sword God From a Fallen World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Awakened to the Ex Skill "Fixed Damage" and Became Invincible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warrior of the Mind Sword</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ninja Reincarnation: Fuuma Kotarou’s Quest to Reclaim His Humanity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empress Maria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnation of the Fist King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There Are No Bad Warriors in the World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return From The Depth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return of the Apocalypse-Class Death Knight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oversummoned, Overpowered, and Over It!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Rogue Guard in a Medieval Fantasy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chronicles of the Lazy Sovereign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Was the Final Boss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tang Clan Legend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Demon-Slaying Madman—reborn as a demon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urek Mazino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demonic Sect Frontline: Thirteen Flying Dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goddess of Abundance and the Genius Rogue Apostle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Goguryeo Chronicles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devil Summoner, I am the Abyss Lord</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legend of Dangun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Tale of the Skeleton Messenger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Great Heavenly Demon Sovereign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Regressor's Tale of Cultivation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jade of the Eight Gates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disciple of the Three Kings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After the School Belle Dumped Me, I Became a Martial Arts God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dead Mansion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return of the King of Hell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plaything</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Regressor Protects Only Me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full-Time Awakening</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebirth of the Divine Demon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return of the First Patriarch: The Strongest Reincarnates into His Descendant 1000 Years Later</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lv. 99 Princess of Black Flame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Battle of the Martial Masters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Yellow-haired Villain in Female Main Character's Novel wants Happiness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From Six to Sovereignty: The Girl Who Ruled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eat and Go</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Shall Seal the Heavens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Executed Sage Who Was Reincarnated as a Lich and Started an All-Out War</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demon Instructor's Return</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Archduke's Bride Is a Hell Warrior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo Leveling: Ragnarok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Became a Patron of Villains</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Crow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Marquis Is the Marital Archduke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dukedom's Legendary Prodigy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnated as the Crazed Heir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lord of the Apocalypse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Don't Tell Me You Think Cultivating Immortality Is Difficult?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immortal Fairy, Please Listen to My Explanation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maplestory: The Last Adventurer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Steel Emperor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Luoyang Branch of the Heavenly Demon Cult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spirit Hunter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Player of the Fallen Family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unrivaled Spear Ghost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnation of the Martial God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After Rebirth, I Used Mirror Reversal For Vengeance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Death Attribute Magician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Great Emperor Shinmadae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenger: Apocalypse of Vengeance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hiding Out in an Apocalypse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bad Born Blood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KaguRai: Kagura to Raito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnated as the Lazy and Villainous Noble, I Broke the Scenario and Became the Most Formidable With Extraordinary Magic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Star Armor꞉ I’ll Slaughter Through the Chaos with Star Soul Generals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Demon King Overrun by Heroes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Monkey King’s Journey to the Murim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Sage who returned from another world wants to live quietly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Returned from Another World, Earth Turned Out to Be Quite the Fantasy Too. Also, Losing Heroines, Stop Looking This Way</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embodiment of the Assassin in the Murim World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Märchen - The Embodiment of Tales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sichuan’s Supreme King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Cold-Blooded Warrior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everyone Loves Her</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paper Tiger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Sword-Eating Swordmaster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The World's Best Kunlun Tavern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defense Breaker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worlds Best Assassin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The World's Best Martial Arts Instructor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How a Realist Hero Rebuilt the Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sleepy Princess in the Demon Castle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To Hell With The Status Window</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Becoming a Cheat-Level Skill Thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sichuan's Supreme King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reborn After the Eight Empresses Betrayed Me, Now I’ll Make Them Regret It</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebirth of the Demon Lord: the Slave who Conquered Fate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I, The Demon Lord am being targeted by my female Disciples!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Strongest Wizard Becomes a Countryside Guard After Taking an Arrow to the Knee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Secret Martial Artist of Demonic Blood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Strongest Hero Who Longs For Revenge Will Peerlessly Annihilate With The Power Of Darkness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Became the Scoundrel of the Cheon Family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supreme Demon of Hyungsan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orc Hero Story - Discovery Chronicles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boukun Meika no Hangyakusha -Aster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jakdu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secretly Cultivating by the Demon Cult Leader's Side</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Old Prisoner Lives in Solitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenge of Young Master Peng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murim’s Dept King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Girlfriend's Friend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teto X Egen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gokusotsu Kraken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Masters of Heaven and Earth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red Storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Dragon Lives in Kunlun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Friend of the Demon King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High Martial Arts: Sweeping Through Three Thousand Emperors with One Hand!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Genius Martial Artist Who Remembers Everything</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Shepherd Wizard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sovereign of a Hundred Blades: Heir to the Strongest Style</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1228,14 +1225,22 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Nimbus Sans"/>
@@ -1277,14 +1282,14 @@
     </fill>
   </fills>
   <borders count="3">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FFD9D9D9"/>
       </left>
@@ -1297,7 +1302,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FFD9D9D9"/>
       </left>
@@ -1313,94 +1318,122 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Nimbus Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF808080"/>
-          <bgColor rgb="FF4F81BD"/>
+          <fgColor rgb="FF4F81BD"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEAF2F8"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1459,74 +1492,57 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{23F4AA61-EEA7-44DB-B4FE-11B577F3E1F5}" name="Table1" displayName="Table1" ref="A1:B386" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="3">
-  <autoFilter ref="A1:B386" xr:uid="{23F4AA61-EEA7-44DB-B4FE-11B577F3E1F5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:B386" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:B386"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{47F72D81-14A6-4D3C-8C16-B26B3E272F3C}" name="Title" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{E0691C27-7DCD-433E-B145-66C758C7198A}" name="Episodes" dataDxfId="1"/>
+    <tableColumn id="1" name="Title"/>
+    <tableColumn id="2" name="Episodes"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1534,12 +1550,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1568,7 +1584,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1589,7 +1605,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1640,7 +1656,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1658,26 +1674,27 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:B386"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="169" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="169"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.43"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1685,3090 +1702,3095 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="4" t="n">
         <v>878</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="6" t="n">
         <v>266</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="6" t="n">
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="4" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="6" t="n">
         <v>135</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="4" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="4" t="n">
         <v>292</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="4" t="n">
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="4" t="n">
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="6" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="4" t="n">
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="6" t="n">
         <v>223</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="4" t="n">
         <v>162</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="6" t="n">
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="4" t="n">
         <v>117</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="6" t="n">
         <v>85</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="4" t="n">
         <v>182</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="6" t="n">
         <v>175</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="4" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="6" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="4" t="n">
         <v>10.1</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="6" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="4" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="6">
+      <c r="B29" s="6" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30" s="4" t="n">
         <v>105</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="6">
+      <c r="B31" s="6" t="n">
         <v>77</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" s="4" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="6">
+      <c r="B33" s="6" t="n">
         <v>88</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34" s="4" t="n">
         <v>99</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="6">
+      <c r="B35" s="6" t="n">
         <v>157</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36" s="4" t="n">
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="6">
+      <c r="B37" s="6" t="n">
         <v>51</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="4">
+      <c r="B38" s="4" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="6">
+      <c r="B39" s="6" t="n">
         <v>58</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="4">
+      <c r="B40" s="4" t="n">
         <v>124</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="6">
+      <c r="B41" s="6" t="n">
         <v>111</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="4">
+      <c r="B42" s="4" t="n">
         <v>63</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="6">
+      <c r="B43" s="6" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B44" s="4">
+      <c r="B44" s="4" t="n">
         <v>162</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B45" s="6">
+      <c r="B45" s="6" t="n">
         <v>64</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B46" s="4">
+      <c r="B46" s="4" t="n">
         <v>140</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="6">
+      <c r="B47" s="6" t="n">
         <v>168</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="4">
+      <c r="B48" s="4" t="n">
         <v>186</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B49" s="6">
+      <c r="B49" s="6" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B50" s="4">
+      <c r="B50" s="4" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B51" s="6">
+      <c r="B51" s="6" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B52" s="4">
+      <c r="B52" s="4" t="n">
         <v>71</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B53" s="6">
+      <c r="B53" s="6" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B54" s="4">
+      <c r="B54" s="4" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B55" s="6">
+      <c r="B55" s="6" t="n">
         <v>156</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B56" s="4">
+      <c r="B56" s="4" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B57" s="6">
+      <c r="B57" s="6" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B58" s="4">
+      <c r="B58" s="4" t="n">
         <v>144</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B59" s="6">
+      <c r="B59" s="6" t="n">
         <v>329</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B60" s="4">
+      <c r="B60" s="4" t="n">
         <v>161</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B61" s="6">
+      <c r="B61" s="6" t="n">
         <v>275</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B62" s="4">
+      <c r="B62" s="4" t="n">
         <v>311</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B63" s="6">
+      <c r="B63" s="6" t="n">
         <v>175</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B64" s="4">
+      <c r="B64" s="4" t="n">
         <v>58</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B65" s="6">
+      <c r="B65" s="6" t="n">
         <v>851</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B66" s="4">
+      <c r="B66" s="4" t="n">
         <v>3644</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B67" s="6">
+      <c r="B67" s="6" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B68" s="4">
+      <c r="B68" s="4" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B69" s="6">
+      <c r="B69" s="6" t="n">
         <v>76</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B70" s="4">
+      <c r="B70" s="4" t="n">
         <v>220</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B71" s="6">
+      <c r="B71" s="6" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B72" s="4">
+      <c r="B72" s="4" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B73" s="6">
+      <c r="B73" s="6" t="n">
         <v>89</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B74" s="4">
+      <c r="B74" s="4" t="n">
         <v>508.1</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B75" s="6">
+      <c r="B75" s="6" t="n">
         <v>43</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B76" s="4">
+      <c r="B76" s="4" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B77" s="6">
+      <c r="B77" s="6" t="n">
         <v>587</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B78" s="4">
+      <c r="B78" s="4" t="n">
         <v>121</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B79" s="6">
+      <c r="B79" s="6" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B80" s="4">
+      <c r="B80" s="4" t="n">
         <v>157</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B81" s="6">
+      <c r="B81" s="6" t="n">
         <v>156</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B82" s="4">
+      <c r="B82" s="4" t="n">
         <v>235</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B83" s="6">
+      <c r="B83" s="6" t="n">
         <v>188</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B84" s="4">
+      <c r="B84" s="4" t="n">
         <v>106</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B85" s="6">
+      <c r="B85" s="6" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B86" s="4">
+      <c r="B86" s="4" t="n">
         <v>33</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B87" s="6">
+      <c r="B87" s="6" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B88" s="4">
+      <c r="B88" s="4" t="n">
         <v>187</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B89" s="6">
+      <c r="B89" s="6" t="n">
         <v>256</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B90" s="4">
+      <c r="B90" s="4" t="n">
         <v>133</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B91" s="6">
+      <c r="B91" s="6" t="n">
         <v>217</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B92" s="4">
+      <c r="B92" s="4" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B93" s="6">
+      <c r="B93" s="6" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B94" s="4">
+      <c r="B94" s="4" t="n">
         <v>65</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B95" s="6">
+      <c r="B95" s="6" t="n">
         <v>56</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B96" s="4">
+      <c r="B96" s="4" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="6">
+      <c r="B97" s="6" t="n">
         <v>52</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B98" s="4">
+      <c r="B98" s="4" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B99" s="6">
+      <c r="B99" s="6" t="n">
         <v>41</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B100" s="4">
+      <c r="B100" s="4" t="n">
         <v>182</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B101" s="6">
+      <c r="B101" s="6" t="n">
         <v>157</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B102" s="4">
+      <c r="B102" s="4" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B103" s="6">
+      <c r="B103" s="6" t="n">
         <v>103</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B104" s="4">
+      <c r="B104" s="4" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B105" s="6">
+      <c r="B105" s="6" t="n">
         <v>94</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B106" s="4">
+      <c r="B106" s="4" t="n">
         <v>221</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B107" s="6">
+      <c r="B107" s="6" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="108" spans="1:2">
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B108" s="4">
+      <c r="B108" s="4" t="n">
         <v>61</v>
       </c>
     </row>
-    <row r="109" spans="1:2">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B109" s="6">
+      <c r="B109" s="6" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:2">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B110" s="4">
+      <c r="B110" s="4" t="n">
         <v>10.1</v>
       </c>
     </row>
-    <row r="111" spans="1:2">
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="B111" s="6">
+      <c r="B111" s="6" t="n">
         <v>79</v>
       </c>
     </row>
-    <row r="112" spans="1:2">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B112" s="4">
+      <c r="B112" s="4" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="113" spans="1:2">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B113" s="6">
+      <c r="B113" s="6" t="n">
         <v>34</v>
       </c>
     </row>
-    <row r="114" spans="1:2">
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B114" s="4">
+      <c r="B114" s="4" t="n">
         <v>38.1</v>
       </c>
     </row>
-    <row r="115" spans="1:2">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B115" s="6">
+      <c r="B115" s="6" t="n">
         <v>63</v>
       </c>
     </row>
-    <row r="116" spans="1:2">
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B116" s="4">
+      <c r="B116" s="4" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="117" spans="1:2">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B117" s="6">
+      <c r="B117" s="6" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="118" spans="1:2">
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B118" s="4">
+      <c r="B118" s="4" t="n">
         <v>49</v>
       </c>
     </row>
-    <row r="119" spans="1:2">
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B119" s="6">
+      <c r="B119" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="120" spans="1:2">
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B120" s="4">
+      <c r="B120" s="4" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="121" spans="1:2">
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B121" s="6">
+      <c r="B121" s="6" t="n">
         <v>43</v>
       </c>
     </row>
-    <row r="122" spans="1:2">
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B122" s="4">
+      <c r="B122" s="4" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="123" spans="1:2">
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B123" s="6">
+      <c r="B123" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="124" spans="1:2">
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B124" s="4">
+      <c r="B124" s="4" t="n">
         <v>33</v>
       </c>
     </row>
-    <row r="125" spans="1:2">
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B125" s="6">
+      <c r="B125" s="6" t="n">
         <v>7.2</v>
       </c>
     </row>
-    <row r="126" spans="1:2">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B126" s="4">
+      <c r="B126" s="4" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="127" spans="1:2">
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B127" s="6">
+      <c r="B127" s="6" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="128" spans="1:2">
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B128" s="4">
+      <c r="B128" s="4" t="n">
         <v>58</v>
       </c>
     </row>
-    <row r="129" spans="1:2">
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="B129" s="6">
+      <c r="B129" s="6" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="130" spans="1:2">
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B130" s="4">
+      <c r="B130" s="4" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="131" spans="1:2">
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B131" s="6">
+      <c r="B131" s="6" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="132" spans="1:2">
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B132" s="4">
+      <c r="B132" s="4" t="n">
         <v>56</v>
       </c>
     </row>
-    <row r="133" spans="1:2">
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B133" s="6">
+      <c r="B133" s="6" t="n">
         <v>12.2</v>
       </c>
     </row>
-    <row r="134" spans="1:2">
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B134" s="4">
+      <c r="B134" s="4" t="n">
         <v>91</v>
       </c>
     </row>
-    <row r="135" spans="1:2">
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B135" s="6">
+      <c r="B135" s="6" t="n">
         <v>165</v>
       </c>
     </row>
-    <row r="136" spans="1:2">
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B136" s="4">
+      <c r="B136" s="4" t="n">
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="1:2">
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="B137" s="6">
+      <c r="B137" s="6" t="n">
         <v>92</v>
       </c>
     </row>
-    <row r="138" spans="1:2">
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B138" s="4">
+      <c r="B138" s="4" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="139" spans="1:2">
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B139" s="6">
+      <c r="B139" s="6" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="140" spans="1:2">
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B140" s="4">
+      <c r="B140" s="4" t="n">
         <v>90</v>
       </c>
     </row>
-    <row r="141" spans="1:2">
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B141" s="6">
+      <c r="B141" s="6" t="n">
         <v>48</v>
       </c>
     </row>
-    <row r="142" spans="1:2">
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B142" s="4">
+      <c r="B142" s="4" t="n">
         <v>39</v>
       </c>
     </row>
-    <row r="143" spans="1:2">
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="B143" s="6">
+      <c r="B143" s="6" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="144" spans="1:2">
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B144" s="4">
+      <c r="B144" s="4" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="145" spans="1:2">
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B145" s="6">
+      <c r="B145" s="6" t="n">
         <v>123</v>
       </c>
     </row>
-    <row r="146" spans="1:2">
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B146" s="4">
+      <c r="B146" s="4" t="n">
         <v>102</v>
       </c>
     </row>
-    <row r="147" spans="1:2">
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B147" s="6">
+      <c r="B147" s="6" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="148" spans="1:2">
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B148" s="4">
+      <c r="B148" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="149" spans="1:2">
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="B149" s="6">
+      <c r="B149" s="6" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="150" spans="1:2">
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B150" s="4">
+      <c r="B150" s="4" t="n">
         <v>73</v>
       </c>
     </row>
-    <row r="151" spans="1:2">
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B151" s="6">
+      <c r="B151" s="6" t="n">
         <v>55</v>
       </c>
     </row>
-    <row r="152" spans="1:2">
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B152" s="4">
+      <c r="B152" s="4" t="n">
         <v>63</v>
       </c>
     </row>
-    <row r="153" spans="1:2">
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B153" s="6">
+      <c r="B153" s="6" t="n">
         <v>83</v>
       </c>
     </row>
-    <row r="154" spans="1:2">
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B154" s="4">
+      <c r="B154" s="4" t="n">
         <v>139</v>
       </c>
     </row>
-    <row r="155" spans="1:2">
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B155" s="6">
+      <c r="B155" s="6" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="156" spans="1:2">
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B156" s="4">
+      <c r="B156" s="4" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="157" spans="1:2">
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B157" s="6">
+      <c r="B157" s="6" t="n">
         <v>76</v>
       </c>
     </row>
-    <row r="158" spans="1:2">
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B158" s="4">
+      <c r="B158" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="159" spans="1:2">
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B159" s="6">
+      <c r="B159" s="6" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="160" spans="1:2">
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B160" s="4">
+      <c r="B160" s="4" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="161" spans="1:2">
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B161" s="6">
+      <c r="B161" s="6" t="n">
         <v>58</v>
       </c>
     </row>
-    <row r="162" spans="1:2">
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B162" s="4">
+      <c r="B162" s="4" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="163" spans="1:2">
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B163" s="6">
+      <c r="B163" s="6" t="n">
         <v>34</v>
       </c>
     </row>
-    <row r="164" spans="1:2">
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B164" s="4">
+      <c r="B164" s="4" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="165" spans="1:2">
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="B165" s="6">
+      <c r="B165" s="6" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="166" spans="1:2">
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B166" s="4">
+      <c r="B166" s="4" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="167" spans="1:2">
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="B167" s="6">
+      <c r="B167" s="6" t="n">
         <v>61</v>
       </c>
     </row>
-    <row r="168" spans="1:2">
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B168" s="4">
+      <c r="B168" s="4" t="n">
         <v>108</v>
       </c>
     </row>
-    <row r="169" spans="1:2">
+    <row r="169" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="B169" s="6">
+      <c r="B169" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="170" spans="1:2">
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B170" s="4">
+      <c r="B170" s="4" t="n">
         <v>49</v>
       </c>
     </row>
-    <row r="171" spans="1:2">
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="B171" s="6">
+      <c r="B171" s="6" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="172" spans="1:2">
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B172" s="4">
+      <c r="B172" s="4" t="n">
         <v>74</v>
       </c>
     </row>
-    <row r="173" spans="1:2">
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="B173" s="6">
+      <c r="B173" s="6" t="n">
         <v>61</v>
       </c>
     </row>
-    <row r="174" spans="1:2">
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B174" s="4">
+      <c r="B174" s="4" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="175" spans="1:2">
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="B175" s="6">
+      <c r="B175" s="6" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="176" spans="1:2">
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B176" s="4">
+      <c r="B176" s="4" t="n">
         <v>104</v>
       </c>
     </row>
-    <row r="177" spans="1:2">
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="B177" s="6">
+      <c r="B177" s="6" t="n">
         <v>76</v>
       </c>
     </row>
-    <row r="178" spans="1:2">
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B178" s="4">
+      <c r="B178" s="4" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="179" spans="1:2">
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="B179" s="6">
+      <c r="B179" s="6" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="180" spans="1:2">
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B180" s="4">
+      <c r="B180" s="4" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="181" spans="1:2">
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="B181" s="6">
+      <c r="B181" s="6" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="182" spans="1:2">
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B182" s="4">
+      <c r="B182" s="4" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="183" spans="1:2">
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="B183" s="6">
+      <c r="B183" s="6" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="184" spans="1:2">
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B184" s="4">
+      <c r="B184" s="4" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="185" spans="1:2">
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="B185" s="6">
+      <c r="B185" s="6" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="186" spans="1:2">
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B186" s="4">
+      <c r="B186" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="187" spans="1:2">
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="B187" s="6">
+      <c r="B187" s="6" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="188" spans="1:2">
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B188" s="4">
+      <c r="B188" s="4" t="n">
         <v>27</v>
       </c>
     </row>
-    <row r="189" spans="1:2">
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="B189" s="6">
+      <c r="B189" s="6" t="n">
         <v>91</v>
       </c>
     </row>
-    <row r="190" spans="1:2">
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B190" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2">
+      <c r="B190" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="B191" s="6">
+      <c r="B191" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="192" spans="1:2">
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B192" s="4">
+      <c r="B192" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="193" spans="1:2">
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B193" s="6">
+      <c r="B193" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="194" spans="1:2">
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B194" s="4">
+      <c r="B194" s="4" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="195" spans="1:2">
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B195" s="6">
+      <c r="B195" s="6" t="n">
         <v>89</v>
       </c>
     </row>
-    <row r="196" spans="1:2">
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B196" s="4">
+      <c r="B196" s="4" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="197" spans="1:2">
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B197" s="6">
+      <c r="B197" s="6" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="198" spans="1:2">
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B198" s="4">
+      <c r="B198" s="4" t="n">
         <v>59</v>
       </c>
     </row>
-    <row r="199" spans="1:2">
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B199" s="6">
+      <c r="B199" s="6" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="200" spans="1:2">
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B200" s="4">
+      <c r="B200" s="4" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="201" spans="1:2">
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="B201" s="6">
+      <c r="B201" s="6" t="n">
         <v>108</v>
       </c>
     </row>
-    <row r="202" spans="1:2">
+    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B202" s="4">
+      <c r="B202" s="4" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="203" spans="1:2">
+    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="B203" s="6">
+      <c r="B203" s="6" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="204" spans="1:2">
+    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B204" s="4">
+      <c r="B204" s="4" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="205" spans="1:2">
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="B205" s="6">
+      <c r="B205" s="6" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="206" spans="1:2">
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B206" s="4">
+      <c r="B206" s="4" t="n">
         <v>17</v>
       </c>
     </row>
-    <row r="207" spans="1:2">
+    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="B207" s="6">
+      <c r="B207" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="208" spans="1:2">
+    <row r="208" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="B208" s="4">
+      <c r="B208" s="4" t="n">
         <v>220</v>
       </c>
     </row>
-    <row r="209" spans="1:2">
+    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="B209" s="6">
+      <c r="B209" s="6" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="210" spans="1:2">
+    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B210" s="4">
+      <c r="B210" s="4" t="n">
         <v>51</v>
       </c>
     </row>
-    <row r="211" spans="1:2">
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="B211" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2">
+      <c r="B211" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B212" s="4">
+      <c r="B212" s="4" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="213" spans="1:2">
+    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="B213" s="6">
+      <c r="B213" s="6" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="214" spans="1:2">
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B214" s="4">
+      <c r="B214" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="215" spans="1:2">
+    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="B215" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="216" spans="1:2">
+      <c r="B215" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="B216" s="4">
+      <c r="B216" s="4" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="217" spans="1:2">
+    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B217" s="6">
+      <c r="B217" s="6" t="n">
         <v>141</v>
       </c>
     </row>
-    <row r="218" spans="1:2">
+    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B218" s="4">
+      <c r="B218" s="4" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="219" spans="1:2">
+    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="B219" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" spans="1:2">
+      <c r="B219" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="B220" s="4">
+      <c r="B220" s="4" t="n">
         <v>49</v>
       </c>
     </row>
-    <row r="221" spans="1:2">
+    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="B221" s="6">
+      <c r="B221" s="6" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="222" spans="1:2">
+    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B222" s="4">
+      <c r="B222" s="4" t="n">
         <v>23</v>
       </c>
     </row>
-    <row r="223" spans="1:2">
+    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="B223" s="6">
+      <c r="B223" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="224" spans="1:2">
+    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B224" s="4">
+      <c r="B224" s="4" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="225" spans="1:2">
+    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="B225" s="6">
+      <c r="B225" s="6" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="226" spans="1:2">
+    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="B226" s="4">
+      <c r="B226" s="4" t="n">
         <v>36</v>
       </c>
     </row>
-    <row r="227" spans="1:2">
+    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="B227" s="6">
+      <c r="B227" s="6" t="n">
         <v>64</v>
       </c>
     </row>
-    <row r="228" spans="1:2">
+    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="B228" s="4">
+      <c r="B228" s="4" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="229" spans="1:2">
+    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="B229" s="6">
+      <c r="B229" s="6" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="230" spans="1:2">
+    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B230" s="4">
+      <c r="B230" s="4" t="n">
         <v>124</v>
       </c>
     </row>
-    <row r="231" spans="1:2">
+    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="B231" s="6">
+      <c r="B231" s="6" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="232" spans="1:2">
+    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="B232" s="4">
+      <c r="B232" s="4" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="233" spans="1:2">
+    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="B233" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234" spans="1:2">
+      <c r="B233" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="B234" s="4">
+      <c r="B234" s="4" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="235" spans="1:2">
+    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="B235" s="6">
+      <c r="B235" s="6" t="n">
         <v>130</v>
       </c>
     </row>
-    <row r="236" spans="1:2">
+    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="B236" s="4">
+      <c r="B236" s="4" t="n">
         <v>67</v>
       </c>
     </row>
-    <row r="237" spans="1:2">
+    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="B237" s="6">
+      <c r="B237" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="238" spans="1:2">
+    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B238" s="4">
+      <c r="B238" s="4" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="239" spans="1:2">
+    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="B239" s="6">
+      <c r="B239" s="6" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="240" spans="1:2">
+    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B240" s="4">
+      <c r="B240" s="4" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="241" spans="1:2">
+    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="B241" s="6">
+      <c r="B241" s="6" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="242" spans="1:2">
+    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="B242" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243" spans="1:2">
+      <c r="B242" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="B243" s="6">
+      <c r="B243" s="6" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="244" spans="1:2">
+    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B244" s="4">
+      <c r="B244" s="4" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="245" spans="1:2">
+    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="B245" s="6">
+      <c r="B245" s="6" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="246" spans="1:2">
+    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="B246" s="4">
+      <c r="B246" s="4" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="247" spans="1:2">
+    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="B247" s="6">
+      <c r="B247" s="6" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="248" spans="1:2">
+    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="B248" s="4">
+      <c r="B248" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="249" spans="1:2">
+    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="B249" s="6">
+      <c r="B249" s="6" t="n">
         <v>81</v>
       </c>
     </row>
-    <row r="250" spans="1:2">
+    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B250" s="4">
+      <c r="B250" s="4" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="251" spans="1:2">
+    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="B251" s="6">
+      <c r="B251" s="6" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="252" spans="1:2">
+    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="B252" s="4">
+      <c r="B252" s="4" t="n">
         <v>57</v>
       </c>
     </row>
-    <row r="253" spans="1:2">
+    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="B253" s="6">
+      <c r="B253" s="6" t="n">
         <v>112</v>
       </c>
     </row>
-    <row r="254" spans="1:2">
+    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B254" s="4">
+      <c r="B254" s="4" t="n">
         <v>126</v>
       </c>
     </row>
-    <row r="255" spans="1:2">
+    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="B255" s="6">
+      <c r="B255" s="6" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="256" spans="1:2">
+    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="B256" s="4">
+      <c r="B256" s="4" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="257" spans="1:2">
+    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="B257" s="6">
+      <c r="B257" s="6" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="258" spans="1:2">
+    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="B258" s="4">
+      <c r="B258" s="4" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="259" spans="1:2">
+    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="B259" s="6">
+      <c r="B259" s="6" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="260" spans="1:2">
+    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="B260" s="4">
+      <c r="B260" s="4" t="n">
         <v>219</v>
       </c>
     </row>
-    <row r="261" spans="1:2">
+    <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="B261" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262" spans="1:2">
+      <c r="B261" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="B262" s="4">
+      <c r="B262" s="4" t="n">
         <v>55</v>
       </c>
     </row>
-    <row r="263" spans="1:2">
+    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="B263" s="6">
+      <c r="B263" s="6" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:2">
+    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="B264" s="4">
+      <c r="B264" s="4" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="265" spans="1:2">
+    <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="B265" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266" spans="1:2">
+      <c r="B265" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="B266" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="267" spans="1:2">
+      <c r="B266" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="B267" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="268" spans="1:2">
+      <c r="B267" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B268" s="4">
+      <c r="B268" s="4" t="n">
         <v>17</v>
       </c>
     </row>
-    <row r="269" spans="1:2">
+    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="B269" s="6">
+      <c r="B269" s="6" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="270" spans="1:2">
+    <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="B270" s="4">
+      <c r="B270" s="4" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="271" spans="1:2">
+    <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="B271" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="272" spans="1:2">
+      <c r="B271" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="B272" s="4">
+      <c r="B272" s="4" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="273" spans="1:2">
+    <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="B273" s="6">
+      <c r="B273" s="6" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="274" spans="1:2">
+    <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="B274" s="4">
+      <c r="B274" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="275" spans="1:2">
+    <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="B275" s="6">
+      <c r="B275" s="6" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="276" spans="1:2">
+    <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="B276" s="4">
+      <c r="B276" s="4" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="277" spans="1:2">
+    <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="B277" s="6">
+      <c r="B277" s="6" t="n">
         <v>34</v>
       </c>
     </row>
-    <row r="278" spans="1:2">
+    <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="B278" s="4">
+      <c r="B278" s="4" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="279" spans="1:2">
+    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="B279" s="6">
+      <c r="B279" s="6" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="280" spans="1:2">
+    <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B280" s="4">
+      <c r="B280" s="4" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="281" spans="1:2">
+    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="B281" s="6">
+      <c r="B281" s="6" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="282" spans="1:2">
+    <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="B282" s="4">
+      <c r="B282" s="4" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="283" spans="1:2">
+    <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="B283" s="6">
+      <c r="B283" s="6" t="n">
         <v>27</v>
       </c>
     </row>
-    <row r="284" spans="1:2">
+    <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="B284" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285" spans="1:2">
+      <c r="B284" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="B285" s="6">
+      <c r="B285" s="6" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="286" spans="1:2">
+    <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="B286" s="4">
+      <c r="B286" s="4" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="287" spans="1:2">
+    <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="B287" s="6">
+      <c r="B287" s="6" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="288" spans="1:2">
+    <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="B288" s="4">
+      <c r="B288" s="4" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="289" spans="1:2">
+    <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="B289" s="6">
+      <c r="B289" s="6" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="290" spans="1:2">
+    <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="B290" s="4">
+      <c r="B290" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="291" spans="1:2">
+    <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="B291" s="6">
+      <c r="B291" s="6" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="292" spans="1:2">
+    <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="B292" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="293" spans="1:2">
+      <c r="B292" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="B293" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="294" spans="1:2">
+      <c r="B293" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="B294" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="295" spans="1:2">
+      <c r="B294" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="B295" s="6">
+      <c r="B295" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="296" spans="1:2">
+    <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="B296" s="4">
+      <c r="B296" s="4" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="297" spans="1:2">
+    <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="B297" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="298" spans="1:2">
+      <c r="B297" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="B298" s="4">
+      <c r="B298" s="4" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="299" spans="1:2">
+    <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="B299" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300" spans="1:2">
+      <c r="B299" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="B300" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="301" spans="1:2">
+      <c r="B300" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="B301" s="6">
+      <c r="B301" s="6" t="n">
         <v>56</v>
       </c>
     </row>
-    <row r="302" spans="1:2">
+    <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="B302" s="4">
+      <c r="B302" s="4" t="n">
         <v>41</v>
       </c>
     </row>
-    <row r="303" spans="1:2">
+    <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="B303" s="6">
+      <c r="B303" s="6" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="304" spans="1:2">
+    <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="B304" s="4">
+      <c r="B304" s="4" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="305" spans="1:2">
+    <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="B305" s="6">
+      <c r="B305" s="6" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="306" spans="1:2">
+    <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="B306" s="4">
+      <c r="B306" s="4" t="n">
         <v>27</v>
       </c>
     </row>
-    <row r="307" spans="1:2">
+    <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="B307" s="6">
+      <c r="B307" s="6" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="308" spans="1:2">
+    <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="B308" s="4">
+      <c r="B308" s="4" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="309" spans="1:2">
+    <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="B309" s="6">
+      <c r="B309" s="6" t="n">
         <v>57</v>
       </c>
     </row>
-    <row r="310" spans="1:2">
+    <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="B310" s="4">
+      <c r="B310" s="4" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="311" spans="1:2">
+    <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="B311" s="6">
+      <c r="B311" s="6" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="312" spans="1:2">
+    <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="B312" s="4">
+      <c r="B312" s="4" t="n">
         <v>55</v>
       </c>
     </row>
-    <row r="313" spans="1:2">
+    <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="B313" s="6">
+      <c r="B313" s="6" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="314" spans="1:2">
+    <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="B314" s="4">
+      <c r="B314" s="4" t="n">
         <v>32</v>
       </c>
     </row>
-    <row r="315" spans="1:2">
+    <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="B315" s="6">
+      <c r="B315" s="6" t="n">
         <v>47</v>
       </c>
     </row>
-    <row r="316" spans="1:2">
+    <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="B316" s="4">
+      <c r="B316" s="4" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="317" spans="1:2">
+    <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B317" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="318" spans="1:2">
+      <c r="B317" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="B318" s="4">
+      <c r="B318" s="4" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="319" spans="1:2">
+    <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="B319" s="6">
+      <c r="B319" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="320" spans="1:2">
+    <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="B320" s="4">
+      <c r="B320" s="4" t="n">
         <v>161</v>
       </c>
     </row>
-    <row r="321" spans="1:2">
+    <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="B321" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="322" spans="1:2">
+      <c r="B321" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="B322" s="4">
+      <c r="B322" s="4" t="n">
         <v>34</v>
       </c>
     </row>
-    <row r="323" spans="1:2">
+    <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="B323" s="6">
+      <c r="B323" s="6" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="324" spans="1:2">
+    <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="B324" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="325" spans="1:2">
+      <c r="B324" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="B325" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="326" spans="1:2">
+      <c r="B325" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="B326" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="327" spans="1:2">
+      <c r="B326" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="B327" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="328" spans="1:2">
+      <c r="B327" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="B328" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="329" spans="1:2">
+      <c r="B328" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="B329" s="6">
+      <c r="B329" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="330" spans="1:2">
+    <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="B330" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="331" spans="1:2">
+      <c r="B330" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="B331" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="332" spans="1:2">
+      <c r="B331" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="B332" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="333" spans="1:2">
+      <c r="B332" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="B333" s="6">
+      <c r="B333" s="6" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="334" spans="1:2">
+    <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="B334" s="4">
+      <c r="B334" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="335" spans="1:2">
+    <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="B335" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="336" spans="1:2">
+      <c r="B335" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="B336" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="337" spans="1:2">
+      <c r="B336" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="B337" s="6">
+      <c r="B337" s="6" t="n">
         <v>27</v>
       </c>
     </row>
-    <row r="338" spans="1:2">
+    <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="B338" s="4">
+      <c r="B338" s="4" t="n">
         <v>17</v>
       </c>
     </row>
-    <row r="339" spans="1:2">
+    <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="B339" s="6">
+      <c r="B339" s="6" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="340" spans="1:2">
+    <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="B340" s="4">
+      <c r="B340" s="4" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="341" spans="1:2">
+    <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="B341" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="342" spans="1:2">
+      <c r="B341" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="B342" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="343" spans="1:2">
+      <c r="B342" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="B343" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="344" spans="1:2">
+      <c r="B343" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="B344" s="4">
+      <c r="B344" s="4" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="345" spans="1:2">
+    <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="B345" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="346" spans="1:2">
+      <c r="B345" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="B346" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="347" spans="1:2">
+      <c r="B346" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="B347" s="6">
+      <c r="B347" s="6" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="348" spans="1:2">
+    <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="B348" s="4">
+      <c r="B348" s="4" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="349" spans="1:2">
+    <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="B349" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="350" spans="1:2">
+      <c r="B349" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="B350" s="4">
+      <c r="B350" s="4" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="351" spans="1:2">
+    <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="B351" s="6">
+      <c r="B351" s="6" t="n">
         <v>97</v>
       </c>
     </row>
-    <row r="352" spans="1:2">
+    <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="B352" s="4">
+      <c r="B352" s="4" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="353" spans="1:2">
+    <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="B353" s="6">
+      <c r="B353" s="6" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="354" spans="1:2">
+    <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="B354" s="4">
+      <c r="B354" s="4" t="n">
         <v>52</v>
       </c>
     </row>
-    <row r="355" spans="1:2">
+    <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="B355" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="356" spans="1:2">
+      <c r="B355" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="B356" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="357" spans="1:2">
+      <c r="B356" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="B357" s="6">
+      <c r="B357" s="6" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="358" spans="1:2">
+    <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="B358" s="4">
+      <c r="B358" s="4" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="359" spans="1:2">
+    <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="B359" s="6">
+      <c r="B359" s="6" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="360" spans="1:2">
+    <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="B360" s="4">
+      <c r="B360" s="4" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="361" spans="1:2">
+    <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="B361" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="362" spans="1:2">
+      <c r="B361" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="B362" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="363" spans="1:2">
+      <c r="B362" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="B363" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="364" spans="1:2">
+      <c r="B363" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="B364" s="4">
+      <c r="B364" s="4" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="365" spans="1:2">
+    <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="B365" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="366" spans="1:2">
+      <c r="B365" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="B366" s="4">
+      <c r="B366" s="4" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="367" spans="1:2">
+    <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="B367" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="368" spans="1:2">
+      <c r="B367" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="B368" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="369" spans="1:2">
+      <c r="B368" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="B369" s="6">
+      <c r="B369" s="6" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="370" spans="1:2">
+    <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="B370" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="371" spans="1:2">
+      <c r="B370" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="B371" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="372" spans="1:2">
+      <c r="B371" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="B372" s="4">
+      <c r="B372" s="4" t="n">
         <v>71</v>
       </c>
     </row>
-    <row r="373" spans="1:2">
+    <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="B373" s="6">
+      <c r="B373" s="6" t="n">
         <v>49</v>
       </c>
     </row>
-    <row r="374" spans="1:2">
+    <row r="374" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="B374" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="375" spans="1:2">
+      <c r="B374" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="B375" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="376" spans="1:2">
+      <c r="B375" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="B376" s="1">
+      <c r="B376" s="1" t="n">
         <v>114</v>
       </c>
     </row>
-    <row r="377" spans="1:2">
+    <row r="377" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="B377" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="378" spans="1:2">
+      <c r="B377" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="B378" s="1">
+      <c r="B378" s="1" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="379" spans="1:2">
+    <row r="379" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="B379" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="380" spans="1:2">
+      <c r="B379" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="B380" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="381" spans="1:2">
+      <c r="B380" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="B381" s="1">
+      <c r="B381" s="1" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="382" spans="1:2">
+    <row r="382" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="B382" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="383" spans="1:2">
+      <c r="B382" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="B383" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="384" spans="1:2">
+      <c r="B383" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="B384" s="1">
+      <c r="B384" s="1" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="385" spans="1:2">
+    <row r="385" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="B385" s="8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="386" spans="1:2">
+      <c r="B385" s="8" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="386" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="B386" s="1">
+      <c r="B386" s="1" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <tableParts count="1">
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <tableParts>
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>

--- a/Manga.Manhwua/Updated manhwua.xlsx
+++ b/Manga.Manhwua/Updated manhwua.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Manga\Manga.Manhwua\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D0B1439-C5D7-4921-B782-67C65E95E8B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -20,513 +25,513 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="386">
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Episodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vagabond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My Dragon System</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Knight King Who Returned With A God</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Player Hides His Past</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disastrous Necromancer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Priest of Corruption</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dragon Emperor Martial God</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mookhyang - Dark Lady</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leveling Up By Hoarding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master Of The Martial Arts Library</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Absolute Necromancer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tales Of A Shinning Sword</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyushu Chronicles Of Immortals And Demons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Level 1 Player</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logging 10,000 Years into the Future</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Swordmaster’S Youngest Son</t>
-  </si>
-  <si>
-    <t xml:space="preserve">World’S Greatest Senior Disciple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dragon Master</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Return Of The Disaster-Class Hero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solo Farming In The Tower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chronicles Of The Demon Faction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demonic Master Of Mount Kunlun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Necromancer's Evolutionary Traits</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="389">
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Episodes</t>
+  </si>
+  <si>
+    <t>Kingdom</t>
+  </si>
+  <si>
+    <t>Vagabond</t>
+  </si>
+  <si>
+    <t>My Dragon System</t>
+  </si>
+  <si>
+    <t>The Knight King Who Returned With A God</t>
+  </si>
+  <si>
+    <t>The Player Hides His Past</t>
+  </si>
+  <si>
+    <t>Disastrous Necromancer</t>
+  </si>
+  <si>
+    <t>The Priest of Corruption</t>
+  </si>
+  <si>
+    <t>Dragon Emperor Martial God</t>
+  </si>
+  <si>
+    <t>Mookhyang - Dark Lady</t>
+  </si>
+  <si>
+    <t>Leveling Up By Hoarding</t>
+  </si>
+  <si>
+    <t>Master Of The Martial Arts Library</t>
+  </si>
+  <si>
+    <t>Absolute Necromancer</t>
+  </si>
+  <si>
+    <t>Tales Of A Shinning Sword</t>
+  </si>
+  <si>
+    <t>Kyushu Chronicles Of Immortals And Demons</t>
+  </si>
+  <si>
+    <t>Level 1 Player</t>
+  </si>
+  <si>
+    <t>Logging 10,000 Years into the Future</t>
+  </si>
+  <si>
+    <t>Swordmaster’S Youngest Son</t>
+  </si>
+  <si>
+    <t>World’S Greatest Senior Disciple</t>
+  </si>
+  <si>
+    <t>Dragon Master</t>
+  </si>
+  <si>
+    <t>The Return Of The Disaster-Class Hero</t>
+  </si>
+  <si>
+    <t>Solo Farming In The Tower</t>
+  </si>
+  <si>
+    <t>Chronicles Of The Demon Faction</t>
+  </si>
+  <si>
+    <t>Demonic Master Of Mount Kunlun</t>
+  </si>
+  <si>
+    <t>Necromancer's Evolutionary Traits</t>
   </si>
   <si>
     <t xml:space="preserve">Samurai In Another World </t>
   </si>
   <si>
-    <t xml:space="preserve">Peerless Quest – The Cheat Skill Only I Can Use</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isekai De Haishin Katsudou Wo Shitara Tairyou No Yandere Shinja Wo Umidashite Shimatta Ken</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boundless Necromancer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Academy’S Genius Swordsman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demon Evolution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Iron-Blooded Necromancer Has Returned</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infinite Mage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Star Instructor  Master Baek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Story Of Thorny Spear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blade debt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martial God Regressed To Level 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What, You Dare Pretend In Front Of Me, The Strongest In The Immortal World?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terminally-Ill Genius Dark Knight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heavenly Inquisition Sword</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tsuki Ga Michibiku Isekai Douchuu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Emperor’s Sword</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Constellations Are My Disciples</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenge of the Iron-Blooded Sword Hound</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Zombie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master: This Villainous Disciple Is Not The Holy Child</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solo Max-Level Newbie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Murim Login</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Great Villain Who Threatened to Kill Himself</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon Maker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Reincarnated Assassin is a Genius Swordsman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I was more overpowered than the hero, so I hid my power!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Million Times Attack Speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I am the descendant of the Divine Dragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hero X Demon Queen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Records Of The Demonic Path’S Return</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Five-Dimensional Zone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legendary Youngest Son Of The Marquis House</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I am fated villain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return Of The Mount Hua Sect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beyond Myriad Peoples</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nano Machine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tensei Shitara Dai Nana Ouji Dattanode, Kimamani Majutsu O Kiwamemasu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scoring the Sacred Body of the Ancients from the Get-go</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magic Emperor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martial Peak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Self-Disciplined Me Is Practically Invincible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Power: I Can Control All The Elements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Slayer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightning Degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The World's Best Sect Of Dependency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Return Of Apocalypses Tyrant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What Do You Do When You Suddenly Become An Immortal?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tales Of Demons And Gods</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Kingdoms Of Ruin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Necromancer Academy And The Genius Summoner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yuan Zun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Greatest Estate Designer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conqueror of modern martial arts Kang Haejin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Records Of The Swordsman Scholar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Scholar's Reincarnation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tale of a Scribe Who Retires To The Countryside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return Of The Bachelor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reincarnation Of The Murim Clan's Former Ranker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regressing with the King’s Power</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Last Cultivator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEAVENLY MOON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infinite Leveling: Murim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volcanic Age</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chronicles Of A Returner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Undefeatable Swordsman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Second Life of Dongfang Bubai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Job Change: I Became The Undead Monarch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relife Player</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My Lucky Encounter From The Game Turned Into Reality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Killed an Academy Player</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bloodhound’s Regression Instinct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Raised the Yandere Villain Empress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Max-Level Player’s 100th Regression</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Heavenly Demon Can't Live A Normal Life</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Player That Can't Level Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reborn As The Enemy Prince</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Archmage's Restaurant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Rely on My Invincibility to Deal Tons of Damage Passively!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wild West Murim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster Pet Evolution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Strongest Sect Of All Times</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Youngest Scion Of The Mages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Will Do Whatever I Want In Ten Thousand Years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genkai Level 1 Kara No Nariagari: Saijaku Level No Ore Ga Isekai Saikyou Ni Naru Made</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How to Live at the Max Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The All-Knowing Cultivator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurasu ≪Mushoku≫ No Eiyuu-Tan ~Koushaku-Ka O Tsuihou Sareta Ga, Jitsu Wa Nagutta Dake De Sukiru O Kakutoku Dekiru To Wakari, Tairiku Ichi No Eiyuu Ni Nobori Tsumeru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Villager A Wants To Save The Villainess No Matter What!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Savage Hero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genkai Koe No Tenpu wa, Tensei-sha ni Shika Atsukaenai Overlimit Skill Holders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maken Tsukai No Moto Shounen Hei Wa, Moto Teki Kanbu No Onee-San To Issho Ni Ikitai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mannen D-Rank No Chuunen Boukensha, Yotta Ikioi De Densetsu No Ken Wo Hikkonuku</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dungeon Sherpa: Meikyuu Michisaki Annainin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Sword Master Childhood Friend Power Harassed Me Harshly, So I Broke Off Our Relationship And Made A Fresh Start At The Frontier As A Magic Swordsman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Summoned The Devil To Grant Me A Wish, But I Married Her Instead Since She Was Adorable ~My New Devil Wife~</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Story About A Dragon And The Rising Of An Adventurer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">After Being Called A Hero: The Unrivaled Man Starts A Family</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Warrior Exiled By The Hero And His Lover</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nimotsu Mochi No Nousuji Musou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Strongest Dull Prince’s Secret Battle for the Throne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Sword of Princess Gluttony</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wistoria's Wand And Sword</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Crafty Mage: Frontier Settling Made Easy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delivery Man From Murim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Henkyou Gurashi No Maou, Tensei Shite Saikyou No Majutsushi Ni Naru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Executed Sage Is Reincarnated As A Lich And Starts An All-Out War</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dungeon Ni Hisomu Yandere Na Kanojo Ni Ore Wa Nando Mo Korosareru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Became A Big-Shot On The Heavenly Leaderboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Dark Magician Transmigrates After 66666 Years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reaper Of The Drifting Moon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Unbeatable Dungeon's Lazy Boss Monster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All My Abilities Are Forbidden Spells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How To Survive As A Dragon With Time-Limit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Myst, Might, Mayhem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark And Light Martial Emperor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The doomsday ruthless man: hoarding trillions of supplies at the beginning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Becoming the Swordmaster Rank Young Lord of the Sichuan Tang Family</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This Account Is Ridiculous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Mysterious World’s Greatest Martial Artist Little Prince</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Reborn Young Lord Is An Assassin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">God-Slaying Copycat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Great Mage Of The Hero’S Party Reincarnates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My Brother Is The Chosen One</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Max Level Hero Strikes Back</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overlord of Insects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Game Of Familia: Kazoku Senki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grand General</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Legendary Spearman Returns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ice lord</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My Inventory is Abnormal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Escort Agency Of The Apocalypse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Heavenly Demon Will Give You a Massage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Twin Swords Of The Sima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Versatile Sword Cultivator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magic Academy’s Genius Blinker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Worthless Profession: Dragon Tamer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expelled Hero Is Too Strong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Ten Thousand Clans Invasion: Guardian Of The Rear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My Disciple Became the Great Demon Empress?!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Greatest In The World</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drawing: The Greatest Mangaka Becomes A Skilled “Martial Artist” In Another World</t>
+    <t>Peerless Quest – The Cheat Skill Only I Can Use</t>
+  </si>
+  <si>
+    <t>Isekai De Haishin Katsudou Wo Shitara Tairyou No Yandere Shinja Wo Umidashite Shimatta Ken</t>
+  </si>
+  <si>
+    <t>Boundless Necromancer</t>
+  </si>
+  <si>
+    <t>Academy’S Genius Swordsman</t>
+  </si>
+  <si>
+    <t>Demon Evolution</t>
+  </si>
+  <si>
+    <t>The Iron-Blooded Necromancer Has Returned</t>
+  </si>
+  <si>
+    <t>Infinite Mage</t>
+  </si>
+  <si>
+    <t>Star Instructor  Master Baek</t>
+  </si>
+  <si>
+    <t>The Story Of Thorny Spear</t>
+  </si>
+  <si>
+    <t>Blade debt</t>
+  </si>
+  <si>
+    <t>Martial God Regressed To Level 2</t>
+  </si>
+  <si>
+    <t>What, You Dare Pretend In Front Of Me, The Strongest In The Immortal World?</t>
+  </si>
+  <si>
+    <t>Terminally-Ill Genius Dark Knight</t>
+  </si>
+  <si>
+    <t>Heavenly Inquisition Sword</t>
+  </si>
+  <si>
+    <t>Tsuki Ga Michibiku Isekai Douchuu</t>
+  </si>
+  <si>
+    <t>The Emperor’s Sword</t>
+  </si>
+  <si>
+    <t>The Constellations Are My Disciples</t>
+  </si>
+  <si>
+    <t>Revenge of the Iron-Blooded Sword Hound</t>
+  </si>
+  <si>
+    <t>Mr. Zombie</t>
+  </si>
+  <si>
+    <t>Master: This Villainous Disciple Is Not The Holy Child</t>
+  </si>
+  <si>
+    <t>Solo Max-Level Newbie</t>
+  </si>
+  <si>
+    <t>Murim Login</t>
+  </si>
+  <si>
+    <t>The Great Villain Who Threatened to Kill Himself</t>
+  </si>
+  <si>
+    <t>Weapon Maker</t>
+  </si>
+  <si>
+    <t>The Reincarnated Assassin is a Genius Swordsman</t>
+  </si>
+  <si>
+    <t>I was more overpowered than the hero, so I hid my power!</t>
+  </si>
+  <si>
+    <t>Million Times Attack Speed</t>
+  </si>
+  <si>
+    <t>I am the descendant of the Divine Dragon</t>
+  </si>
+  <si>
+    <t>Hero X Demon Queen</t>
+  </si>
+  <si>
+    <t>Records Of The Demonic Path’S Return</t>
+  </si>
+  <si>
+    <t>Five-Dimensional Zone</t>
+  </si>
+  <si>
+    <t>Legendary Youngest Son Of The Marquis House</t>
+  </si>
+  <si>
+    <t>I am fated villain</t>
+  </si>
+  <si>
+    <t>Return Of The Mount Hua Sect</t>
+  </si>
+  <si>
+    <t>Beyond Myriad Peoples</t>
+  </si>
+  <si>
+    <t>Nano Machine</t>
+  </si>
+  <si>
+    <t>Tensei Shitara Dai Nana Ouji Dattanode, Kimamani Majutsu O Kiwamemasu</t>
+  </si>
+  <si>
+    <t>Scoring the Sacred Body of the Ancients from the Get-go</t>
+  </si>
+  <si>
+    <t>Magic Emperor</t>
+  </si>
+  <si>
+    <t>Martial Peak</t>
+  </si>
+  <si>
+    <t>The Self-Disciplined Me Is Practically Invincible</t>
+  </si>
+  <si>
+    <t>Global Power: I Can Control All The Elements</t>
+  </si>
+  <si>
+    <t>Moon Slayer</t>
+  </si>
+  <si>
+    <t>Lightning Degree</t>
+  </si>
+  <si>
+    <t>The World's Best Sect Of Dependency</t>
+  </si>
+  <si>
+    <t>The Return Of Apocalypses Tyrant</t>
+  </si>
+  <si>
+    <t>What Do You Do When You Suddenly Become An Immortal?</t>
+  </si>
+  <si>
+    <t>Tales Of Demons And Gods</t>
+  </si>
+  <si>
+    <t>The Kingdoms Of Ruin</t>
+  </si>
+  <si>
+    <t>Necromancer Academy And The Genius Summoner</t>
+  </si>
+  <si>
+    <t>Yuan Zun</t>
+  </si>
+  <si>
+    <t>The Greatest Estate Designer</t>
+  </si>
+  <si>
+    <t>Conqueror of modern martial arts Kang Haejin</t>
+  </si>
+  <si>
+    <t>Records Of The Swordsman Scholar</t>
+  </si>
+  <si>
+    <t>The Scholar's Reincarnation</t>
+  </si>
+  <si>
+    <t>Tale of a Scribe Who Retires To The Countryside</t>
+  </si>
+  <si>
+    <t>Return Of The Bachelor</t>
+  </si>
+  <si>
+    <t>Reincarnation Of The Murim Clan's Former Ranker</t>
+  </si>
+  <si>
+    <t>Regressing with the King’s Power</t>
+  </si>
+  <si>
+    <t>The Last Cultivator</t>
+  </si>
+  <si>
+    <t>HEAVENLY MOON</t>
+  </si>
+  <si>
+    <t>Infinite Leveling: Murim</t>
+  </si>
+  <si>
+    <t>Volcanic Age</t>
+  </si>
+  <si>
+    <t>Chronicles Of A Returner</t>
+  </si>
+  <si>
+    <t>The Undefeatable Swordsman</t>
+  </si>
+  <si>
+    <t>Second Life of Dongfang Bubai</t>
+  </si>
+  <si>
+    <t>Job Change: I Became The Undead Monarch</t>
+  </si>
+  <si>
+    <t>Relife Player</t>
+  </si>
+  <si>
+    <t>My Lucky Encounter From The Game Turned Into Reality</t>
+  </si>
+  <si>
+    <t>I Killed an Academy Player</t>
+  </si>
+  <si>
+    <t>Bloodhound’s Regression Instinct</t>
+  </si>
+  <si>
+    <t>I Raised the Yandere Villain Empress</t>
+  </si>
+  <si>
+    <t>The Max-Level Player’s 100th Regression</t>
+  </si>
+  <si>
+    <t>The Heavenly Demon Can't Live A Normal Life</t>
+  </si>
+  <si>
+    <t>The Player That Can't Level Up</t>
+  </si>
+  <si>
+    <t>Reborn As The Enemy Prince</t>
+  </si>
+  <si>
+    <t>The Archmage's Restaurant</t>
+  </si>
+  <si>
+    <t>I Rely on My Invincibility to Deal Tons of Damage Passively!</t>
+  </si>
+  <si>
+    <t>Wild West Murim</t>
+  </si>
+  <si>
+    <t>Monster Pet Evolution</t>
+  </si>
+  <si>
+    <t>The Strongest Sect Of All Times</t>
+  </si>
+  <si>
+    <t>Youngest Scion Of The Mages</t>
+  </si>
+  <si>
+    <t>I Will Do Whatever I Want In Ten Thousand Years</t>
+  </si>
+  <si>
+    <t>Genkai Level 1 Kara No Nariagari: Saijaku Level No Ore Ga Isekai Saikyou Ni Naru Made</t>
+  </si>
+  <si>
+    <t>How to Live at the Max Level</t>
+  </si>
+  <si>
+    <t>The All-Knowing Cultivator</t>
+  </si>
+  <si>
+    <t>Kurasu ≪Mushoku≫ No Eiyuu-Tan ~Koushaku-Ka O Tsuihou Sareta Ga, Jitsu Wa Nagutta Dake De Sukiru O Kakutoku Dekiru To Wakari, Tairiku Ichi No Eiyuu Ni Nobori Tsumeru</t>
+  </si>
+  <si>
+    <t>Villager A Wants To Save The Villainess No Matter What!</t>
+  </si>
+  <si>
+    <t>Savage Hero</t>
+  </si>
+  <si>
+    <t>Genkai Koe No Tenpu wa, Tensei-sha ni Shika Atsukaenai Overlimit Skill Holders</t>
+  </si>
+  <si>
+    <t>Maken Tsukai No Moto Shounen Hei Wa, Moto Teki Kanbu No Onee-San To Issho Ni Ikitai</t>
+  </si>
+  <si>
+    <t>Mannen D-Rank No Chuunen Boukensha, Yotta Ikioi De Densetsu No Ken Wo Hikkonuku</t>
+  </si>
+  <si>
+    <t>Dungeon Sherpa: Meikyuu Michisaki Annainin</t>
+  </si>
+  <si>
+    <t>A Sword Master Childhood Friend Power Harassed Me Harshly, So I Broke Off Our Relationship And Made A Fresh Start At The Frontier As A Magic Swordsman</t>
+  </si>
+  <si>
+    <t>I Summoned The Devil To Grant Me A Wish, But I Married Her Instead Since She Was Adorable ~My New Devil Wife~</t>
+  </si>
+  <si>
+    <t>A Story About A Dragon And The Rising Of An Adventurer</t>
+  </si>
+  <si>
+    <t>After Being Called A Hero: The Unrivaled Man Starts A Family</t>
+  </si>
+  <si>
+    <t>A Warrior Exiled By The Hero And His Lover</t>
+  </si>
+  <si>
+    <t>Nimotsu Mochi No Nousuji Musou</t>
+  </si>
+  <si>
+    <t>The Strongest Dull Prince’s Secret Battle for the Throne</t>
+  </si>
+  <si>
+    <t>The Sword of Princess Gluttony</t>
+  </si>
+  <si>
+    <t>Wistoria's Wand And Sword</t>
+  </si>
+  <si>
+    <t>The Crafty Mage: Frontier Settling Made Easy</t>
+  </si>
+  <si>
+    <t>Delivery Man From Murim</t>
+  </si>
+  <si>
+    <t>Henkyou Gurashi No Maou, Tensei Shite Saikyou No Majutsushi Ni Naru</t>
+  </si>
+  <si>
+    <t>The Executed Sage Is Reincarnated As A Lich And Starts An All-Out War</t>
+  </si>
+  <si>
+    <t>Dungeon Ni Hisomu Yandere Na Kanojo Ni Ore Wa Nando Mo Korosareru</t>
+  </si>
+  <si>
+    <t>I Became A Big-Shot On The Heavenly Leaderboard</t>
+  </si>
+  <si>
+    <t>The Dark Magician Transmigrates After 66666 Years</t>
+  </si>
+  <si>
+    <t>Reaper Of The Drifting Moon</t>
+  </si>
+  <si>
+    <t>The Unbeatable Dungeon's Lazy Boss Monster</t>
+  </si>
+  <si>
+    <t>All My Abilities Are Forbidden Spells</t>
+  </si>
+  <si>
+    <t>How To Survive As A Dragon With Time-Limit</t>
+  </si>
+  <si>
+    <t>Myst, Might, Mayhem</t>
+  </si>
+  <si>
+    <t>Dark And Light Martial Emperor</t>
+  </si>
+  <si>
+    <t>The doomsday ruthless man: hoarding trillions of supplies at the beginning</t>
+  </si>
+  <si>
+    <t>Becoming the Swordmaster Rank Young Lord of the Sichuan Tang Family</t>
+  </si>
+  <si>
+    <t>This Account Is Ridiculous</t>
+  </si>
+  <si>
+    <t>The Mysterious World’s Greatest Martial Artist Little Prince</t>
+  </si>
+  <si>
+    <t>The Reborn Young Lord Is An Assassin</t>
+  </si>
+  <si>
+    <t>God-Slaying Copycat</t>
+  </si>
+  <si>
+    <t>The Great Mage Of The Hero’S Party Reincarnates</t>
+  </si>
+  <si>
+    <t>My Brother Is The Chosen One</t>
+  </si>
+  <si>
+    <t>The Max Level Hero Strikes Back</t>
+  </si>
+  <si>
+    <t>Overlord of Insects</t>
+  </si>
+  <si>
+    <t>Game Of Familia: Kazoku Senki</t>
+  </si>
+  <si>
+    <t>Grand General</t>
+  </si>
+  <si>
+    <t>The Legendary Spearman Returns</t>
+  </si>
+  <si>
+    <t>Ice lord</t>
+  </si>
+  <si>
+    <t>My Inventory is Abnormal</t>
+  </si>
+  <si>
+    <t>Escort Agency Of The Apocalypse</t>
+  </si>
+  <si>
+    <t>The Heavenly Demon Will Give You a Massage</t>
+  </si>
+  <si>
+    <t>The Twin Swords Of The Sima</t>
+  </si>
+  <si>
+    <t>Versatile Sword Cultivator</t>
+  </si>
+  <si>
+    <t>Asura</t>
+  </si>
+  <si>
+    <t>Magic Academy’s Genius Blinker</t>
+  </si>
+  <si>
+    <t>Worthless Profession: Dragon Tamer</t>
+  </si>
+  <si>
+    <t>Expelled Hero Is Too Strong</t>
+  </si>
+  <si>
+    <t>The Ten Thousand Clans Invasion: Guardian Of The Rear</t>
+  </si>
+  <si>
+    <t>My Disciple Became the Great Demon Empress?!</t>
+  </si>
+  <si>
+    <t>The Greatest In The World</t>
+  </si>
+  <si>
+    <t>Drawing: The Greatest Mangaka Becomes A Skilled “Martial Artist” In Another World</t>
   </si>
   <si>
     <r>
@@ -547,7 +552,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">～</t>
+      <t>～</t>
     </r>
     <r>
       <rPr>
@@ -557,666 +562,672 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">I Returned To The Past To Rewrite It As The World's Strongest</t>
+      <t>I Returned To The Past To Rewrite It As The World's Strongest</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Hundreds of Invincible Strikes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">arctic cold war</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apocalyptic Super Farm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sword Sheath's Child</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reincarnator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hunter Academy’S Strongest Battle God</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Childhood Friend of the Zenith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Absolute Regression</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warrior Grandpa And Supreme Granddaughter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Scared the Divine Lord as I Handed over the Ancient Immortal Pill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Become a Legendary Arch Mage by Reading a Book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hiding a logistics center in the apocalypse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Hated Black Mage Returns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Masters Are Subscribing To Me</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Ranker's Guide To The Good Life</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black Serpent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conquering the Academy with Just a Sashimi Knife</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Magic Genius Of The Marquis House</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Reversal Of My Life As A Side Character</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Absolute Dominion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fatal Reset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Necromancer Family’s Young Heir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Starting As A Master Of Female Disciples' Leisure Skills</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Song Baek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surviving as a Genius on Borrowed Time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Regressed Mercenary’s Machinations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Traveling Through Time And Space To Become An Unlucky Npc: I Have A Wife To Protect Me</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cultivation: The Heaven's Fated Useless Genius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Edgeless Sword From The Village</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Levelling Up In An Exclusive Dungeon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reincarnated As A Genius Prodigy Of A Prestigious Family</t>
-  </si>
-  <si>
-    <t xml:space="preserve">From Goblin To Goblin God</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Margrave’S Bastard Son Was The Emperor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Second Eunuch Regains His Manhood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return Of The Runebound Professor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regressing as the Reincarnated Bastard of the Sword Clan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I, The Demon Lord, Am Being Targeted By My Female Disciples!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fated to Be Loved by Villains</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Chaebeol’s Youngest Son</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heavenly Demon Wants To Be A Chef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entomologist In Sichuan Tang Clan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Last Word of the World</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cosmic Heavenly Demon 3077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solo Resurrection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dao of the Bizarre Immortal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tenkaichi: Nihon Saikyou Bugeisha Ketteisen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reincarnation Of The Heavenly Demon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black Corporation: Joseon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perhaps Invincible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The mad gate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surviving the Apocalypse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genius Prismatic Mage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Becoming a God, Starting as water monkey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Became the Successor of the Martial God</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regression of the Yong Clan Heir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chronicles of the Reincarnated Demon God</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenge Of the Bloom Flower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Heavenly Demon Wants a Quiet Life</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster General Recorded Legacy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Using My Cooking Skills in a Murim World</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I’m a Martial Art Villainess, but I’m the Strongest!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metcha Shoukan Sareta Ken</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mount Hua Sect's Genius Phantom Swordsman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I'm going to destroy this country</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The New Beggars' Sect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overgeared</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regressed life of the Sword Clan’s Ignoble Reincarnator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black Fox: Sword Master Of Mount Kunlun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">God-level Assassin, I’m the Shadow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">War Of The Corpses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Illegitimate Who Devours Weapons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Great Sage of the Namgung Clan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limitless Ascension: Strength Amid Adversity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apocalypse: Cockroaches Gives Me Buff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Legendary Hero is an Academy Honors Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Like a Fiery Flame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Magic Tower's Problem Child</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Became the Husband of the Cult Leader of the Demonic Sect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Apocalypse is Here</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If I Don’t Die Soon, I Will Rule The Demon Realm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Will Raise This Family to Greatness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Villain Wants to Live</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genius Archer’s Livestreaming</t>
-  </si>
-  <si>
-    <t xml:space="preserve">After Ten Millennia in Hell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heavenly Grand Archive's Young Master</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Space Cheon-ma 3077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iljin Romance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shut Up, Evil Dragon! I Don't Want to Raise a Child With You Anymore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On the Way to Meet Mom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ultimate Shut-in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The beginning after the end</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reborn in a Cyber Cultivation World, I Fight My Way to the Top</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Level 999 Goblin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dominating the Wasteland: I Control an Immortal Sect in the Apocalypse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Starting As The God Of Wealth, Taming Billions Of Divine Pets!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martial Evolution: Start by Awakening the King of Monsters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Girl from Random Chatting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return of the Legend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elven Queen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emperor of Solo Play</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Fox-Eyed Villain of the Demon Academy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Awakening Contract</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Sword God From a Fallen World</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Awakened to the Ex Skill "Fixed Damage" and Became Invincible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warrior of the Mind Sword</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ninja Reincarnation: Fuuma Kotarou’s Quest to Reclaim His Humanity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empress Maria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reincarnation of the Fist King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">There Are No Bad Warriors in the World</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return From The Depth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return of the Apocalypse-Class Death Knight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oversummoned, Overpowered, and Over It!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Rogue Guard in a Medieval Fantasy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chronicles of the Lazy Sovereign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Was the Final Boss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tang Clan Legend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Demon-Slaying Madman—reborn as a demon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Urek Mazino</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demonic Sect Frontline: Thirteen Flying Dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Goddess of Abundance and the Genius Rogue Apostle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Goguryeo Chronicles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devil Summoner, I am the Abyss Lord</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legend of Dangun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Tale of the Skeleton Messenger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Great Heavenly Demon Sovereign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Regressor's Tale of Cultivation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jade of the Eight Gates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disciple of the Three Kings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">After the School Belle Dumped Me, I Became a Martial Arts God</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dead Mansion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return of the King of Hell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plaything</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Regressor Protects Only Me</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full-Time Awakening</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rebirth of the Divine Demon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return of the First Patriarch: The Strongest Reincarnates into His Descendant 1000 Years Later</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lv. 99 Princess of Black Flame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Battle of the Martial Masters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Yellow-haired Villain in Female Main Character's Novel wants Happiness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">From Six to Sovereignty: The Girl Who Ruled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eat and Go</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Shall Seal the Heavens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Executed Sage Who Was Reincarnated as a Lich and Started an All-Out War</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demon Instructor's Return</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Archduke's Bride Is a Hell Warrior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solo Leveling: Ragnarok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Became a Patron of Villains</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black Crow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Marquis Is the Marital Archduke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dukedom's Legendary Prodigy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reincarnated as the Crazed Heir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lord of the Apocalypse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Don't Tell Me You Think Cultivating Immortality Is Difficult?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immortal Fairy, Please Listen to My Explanation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maplestory: The Last Adventurer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Steel Emperor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Luoyang Branch of the Heavenly Demon Cult</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spirit Hunter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Player of the Fallen Family</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unrivaled Spear Ghost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reincarnation of the Martial God</t>
-  </si>
-  <si>
-    <t xml:space="preserve">After Rebirth, I Used Mirror Reversal For Vengeance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Death Attribute Magician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Great Emperor Shinmadae</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenger: Apocalypse of Vengeance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hiding Out in an Apocalypse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bad Born Blood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KaguRai: Kagura to Raito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reincarnated as the Lazy and Villainous Noble, I Broke the Scenario and Became the Most Formidable With Extraordinary Magic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Star Armor꞉ I’ll Slaughter Through the Chaos with Star Soul Generals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Demon King Overrun by Heroes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Monkey King’s Journey to the Murim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Sage who returned from another world wants to live quietly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Returned from Another World, Earth Turned Out to Be Quite the Fantasy Too. Also, Losing Heroines, Stop Looking This Way</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Embodiment of the Assassin in the Murim World</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Märchen - The Embodiment of Tales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sichuan’s Supreme King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Cold-Blooded Warrior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Everyone Loves Her</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paper Tiger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Sword-Eating Swordmaster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The World's Best Kunlun Tavern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Defense Breaker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Worlds Best Assassin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The World's Best Martial Arts Instructor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How a Realist Hero Rebuilt the Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sleepy Princess in the Demon Castle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To Hell With The Status Window</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Becoming a Cheat-Level Skill Thief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sichuan's Supreme King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reborn After the Eight Empresses Betrayed Me, Now I’ll Make Them Regret It</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rebirth of the Demon Lord: the Slave who Conquered Fate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I, The Demon Lord am being targeted by my female Disciples!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Strongest Wizard Becomes a Countryside Guard After Taking an Arrow to the Knee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Secret Martial Artist of Demonic Blood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Strongest Hero Who Longs For Revenge Will Peerlessly Annihilate With The Power Of Darkness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Became the Scoundrel of the Cheon Family</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supreme Demon of Hyungsan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orc Hero Story - Discovery Chronicles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boukun Meika no Hangyakusha -Aster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jakdu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secretly Cultivating by the Demon Cult Leader's Side</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Old Prisoner Lives in Solitude</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenge of Young Master Peng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Murim’s Dept King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My Girlfriend's Friend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teto X Egen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gokusotsu Kraken</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Masters of Heaven and Earth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Red Storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Dragon Lives in Kunlun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Friend of the Demon King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High Martial Arts: Sweeping Through Three Thousand Emperors with One Hand!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Genius Martial Artist Who Remembers Everything</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Shepherd Wizard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sovereign of a Hundred Blades: Heir to the Strongest Style</t>
+    <t>Hundreds of Invincible Strikes</t>
+  </si>
+  <si>
+    <t>arctic cold war</t>
+  </si>
+  <si>
+    <t>Apocalyptic Super Farm</t>
+  </si>
+  <si>
+    <t>Sword Sheath's Child</t>
+  </si>
+  <si>
+    <t>Reincarnator</t>
+  </si>
+  <si>
+    <t>Hunter Academy’S Strongest Battle God</t>
+  </si>
+  <si>
+    <t>Childhood Friend of the Zenith</t>
+  </si>
+  <si>
+    <t>Absolute Regression</t>
+  </si>
+  <si>
+    <t>Warrior Grandpa And Supreme Granddaughter</t>
+  </si>
+  <si>
+    <t>I Scared the Divine Lord as I Handed over the Ancient Immortal Pill</t>
+  </si>
+  <si>
+    <t>I Become a Legendary Arch Mage by Reading a Book</t>
+  </si>
+  <si>
+    <t>Hiding a logistics center in the apocalypse</t>
+  </si>
+  <si>
+    <t>The Hated Black Mage Returns</t>
+  </si>
+  <si>
+    <t>The Masters Are Subscribing To Me</t>
+  </si>
+  <si>
+    <t>A Ranker's Guide To The Good Life</t>
+  </si>
+  <si>
+    <t>Black Serpent</t>
+  </si>
+  <si>
+    <t>Conquering the Academy with Just a Sashimi Knife</t>
+  </si>
+  <si>
+    <t>The Magic Genius Of The Marquis House</t>
+  </si>
+  <si>
+    <t>The Reversal Of My Life As A Side Character</t>
+  </si>
+  <si>
+    <t>Absolute Dominion</t>
+  </si>
+  <si>
+    <t>Fatal Reset</t>
+  </si>
+  <si>
+    <t>The Necromancer Family’s Young Heir</t>
+  </si>
+  <si>
+    <t>Starting As A Master Of Female Disciples' Leisure Skills</t>
+  </si>
+  <si>
+    <t>Song Baek</t>
+  </si>
+  <si>
+    <t>Surviving as a Genius on Borrowed Time</t>
+  </si>
+  <si>
+    <t>The Regressed Mercenary’s Machinations</t>
+  </si>
+  <si>
+    <t>Traveling Through Time And Space To Become An Unlucky Npc: I Have A Wife To Protect Me</t>
+  </si>
+  <si>
+    <t>Cultivation: The Heaven's Fated Useless Genius</t>
+  </si>
+  <si>
+    <t>The Edgeless Sword From The Village</t>
+  </si>
+  <si>
+    <t>Levelling Up In An Exclusive Dungeon</t>
+  </si>
+  <si>
+    <t>Reincarnated As A Genius Prodigy Of A Prestigious Family</t>
+  </si>
+  <si>
+    <t>From Goblin To Goblin God</t>
+  </si>
+  <si>
+    <t>Margrave’S Bastard Son Was The Emperor</t>
+  </si>
+  <si>
+    <t>The Second Eunuch Regains His Manhood</t>
+  </si>
+  <si>
+    <t>Return Of The Runebound Professor</t>
+  </si>
+  <si>
+    <t>Regressing as the Reincarnated Bastard of the Sword Clan</t>
+  </si>
+  <si>
+    <t>I, The Demon Lord, Am Being Targeted By My Female Disciples!</t>
+  </si>
+  <si>
+    <t>Fated to Be Loved by Villains</t>
+  </si>
+  <si>
+    <t>The Chaebeol’s Youngest Son</t>
+  </si>
+  <si>
+    <t>Heavenly Demon Wants To Be A Chef</t>
+  </si>
+  <si>
+    <t>Entomologist In Sichuan Tang Clan</t>
+  </si>
+  <si>
+    <t>Last Word of the World</t>
+  </si>
+  <si>
+    <t>Cosmic Heavenly Demon 3077</t>
+  </si>
+  <si>
+    <t>Solo Resurrection</t>
+  </si>
+  <si>
+    <t>Dao of the Bizarre Immortal</t>
+  </si>
+  <si>
+    <t>Tenkaichi: Nihon Saikyou Bugeisha Ketteisen</t>
+  </si>
+  <si>
+    <t>Reincarnation Of The Heavenly Demon</t>
+  </si>
+  <si>
+    <t>Black Corporation: Joseon</t>
+  </si>
+  <si>
+    <t>Perhaps Invincible</t>
+  </si>
+  <si>
+    <t>The mad gate</t>
+  </si>
+  <si>
+    <t>Surviving the Apocalypse</t>
+  </si>
+  <si>
+    <t>Genius Prismatic Mage</t>
+  </si>
+  <si>
+    <t>Becoming a God, Starting as water monkey</t>
+  </si>
+  <si>
+    <t>I Became the Successor of the Martial God</t>
+  </si>
+  <si>
+    <t>Regression of the Yong Clan Heir</t>
+  </si>
+  <si>
+    <t>Chronicles of the Reincarnated Demon God</t>
+  </si>
+  <si>
+    <t>Revenge Of the Bloom Flower</t>
+  </si>
+  <si>
+    <t>The Heavenly Demon Wants a Quiet Life</t>
+  </si>
+  <si>
+    <t>Monster General Recorded Legacy</t>
+  </si>
+  <si>
+    <t>Using My Cooking Skills in a Murim World</t>
+  </si>
+  <si>
+    <t>I’m a Martial Art Villainess, but I’m the Strongest!</t>
+  </si>
+  <si>
+    <t>Metcha Shoukan Sareta Ken</t>
+  </si>
+  <si>
+    <t>Mount Hua Sect's Genius Phantom Swordsman</t>
+  </si>
+  <si>
+    <t>I'm going to destroy this country</t>
+  </si>
+  <si>
+    <t>The New Beggars' Sect</t>
+  </si>
+  <si>
+    <t>Overgeared</t>
+  </si>
+  <si>
+    <t>Regressed life of the Sword Clan’s Ignoble Reincarnator</t>
+  </si>
+  <si>
+    <t>Black Fox: Sword Master Of Mount Kunlun</t>
+  </si>
+  <si>
+    <t>God-level Assassin, I’m the Shadow</t>
+  </si>
+  <si>
+    <t>War Of The Corpses</t>
+  </si>
+  <si>
+    <t>The Illegitimate Who Devours Weapons</t>
+  </si>
+  <si>
+    <t>The Great Sage of the Namgung Clan</t>
+  </si>
+  <si>
+    <t>Limitless Ascension: Strength Amid Adversity</t>
+  </si>
+  <si>
+    <t>Apocalypse: Cockroaches Gives Me Buff</t>
+  </si>
+  <si>
+    <t>The Legendary Hero is an Academy Honors Student</t>
+  </si>
+  <si>
+    <t>Like a Fiery Flame</t>
+  </si>
+  <si>
+    <t>The Magic Tower's Problem Child</t>
+  </si>
+  <si>
+    <t>I Became the Husband of the Cult Leader of the Demonic Sect</t>
+  </si>
+  <si>
+    <t>The Apocalypse is Here</t>
+  </si>
+  <si>
+    <t>If I Don’t Die Soon, I Will Rule The Demon Realm</t>
+  </si>
+  <si>
+    <t>I Will Raise This Family to Greatness</t>
+  </si>
+  <si>
+    <t>The Villain Wants to Live</t>
+  </si>
+  <si>
+    <t>Genius Archer’s Livestreaming</t>
+  </si>
+  <si>
+    <t>After Ten Millennia in Hell</t>
+  </si>
+  <si>
+    <t>Heavenly Grand Archive's Young Master</t>
+  </si>
+  <si>
+    <t>Space Cheon-ma 3077</t>
+  </si>
+  <si>
+    <t>Iljin Romance</t>
+  </si>
+  <si>
+    <t>Shut Up, Evil Dragon! I Don't Want to Raise a Child With You Anymore</t>
+  </si>
+  <si>
+    <t>On the Way to Meet Mom</t>
+  </si>
+  <si>
+    <t>Ultimate Shut-in</t>
+  </si>
+  <si>
+    <t>The beginning after the end</t>
+  </si>
+  <si>
+    <t>Reborn in a Cyber Cultivation World, I Fight My Way to the Top</t>
+  </si>
+  <si>
+    <t>Level 999 Goblin</t>
+  </si>
+  <si>
+    <t>Dominating the Wasteland: I Control an Immortal Sect in the Apocalypse</t>
+  </si>
+  <si>
+    <t>Starting As The God Of Wealth, Taming Billions Of Divine Pets!</t>
+  </si>
+  <si>
+    <t>Martial Evolution: Start by Awakening the King of Monsters</t>
+  </si>
+  <si>
+    <t>The Girl from Random Chatting</t>
+  </si>
+  <si>
+    <t>Return of the Legend</t>
+  </si>
+  <si>
+    <t>Elven Queen</t>
+  </si>
+  <si>
+    <t>Emperor of Solo Play</t>
+  </si>
+  <si>
+    <t>The Fox-Eyed Villain of the Demon Academy</t>
+  </si>
+  <si>
+    <t>The Awakening Contract</t>
+  </si>
+  <si>
+    <t>The Sword God From a Fallen World</t>
+  </si>
+  <si>
+    <t>I Awakened to the Ex Skill "Fixed Damage" and Became Invincible</t>
+  </si>
+  <si>
+    <t>Warrior of the Mind Sword</t>
+  </si>
+  <si>
+    <t>Ninja Reincarnation: Fuuma Kotarou’s Quest to Reclaim His Humanity</t>
+  </si>
+  <si>
+    <t>Empress Maria</t>
+  </si>
+  <si>
+    <t>Reincarnation of the Fist King</t>
+  </si>
+  <si>
+    <t>There Are No Bad Warriors in the World</t>
+  </si>
+  <si>
+    <t>Return From The Depth</t>
+  </si>
+  <si>
+    <t>Return of the Apocalypse-Class Death Knight</t>
+  </si>
+  <si>
+    <t>Oversummoned, Overpowered, and Over It!</t>
+  </si>
+  <si>
+    <t>A Rogue Guard in a Medieval Fantasy</t>
+  </si>
+  <si>
+    <t>Chronicles of the Lazy Sovereign</t>
+  </si>
+  <si>
+    <t>I Was the Final Boss</t>
+  </si>
+  <si>
+    <t>Tang Clan Legend</t>
+  </si>
+  <si>
+    <t>The Demon-Slaying Madman—reborn as a demon</t>
+  </si>
+  <si>
+    <t>Urek Mazino</t>
+  </si>
+  <si>
+    <t>Demonic Sect Frontline: Thirteen Flying Dragons</t>
+  </si>
+  <si>
+    <t>Goddess of Abundance and the Genius Rogue Apostle</t>
+  </si>
+  <si>
+    <t>New Goguryeo Chronicles</t>
+  </si>
+  <si>
+    <t>Devil Summoner, I am the Abyss Lord</t>
+  </si>
+  <si>
+    <t>Legend of Dangun</t>
+  </si>
+  <si>
+    <t>The Tale of the Skeleton Messenger</t>
+  </si>
+  <si>
+    <t>The Great Heavenly Demon Sovereign</t>
+  </si>
+  <si>
+    <t>A Regressor's Tale of Cultivation</t>
+  </si>
+  <si>
+    <t>Jade of the Eight Gates</t>
+  </si>
+  <si>
+    <t>Disciple of the Three Kings</t>
+  </si>
+  <si>
+    <t>After the School Belle Dumped Me, I Became a Martial Arts God</t>
+  </si>
+  <si>
+    <t>Dead Mansion</t>
+  </si>
+  <si>
+    <t>Return of the King of Hell</t>
+  </si>
+  <si>
+    <t>Plaything</t>
+  </si>
+  <si>
+    <t>The Regressor Protects Only Me</t>
+  </si>
+  <si>
+    <t>Full-Time Awakening</t>
+  </si>
+  <si>
+    <t>Rebirth of the Divine Demon</t>
+  </si>
+  <si>
+    <t>Return of the First Patriarch: The Strongest Reincarnates into His Descendant 1000 Years Later</t>
+  </si>
+  <si>
+    <t>Lv. 99 Princess of Black Flame</t>
+  </si>
+  <si>
+    <t>Battle of the Martial Masters</t>
+  </si>
+  <si>
+    <t>The Yellow-haired Villain in Female Main Character's Novel wants Happiness</t>
+  </si>
+  <si>
+    <t>From Six to Sovereignty: The Girl Who Ruled</t>
+  </si>
+  <si>
+    <t>Eat and Go</t>
+  </si>
+  <si>
+    <t>I Shall Seal the Heavens</t>
+  </si>
+  <si>
+    <t>The Executed Sage Who Was Reincarnated as a Lich and Started an All-Out War</t>
+  </si>
+  <si>
+    <t>Demon Instructor's Return</t>
+  </si>
+  <si>
+    <t>The Archduke's Bride Is a Hell Warrior</t>
+  </si>
+  <si>
+    <t>Solo Leveling: Ragnarok</t>
+  </si>
+  <si>
+    <t>I Became a Patron of Villains</t>
+  </si>
+  <si>
+    <t>Black Crow</t>
+  </si>
+  <si>
+    <t>The Marquis Is the Marital Archduke</t>
+  </si>
+  <si>
+    <t>Dukedom's Legendary Prodigy</t>
+  </si>
+  <si>
+    <t>Reincarnated as the Crazed Heir</t>
+  </si>
+  <si>
+    <t>Lord of the Apocalypse</t>
+  </si>
+  <si>
+    <t>Don't Tell Me You Think Cultivating Immortality Is Difficult?</t>
+  </si>
+  <si>
+    <t>Immortal Fairy, Please Listen to My Explanation</t>
+  </si>
+  <si>
+    <t>Maplestory: The Last Adventurer</t>
+  </si>
+  <si>
+    <t>The Steel Emperor</t>
+  </si>
+  <si>
+    <t>The Luoyang Branch of the Heavenly Demon Cult</t>
+  </si>
+  <si>
+    <t>Spirit Hunter</t>
+  </si>
+  <si>
+    <t>Player of the Fallen Family</t>
+  </si>
+  <si>
+    <t>Unrivaled Spear Ghost</t>
+  </si>
+  <si>
+    <t>Reincarnation of the Martial God</t>
+  </si>
+  <si>
+    <t>After Rebirth, I Used Mirror Reversal For Vengeance</t>
+  </si>
+  <si>
+    <t>Death Attribute Magician</t>
+  </si>
+  <si>
+    <t>The Great Emperor Shinmadae</t>
+  </si>
+  <si>
+    <t>Revenger: Apocalypse of Vengeance</t>
+  </si>
+  <si>
+    <t>Hiding Out in an Apocalypse</t>
+  </si>
+  <si>
+    <t>Bad Born Blood</t>
+  </si>
+  <si>
+    <t>KaguRai: Kagura to Raito</t>
+  </si>
+  <si>
+    <t>Reincarnated as the Lazy and Villainous Noble, I Broke the Scenario and Became the Most Formidable With Extraordinary Magic</t>
+  </si>
+  <si>
+    <t>Star Armor꞉ I’ll Slaughter Through the Chaos with Star Soul Generals</t>
+  </si>
+  <si>
+    <t>The Demon King Overrun by Heroes</t>
+  </si>
+  <si>
+    <t>The Monkey King’s Journey to the Murim</t>
+  </si>
+  <si>
+    <t>The Sage who returned from another world wants to live quietly</t>
+  </si>
+  <si>
+    <t>Returned from Another World, Earth Turned Out to Be Quite the Fantasy Too. Also, Losing Heroines, Stop Looking This Way</t>
+  </si>
+  <si>
+    <t>Embodiment of the Assassin in the Murim World</t>
+  </si>
+  <si>
+    <t>Märchen - The Embodiment of Tales</t>
+  </si>
+  <si>
+    <t>Sichuan’s Supreme King</t>
+  </si>
+  <si>
+    <t>The Cold-Blooded Warrior</t>
+  </si>
+  <si>
+    <t>Everyone Loves Her</t>
+  </si>
+  <si>
+    <t>Paper Tiger</t>
+  </si>
+  <si>
+    <t>The Sword-Eating Swordmaster</t>
+  </si>
+  <si>
+    <t>The World's Best Kunlun Tavern</t>
+  </si>
+  <si>
+    <t>Defense Breaker</t>
+  </si>
+  <si>
+    <t>Worlds Best Assassin</t>
+  </si>
+  <si>
+    <t>The World's Best Martial Arts Instructor</t>
+  </si>
+  <si>
+    <t>How a Realist Hero Rebuilt the Kingdom</t>
+  </si>
+  <si>
+    <t>Sleepy Princess in the Demon Castle</t>
+  </si>
+  <si>
+    <t>To Hell With The Status Window</t>
+  </si>
+  <si>
+    <t>Becoming a Cheat-Level Skill Thief</t>
+  </si>
+  <si>
+    <t>Sichuan's Supreme King</t>
+  </si>
+  <si>
+    <t>Reborn After the Eight Empresses Betrayed Me, Now I’ll Make Them Regret It</t>
+  </si>
+  <si>
+    <t>Rebirth of the Demon Lord: the Slave who Conquered Fate</t>
+  </si>
+  <si>
+    <t>I, The Demon Lord am being targeted by my female Disciples!</t>
+  </si>
+  <si>
+    <t>The Strongest Wizard Becomes a Countryside Guard After Taking an Arrow to the Knee</t>
+  </si>
+  <si>
+    <t>The Secret Martial Artist of Demonic Blood</t>
+  </si>
+  <si>
+    <t>The Strongest Hero Who Longs For Revenge Will Peerlessly Annihilate With The Power Of Darkness</t>
+  </si>
+  <si>
+    <t>I Became the Scoundrel of the Cheon Family</t>
+  </si>
+  <si>
+    <t>Supreme Demon of Hyungsan</t>
+  </si>
+  <si>
+    <t>Orc Hero Story - Discovery Chronicles</t>
+  </si>
+  <si>
+    <t>Boukun Meika no Hangyakusha -Aster</t>
+  </si>
+  <si>
+    <t>Jakdu</t>
+  </si>
+  <si>
+    <t>Secretly Cultivating by the Demon Cult Leader's Side</t>
+  </si>
+  <si>
+    <t>The Old Prisoner Lives in Solitude</t>
+  </si>
+  <si>
+    <t>Revenge of Young Master Peng</t>
+  </si>
+  <si>
+    <t>Murim’s Dept King</t>
+  </si>
+  <si>
+    <t>My Girlfriend's Friend</t>
+  </si>
+  <si>
+    <t>Teto X Egen</t>
+  </si>
+  <si>
+    <t>Gokusotsu Kraken</t>
+  </si>
+  <si>
+    <t>The Masters of Heaven and Earth</t>
+  </si>
+  <si>
+    <t>Red Storm</t>
+  </si>
+  <si>
+    <t>A Dragon Lives in Kunlun</t>
+  </si>
+  <si>
+    <t>Friend of the Demon King</t>
+  </si>
+  <si>
+    <t>High Martial Arts: Sweeping Through Three Thousand Emperors with One Hand!</t>
+  </si>
+  <si>
+    <t>The Genius Martial Artist Who Remembers Everything</t>
+  </si>
+  <si>
+    <t>The Shepherd Wizard</t>
+  </si>
+  <si>
+    <t>Sovereign of a Hundred Blades: Heir to the Strongest Style</t>
+  </si>
+  <si>
+    <t>Shadow Slave</t>
+  </si>
+  <si>
+    <t>The Tale of Cultivation and Demon Extermination</t>
+  </si>
+  <si>
+    <t>The Tang Clan Chronicles</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1225,22 +1236,14 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Nimbus Sans"/>
@@ -1253,6 +1256,13 @@
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1282,14 +1292,14 @@
     </fill>
   </fills>
   <borders count="3">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFD9D9D9"/>
       </left>
@@ -1302,7 +1312,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFD9D9D9"/>
       </left>
@@ -1318,122 +1328,48 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF4F81BD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEAF2F8"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1492,57 +1428,74 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:B386" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:B386"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:B389" totalsRowShown="0">
+  <autoFilter ref="A1:B389" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="2">
-    <tableColumn id="1" name="Title"/>
-    <tableColumn id="2" name="Episodes"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Title"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Episodes"/>
   </tableColumns>
+  <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1550,12 +1503,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1584,7 +1537,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1605,7 +1558,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1656,7 +1609,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1674,27 +1627,26 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:B386"/>
-  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B389"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="169"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.43"/>
+    <col min="1" max="1" width="169" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:2" ht="15.75">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1702,3095 +1654,3114 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="4">
         <v>878</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:2">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="6">
         <v>266</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="4">
         <v>38</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:2">
       <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="6">
         <v>51</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:2">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="4">
         <v>31</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:2">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="6">
         <v>135</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:2">
       <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:2">
       <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:2">
       <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="4">
         <v>292</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:2">
       <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="6">
         <v>25</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:2">
       <c r="A12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="4">
         <v>39</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:2">
       <c r="A13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="6">
         <v>25</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:2">
       <c r="A14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="4">
         <v>116</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:2">
       <c r="A15" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:2">
       <c r="A16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="4">
         <v>73</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:2">
       <c r="A17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="6">
         <v>223</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:2">
       <c r="A18" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="4">
         <v>162</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:2">
       <c r="A19" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="6">
         <v>102</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:2">
       <c r="A20" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" s="4">
         <v>117</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:2">
       <c r="A21" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="6">
         <v>85</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:2">
       <c r="A22" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="4">
         <v>182</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:2">
       <c r="A23" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="6">
         <v>175</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:2">
       <c r="A24" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="4" t="n">
+      <c r="B24" s="4">
         <v>50</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:2">
       <c r="A25" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="6">
         <v>31</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:2">
       <c r="A26" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="4" t="n">
+      <c r="B26" s="4">
         <v>10.1</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:2">
       <c r="A27" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:2">
       <c r="A28" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="4" t="n">
+      <c r="B28" s="4">
         <v>19</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:2">
       <c r="A29" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="6">
         <v>54</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:2">
       <c r="A30" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="4" t="n">
+      <c r="B30" s="4">
         <v>105</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:2">
       <c r="A31" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="6">
         <v>77</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:2">
       <c r="A32" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="4" t="n">
+      <c r="B32" s="4">
         <v>37</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:2">
       <c r="A33" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="6">
         <v>88</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:2">
       <c r="A34" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="4" t="n">
+      <c r="B34" s="4">
         <v>99</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:2">
       <c r="A35" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="6">
         <v>157</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:2">
       <c r="A36" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="4" t="n">
+      <c r="B36" s="4">
         <v>39</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:2">
       <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="6">
         <v>51</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:2">
       <c r="A38" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="4" t="n">
+      <c r="B38" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:2">
       <c r="A39" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:2">
       <c r="A40" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="4" t="n">
+      <c r="B40" s="4">
         <v>124</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:2">
       <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="6">
         <v>111</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:2">
       <c r="A42" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="4" t="n">
+      <c r="B42" s="4">
         <v>63</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:2">
       <c r="A43" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="6">
         <v>45</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:2">
       <c r="A44" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B44" s="4" t="n">
+      <c r="B44" s="4">
         <v>162</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" spans="1:2">
       <c r="A45" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B45" s="6">
         <v>64</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:2">
       <c r="A46" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B46" s="4" t="n">
+      <c r="B46" s="4">
         <v>140</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" spans="1:2">
       <c r="A47" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B47" s="6">
         <v>168</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" spans="1:2">
       <c r="A48" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="4" t="n">
+      <c r="B48" s="4">
         <v>186</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" spans="1:2">
       <c r="A49" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B49" s="6" t="n">
+      <c r="B49" s="6">
         <v>12</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" spans="1:2">
       <c r="A50" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B50" s="4" t="n">
+      <c r="B50" s="4">
         <v>21</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" spans="1:2">
       <c r="A51" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B51" s="6" t="n">
+      <c r="B51" s="6">
         <v>37</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" spans="1:2">
       <c r="A52" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B52" s="4" t="n">
+      <c r="B52" s="4">
         <v>71</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" spans="1:2">
       <c r="A53" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B53" s="6" t="n">
+      <c r="B53" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" spans="1:2">
       <c r="A54" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B54" s="4" t="n">
+      <c r="B54" s="4">
         <v>25</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" spans="1:2">
       <c r="A55" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B55" s="6">
         <v>156</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" spans="1:2">
       <c r="A56" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B56" s="4" t="n">
+      <c r="B56" s="4">
         <v>45</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" spans="1:2">
       <c r="A57" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B57" s="6" t="n">
+      <c r="B57" s="6">
         <v>22</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" spans="1:2">
       <c r="A58" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B58" s="4" t="n">
+      <c r="B58" s="4">
         <v>144</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" spans="1:2">
       <c r="A59" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B59" s="6">
         <v>329</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" spans="1:2">
       <c r="A60" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B60" s="4" t="n">
+      <c r="B60" s="4">
         <v>161</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" spans="1:2">
       <c r="A61" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B61" s="6" t="n">
+      <c r="B61" s="6">
         <v>275</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" spans="1:2">
       <c r="A62" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B62" s="4" t="n">
+      <c r="B62" s="4">
         <v>311</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" spans="1:2">
       <c r="A63" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B63" s="6" t="n">
+      <c r="B63" s="6">
         <v>175</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" spans="1:2">
       <c r="A64" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B64" s="4" t="n">
+      <c r="B64" s="4">
         <v>58</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" spans="1:2">
       <c r="A65" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B65" s="6" t="n">
+      <c r="B65" s="6">
         <v>851</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" spans="1:2">
       <c r="A66" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B66" s="4" t="n">
+      <c r="B66" s="4">
         <v>3644</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" spans="1:2">
       <c r="A67" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B67" s="6" t="n">
+      <c r="B67" s="6">
         <v>46</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" spans="1:2">
       <c r="A68" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B68" s="4" t="n">
+      <c r="B68" s="4">
         <v>44</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" spans="1:2">
       <c r="A69" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B69" s="6" t="n">
+      <c r="B69" s="6">
         <v>76</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" spans="1:2">
       <c r="A70" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B70" s="4" t="n">
+      <c r="B70" s="4">
         <v>220</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" spans="1:2">
       <c r="A71" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B71" s="6" t="n">
+      <c r="B71" s="6">
         <v>29</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" spans="1:2">
       <c r="A72" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B72" s="4" t="n">
+      <c r="B72" s="4">
         <v>25</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" spans="1:2">
       <c r="A73" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B73" s="6" t="n">
+      <c r="B73" s="6">
         <v>89</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" spans="1:2">
       <c r="A74" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B74" s="4" t="n">
+      <c r="B74" s="4">
         <v>508.1</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" spans="1:2">
       <c r="A75" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B75" s="6" t="n">
+      <c r="B75" s="6">
         <v>43</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" spans="1:2">
       <c r="A76" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B76" s="4" t="n">
+      <c r="B76" s="4">
         <v>44</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" spans="1:2">
       <c r="A77" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B77" s="6" t="n">
+      <c r="B77" s="6">
         <v>587</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" spans="1:2">
       <c r="A78" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B78" s="4" t="n">
+      <c r="B78" s="4">
         <v>121</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" spans="1:2">
       <c r="A79" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B79" s="6" t="n">
+      <c r="B79" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" spans="1:2">
       <c r="A80" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B80" s="4" t="n">
+      <c r="B80" s="4">
         <v>157</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" spans="1:2">
       <c r="A81" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B81" s="6" t="n">
+      <c r="B81" s="6">
         <v>156</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" spans="1:2">
       <c r="A82" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B82" s="4" t="n">
+      <c r="B82" s="4">
         <v>235</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" spans="1:2">
       <c r="A83" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B83" s="6" t="n">
+      <c r="B83" s="6">
         <v>188</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" spans="1:2">
       <c r="A84" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B84" s="4" t="n">
+      <c r="B84" s="4">
         <v>106</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" spans="1:2">
       <c r="A85" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B85" s="6" t="n">
+      <c r="B85" s="6">
         <v>46</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" spans="1:2">
       <c r="A86" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B86" s="4" t="n">
+      <c r="B86" s="4">
         <v>33</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" spans="1:2">
       <c r="A87" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B87" s="6" t="n">
+      <c r="B87" s="6">
         <v>15</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" spans="1:2">
       <c r="A88" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B88" s="4" t="n">
+      <c r="B88" s="4">
         <v>187</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" spans="1:2">
       <c r="A89" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B89" s="6" t="n">
+      <c r="B89" s="6">
         <v>256</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" spans="1:2">
       <c r="A90" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B90" s="4" t="n">
+      <c r="B90" s="4">
         <v>133</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" spans="1:2">
       <c r="A91" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B91" s="6" t="n">
+      <c r="B91" s="6">
         <v>217</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" spans="1:2">
       <c r="A92" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B92" s="4" t="n">
+      <c r="B92" s="4">
         <v>20</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" spans="1:2">
       <c r="A93" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B93" s="6" t="n">
+      <c r="B93" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" spans="1:2">
       <c r="A94" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B94" s="4" t="n">
+      <c r="B94" s="4">
         <v>65</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" spans="1:2">
       <c r="A95" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B95" s="6" t="n">
+      <c r="B95" s="6">
         <v>56</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" spans="1:2">
       <c r="A96" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B96" s="4" t="n">
+      <c r="B96" s="4">
         <v>25</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" spans="1:2">
       <c r="A97" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="6" t="n">
+      <c r="B97" s="6">
         <v>52</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" spans="1:2">
       <c r="A98" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B98" s="4" t="n">
+      <c r="B98" s="4">
         <v>15</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" spans="1:2">
       <c r="A99" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B99" s="6" t="n">
+      <c r="B99" s="6">
         <v>41</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" spans="1:2">
       <c r="A100" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B100" s="4" t="n">
+      <c r="B100" s="4">
         <v>182</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" spans="1:2">
       <c r="A101" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B101" s="6" t="n">
+      <c r="B101" s="6">
         <v>157</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" spans="1:2">
       <c r="A102" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B102" s="4" t="n">
+      <c r="B102" s="4">
         <v>31</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" spans="1:2">
       <c r="A103" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B103" s="6" t="n">
+      <c r="B103" s="6">
         <v>103</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" spans="1:2">
       <c r="A104" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B104" s="4" t="n">
+      <c r="B104" s="4">
         <v>15</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" spans="1:2">
       <c r="A105" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B105" s="6" t="n">
+      <c r="B105" s="6">
         <v>94</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" spans="1:2">
       <c r="A106" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B106" s="4" t="n">
+      <c r="B106" s="4">
         <v>221</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" spans="1:2">
       <c r="A107" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B107" s="6" t="n">
+      <c r="B107" s="6">
         <v>50</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" spans="1:2">
       <c r="A108" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B108" s="4" t="n">
+      <c r="B108" s="4">
         <v>61</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" spans="1:2">
       <c r="A109" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B109" s="6" t="n">
+      <c r="B109" s="6">
         <v>7</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" spans="1:2">
       <c r="A110" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B110" s="4" t="n">
+      <c r="B110" s="4">
         <v>10.1</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" spans="1:2">
       <c r="A111" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="B111" s="6" t="n">
+      <c r="B111" s="6">
         <v>79</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" spans="1:2">
       <c r="A112" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B112" s="4" t="n">
+      <c r="B112" s="4">
         <v>46</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" spans="1:2">
       <c r="A113" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B113" s="6" t="n">
+      <c r="B113" s="6">
         <v>34</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" spans="1:2">
       <c r="A114" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B114" s="4" t="n">
+      <c r="B114" s="4">
         <v>38.1</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" spans="1:2">
       <c r="A115" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B115" s="6" t="n">
+      <c r="B115" s="6">
         <v>63</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" spans="1:2">
       <c r="A116" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B116" s="4" t="n">
+      <c r="B116" s="4">
         <v>31</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" spans="1:2">
       <c r="A117" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B117" s="6" t="n">
+      <c r="B117" s="6">
         <v>29</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" spans="1:2">
       <c r="A118" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B118" s="4" t="n">
+      <c r="B118" s="4">
         <v>49</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" spans="1:2">
       <c r="A119" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B119" s="6" t="n">
+      <c r="B119" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" spans="1:2">
       <c r="A120" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B120" s="4" t="n">
+      <c r="B120" s="4">
         <v>20</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" spans="1:2">
       <c r="A121" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B121" s="6" t="n">
+      <c r="B121" s="6">
         <v>43</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" spans="1:2">
       <c r="A122" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B122" s="4" t="n">
+      <c r="B122" s="4">
         <v>19</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" spans="1:2">
       <c r="A123" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B123" s="6" t="n">
+      <c r="B123" s="6">
         <v>25</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" spans="1:2">
       <c r="A124" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B124" s="4" t="n">
+      <c r="B124" s="4">
         <v>33</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" spans="1:2">
       <c r="A125" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B125" s="6" t="n">
+      <c r="B125" s="6">
         <v>7.2</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" spans="1:2">
       <c r="A126" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B126" s="4" t="n">
+      <c r="B126" s="4">
         <v>29</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" spans="1:2">
       <c r="A127" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B127" s="6" t="n">
+      <c r="B127" s="6">
         <v>38</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" spans="1:2">
       <c r="A128" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B128" s="4" t="n">
+      <c r="B128" s="4">
         <v>58</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" spans="1:2">
       <c r="A129" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="B129" s="6" t="n">
+      <c r="B129" s="6">
         <v>18</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" spans="1:2">
       <c r="A130" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B130" s="4" t="n">
+      <c r="B130" s="4">
         <v>54</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" spans="1:2">
       <c r="A131" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B131" s="6" t="n">
+      <c r="B131" s="6">
         <v>37</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" spans="1:2">
       <c r="A132" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B132" s="4" t="n">
+      <c r="B132" s="4">
         <v>56</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" spans="1:2">
       <c r="A133" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B133" s="6" t="n">
+      <c r="B133" s="6">
         <v>12.2</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" spans="1:2">
       <c r="A134" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B134" s="4" t="n">
+      <c r="B134" s="4">
         <v>91</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" spans="1:2">
       <c r="A135" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B135" s="6" t="n">
+      <c r="B135" s="6">
         <v>165</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" spans="1:2">
       <c r="A136" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B136" s="4" t="n">
+      <c r="B136" s="4">
         <v>135</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" spans="1:2">
       <c r="A137" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="B137" s="6" t="n">
+      <c r="B137" s="6">
         <v>92</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" spans="1:2">
       <c r="A138" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B138" s="4" t="n">
+      <c r="B138" s="4">
         <v>14</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" spans="1:2">
       <c r="A139" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B139" s="6" t="n">
+      <c r="B139" s="6">
         <v>31</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" spans="1:2">
       <c r="A140" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B140" s="4" t="n">
+      <c r="B140" s="4">
         <v>90</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" spans="1:2">
       <c r="A141" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B141" s="6" t="n">
+      <c r="B141" s="6">
         <v>48</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" spans="1:2">
       <c r="A142" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B142" s="4" t="n">
+      <c r="B142" s="4">
         <v>39</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" spans="1:2">
       <c r="A143" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="B143" s="6" t="n">
+      <c r="B143" s="6">
         <v>120</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" spans="1:2">
       <c r="A144" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B144" s="4" t="n">
+      <c r="B144" s="4">
         <v>22</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" spans="1:2">
       <c r="A145" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B145" s="6" t="n">
+      <c r="B145" s="6">
         <v>123</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" spans="1:2">
       <c r="A146" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B146" s="4" t="n">
+      <c r="B146" s="4">
         <v>102</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" spans="1:2">
       <c r="A147" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B147" s="6" t="n">
+      <c r="B147" s="6">
         <v>12</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" spans="1:2">
       <c r="A148" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B148" s="4" t="n">
+      <c r="B148" s="4">
         <v>38</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" spans="1:2">
       <c r="A149" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="B149" s="6" t="n">
+      <c r="B149" s="6">
         <v>22</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" spans="1:2">
       <c r="A150" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B150" s="4" t="n">
+      <c r="B150" s="4">
         <v>73</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" spans="1:2">
       <c r="A151" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B151" s="6" t="n">
+      <c r="B151" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" spans="1:2">
       <c r="A152" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B152" s="4" t="n">
+      <c r="B152" s="4">
         <v>63</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" spans="1:2">
       <c r="A153" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B153" s="6" t="n">
+      <c r="B153" s="6">
         <v>83</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" spans="1:2">
       <c r="A154" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B154" s="4" t="n">
+      <c r="B154" s="4">
         <v>139</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" spans="1:2">
       <c r="A155" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B155" s="6" t="n">
+      <c r="B155" s="6">
         <v>15</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" spans="1:2">
       <c r="A156" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B156" s="4" t="n">
+      <c r="B156" s="4">
         <v>24</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" spans="1:2">
       <c r="A157" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B157" s="6" t="n">
+      <c r="B157" s="6">
         <v>76</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" spans="1:2">
       <c r="A158" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B158" s="4" t="n">
+      <c r="B158" s="4">
         <v>38</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" spans="1:2">
       <c r="A159" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B159" s="6" t="n">
+      <c r="B159" s="6">
         <v>44</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" spans="1:2">
       <c r="A160" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B160" s="4" t="n">
+      <c r="B160" s="4">
         <v>26</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" spans="1:2">
       <c r="A161" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B161" s="6" t="n">
+      <c r="B161" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" spans="1:2">
       <c r="A162" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B162" s="4" t="n">
+      <c r="B162" s="4">
         <v>29</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" spans="1:2">
       <c r="A163" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B163" s="6" t="n">
+      <c r="B163" s="6">
         <v>34</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" spans="1:2">
       <c r="A164" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B164" s="4" t="n">
+      <c r="B164" s="4">
         <v>11</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" spans="1:2">
       <c r="A165" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="B165" s="6" t="n">
+      <c r="B165" s="6">
         <v>18</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" spans="1:2">
       <c r="A166" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B166" s="4" t="n">
+      <c r="B166" s="4">
         <v>26</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" spans="1:2">
       <c r="A167" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="B167" s="6" t="n">
+      <c r="B167" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" spans="1:2">
       <c r="A168" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B168" s="4" t="n">
+      <c r="B168" s="4">
         <v>108</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" spans="1:2">
       <c r="A169" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="B169" s="6" t="n">
+      <c r="B169" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" spans="1:2">
       <c r="A170" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B170" s="4" t="n">
+      <c r="B170" s="4">
         <v>49</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" spans="1:2">
       <c r="A171" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="B171" s="6" t="n">
+      <c r="B171" s="6">
         <v>54</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" spans="1:2">
       <c r="A172" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B172" s="4" t="n">
+      <c r="B172" s="4">
         <v>74</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" spans="1:2">
       <c r="A173" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="B173" s="6" t="n">
+      <c r="B173" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" spans="1:2">
       <c r="A174" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B174" s="4" t="n">
+      <c r="B174" s="4">
         <v>37</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" spans="1:2">
       <c r="A175" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="B175" s="6" t="n">
+      <c r="B175" s="6">
         <v>40</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" spans="1:2">
       <c r="A176" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B176" s="4" t="n">
+      <c r="B176" s="4">
         <v>104</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" spans="1:2">
       <c r="A177" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="B177" s="6" t="n">
+      <c r="B177" s="6">
         <v>76</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" spans="1:2">
       <c r="A178" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B178" s="4" t="n">
+      <c r="B178" s="4">
         <v>100</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" spans="1:2">
       <c r="A179" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="B179" s="6" t="n">
+      <c r="B179" s="6">
         <v>50</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" spans="1:2">
       <c r="A180" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B180" s="4" t="n">
+      <c r="B180" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" spans="1:2">
       <c r="A181" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="B181" s="6" t="n">
+      <c r="B181" s="6">
         <v>45</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" spans="1:2">
       <c r="A182" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B182" s="4" t="n">
+      <c r="B182" s="4">
         <v>9</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" spans="1:2">
       <c r="A183" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="B183" s="6" t="n">
+      <c r="B183" s="6">
         <v>15</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" spans="1:2">
       <c r="A184" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B184" s="4" t="n">
+      <c r="B184" s="4">
         <v>37</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" spans="1:2">
       <c r="A185" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="B185" s="6" t="n">
+      <c r="B185" s="6">
         <v>28</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" spans="1:2">
       <c r="A186" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B186" s="4" t="n">
+      <c r="B186" s="4">
         <v>38</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" spans="1:2">
       <c r="A187" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="B187" s="6" t="n">
+      <c r="B187" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" spans="1:2">
       <c r="A188" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B188" s="4" t="n">
+      <c r="B188" s="4">
         <v>27</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" spans="1:2">
       <c r="A189" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="B189" s="6" t="n">
+      <c r="B189" s="6">
         <v>91</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" spans="1:2">
       <c r="A190" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B190" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B190" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
       <c r="A191" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="B191" s="6" t="n">
+      <c r="B191" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" spans="1:2">
       <c r="A192" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B192" s="4" t="n">
+      <c r="B192" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" spans="1:2">
       <c r="A193" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B193" s="6" t="n">
+      <c r="B193" s="6">
         <v>25</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" spans="1:2">
       <c r="A194" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B194" s="4" t="n">
+      <c r="B194" s="4">
         <v>54</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" spans="1:2">
       <c r="A195" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B195" s="6" t="n">
+      <c r="B195" s="6">
         <v>89</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" spans="1:2">
       <c r="A196" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B196" s="4" t="n">
+      <c r="B196" s="4">
         <v>54</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" spans="1:2">
       <c r="A197" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B197" s="6" t="n">
+      <c r="B197" s="6">
         <v>29</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" spans="1:2">
       <c r="A198" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B198" s="4" t="n">
+      <c r="B198" s="4">
         <v>59</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" spans="1:2">
       <c r="A199" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B199" s="6" t="n">
+      <c r="B199" s="6">
         <v>26</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" spans="1:2">
       <c r="A200" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B200" s="4" t="n">
+      <c r="B200" s="4">
         <v>26</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" spans="1:2">
       <c r="A201" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="B201" s="6" t="n">
+      <c r="B201" s="6">
         <v>108</v>
       </c>
     </row>
-    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" spans="1:2">
       <c r="A202" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B202" s="4" t="n">
+      <c r="B202" s="4">
         <v>44</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" spans="1:2">
       <c r="A203" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="B203" s="6" t="n">
+      <c r="B203" s="6">
         <v>15</v>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" spans="1:2">
       <c r="A204" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B204" s="4" t="n">
+      <c r="B204" s="4">
         <v>9</v>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" spans="1:2">
       <c r="A205" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="B205" s="6" t="n">
+      <c r="B205" s="6">
         <v>26</v>
       </c>
     </row>
-    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" spans="1:2">
       <c r="A206" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B206" s="4" t="n">
+      <c r="B206" s="4">
         <v>17</v>
       </c>
     </row>
-    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" spans="1:2">
       <c r="A207" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="B207" s="6" t="n">
+      <c r="B207" s="6">
         <v>25</v>
       </c>
     </row>
-    <row r="208" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" spans="1:2">
       <c r="A208" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="B208" s="4" t="n">
+      <c r="B208" s="4">
         <v>220</v>
       </c>
     </row>
-    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" spans="1:2">
       <c r="A209" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="B209" s="6" t="n">
+      <c r="B209" s="6">
         <v>22</v>
       </c>
     </row>
-    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" spans="1:2">
       <c r="A210" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B210" s="4" t="n">
+      <c r="B210" s="4">
         <v>51</v>
       </c>
     </row>
-    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" spans="1:2">
       <c r="A211" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="B211" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B211" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
       <c r="A212" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B212" s="4" t="n">
+      <c r="B212" s="4">
         <v>60</v>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" spans="1:2">
       <c r="A213" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="B213" s="6" t="n">
+      <c r="B213" s="6">
         <v>31</v>
       </c>
     </row>
-    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="214" spans="1:2">
       <c r="A214" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B214" s="4" t="n">
+      <c r="B214" s="4">
         <v>38</v>
       </c>
     </row>
-    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="215" spans="1:2">
       <c r="A215" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="B215" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B215" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
       <c r="A216" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="B216" s="4" t="n">
+      <c r="B216" s="4">
         <v>70</v>
       </c>
     </row>
-    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="217" spans="1:2">
       <c r="A217" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B217" s="6" t="n">
+      <c r="B217" s="6">
         <v>141</v>
       </c>
     </row>
-    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="218" spans="1:2">
       <c r="A218" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B218" s="4" t="n">
+      <c r="B218" s="4">
         <v>31</v>
       </c>
     </row>
-    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="219" spans="1:2">
       <c r="A219" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="B219" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B219" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
       <c r="A220" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="B220" s="4" t="n">
+      <c r="B220" s="4">
         <v>49</v>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" spans="1:2">
       <c r="A221" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="B221" s="6" t="n">
+      <c r="B221" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" spans="1:2">
       <c r="A222" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B222" s="4" t="n">
+      <c r="B222" s="4">
         <v>23</v>
       </c>
     </row>
-    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="223" spans="1:2">
       <c r="A223" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="B223" s="6" t="n">
+      <c r="B223" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="224" spans="1:2">
       <c r="A224" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B224" s="4" t="n">
+      <c r="B224" s="4">
         <v>21</v>
       </c>
     </row>
-    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" spans="1:2">
       <c r="A225" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="B225" s="6" t="n">
+      <c r="B225" s="6">
         <v>26</v>
       </c>
     </row>
-    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" spans="1:2">
       <c r="A226" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="B226" s="4" t="n">
+      <c r="B226" s="4">
         <v>36</v>
       </c>
     </row>
-    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="227" spans="1:2">
       <c r="A227" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="B227" s="6" t="n">
+      <c r="B227" s="6">
         <v>64</v>
       </c>
     </row>
-    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="228" spans="1:2">
       <c r="A228" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="B228" s="4" t="n">
+      <c r="B228" s="4">
         <v>37</v>
       </c>
     </row>
-    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="229" spans="1:2">
       <c r="A229" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="B229" s="6" t="n">
+      <c r="B229" s="6">
         <v>22</v>
       </c>
     </row>
-    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="230" spans="1:2">
       <c r="A230" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B230" s="4" t="n">
+      <c r="B230" s="4">
         <v>124</v>
       </c>
     </row>
-    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="231" spans="1:2">
       <c r="A231" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="B231" s="6" t="n">
+      <c r="B231" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="232" spans="1:2">
       <c r="A232" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="B232" s="4" t="n">
+      <c r="B232" s="4">
         <v>18</v>
       </c>
     </row>
-    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="233" spans="1:2">
       <c r="A233" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="B233" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B233" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
       <c r="A234" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="B234" s="4" t="n">
+      <c r="B234" s="4">
         <v>16</v>
       </c>
     </row>
-    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="235" spans="1:2">
       <c r="A235" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="B235" s="6" t="n">
+      <c r="B235" s="6">
         <v>130</v>
       </c>
     </row>
-    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="236" spans="1:2">
       <c r="A236" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="B236" s="4" t="n">
+      <c r="B236" s="4">
         <v>67</v>
       </c>
     </row>
-    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="237" spans="1:2">
       <c r="A237" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="B237" s="6" t="n">
+      <c r="B237" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="238" spans="1:2">
       <c r="A238" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B238" s="4" t="n">
+      <c r="B238" s="4">
         <v>12</v>
       </c>
     </row>
-    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="239" spans="1:2">
       <c r="A239" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="B239" s="6" t="n">
+      <c r="B239" s="6">
         <v>9</v>
       </c>
     </row>
-    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" spans="1:2">
       <c r="A240" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B240" s="4" t="n">
+      <c r="B240" s="4">
         <v>21</v>
       </c>
     </row>
-    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="241" spans="1:2">
       <c r="A241" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="B241" s="6" t="n">
+      <c r="B241" s="6">
         <v>14</v>
       </c>
     </row>
-    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="242" spans="1:2">
       <c r="A242" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="B242" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B242" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
       <c r="A243" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="B243" s="6" t="n">
+      <c r="B243" s="6">
         <v>12</v>
       </c>
     </row>
-    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="244" spans="1:2">
       <c r="A244" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B244" s="4" t="n">
+      <c r="B244" s="4">
         <v>25</v>
       </c>
     </row>
-    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="245" spans="1:2">
       <c r="A245" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="B245" s="6" t="n">
+      <c r="B245" s="6">
         <v>9</v>
       </c>
     </row>
-    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="246" spans="1:2">
       <c r="A246" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="B246" s="4" t="n">
+      <c r="B246" s="4">
         <v>8</v>
       </c>
     </row>
-    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="247" spans="1:2">
       <c r="A247" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="B247" s="6" t="n">
+      <c r="B247" s="6">
         <v>12</v>
       </c>
     </row>
-    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="248" spans="1:2">
       <c r="A248" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="B248" s="4" t="n">
+      <c r="B248" s="4">
         <v>38</v>
       </c>
     </row>
-    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="249" spans="1:2">
       <c r="A249" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="B249" s="6" t="n">
+      <c r="B249" s="6">
         <v>81</v>
       </c>
     </row>
-    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="250" spans="1:2">
       <c r="A250" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B250" s="4" t="n">
+      <c r="B250" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="251" spans="1:2">
       <c r="A251" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="B251" s="6" t="n">
+      <c r="B251" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="252" spans="1:2">
       <c r="A252" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="B252" s="4" t="n">
+      <c r="B252" s="4">
         <v>57</v>
       </c>
     </row>
-    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="253" spans="1:2">
       <c r="A253" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="B253" s="6" t="n">
+      <c r="B253" s="6">
         <v>112</v>
       </c>
     </row>
-    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="254" spans="1:2">
       <c r="A254" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B254" s="4" t="n">
+      <c r="B254" s="4">
         <v>126</v>
       </c>
     </row>
-    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="255" spans="1:2">
       <c r="A255" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="B255" s="6" t="n">
+      <c r="B255" s="6">
         <v>44</v>
       </c>
     </row>
-    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="256" spans="1:2">
       <c r="A256" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="B256" s="4" t="n">
+      <c r="B256" s="4">
         <v>46</v>
       </c>
     </row>
-    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="257" spans="1:2">
       <c r="A257" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="B257" s="6" t="n">
+      <c r="B257" s="6">
         <v>40</v>
       </c>
     </row>
-    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="258" spans="1:2">
       <c r="A258" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="B258" s="4" t="n">
+      <c r="B258" s="4">
         <v>28</v>
       </c>
     </row>
-    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="259" spans="1:2">
       <c r="A259" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="B259" s="6" t="n">
+      <c r="B259" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="260" spans="1:2">
       <c r="A260" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="B260" s="4" t="n">
+      <c r="B260" s="4">
         <v>219</v>
       </c>
     </row>
-    <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="261" spans="1:2">
       <c r="A261" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="B261" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B261" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
       <c r="A262" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="B262" s="4" t="n">
+      <c r="B262" s="4">
         <v>55</v>
       </c>
     </row>
-    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="263" spans="1:2">
       <c r="A263" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="B263" s="6" t="n">
+      <c r="B263" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="264" spans="1:2">
       <c r="A264" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="B264" s="4" t="n">
+      <c r="B264" s="4">
         <v>22</v>
       </c>
     </row>
-    <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="265" spans="1:2">
       <c r="A265" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="B265" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B265" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
       <c r="A266" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="B266" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B266" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
       <c r="A267" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="B267" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B267" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
       <c r="A268" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B268" s="4" t="n">
+      <c r="B268" s="4">
         <v>17</v>
       </c>
     </row>
-    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="269" spans="1:2">
       <c r="A269" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="B269" s="6" t="n">
+      <c r="B269" s="6">
         <v>18</v>
       </c>
     </row>
-    <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="270" spans="1:2">
       <c r="A270" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="B270" s="4" t="n">
+      <c r="B270" s="4">
         <v>29</v>
       </c>
     </row>
-    <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="271" spans="1:2">
       <c r="A271" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="B271" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B271" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
       <c r="A272" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="B272" s="4" t="n">
+      <c r="B272" s="4">
         <v>22</v>
       </c>
     </row>
-    <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="273" spans="1:2">
       <c r="A273" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="B273" s="6" t="n">
+      <c r="B273" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="274" spans="1:2">
       <c r="A274" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="B274" s="4" t="n">
+      <c r="B274" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="275" spans="1:2">
       <c r="A275" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="B275" s="6" t="n">
+      <c r="B275" s="6">
         <v>45</v>
       </c>
     </row>
-    <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="276" spans="1:2">
       <c r="A276" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="B276" s="4" t="n">
+      <c r="B276" s="4">
         <v>21</v>
       </c>
     </row>
-    <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="277" spans="1:2">
       <c r="A277" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="B277" s="6" t="n">
+      <c r="B277" s="6">
         <v>34</v>
       </c>
     </row>
-    <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="278" spans="1:2">
       <c r="A278" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="B278" s="4" t="n">
+      <c r="B278" s="4">
         <v>40</v>
       </c>
     </row>
-    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="279" spans="1:2">
       <c r="A279" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="B279" s="6" t="n">
+      <c r="B279" s="6">
         <v>22</v>
       </c>
     </row>
-    <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="280" spans="1:2">
       <c r="A280" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B280" s="4" t="n">
+      <c r="B280" s="4">
         <v>25</v>
       </c>
     </row>
-    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="281" spans="1:2">
       <c r="A281" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="B281" s="6" t="n">
+      <c r="B281" s="6">
         <v>45</v>
       </c>
     </row>
-    <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="282" spans="1:2">
       <c r="A282" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="B282" s="4" t="n">
+      <c r="B282" s="4">
         <v>28</v>
       </c>
     </row>
-    <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="283" spans="1:2">
       <c r="A283" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="B283" s="6" t="n">
+      <c r="B283" s="6">
         <v>27</v>
       </c>
     </row>
-    <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="284" spans="1:2">
       <c r="A284" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="B284" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B284" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
       <c r="A285" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="B285" s="6" t="n">
+      <c r="B285" s="6">
         <v>13</v>
       </c>
     </row>
-    <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="286" spans="1:2">
       <c r="A286" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="B286" s="4" t="n">
+      <c r="B286" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="287" spans="1:2">
       <c r="A287" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="B287" s="6" t="n">
+      <c r="B287" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="288" spans="1:2">
       <c r="A288" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="B288" s="4" t="n">
+      <c r="B288" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="289" spans="1:2">
       <c r="A289" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="B289" s="6" t="n">
+      <c r="B289" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="290" spans="1:2">
       <c r="A290" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="B290" s="4" t="n">
+      <c r="B290" s="4">
         <v>38</v>
       </c>
     </row>
-    <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="291" spans="1:2">
       <c r="A291" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="B291" s="6" t="n">
+      <c r="B291" s="6">
         <v>31</v>
       </c>
     </row>
-    <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="292" spans="1:2">
       <c r="A292" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="B292" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B292" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
       <c r="A293" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="B293" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B293" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
       <c r="A294" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="B294" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B294" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
       <c r="A295" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="B295" s="6" t="n">
+      <c r="B295" s="6">
         <v>25</v>
       </c>
     </row>
-    <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="296" spans="1:2">
       <c r="A296" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="B296" s="4" t="n">
+      <c r="B296" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="297" spans="1:2">
       <c r="A297" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="B297" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B297" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
       <c r="A298" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="B298" s="4" t="n">
+      <c r="B298" s="4">
         <v>29</v>
       </c>
     </row>
-    <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="299" spans="1:2">
       <c r="A299" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="B299" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B299" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
       <c r="A300" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="B300" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B300" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
       <c r="A301" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="B301" s="6" t="n">
+      <c r="B301" s="6">
         <v>56</v>
       </c>
     </row>
-    <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="302" spans="1:2">
       <c r="A302" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="B302" s="4" t="n">
+      <c r="B302" s="4">
         <v>41</v>
       </c>
     </row>
-    <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="303" spans="1:2">
       <c r="A303" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="B303" s="6" t="n">
+      <c r="B303" s="6">
         <v>21</v>
       </c>
     </row>
-    <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="304" spans="1:2">
       <c r="A304" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="B304" s="4" t="n">
+      <c r="B304" s="4">
         <v>9</v>
       </c>
     </row>
-    <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="305" spans="1:2">
       <c r="A305" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="B305" s="6" t="n">
+      <c r="B305" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="306" spans="1:2">
       <c r="A306" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="B306" s="4" t="n">
+      <c r="B306" s="4">
         <v>27</v>
       </c>
     </row>
-    <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="307" spans="1:2">
       <c r="A307" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="B307" s="6" t="n">
+      <c r="B307" s="6">
         <v>15</v>
       </c>
     </row>
-    <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="308" spans="1:2">
       <c r="A308" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="B308" s="4" t="n">
+      <c r="B308" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="309" spans="1:2">
       <c r="A309" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="B309" s="6" t="n">
+      <c r="B309" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="310" spans="1:2">
       <c r="A310" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="B310" s="4" t="n">
+      <c r="B310" s="4">
         <v>21</v>
       </c>
     </row>
-    <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="311" spans="1:2">
       <c r="A311" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="B311" s="6" t="n">
+      <c r="B311" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="312" spans="1:2">
       <c r="A312" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="B312" s="4" t="n">
+      <c r="B312" s="4">
         <v>55</v>
       </c>
     </row>
-    <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="313" spans="1:2">
       <c r="A313" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="B313" s="6" t="n">
+      <c r="B313" s="6">
         <v>28</v>
       </c>
     </row>
-    <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="314" spans="1:2">
       <c r="A314" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="B314" s="4" t="n">
+      <c r="B314" s="4">
         <v>32</v>
       </c>
     </row>
-    <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="315" spans="1:2">
       <c r="A315" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="B315" s="6" t="n">
+      <c r="B315" s="6">
         <v>47</v>
       </c>
     </row>
-    <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="316" spans="1:2">
       <c r="A316" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="B316" s="4" t="n">
+      <c r="B316" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="317" spans="1:2">
       <c r="A317" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B317" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B317" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
       <c r="A318" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="B318" s="4" t="n">
+      <c r="B318" s="4">
         <v>18</v>
       </c>
     </row>
-    <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="319" spans="1:2">
       <c r="A319" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="B319" s="6" t="n">
+      <c r="B319" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="320" spans="1:2">
       <c r="A320" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="B320" s="4" t="n">
+      <c r="B320" s="4">
         <v>161</v>
       </c>
     </row>
-    <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="321" spans="1:2">
       <c r="A321" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="B321" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B321" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
       <c r="A322" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="B322" s="4" t="n">
+      <c r="B322" s="4">
         <v>34</v>
       </c>
     </row>
-    <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="323" spans="1:2">
       <c r="A323" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="B323" s="6" t="n">
+      <c r="B323" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="324" spans="1:2">
       <c r="A324" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="B324" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B324" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
       <c r="A325" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="B325" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B325" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
       <c r="A326" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="B326" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B326" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
       <c r="A327" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="B327" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B327" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
       <c r="A328" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="B328" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B328" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
       <c r="A329" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="B329" s="6" t="n">
+      <c r="B329" s="6">
         <v>25</v>
       </c>
     </row>
-    <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="330" spans="1:2">
       <c r="A330" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="B330" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B330" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
       <c r="A331" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="B331" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B331" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
       <c r="A332" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="B332" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B332" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
       <c r="A333" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="B333" s="6" t="n">
+      <c r="B333" s="6">
         <v>29</v>
       </c>
     </row>
-    <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="334" spans="1:2">
       <c r="A334" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="B334" s="4" t="n">
+      <c r="B334" s="4">
         <v>38</v>
       </c>
     </row>
-    <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="335" spans="1:2">
       <c r="A335" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="B335" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B335" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
       <c r="A336" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="B336" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B336" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
       <c r="A337" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="B337" s="6" t="n">
+      <c r="B337" s="6">
         <v>27</v>
       </c>
     </row>
-    <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="338" spans="1:2">
       <c r="A338" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="B338" s="4" t="n">
+      <c r="B338" s="4">
         <v>17</v>
       </c>
     </row>
-    <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="339" spans="1:2">
       <c r="A339" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="B339" s="6" t="n">
+      <c r="B339" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="340" spans="1:2">
       <c r="A340" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="B340" s="4" t="n">
+      <c r="B340" s="4">
         <v>8</v>
       </c>
     </row>
-    <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="341" spans="1:2">
       <c r="A341" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="B341" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B341" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
       <c r="A342" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="B342" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B342" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
       <c r="A343" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="B343" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B343" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
       <c r="A344" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="B344" s="4" t="n">
+      <c r="B344" s="4">
         <v>12</v>
       </c>
     </row>
-    <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="345" spans="1:2">
       <c r="A345" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="B345" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B345" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
       <c r="A346" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="B346" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B346" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
       <c r="A347" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="B347" s="6" t="n">
+      <c r="B347" s="6">
         <v>40</v>
       </c>
     </row>
-    <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="348" spans="1:2">
       <c r="A348" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="B348" s="4" t="n">
+      <c r="B348" s="4">
         <v>44</v>
       </c>
     </row>
-    <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="349" spans="1:2">
       <c r="A349" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="B349" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B349" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
       <c r="A350" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="B350" s="4" t="n">
+      <c r="B350" s="4">
         <v>7</v>
       </c>
     </row>
-    <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="351" spans="1:2">
       <c r="A351" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="B351" s="6" t="n">
+      <c r="B351" s="6">
         <v>97</v>
       </c>
     </row>
-    <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="352" spans="1:2">
       <c r="A352" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="B352" s="4" t="n">
+      <c r="B352" s="4">
         <v>29</v>
       </c>
     </row>
-    <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="353" spans="1:2">
       <c r="A353" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="B353" s="6" t="n">
+      <c r="B353" s="6">
         <v>50</v>
       </c>
     </row>
-    <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="354" spans="1:2">
       <c r="A354" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="B354" s="4" t="n">
+      <c r="B354" s="4">
         <v>52</v>
       </c>
     </row>
-    <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="355" spans="1:2">
       <c r="A355" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="B355" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B355" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
       <c r="A356" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="B356" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B356" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
       <c r="A357" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="B357" s="6" t="n">
+      <c r="B357" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="358" spans="1:2">
       <c r="A358" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="B358" s="4" t="n">
+      <c r="B358" s="4">
         <v>15</v>
       </c>
     </row>
-    <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="359" spans="1:2">
       <c r="A359" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="B359" s="6" t="n">
+      <c r="B359" s="6">
         <v>7</v>
       </c>
     </row>
-    <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="360" spans="1:2">
       <c r="A360" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="B360" s="4" t="n">
+      <c r="B360" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="361" spans="1:2">
       <c r="A361" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="B361" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B361" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
       <c r="A362" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="B362" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B362" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
       <c r="A363" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="B363" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B363" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
       <c r="A364" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="B364" s="4" t="n">
+      <c r="B364" s="4">
         <v>12</v>
       </c>
     </row>
-    <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="365" spans="1:2">
       <c r="A365" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="B365" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B365" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
       <c r="A366" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="B366" s="4" t="n">
+      <c r="B366" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="367" spans="1:2">
       <c r="A367" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="B367" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B367" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
       <c r="A368" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="B368" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B368" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
       <c r="A369" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="B369" s="6" t="n">
+      <c r="B369" s="6">
         <v>9</v>
       </c>
     </row>
-    <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="370" spans="1:2">
       <c r="A370" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="B370" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B370" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
       <c r="A371" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="B371" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B371" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
       <c r="A372" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="B372" s="4" t="n">
+      <c r="B372" s="4">
         <v>71</v>
       </c>
     </row>
-    <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="373" spans="1:2">
       <c r="A373" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="B373" s="6" t="n">
+      <c r="B373" s="6">
         <v>49</v>
       </c>
     </row>
-    <row r="374" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="374" spans="1:2">
       <c r="A374" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="B374" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="375" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B374" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
       <c r="A375" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="B375" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="376" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B375" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
       <c r="A376" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="B376" s="1" t="n">
+      <c r="B376" s="1">
         <v>114</v>
       </c>
     </row>
-    <row r="377" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="377" spans="1:2">
       <c r="A377" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="B377" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="378" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B377" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
       <c r="A378" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="B378" s="1" t="n">
+      <c r="B378" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="379" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="379" spans="1:2">
       <c r="A379" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="B379" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="380" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B379" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
       <c r="A380" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="B380" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="381" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B380" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
       <c r="A381" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="B381" s="1" t="n">
+      <c r="B381" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="382" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="382" spans="1:2">
       <c r="A382" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="B382" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="383" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B382" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
       <c r="A383" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="B383" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="384" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B383" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
       <c r="A384" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="B384" s="1" t="n">
+      <c r="B384" s="1">
         <v>26</v>
       </c>
     </row>
-    <row r="385" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="385" spans="1:2">
       <c r="A385" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="B385" s="8" t="n">
+      <c r="B385" s="8">
         <v>36</v>
       </c>
     </row>
-    <row r="386" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="386" spans="1:2">
       <c r="A386" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="B386" s="1" t="n">
+      <c r="B386" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387" t="s">
+        <v>386</v>
+      </c>
+      <c r="B387" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="B388" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" ht="15.75">
+      <c r="A389" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="B389" s="1">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <tableParts>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>

--- a/Manga.Manhwua/Updated manhwua.xlsx
+++ b/Manga.Manhwua/Updated manhwua.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Manga\Manga.Manhwua\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D0B1439-C5D7-4921-B782-67C65E95E8B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A6AA48C-91D1-4FEB-856F-419EFCAEC881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -911,9 +911,6 @@
     <t>I Was the Final Boss</t>
   </si>
   <si>
-    <t>Tang Clan Legend</t>
-  </si>
-  <si>
     <t>The Demon-Slaying Madman—reborn as a demon</t>
   </si>
   <si>
@@ -1221,19 +1218,29 @@
   </si>
   <si>
     <t>The Tang Clan Chronicles</t>
+  </si>
+  <si>
+    <t>The Former Supreme</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1331,12 +1338,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1360,9 +1367,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3918,17 +3928,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:2">
-      <c r="A285" s="5" t="s">
-        <v>285</v>
+    <row r="285" spans="1:2" ht="15.75">
+      <c r="A285" s="11" t="s">
+        <v>387</v>
       </c>
       <c r="B285" s="6">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="286" spans="1:2">
       <c r="A286" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B286" s="4">
         <v>4</v>
@@ -3936,7 +3946,7 @@
     </row>
     <row r="287" spans="1:2">
       <c r="A287" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B287" s="6">
         <v>30</v>
@@ -3944,7 +3954,7 @@
     </row>
     <row r="288" spans="1:2">
       <c r="A288" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B288" s="4">
         <v>6</v>
@@ -3952,7 +3962,7 @@
     </row>
     <row r="289" spans="1:2">
       <c r="A289" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B289" s="6">
         <v>6</v>
@@ -3960,7 +3970,7 @@
     </row>
     <row r="290" spans="1:2">
       <c r="A290" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B290" s="4">
         <v>38</v>
@@ -3968,7 +3978,7 @@
     </row>
     <row r="291" spans="1:2">
       <c r="A291" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B291" s="6">
         <v>31</v>
@@ -3976,7 +3986,7 @@
     </row>
     <row r="292" spans="1:2">
       <c r="A292" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B292" s="4">
         <v>0</v>
@@ -3984,7 +3994,7 @@
     </row>
     <row r="293" spans="1:2">
       <c r="A293" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B293" s="6">
         <v>0</v>
@@ -3992,7 +4002,7 @@
     </row>
     <row r="294" spans="1:2">
       <c r="A294" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B294" s="4">
         <v>0</v>
@@ -4000,7 +4010,7 @@
     </row>
     <row r="295" spans="1:2">
       <c r="A295" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B295" s="6">
         <v>25</v>
@@ -4008,7 +4018,7 @@
     </row>
     <row r="296" spans="1:2">
       <c r="A296" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B296" s="4">
         <v>6</v>
@@ -4016,7 +4026,7 @@
     </row>
     <row r="297" spans="1:2">
       <c r="A297" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B297" s="6">
         <v>0</v>
@@ -4024,7 +4034,7 @@
     </row>
     <row r="298" spans="1:2">
       <c r="A298" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B298" s="4">
         <v>29</v>
@@ -4032,7 +4042,7 @@
     </row>
     <row r="299" spans="1:2">
       <c r="A299" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B299" s="6">
         <v>0</v>
@@ -4040,7 +4050,7 @@
     </row>
     <row r="300" spans="1:2">
       <c r="A300" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B300" s="4">
         <v>0</v>
@@ -4048,7 +4058,7 @@
     </row>
     <row r="301" spans="1:2">
       <c r="A301" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B301" s="6">
         <v>56</v>
@@ -4056,7 +4066,7 @@
     </row>
     <row r="302" spans="1:2">
       <c r="A302" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B302" s="4">
         <v>41</v>
@@ -4064,7 +4074,7 @@
     </row>
     <row r="303" spans="1:2">
       <c r="A303" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B303" s="6">
         <v>21</v>
@@ -4072,7 +4082,7 @@
     </row>
     <row r="304" spans="1:2">
       <c r="A304" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B304" s="4">
         <v>9</v>
@@ -4080,7 +4090,7 @@
     </row>
     <row r="305" spans="1:2">
       <c r="A305" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B305" s="6">
         <v>6</v>
@@ -4088,7 +4098,7 @@
     </row>
     <row r="306" spans="1:2">
       <c r="A306" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B306" s="4">
         <v>27</v>
@@ -4096,7 +4106,7 @@
     </row>
     <row r="307" spans="1:2">
       <c r="A307" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B307" s="6">
         <v>15</v>
@@ -4104,7 +4114,7 @@
     </row>
     <row r="308" spans="1:2">
       <c r="A308" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B308" s="4">
         <v>30</v>
@@ -4112,7 +4122,7 @@
     </row>
     <row r="309" spans="1:2">
       <c r="A309" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B309" s="6">
         <v>57</v>
@@ -4120,7 +4130,7 @@
     </row>
     <row r="310" spans="1:2">
       <c r="A310" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B310" s="4">
         <v>21</v>
@@ -4128,7 +4138,7 @@
     </row>
     <row r="311" spans="1:2">
       <c r="A311" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B311" s="6">
         <v>8</v>
@@ -4136,7 +4146,7 @@
     </row>
     <row r="312" spans="1:2">
       <c r="A312" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B312" s="4">
         <v>55</v>
@@ -4144,7 +4154,7 @@
     </row>
     <row r="313" spans="1:2">
       <c r="A313" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B313" s="6">
         <v>28</v>
@@ -4152,7 +4162,7 @@
     </row>
     <row r="314" spans="1:2">
       <c r="A314" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B314" s="4">
         <v>32</v>
@@ -4160,7 +4170,7 @@
     </row>
     <row r="315" spans="1:2">
       <c r="A315" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B315" s="6">
         <v>47</v>
@@ -4168,7 +4178,7 @@
     </row>
     <row r="316" spans="1:2">
       <c r="A316" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B316" s="4">
         <v>6</v>
@@ -4176,7 +4186,7 @@
     </row>
     <row r="317" spans="1:2">
       <c r="A317" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B317" s="6">
         <v>0</v>
@@ -4184,7 +4194,7 @@
     </row>
     <row r="318" spans="1:2">
       <c r="A318" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B318" s="4">
         <v>18</v>
@@ -4192,7 +4202,7 @@
     </row>
     <row r="319" spans="1:2">
       <c r="A319" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B319" s="6">
         <v>20</v>
@@ -4200,7 +4210,7 @@
     </row>
     <row r="320" spans="1:2">
       <c r="A320" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B320" s="4">
         <v>161</v>
@@ -4208,7 +4218,7 @@
     </row>
     <row r="321" spans="1:2">
       <c r="A321" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B321" s="6">
         <v>0</v>
@@ -4216,7 +4226,7 @@
     </row>
     <row r="322" spans="1:2">
       <c r="A322" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B322" s="4">
         <v>34</v>
@@ -4224,7 +4234,7 @@
     </row>
     <row r="323" spans="1:2">
       <c r="A323" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B323" s="6">
         <v>10</v>
@@ -4232,7 +4242,7 @@
     </row>
     <row r="324" spans="1:2">
       <c r="A324" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B324" s="4">
         <v>0</v>
@@ -4240,7 +4250,7 @@
     </row>
     <row r="325" spans="1:2">
       <c r="A325" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B325" s="6">
         <v>0</v>
@@ -4248,7 +4258,7 @@
     </row>
     <row r="326" spans="1:2">
       <c r="A326" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B326" s="4">
         <v>0</v>
@@ -4256,7 +4266,7 @@
     </row>
     <row r="327" spans="1:2">
       <c r="A327" s="5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B327" s="6">
         <v>0</v>
@@ -4264,7 +4274,7 @@
     </row>
     <row r="328" spans="1:2">
       <c r="A328" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B328" s="4">
         <v>0</v>
@@ -4272,7 +4282,7 @@
     </row>
     <row r="329" spans="1:2">
       <c r="A329" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B329" s="6">
         <v>25</v>
@@ -4280,7 +4290,7 @@
     </row>
     <row r="330" spans="1:2">
       <c r="A330" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B330" s="4">
         <v>0</v>
@@ -4288,7 +4298,7 @@
     </row>
     <row r="331" spans="1:2">
       <c r="A331" s="5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B331" s="6">
         <v>0</v>
@@ -4296,7 +4306,7 @@
     </row>
     <row r="332" spans="1:2">
       <c r="A332" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B332" s="4">
         <v>0</v>
@@ -4304,7 +4314,7 @@
     </row>
     <row r="333" spans="1:2">
       <c r="A333" s="5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B333" s="6">
         <v>29</v>
@@ -4312,7 +4322,7 @@
     </row>
     <row r="334" spans="1:2">
       <c r="A334" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B334" s="4">
         <v>38</v>
@@ -4320,7 +4330,7 @@
     </row>
     <row r="335" spans="1:2">
       <c r="A335" s="5" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B335" s="6">
         <v>0</v>
@@ -4328,7 +4338,7 @@
     </row>
     <row r="336" spans="1:2">
       <c r="A336" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B336" s="4">
         <v>0</v>
@@ -4336,7 +4346,7 @@
     </row>
     <row r="337" spans="1:2">
       <c r="A337" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B337" s="6">
         <v>27</v>
@@ -4344,7 +4354,7 @@
     </row>
     <row r="338" spans="1:2">
       <c r="A338" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B338" s="4">
         <v>17</v>
@@ -4352,7 +4362,7 @@
     </row>
     <row r="339" spans="1:2">
       <c r="A339" s="5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B339" s="6">
         <v>5</v>
@@ -4360,7 +4370,7 @@
     </row>
     <row r="340" spans="1:2">
       <c r="A340" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B340" s="4">
         <v>8</v>
@@ -4368,7 +4378,7 @@
     </row>
     <row r="341" spans="1:2">
       <c r="A341" s="5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B341" s="6">
         <v>0</v>
@@ -4376,7 +4386,7 @@
     </row>
     <row r="342" spans="1:2">
       <c r="A342" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B342" s="4">
         <v>0</v>
@@ -4384,7 +4394,7 @@
     </row>
     <row r="343" spans="1:2">
       <c r="A343" s="5" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B343" s="6">
         <v>0</v>
@@ -4392,7 +4402,7 @@
     </row>
     <row r="344" spans="1:2">
       <c r="A344" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B344" s="4">
         <v>12</v>
@@ -4400,7 +4410,7 @@
     </row>
     <row r="345" spans="1:2">
       <c r="A345" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B345" s="6">
         <v>0</v>
@@ -4408,7 +4418,7 @@
     </row>
     <row r="346" spans="1:2">
       <c r="A346" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B346" s="4">
         <v>0</v>
@@ -4416,7 +4426,7 @@
     </row>
     <row r="347" spans="1:2">
       <c r="A347" s="5" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B347" s="6">
         <v>40</v>
@@ -4424,7 +4434,7 @@
     </row>
     <row r="348" spans="1:2">
       <c r="A348" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B348" s="4">
         <v>44</v>
@@ -4432,7 +4442,7 @@
     </row>
     <row r="349" spans="1:2">
       <c r="A349" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B349" s="6">
         <v>0</v>
@@ -4440,7 +4450,7 @@
     </row>
     <row r="350" spans="1:2">
       <c r="A350" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B350" s="4">
         <v>7</v>
@@ -4448,7 +4458,7 @@
     </row>
     <row r="351" spans="1:2">
       <c r="A351" s="5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B351" s="6">
         <v>97</v>
@@ -4456,7 +4466,7 @@
     </row>
     <row r="352" spans="1:2">
       <c r="A352" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B352" s="4">
         <v>29</v>
@@ -4464,7 +4474,7 @@
     </row>
     <row r="353" spans="1:2">
       <c r="A353" s="5" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B353" s="6">
         <v>50</v>
@@ -4472,7 +4482,7 @@
     </row>
     <row r="354" spans="1:2">
       <c r="A354" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B354" s="4">
         <v>52</v>
@@ -4480,7 +4490,7 @@
     </row>
     <row r="355" spans="1:2">
       <c r="A355" s="5" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B355" s="6">
         <v>0</v>
@@ -4488,7 +4498,7 @@
     </row>
     <row r="356" spans="1:2">
       <c r="A356" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B356" s="4">
         <v>0</v>
@@ -4496,7 +4506,7 @@
     </row>
     <row r="357" spans="1:2">
       <c r="A357" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B357" s="6">
         <v>4</v>
@@ -4504,7 +4514,7 @@
     </row>
     <row r="358" spans="1:2">
       <c r="A358" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B358" s="4">
         <v>15</v>
@@ -4512,7 +4522,7 @@
     </row>
     <row r="359" spans="1:2">
       <c r="A359" s="5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B359" s="6">
         <v>7</v>
@@ -4520,7 +4530,7 @@
     </row>
     <row r="360" spans="1:2">
       <c r="A360" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B360" s="4">
         <v>5</v>
@@ -4528,7 +4538,7 @@
     </row>
     <row r="361" spans="1:2">
       <c r="A361" s="5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B361" s="6">
         <v>0</v>
@@ -4536,7 +4546,7 @@
     </row>
     <row r="362" spans="1:2">
       <c r="A362" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B362" s="4">
         <v>0</v>
@@ -4544,7 +4554,7 @@
     </row>
     <row r="363" spans="1:2">
       <c r="A363" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B363" s="6">
         <v>0</v>
@@ -4552,7 +4562,7 @@
     </row>
     <row r="364" spans="1:2">
       <c r="A364" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B364" s="4">
         <v>12</v>
@@ -4560,7 +4570,7 @@
     </row>
     <row r="365" spans="1:2">
       <c r="A365" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B365" s="6">
         <v>0</v>
@@ -4568,7 +4578,7 @@
     </row>
     <row r="366" spans="1:2">
       <c r="A366" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B366" s="4">
         <v>6</v>
@@ -4576,7 +4586,7 @@
     </row>
     <row r="367" spans="1:2">
       <c r="A367" s="5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B367" s="6">
         <v>0</v>
@@ -4584,7 +4594,7 @@
     </row>
     <row r="368" spans="1:2">
       <c r="A368" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B368" s="4">
         <v>0</v>
@@ -4592,7 +4602,7 @@
     </row>
     <row r="369" spans="1:2">
       <c r="A369" s="5" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B369" s="6">
         <v>9</v>
@@ -4600,7 +4610,7 @@
     </row>
     <row r="370" spans="1:2">
       <c r="A370" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B370" s="4">
         <v>0</v>
@@ -4608,7 +4618,7 @@
     </row>
     <row r="371" spans="1:2">
       <c r="A371" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B371" s="6">
         <v>0</v>
@@ -4616,7 +4626,7 @@
     </row>
     <row r="372" spans="1:2">
       <c r="A372" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B372" s="4">
         <v>71</v>
@@ -4624,7 +4634,7 @@
     </row>
     <row r="373" spans="1:2">
       <c r="A373" s="5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B373" s="6">
         <v>49</v>
@@ -4632,7 +4642,7 @@
     </row>
     <row r="374" spans="1:2">
       <c r="A374" s="7" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B374" s="1">
         <v>0</v>
@@ -4640,7 +4650,7 @@
     </row>
     <row r="375" spans="1:2">
       <c r="A375" s="7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B375" s="1">
         <v>0</v>
@@ -4648,7 +4658,7 @@
     </row>
     <row r="376" spans="1:2">
       <c r="A376" s="7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B376" s="1">
         <v>114</v>
@@ -4656,7 +4666,7 @@
     </row>
     <row r="377" spans="1:2">
       <c r="A377" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B377" s="1">
         <v>0</v>
@@ -4664,7 +4674,7 @@
     </row>
     <row r="378" spans="1:2">
       <c r="A378" s="7" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B378" s="1">
         <v>3</v>
@@ -4672,7 +4682,7 @@
     </row>
     <row r="379" spans="1:2">
       <c r="A379" s="7" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B379" s="1">
         <v>0</v>
@@ -4680,7 +4690,7 @@
     </row>
     <row r="380" spans="1:2">
       <c r="A380" s="7" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B380" s="1">
         <v>0</v>
@@ -4688,7 +4698,7 @@
     </row>
     <row r="381" spans="1:2">
       <c r="A381" s="7" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B381" s="1">
         <v>8</v>
@@ -4696,7 +4706,7 @@
     </row>
     <row r="382" spans="1:2">
       <c r="A382" s="7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B382" s="1">
         <v>0</v>
@@ -4704,7 +4714,7 @@
     </row>
     <row r="383" spans="1:2">
       <c r="A383" s="7" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B383" s="1">
         <v>0</v>
@@ -4712,7 +4722,7 @@
     </row>
     <row r="384" spans="1:2">
       <c r="A384" s="7" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B384" s="1">
         <v>26</v>
@@ -4720,7 +4730,7 @@
     </row>
     <row r="385" spans="1:2">
       <c r="A385" s="7" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B385" s="8">
         <v>36</v>
@@ -4728,7 +4738,7 @@
     </row>
     <row r="386" spans="1:2">
       <c r="A386" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B386" s="1">
         <v>6</v>
@@ -4736,7 +4746,7 @@
     </row>
     <row r="387" spans="1:2">
       <c r="A387" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B387" s="1">
         <v>0</v>
@@ -4744,18 +4754,18 @@
     </row>
     <row r="388" spans="1:2">
       <c r="A388" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B388" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="389" spans="1:2" ht="15.75">
-      <c r="A389" s="11" t="s">
+    <row r="389" spans="1:2">
+      <c r="A389" s="12" t="s">
         <v>388</v>
       </c>
       <c r="B389" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Manga.Manhwua/Updated manhwua.xlsx
+++ b/Manga.Manhwua/Updated manhwua.xlsx
@@ -1,21 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Manga\Manga.Manhwua\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A11652-F954-419D-B758-D2D2F7863FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -25,513 +20,513 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="393">
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Episodes</t>
-  </si>
-  <si>
-    <t>Kingdom</t>
-  </si>
-  <si>
-    <t>Vagabond</t>
-  </si>
-  <si>
-    <t>My Dragon System</t>
-  </si>
-  <si>
-    <t>The Knight King Who Returned With A God</t>
-  </si>
-  <si>
-    <t>The Player Hides His Past</t>
-  </si>
-  <si>
-    <t>Disastrous Necromancer</t>
-  </si>
-  <si>
-    <t>The Priest of Corruption</t>
-  </si>
-  <si>
-    <t>Dragon Emperor Martial God</t>
-  </si>
-  <si>
-    <t>Mookhyang - Dark Lady</t>
-  </si>
-  <si>
-    <t>Leveling Up By Hoarding</t>
-  </si>
-  <si>
-    <t>Master Of The Martial Arts Library</t>
-  </si>
-  <si>
-    <t>Absolute Necromancer</t>
-  </si>
-  <si>
-    <t>Tales Of A Shinning Sword</t>
-  </si>
-  <si>
-    <t>Kyushu Chronicles Of Immortals And Demons</t>
-  </si>
-  <si>
-    <t>Level 1 Player</t>
-  </si>
-  <si>
-    <t>Logging 10,000 Years into the Future</t>
-  </si>
-  <si>
-    <t>Swordmaster’S Youngest Son</t>
-  </si>
-  <si>
-    <t>World’S Greatest Senior Disciple</t>
-  </si>
-  <si>
-    <t>Dragon Master</t>
-  </si>
-  <si>
-    <t>The Return Of The Disaster-Class Hero</t>
-  </si>
-  <si>
-    <t>Solo Farming In The Tower</t>
-  </si>
-  <si>
-    <t>Chronicles Of The Demon Faction</t>
-  </si>
-  <si>
-    <t>Demonic Master Of Mount Kunlun</t>
-  </si>
-  <si>
-    <t>Necromancer's Evolutionary Traits</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="394">
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Episodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vagabond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Dragon System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Knight King Who Returned With A God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Player Hides His Past</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disastrous Necromancer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Priest of Corruption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragon Emperor Martial God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mookhyang - Dark Lady</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leveling Up By Hoarding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master Of The Martial Arts Library</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Absolute Necromancer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tales Of A Shinning Sword</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyushu Chronicles Of Immortals And Demons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level 1 Player</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logging 10,000 Years into the Future</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swordmaster’S Youngest Son</t>
+  </si>
+  <si>
+    <t xml:space="preserve">World’S Greatest Senior Disciple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragon Master</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Return Of The Disaster-Class Hero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo Farming In The Tower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chronicles Of The Demon Faction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demonic Master Of Mount Kunlun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Necromancer's Evolutionary Traits</t>
   </si>
   <si>
     <t xml:space="preserve">Samurai In Another World </t>
   </si>
   <si>
-    <t>Peerless Quest – The Cheat Skill Only I Can Use</t>
-  </si>
-  <si>
-    <t>Isekai De Haishin Katsudou Wo Shitara Tairyou No Yandere Shinja Wo Umidashite Shimatta Ken</t>
-  </si>
-  <si>
-    <t>Boundless Necromancer</t>
-  </si>
-  <si>
-    <t>Academy’S Genius Swordsman</t>
-  </si>
-  <si>
-    <t>Demon Evolution</t>
-  </si>
-  <si>
-    <t>The Iron-Blooded Necromancer Has Returned</t>
-  </si>
-  <si>
-    <t>Infinite Mage</t>
-  </si>
-  <si>
-    <t>Star Instructor  Master Baek</t>
-  </si>
-  <si>
-    <t>The Story Of Thorny Spear</t>
-  </si>
-  <si>
-    <t>Blade debt</t>
-  </si>
-  <si>
-    <t>Martial God Regressed To Level 2</t>
-  </si>
-  <si>
-    <t>What, You Dare Pretend In Front Of Me, The Strongest In The Immortal World?</t>
-  </si>
-  <si>
-    <t>Terminally-Ill Genius Dark Knight</t>
-  </si>
-  <si>
-    <t>Heavenly Inquisition Sword</t>
-  </si>
-  <si>
-    <t>Tsuki Ga Michibiku Isekai Douchuu</t>
-  </si>
-  <si>
-    <t>The Emperor’s Sword</t>
-  </si>
-  <si>
-    <t>The Constellations Are My Disciples</t>
-  </si>
-  <si>
-    <t>Revenge of the Iron-Blooded Sword Hound</t>
-  </si>
-  <si>
-    <t>Mr. Zombie</t>
-  </si>
-  <si>
-    <t>Master: This Villainous Disciple Is Not The Holy Child</t>
-  </si>
-  <si>
-    <t>Solo Max-Level Newbie</t>
-  </si>
-  <si>
-    <t>Murim Login</t>
-  </si>
-  <si>
-    <t>The Great Villain Who Threatened to Kill Himself</t>
-  </si>
-  <si>
-    <t>Weapon Maker</t>
-  </si>
-  <si>
-    <t>The Reincarnated Assassin is a Genius Swordsman</t>
-  </si>
-  <si>
-    <t>I was more overpowered than the hero, so I hid my power!</t>
-  </si>
-  <si>
-    <t>Million Times Attack Speed</t>
-  </si>
-  <si>
-    <t>I am the descendant of the Divine Dragon</t>
-  </si>
-  <si>
-    <t>Hero X Demon Queen</t>
-  </si>
-  <si>
-    <t>Records Of The Demonic Path’S Return</t>
-  </si>
-  <si>
-    <t>Five-Dimensional Zone</t>
-  </si>
-  <si>
-    <t>Legendary Youngest Son Of The Marquis House</t>
-  </si>
-  <si>
-    <t>I am fated villain</t>
-  </si>
-  <si>
-    <t>Return Of The Mount Hua Sect</t>
-  </si>
-  <si>
-    <t>Beyond Myriad Peoples</t>
-  </si>
-  <si>
-    <t>Nano Machine</t>
-  </si>
-  <si>
-    <t>Tensei Shitara Dai Nana Ouji Dattanode, Kimamani Majutsu O Kiwamemasu</t>
-  </si>
-  <si>
-    <t>Scoring the Sacred Body of the Ancients from the Get-go</t>
-  </si>
-  <si>
-    <t>Magic Emperor</t>
-  </si>
-  <si>
-    <t>Martial Peak</t>
-  </si>
-  <si>
-    <t>The Self-Disciplined Me Is Practically Invincible</t>
-  </si>
-  <si>
-    <t>Global Power: I Can Control All The Elements</t>
-  </si>
-  <si>
-    <t>Moon Slayer</t>
-  </si>
-  <si>
-    <t>Lightning Degree</t>
-  </si>
-  <si>
-    <t>The World's Best Sect Of Dependency</t>
-  </si>
-  <si>
-    <t>The Return Of Apocalypses Tyrant</t>
-  </si>
-  <si>
-    <t>What Do You Do When You Suddenly Become An Immortal?</t>
-  </si>
-  <si>
-    <t>Tales Of Demons And Gods</t>
-  </si>
-  <si>
-    <t>The Kingdoms Of Ruin</t>
-  </si>
-  <si>
-    <t>Necromancer Academy And The Genius Summoner</t>
-  </si>
-  <si>
-    <t>Yuan Zun</t>
-  </si>
-  <si>
-    <t>The Greatest Estate Designer</t>
-  </si>
-  <si>
-    <t>Conqueror of modern martial arts Kang Haejin</t>
-  </si>
-  <si>
-    <t>Records Of The Swordsman Scholar</t>
-  </si>
-  <si>
-    <t>The Scholar's Reincarnation</t>
-  </si>
-  <si>
-    <t>Tale of a Scribe Who Retires To The Countryside</t>
-  </si>
-  <si>
-    <t>Return Of The Bachelor</t>
-  </si>
-  <si>
-    <t>Reincarnation Of The Murim Clan's Former Ranker</t>
-  </si>
-  <si>
-    <t>Regressing with the King’s Power</t>
-  </si>
-  <si>
-    <t>The Last Cultivator</t>
-  </si>
-  <si>
-    <t>HEAVENLY MOON</t>
-  </si>
-  <si>
-    <t>Infinite Leveling: Murim</t>
-  </si>
-  <si>
-    <t>Volcanic Age</t>
-  </si>
-  <si>
-    <t>Chronicles Of A Returner</t>
-  </si>
-  <si>
-    <t>The Undefeatable Swordsman</t>
-  </si>
-  <si>
-    <t>Second Life of Dongfang Bubai</t>
-  </si>
-  <si>
-    <t>Job Change: I Became The Undead Monarch</t>
-  </si>
-  <si>
-    <t>Relife Player</t>
-  </si>
-  <si>
-    <t>My Lucky Encounter From The Game Turned Into Reality</t>
-  </si>
-  <si>
-    <t>I Killed an Academy Player</t>
-  </si>
-  <si>
-    <t>Bloodhound’s Regression Instinct</t>
-  </si>
-  <si>
-    <t>I Raised the Yandere Villain Empress</t>
-  </si>
-  <si>
-    <t>The Max-Level Player’s 100th Regression</t>
-  </si>
-  <si>
-    <t>The Heavenly Demon Can't Live A Normal Life</t>
-  </si>
-  <si>
-    <t>The Player That Can't Level Up</t>
-  </si>
-  <si>
-    <t>Reborn As The Enemy Prince</t>
-  </si>
-  <si>
-    <t>The Archmage's Restaurant</t>
-  </si>
-  <si>
-    <t>I Rely on My Invincibility to Deal Tons of Damage Passively!</t>
-  </si>
-  <si>
-    <t>Wild West Murim</t>
-  </si>
-  <si>
-    <t>Monster Pet Evolution</t>
-  </si>
-  <si>
-    <t>The Strongest Sect Of All Times</t>
-  </si>
-  <si>
-    <t>Youngest Scion Of The Mages</t>
-  </si>
-  <si>
-    <t>I Will Do Whatever I Want In Ten Thousand Years</t>
-  </si>
-  <si>
-    <t>Genkai Level 1 Kara No Nariagari: Saijaku Level No Ore Ga Isekai Saikyou Ni Naru Made</t>
-  </si>
-  <si>
-    <t>How to Live at the Max Level</t>
-  </si>
-  <si>
-    <t>The All-Knowing Cultivator</t>
-  </si>
-  <si>
-    <t>Kurasu ≪Mushoku≫ No Eiyuu-Tan ~Koushaku-Ka O Tsuihou Sareta Ga, Jitsu Wa Nagutta Dake De Sukiru O Kakutoku Dekiru To Wakari, Tairiku Ichi No Eiyuu Ni Nobori Tsumeru</t>
-  </si>
-  <si>
-    <t>Villager A Wants To Save The Villainess No Matter What!</t>
-  </si>
-  <si>
-    <t>Savage Hero</t>
-  </si>
-  <si>
-    <t>Genkai Koe No Tenpu wa, Tensei-sha ni Shika Atsukaenai Overlimit Skill Holders</t>
-  </si>
-  <si>
-    <t>Maken Tsukai No Moto Shounen Hei Wa, Moto Teki Kanbu No Onee-San To Issho Ni Ikitai</t>
-  </si>
-  <si>
-    <t>Mannen D-Rank No Chuunen Boukensha, Yotta Ikioi De Densetsu No Ken Wo Hikkonuku</t>
-  </si>
-  <si>
-    <t>Dungeon Sherpa: Meikyuu Michisaki Annainin</t>
-  </si>
-  <si>
-    <t>A Sword Master Childhood Friend Power Harassed Me Harshly, So I Broke Off Our Relationship And Made A Fresh Start At The Frontier As A Magic Swordsman</t>
-  </si>
-  <si>
-    <t>I Summoned The Devil To Grant Me A Wish, But I Married Her Instead Since She Was Adorable ~My New Devil Wife~</t>
-  </si>
-  <si>
-    <t>A Story About A Dragon And The Rising Of An Adventurer</t>
-  </si>
-  <si>
-    <t>After Being Called A Hero: The Unrivaled Man Starts A Family</t>
-  </si>
-  <si>
-    <t>A Warrior Exiled By The Hero And His Lover</t>
-  </si>
-  <si>
-    <t>Nimotsu Mochi No Nousuji Musou</t>
-  </si>
-  <si>
-    <t>The Strongest Dull Prince’s Secret Battle for the Throne</t>
-  </si>
-  <si>
-    <t>The Sword of Princess Gluttony</t>
-  </si>
-  <si>
-    <t>Wistoria's Wand And Sword</t>
-  </si>
-  <si>
-    <t>The Crafty Mage: Frontier Settling Made Easy</t>
-  </si>
-  <si>
-    <t>Delivery Man From Murim</t>
-  </si>
-  <si>
-    <t>Henkyou Gurashi No Maou, Tensei Shite Saikyou No Majutsushi Ni Naru</t>
-  </si>
-  <si>
-    <t>The Executed Sage Is Reincarnated As A Lich And Starts An All-Out War</t>
-  </si>
-  <si>
-    <t>Dungeon Ni Hisomu Yandere Na Kanojo Ni Ore Wa Nando Mo Korosareru</t>
-  </si>
-  <si>
-    <t>I Became A Big-Shot On The Heavenly Leaderboard</t>
-  </si>
-  <si>
-    <t>The Dark Magician Transmigrates After 66666 Years</t>
-  </si>
-  <si>
-    <t>Reaper Of The Drifting Moon</t>
-  </si>
-  <si>
-    <t>The Unbeatable Dungeon's Lazy Boss Monster</t>
-  </si>
-  <si>
-    <t>All My Abilities Are Forbidden Spells</t>
-  </si>
-  <si>
-    <t>How To Survive As A Dragon With Time-Limit</t>
-  </si>
-  <si>
-    <t>Myst, Might, Mayhem</t>
-  </si>
-  <si>
-    <t>Dark And Light Martial Emperor</t>
-  </si>
-  <si>
-    <t>The doomsday ruthless man: hoarding trillions of supplies at the beginning</t>
-  </si>
-  <si>
-    <t>Becoming the Swordmaster Rank Young Lord of the Sichuan Tang Family</t>
-  </si>
-  <si>
-    <t>This Account Is Ridiculous</t>
-  </si>
-  <si>
-    <t>The Mysterious World’s Greatest Martial Artist Little Prince</t>
-  </si>
-  <si>
-    <t>The Reborn Young Lord Is An Assassin</t>
-  </si>
-  <si>
-    <t>God-Slaying Copycat</t>
-  </si>
-  <si>
-    <t>The Great Mage Of The Hero’S Party Reincarnates</t>
-  </si>
-  <si>
-    <t>My Brother Is The Chosen One</t>
-  </si>
-  <si>
-    <t>The Max Level Hero Strikes Back</t>
-  </si>
-  <si>
-    <t>Overlord of Insects</t>
-  </si>
-  <si>
-    <t>Game Of Familia: Kazoku Senki</t>
-  </si>
-  <si>
-    <t>Grand General</t>
-  </si>
-  <si>
-    <t>The Legendary Spearman Returns</t>
-  </si>
-  <si>
-    <t>Ice lord</t>
-  </si>
-  <si>
-    <t>My Inventory is Abnormal</t>
-  </si>
-  <si>
-    <t>Escort Agency Of The Apocalypse</t>
-  </si>
-  <si>
-    <t>The Heavenly Demon Will Give You a Massage</t>
-  </si>
-  <si>
-    <t>The Twin Swords Of The Sima</t>
-  </si>
-  <si>
-    <t>Versatile Sword Cultivator</t>
-  </si>
-  <si>
-    <t>Asura</t>
-  </si>
-  <si>
-    <t>Magic Academy’s Genius Blinker</t>
-  </si>
-  <si>
-    <t>Worthless Profession: Dragon Tamer</t>
-  </si>
-  <si>
-    <t>Expelled Hero Is Too Strong</t>
-  </si>
-  <si>
-    <t>The Ten Thousand Clans Invasion: Guardian Of The Rear</t>
-  </si>
-  <si>
-    <t>My Disciple Became the Great Demon Empress?!</t>
-  </si>
-  <si>
-    <t>The Greatest In The World</t>
-  </si>
-  <si>
-    <t>Drawing: The Greatest Mangaka Becomes A Skilled “Martial Artist” In Another World</t>
+    <t xml:space="preserve">Peerless Quest – The Cheat Skill Only I Can Use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isekai De Haishin Katsudou Wo Shitara Tairyou No Yandere Shinja Wo Umidashite Shimatta Ken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boundless Necromancer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Academy’S Genius Swordsman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demon Evolution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Iron-Blooded Necromancer Has Returned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infinite Mage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Star Instructor  Master Baek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Story Of Thorny Spear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blade debt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martial God Regressed To Level 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What, You Dare Pretend In Front Of Me, The Strongest In The Immortal World?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminally-Ill Genius Dark Knight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heavenly Inquisition Sword</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tsuki Ga Michibiku Isekai Douchuu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Emperor’s Sword</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Constellations Are My Disciples</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenge of the Iron-Blooded Sword Hound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Zombie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master: This Villainous Disciple Is Not The Holy Child</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo Max-Level Newbie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murim Login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Great Villain Who Threatened to Kill Himself</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon Maker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Reincarnated Assassin is a Genius Swordsman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I was more overpowered than the hero, so I hid my power!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Million Times Attack Speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I am the descendant of the Divine Dragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hero X Demon Queen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Records Of The Demonic Path’S Return</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Five-Dimensional Zone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legendary Youngest Son Of The Marquis House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I am fated villain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return Of The Mount Hua Sect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beyond Myriad Peoples</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nano Machine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tensei Shitara Dai Nana Ouji Dattanode, Kimamani Majutsu O Kiwamemasu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scoring the Sacred Body of the Ancients from the Get-go</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magic Emperor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martial Peak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Self-Disciplined Me Is Practically Invincible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Power: I Can Control All The Elements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Slayer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightning Degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The World's Best Sect Of Dependency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Return Of Apocalypses Tyrant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What Do You Do When You Suddenly Become An Immortal?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tales Of Demons And Gods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Kingdoms Of Ruin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Necromancer Academy And The Genius Summoner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yuan Zun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Greatest Estate Designer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conqueror of modern martial arts Kang Haejin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Records Of The Swordsman Scholar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Scholar's Reincarnation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tale of a Scribe Who Retires To The Countryside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return Of The Bachelor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnation Of The Murim Clan's Former Ranker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regressing with the King’s Power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Last Cultivator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEAVENLY MOON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infinite Leveling: Murim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volcanic Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chronicles Of A Returner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Undefeatable Swordsman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Second Life of Dongfang Bubai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job Change: I Became The Undead Monarch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relife Player</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Lucky Encounter From The Game Turned Into Reality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Killed an Academy Player</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bloodhound’s Regression Instinct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Raised the Yandere Villain Empress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Max-Level Player’s 100th Regression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Heavenly Demon Can't Live A Normal Life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Player That Can't Level Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reborn As The Enemy Prince</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Archmage's Restaurant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Rely on My Invincibility to Deal Tons of Damage Passively!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wild West Murim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster Pet Evolution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Strongest Sect Of All Times</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Youngest Scion Of The Mages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Will Do Whatever I Want In Ten Thousand Years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genkai Level 1 Kara No Nariagari: Saijaku Level No Ore Ga Isekai Saikyou Ni Naru Made</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How to Live at the Max Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The All-Knowing Cultivator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurasu ≪Mushoku≫ No Eiyuu-Tan ~Koushaku-Ka O Tsuihou Sareta Ga, Jitsu Wa Nagutta Dake De Sukiru O Kakutoku Dekiru To Wakari, Tairiku Ichi No Eiyuu Ni Nobori Tsumeru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villager A Wants To Save The Villainess No Matter What!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Savage Hero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genkai Koe No Tenpu wa, Tensei-sha ni Shika Atsukaenai Overlimit Skill Holders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maken Tsukai No Moto Shounen Hei Wa, Moto Teki Kanbu No Onee-San To Issho Ni Ikitai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mannen D-Rank No Chuunen Boukensha, Yotta Ikioi De Densetsu No Ken Wo Hikkonuku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dungeon Sherpa: Meikyuu Michisaki Annainin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Sword Master Childhood Friend Power Harassed Me Harshly, So I Broke Off Our Relationship And Made A Fresh Start At The Frontier As A Magic Swordsman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Summoned The Devil To Grant Me A Wish, But I Married Her Instead Since She Was Adorable ~My New Devil Wife~</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Story About A Dragon And The Rising Of An Adventurer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After Being Called A Hero: The Unrivaled Man Starts A Family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Warrior Exiled By The Hero And His Lover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimotsu Mochi No Nousuji Musou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Strongest Dull Prince’s Secret Battle for the Throne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Sword of Princess Gluttony</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wistoria's Wand And Sword</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Crafty Mage: Frontier Settling Made Easy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delivery Man From Murim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Henkyou Gurashi No Maou, Tensei Shite Saikyou No Majutsushi Ni Naru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Executed Sage Is Reincarnated As A Lich And Starts An All-Out War</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dungeon Ni Hisomu Yandere Na Kanojo Ni Ore Wa Nando Mo Korosareru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Became A Big-Shot On The Heavenly Leaderboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Dark Magician Transmigrates After 66666 Years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reaper Of The Drifting Moon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Unbeatable Dungeon's Lazy Boss Monster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All My Abilities Are Forbidden Spells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How To Survive As A Dragon With Time-Limit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myst, Might, Mayhem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark And Light Martial Emperor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The doomsday ruthless man: hoarding trillions of supplies at the beginning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Becoming the Swordmaster Rank Young Lord of the Sichuan Tang Family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This Account Is Ridiculous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Mysterious World’s Greatest Martial Artist Little Prince</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Reborn Young Lord Is An Assassin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">God-Slaying Copycat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Great Mage Of The Hero’S Party Reincarnates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Brother Is The Chosen One</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Max Level Hero Strikes Back</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overlord of Insects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Game Of Familia: Kazoku Senki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grand General</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Legendary Spearman Returns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ice lord</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Inventory is Abnormal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escort Agency Of The Apocalypse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Heavenly Demon Will Give You a Massage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Twin Swords Of The Sima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Versatile Sword Cultivator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magic Academy’s Genius Blinker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worthless Profession: Dragon Tamer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expelled Hero Is Too Strong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Ten Thousand Clans Invasion: Guardian Of The Rear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Disciple Became the Great Demon Empress?!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Greatest In The World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drawing: The Greatest Mangaka Becomes A Skilled “Martial Artist” In Another World</t>
   </si>
   <si>
     <r>
@@ -552,7 +547,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t>～</t>
+      <t xml:space="preserve">～</t>
     </r>
     <r>
       <rPr>
@@ -562,684 +557,690 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t>I Returned To The Past To Rewrite It As The World's Strongest</t>
+      <t xml:space="preserve">I Returned To The Past To Rewrite It As The World's Strongest</t>
     </r>
   </si>
   <si>
-    <t>Hundreds of Invincible Strikes</t>
-  </si>
-  <si>
-    <t>arctic cold war</t>
-  </si>
-  <si>
-    <t>Apocalyptic Super Farm</t>
-  </si>
-  <si>
-    <t>Sword Sheath's Child</t>
-  </si>
-  <si>
-    <t>Reincarnator</t>
-  </si>
-  <si>
-    <t>Hunter Academy’S Strongest Battle God</t>
-  </si>
-  <si>
-    <t>Childhood Friend of the Zenith</t>
-  </si>
-  <si>
-    <t>Absolute Regression</t>
-  </si>
-  <si>
-    <t>Warrior Grandpa And Supreme Granddaughter</t>
-  </si>
-  <si>
-    <t>I Scared the Divine Lord as I Handed over the Ancient Immortal Pill</t>
-  </si>
-  <si>
-    <t>I Become a Legendary Arch Mage by Reading a Book</t>
-  </si>
-  <si>
-    <t>Hiding a logistics center in the apocalypse</t>
-  </si>
-  <si>
-    <t>The Hated Black Mage Returns</t>
-  </si>
-  <si>
-    <t>The Masters Are Subscribing To Me</t>
-  </si>
-  <si>
-    <t>A Ranker's Guide To The Good Life</t>
-  </si>
-  <si>
-    <t>Black Serpent</t>
-  </si>
-  <si>
-    <t>Conquering the Academy with Just a Sashimi Knife</t>
-  </si>
-  <si>
-    <t>The Magic Genius Of The Marquis House</t>
-  </si>
-  <si>
-    <t>The Reversal Of My Life As A Side Character</t>
-  </si>
-  <si>
-    <t>Absolute Dominion</t>
-  </si>
-  <si>
-    <t>Fatal Reset</t>
-  </si>
-  <si>
-    <t>The Necromancer Family’s Young Heir</t>
-  </si>
-  <si>
-    <t>Starting As A Master Of Female Disciples' Leisure Skills</t>
-  </si>
-  <si>
-    <t>Song Baek</t>
-  </si>
-  <si>
-    <t>Surviving as a Genius on Borrowed Time</t>
-  </si>
-  <si>
-    <t>The Regressed Mercenary’s Machinations</t>
-  </si>
-  <si>
-    <t>Traveling Through Time And Space To Become An Unlucky Npc: I Have A Wife To Protect Me</t>
-  </si>
-  <si>
-    <t>Cultivation: The Heaven's Fated Useless Genius</t>
-  </si>
-  <si>
-    <t>The Edgeless Sword From The Village</t>
-  </si>
-  <si>
-    <t>Levelling Up In An Exclusive Dungeon</t>
-  </si>
-  <si>
-    <t>Reincarnated As A Genius Prodigy Of A Prestigious Family</t>
-  </si>
-  <si>
-    <t>From Goblin To Goblin God</t>
-  </si>
-  <si>
-    <t>Margrave’S Bastard Son Was The Emperor</t>
-  </si>
-  <si>
-    <t>The Second Eunuch Regains His Manhood</t>
-  </si>
-  <si>
-    <t>Return Of The Runebound Professor</t>
-  </si>
-  <si>
-    <t>Regressing as the Reincarnated Bastard of the Sword Clan</t>
-  </si>
-  <si>
-    <t>I, The Demon Lord, Am Being Targeted By My Female Disciples!</t>
-  </si>
-  <si>
-    <t>Fated to Be Loved by Villains</t>
-  </si>
-  <si>
-    <t>The Chaebeol’s Youngest Son</t>
-  </si>
-  <si>
-    <t>Heavenly Demon Wants To Be A Chef</t>
-  </si>
-  <si>
-    <t>Entomologist In Sichuan Tang Clan</t>
-  </si>
-  <si>
-    <t>Last Word of the World</t>
-  </si>
-  <si>
-    <t>Cosmic Heavenly Demon 3077</t>
-  </si>
-  <si>
-    <t>Solo Resurrection</t>
-  </si>
-  <si>
-    <t>Dao of the Bizarre Immortal</t>
-  </si>
-  <si>
-    <t>Tenkaichi: Nihon Saikyou Bugeisha Ketteisen</t>
-  </si>
-  <si>
-    <t>Reincarnation Of The Heavenly Demon</t>
-  </si>
-  <si>
-    <t>Black Corporation: Joseon</t>
-  </si>
-  <si>
-    <t>Perhaps Invincible</t>
-  </si>
-  <si>
-    <t>The mad gate</t>
-  </si>
-  <si>
-    <t>Surviving the Apocalypse</t>
-  </si>
-  <si>
-    <t>Genius Prismatic Mage</t>
-  </si>
-  <si>
-    <t>Becoming a God, Starting as water monkey</t>
-  </si>
-  <si>
-    <t>I Became the Successor of the Martial God</t>
-  </si>
-  <si>
-    <t>Regression of the Yong Clan Heir</t>
-  </si>
-  <si>
-    <t>Chronicles of the Reincarnated Demon God</t>
-  </si>
-  <si>
-    <t>Revenge Of the Bloom Flower</t>
-  </si>
-  <si>
-    <t>The Heavenly Demon Wants a Quiet Life</t>
-  </si>
-  <si>
-    <t>Monster General Recorded Legacy</t>
-  </si>
-  <si>
-    <t>Using My Cooking Skills in a Murim World</t>
-  </si>
-  <si>
-    <t>I’m a Martial Art Villainess, but I’m the Strongest!</t>
-  </si>
-  <si>
-    <t>Metcha Shoukan Sareta Ken</t>
-  </si>
-  <si>
-    <t>Mount Hua Sect's Genius Phantom Swordsman</t>
-  </si>
-  <si>
-    <t>I'm going to destroy this country</t>
-  </si>
-  <si>
-    <t>The New Beggars' Sect</t>
-  </si>
-  <si>
-    <t>Overgeared</t>
-  </si>
-  <si>
-    <t>Regressed life of the Sword Clan’s Ignoble Reincarnator</t>
-  </si>
-  <si>
-    <t>Black Fox: Sword Master Of Mount Kunlun</t>
-  </si>
-  <si>
-    <t>God-level Assassin, I’m the Shadow</t>
-  </si>
-  <si>
-    <t>War Of The Corpses</t>
-  </si>
-  <si>
-    <t>The Illegitimate Who Devours Weapons</t>
-  </si>
-  <si>
-    <t>The Great Sage of the Namgung Clan</t>
-  </si>
-  <si>
-    <t>Limitless Ascension: Strength Amid Adversity</t>
-  </si>
-  <si>
-    <t>Apocalypse: Cockroaches Gives Me Buff</t>
-  </si>
-  <si>
-    <t>The Legendary Hero is an Academy Honors Student</t>
-  </si>
-  <si>
-    <t>Like a Fiery Flame</t>
-  </si>
-  <si>
-    <t>The Magic Tower's Problem Child</t>
-  </si>
-  <si>
-    <t>I Became the Husband of the Cult Leader of the Demonic Sect</t>
-  </si>
-  <si>
-    <t>The Apocalypse is Here</t>
-  </si>
-  <si>
-    <t>If I Don’t Die Soon, I Will Rule The Demon Realm</t>
-  </si>
-  <si>
-    <t>I Will Raise This Family to Greatness</t>
-  </si>
-  <si>
-    <t>The Villain Wants to Live</t>
-  </si>
-  <si>
-    <t>Genius Archer’s Livestreaming</t>
-  </si>
-  <si>
-    <t>After Ten Millennia in Hell</t>
-  </si>
-  <si>
-    <t>Heavenly Grand Archive's Young Master</t>
-  </si>
-  <si>
-    <t>Space Cheon-ma 3077</t>
-  </si>
-  <si>
-    <t>Iljin Romance</t>
-  </si>
-  <si>
-    <t>Shut Up, Evil Dragon! I Don't Want to Raise a Child With You Anymore</t>
-  </si>
-  <si>
-    <t>On the Way to Meet Mom</t>
-  </si>
-  <si>
-    <t>Ultimate Shut-in</t>
-  </si>
-  <si>
-    <t>The beginning after the end</t>
-  </si>
-  <si>
-    <t>Reborn in a Cyber Cultivation World, I Fight My Way to the Top</t>
-  </si>
-  <si>
-    <t>Level 999 Goblin</t>
-  </si>
-  <si>
-    <t>Dominating the Wasteland: I Control an Immortal Sect in the Apocalypse</t>
-  </si>
-  <si>
-    <t>Starting As The God Of Wealth, Taming Billions Of Divine Pets!</t>
-  </si>
-  <si>
-    <t>Martial Evolution: Start by Awakening the King of Monsters</t>
-  </si>
-  <si>
-    <t>The Girl from Random Chatting</t>
-  </si>
-  <si>
-    <t>Return of the Legend</t>
-  </si>
-  <si>
-    <t>Elven Queen</t>
-  </si>
-  <si>
-    <t>Emperor of Solo Play</t>
-  </si>
-  <si>
-    <t>The Fox-Eyed Villain of the Demon Academy</t>
-  </si>
-  <si>
-    <t>The Awakening Contract</t>
-  </si>
-  <si>
-    <t>The Sword God From a Fallen World</t>
-  </si>
-  <si>
-    <t>I Awakened to the Ex Skill "Fixed Damage" and Became Invincible</t>
-  </si>
-  <si>
-    <t>Warrior of the Mind Sword</t>
-  </si>
-  <si>
-    <t>Ninja Reincarnation: Fuuma Kotarou’s Quest to Reclaim His Humanity</t>
-  </si>
-  <si>
-    <t>Empress Maria</t>
-  </si>
-  <si>
-    <t>Reincarnation of the Fist King</t>
-  </si>
-  <si>
-    <t>There Are No Bad Warriors in the World</t>
-  </si>
-  <si>
-    <t>Return From The Depth</t>
-  </si>
-  <si>
-    <t>Return of the Apocalypse-Class Death Knight</t>
-  </si>
-  <si>
-    <t>Oversummoned, Overpowered, and Over It!</t>
-  </si>
-  <si>
-    <t>A Rogue Guard in a Medieval Fantasy</t>
-  </si>
-  <si>
-    <t>Chronicles of the Lazy Sovereign</t>
-  </si>
-  <si>
-    <t>I Was the Final Boss</t>
-  </si>
-  <si>
-    <t>The Tang Clan Chronicles</t>
-  </si>
-  <si>
-    <t>The Demon-Slaying Madman—reborn as a demon</t>
-  </si>
-  <si>
-    <t>Urek Mazino</t>
-  </si>
-  <si>
-    <t>Demonic Sect Frontline: Thirteen Flying Dragons</t>
-  </si>
-  <si>
-    <t>Goddess of Abundance and the Genius Rogue Apostle</t>
-  </si>
-  <si>
-    <t>New Goguryeo Chronicles</t>
-  </si>
-  <si>
-    <t>Devil Summoner, I am the Abyss Lord</t>
-  </si>
-  <si>
-    <t>Legend of Dangun</t>
-  </si>
-  <si>
-    <t>The Tale of the Skeleton Messenger</t>
-  </si>
-  <si>
-    <t>The Great Heavenly Demon Sovereign</t>
-  </si>
-  <si>
-    <t>A Regressor's Tale of Cultivation</t>
-  </si>
-  <si>
-    <t>Jade of the Eight Gates</t>
-  </si>
-  <si>
-    <t>Disciple of the Three Kings</t>
-  </si>
-  <si>
-    <t>After the School Belle Dumped Me, I Became a Martial Arts God</t>
-  </si>
-  <si>
-    <t>Dead Mansion</t>
-  </si>
-  <si>
-    <t>Return of the King of Hell</t>
-  </si>
-  <si>
-    <t>Plaything</t>
-  </si>
-  <si>
-    <t>The Regressor Protects Only Me</t>
-  </si>
-  <si>
-    <t>Full-Time Awakening</t>
-  </si>
-  <si>
-    <t>Rebirth of the Divine Demon</t>
-  </si>
-  <si>
-    <t>Return of the First Patriarch: The Strongest Reincarnates into His Descendant 1000 Years Later</t>
-  </si>
-  <si>
-    <t>Lv. 99 Princess of Black Flame</t>
-  </si>
-  <si>
-    <t>Battle of the Martial Masters</t>
-  </si>
-  <si>
-    <t>The Yellow-haired Villain in Female Main Character's Novel wants Happiness</t>
-  </si>
-  <si>
-    <t>From Six to Sovereignty: The Girl Who Ruled</t>
-  </si>
-  <si>
-    <t>Eat and Go</t>
-  </si>
-  <si>
-    <t>I Shall Seal the Heavens</t>
-  </si>
-  <si>
-    <t>The Executed Sage Who Was Reincarnated as a Lich and Started an All-Out War</t>
-  </si>
-  <si>
-    <t>Demon Instructor's Return</t>
-  </si>
-  <si>
-    <t>The Archduke's Bride Is a Hell Warrior</t>
-  </si>
-  <si>
-    <t>Solo Leveling: Ragnarok</t>
-  </si>
-  <si>
-    <t>I Became a Patron of Villains</t>
-  </si>
-  <si>
-    <t>Black Crow</t>
-  </si>
-  <si>
-    <t>The Marquis Is the Marital Archduke</t>
-  </si>
-  <si>
-    <t>Dukedom's Legendary Prodigy</t>
-  </si>
-  <si>
-    <t>Reincarnated as the Crazed Heir</t>
-  </si>
-  <si>
-    <t>Lord of the Apocalypse</t>
-  </si>
-  <si>
-    <t>Don't Tell Me You Think Cultivating Immortality Is Difficult?</t>
-  </si>
-  <si>
-    <t>Immortal Fairy, Please Listen to My Explanation</t>
-  </si>
-  <si>
-    <t>Maplestory: The Last Adventurer</t>
-  </si>
-  <si>
-    <t>The Steel Emperor</t>
-  </si>
-  <si>
-    <t>The Luoyang Branch of the Heavenly Demon Cult</t>
-  </si>
-  <si>
-    <t>Spirit Hunter</t>
-  </si>
-  <si>
-    <t>Player of the Fallen Family</t>
-  </si>
-  <si>
-    <t>Unrivaled Spear Ghost</t>
-  </si>
-  <si>
-    <t>Reincarnation of the Martial God</t>
-  </si>
-  <si>
-    <t>After Rebirth, I Used Mirror Reversal For Vengeance</t>
-  </si>
-  <si>
-    <t>Death Attribute Magician</t>
-  </si>
-  <si>
-    <t>The Great Emperor Shinmadae</t>
-  </si>
-  <si>
-    <t>Revenger: Apocalypse of Vengeance</t>
-  </si>
-  <si>
-    <t>Hiding Out in an Apocalypse</t>
-  </si>
-  <si>
-    <t>Bad Born Blood</t>
-  </si>
-  <si>
-    <t>KaguRai: Kagura to Raito</t>
-  </si>
-  <si>
-    <t>Reincarnated as the Lazy and Villainous Noble, I Broke the Scenario and Became the Most Formidable With Extraordinary Magic</t>
-  </si>
-  <si>
-    <t>Star Armor꞉ I’ll Slaughter Through the Chaos with Star Soul Generals</t>
-  </si>
-  <si>
-    <t>The Demon King Overrun by Heroes</t>
-  </si>
-  <si>
-    <t>The Monkey King’s Journey to the Murim</t>
-  </si>
-  <si>
-    <t>The Sage who returned from another world wants to live quietly</t>
-  </si>
-  <si>
-    <t>Returned from Another World, Earth Turned Out to Be Quite the Fantasy Too. Also, Losing Heroines, Stop Looking This Way</t>
-  </si>
-  <si>
-    <t>Embodiment of the Assassin in the Murim World</t>
-  </si>
-  <si>
-    <t>Märchen - The Embodiment of Tales</t>
-  </si>
-  <si>
-    <t>Sichuan’s Supreme King</t>
-  </si>
-  <si>
-    <t>The Cold-Blooded Warrior</t>
-  </si>
-  <si>
-    <t>Everyone Loves Her</t>
-  </si>
-  <si>
-    <t>Paper Tiger</t>
-  </si>
-  <si>
-    <t>The Sword-Eating Swordmaster</t>
-  </si>
-  <si>
-    <t>The World's Best Kunlun Tavern</t>
-  </si>
-  <si>
-    <t>Defense Breaker</t>
-  </si>
-  <si>
-    <t>Worlds Best Assassin</t>
-  </si>
-  <si>
-    <t>The World's Best Martial Arts Instructor</t>
-  </si>
-  <si>
-    <t>How a Realist Hero Rebuilt the Kingdom</t>
-  </si>
-  <si>
-    <t>Sleepy Princess in the Demon Castle</t>
-  </si>
-  <si>
-    <t>To Hell With The Status Window</t>
-  </si>
-  <si>
-    <t>Becoming a Cheat-Level Skill Thief</t>
-  </si>
-  <si>
-    <t>Sichuan's Supreme King</t>
-  </si>
-  <si>
-    <t>Reborn After the Eight Empresses Betrayed Me, Now I’ll Make Them Regret It</t>
-  </si>
-  <si>
-    <t>Rebirth of the Demon Lord: the Slave who Conquered Fate</t>
-  </si>
-  <si>
-    <t>The Strongest Wizard Becomes a Countryside Guard After Taking an Arrow to the Knee</t>
-  </si>
-  <si>
-    <t>The Secret Martial Artist of Demonic Blood</t>
-  </si>
-  <si>
-    <t>The Strongest Hero Who Longs For Revenge Will Peerlessly Annihilate With The Power Of Darkness</t>
-  </si>
-  <si>
-    <t>I Became the Scoundrel of the Cheon Family</t>
-  </si>
-  <si>
-    <t>Supreme Demon of Hyungsan</t>
-  </si>
-  <si>
-    <t>Orc Hero Story - Discovery Chronicles</t>
-  </si>
-  <si>
-    <t>Boukun Meika no Hangyakusha -Aster</t>
-  </si>
-  <si>
-    <t>Jakdu</t>
-  </si>
-  <si>
-    <t>Secretly Cultivating by the Demon Cult Leader's Side</t>
-  </si>
-  <si>
-    <t>The Old Prisoner Lives in Solitude</t>
-  </si>
-  <si>
-    <t>Revenge of Young Master Peng</t>
-  </si>
-  <si>
-    <t>Murim’s Dept King</t>
-  </si>
-  <si>
-    <t>My Girlfriend's Friend</t>
-  </si>
-  <si>
-    <t>Teto X Egen</t>
-  </si>
-  <si>
-    <t>Gokusotsu Kraken</t>
-  </si>
-  <si>
-    <t>The Masters of Heaven and Earth</t>
-  </si>
-  <si>
-    <t>Red Storm</t>
-  </si>
-  <si>
-    <t>A Dragon Lives in Kunlun</t>
-  </si>
-  <si>
-    <t>Friend of the Demon King</t>
-  </si>
-  <si>
-    <t>High Martial Arts: Sweeping Through Three Thousand Emperors with One Hand!</t>
-  </si>
-  <si>
-    <t>The Genius Martial Artist Who Remembers Everything</t>
-  </si>
-  <si>
-    <t>The Shepherd Wizard</t>
-  </si>
-  <si>
-    <t>Sovereign of a Hundred Blades: Heir to the Strongest Style</t>
-  </si>
-  <si>
-    <t>Shadow Slave</t>
-  </si>
-  <si>
-    <t>The Tale of Cultivation and Demon Extermination</t>
-  </si>
-  <si>
-    <t>The Former Supreme</t>
-  </si>
-  <si>
-    <t>What a Bountiful Harvest, Demon Lord!</t>
-  </si>
-  <si>
-    <t>sa</t>
-  </si>
-  <si>
-    <t>The Sword Emperor’s Rise of Namgung</t>
-  </si>
-  <si>
-    <t>I Kidnapped the Youngest Daughter of the Sichuan Tang Clan</t>
-  </si>
-  <si>
-    <t>War of Extinction</t>
+    <t xml:space="preserve">Hundreds of Invincible Strikes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">arctic cold war</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apocalyptic Super Farm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sword Sheath's Child</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunter Academy’S Strongest Battle God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Childhood Friend of the Zenith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Absolute Regression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warrior Grandpa And Supreme Granddaughter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Scared the Divine Lord as I Handed over the Ancient Immortal Pill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Become a Legendary Arch Mage by Reading a Book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hiding a logistics center in the apocalypse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Hated Black Mage Returns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Masters Are Subscribing To Me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Ranker's Guide To The Good Life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Serpent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conquering the Academy with Just a Sashimi Knife</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Magic Genius Of The Marquis House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Reversal Of My Life As A Side Character</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Absolute Dominion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fatal Reset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Necromancer Family’s Young Heir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starting As A Master Of Female Disciples' Leisure Skills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Song Baek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surviving as a Genius on Borrowed Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Regressed Mercenary’s Machinations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traveling Through Time And Space To Become An Unlucky Npc: I Have A Wife To Protect Me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cultivation: The Heaven's Fated Useless Genius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Edgeless Sword From The Village</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Levelling Up In An Exclusive Dungeon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnated As A Genius Prodigy Of A Prestigious Family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From Goblin To Goblin God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margrave’S Bastard Son Was The Emperor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Second Eunuch Regains His Manhood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return Of The Runebound Professor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regressing as the Reincarnated Bastard of the Sword Clan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I, The Demon Lord, Am Being Targeted By My Female Disciples!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fated to Be Loved by Villains</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Chaebeol’s Youngest Son</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heavenly Demon Wants To Be A Chef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entomologist In Sichuan Tang Clan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last Word of the World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cosmic Heavenly Demon 3077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo Resurrection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dao of the Bizarre Immortal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tenkaichi: Nihon Saikyou Bugeisha Ketteisen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnation Of The Heavenly Demon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Corporation: Joseon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perhaps Invincible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The mad gate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surviving the Apocalypse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genius Prismatic Mage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Becoming a God, Starting as water monkey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Became the Successor of the Martial God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regression of the Yong Clan Heir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chronicles of the Reincarnated Demon God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenge Of the Bloom Flower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Heavenly Demon Wants a Quiet Life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster General Recorded Legacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Using My Cooking Skills in a Murim World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I’m a Martial Art Villainess, but I’m the Strongest!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metcha Shoukan Sareta Ken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mount Hua Sect's Genius Phantom Swordsman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I'm going to destroy this country</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The New Beggars' Sect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overgeared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regressed life of the Sword Clan’s Ignoble Reincarnator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Fox: Sword Master Of Mount Kunlun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">God-level Assassin, I’m the Shadow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">War Of The Corpses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Illegitimate Who Devours Weapons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Great Sage of the Namgung Clan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limitless Ascension: Strength Amid Adversity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apocalypse: Cockroaches Gives Me Buff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Legendary Hero is an Academy Honors Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Like a Fiery Flame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Magic Tower's Problem Child</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Became the Husband of the Cult Leader of the Demonic Sect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Apocalypse is Here</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If I Don’t Die Soon, I Will Rule The Demon Realm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Will Raise This Family to Greatness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Villain Wants to Live</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genius Archer’s Livestreaming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After Ten Millennia in Hell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heavenly Grand Archive's Young Master</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Space Cheon-ma 3077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iljin Romance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shut Up, Evil Dragon! I Don't Want to Raise a Child With You Anymore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On the Way to Meet Mom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultimate Shut-in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The beginning after the end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reborn in a Cyber Cultivation World, I Fight My Way to the Top</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level 999 Goblin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominating the Wasteland: I Control an Immortal Sect in the Apocalypse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starting As The God Of Wealth, Taming Billions Of Divine Pets!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martial Evolution: Start by Awakening the King of Monsters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Girl from Random Chatting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return of the Legend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elven Queen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emperor of Solo Play</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Fox-Eyed Villain of the Demon Academy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Awakening Contract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Sword God From a Fallen World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Awakened to the Ex Skill "Fixed Damage" and Became Invincible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warrior of the Mind Sword</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ninja Reincarnation: Fuuma Kotarou’s Quest to Reclaim His Humanity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empress Maria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnation of the Fist King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There Are No Bad Warriors in the World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return From The Depth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return of the Apocalypse-Class Death Knight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oversummoned, Overpowered, and Over It!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Rogue Guard in a Medieval Fantasy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chronicles of the Lazy Sovereign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Was the Final Boss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Tang Clan Chronicles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Demon-Slaying Madman—reborn as a demon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urek Mazino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demonic Sect Frontline: Thirteen Flying Dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goddess of Abundance and the Genius Rogue Apostle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Goguryeo Chronicles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devil Summoner, I am the Abyss Lord</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legend of Dangun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Tale of the Skeleton Messenger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Great Heavenly Demon Sovereign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Regressor's Tale of Cultivation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jade of the Eight Gates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disciple of the Three Kings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After the School Belle Dumped Me, I Became a Martial Arts God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dead Mansion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return of the King of Hell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plaything</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Regressor Protects Only Me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full-Time Awakening</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebirth of the Divine Demon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return of the First Patriarch: The Strongest Reincarnates into His Descendant 1000 Years Later</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lv. 99 Princess of Black Flame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Battle of the Martial Masters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Yellow-haired Villain in Female Main Character's Novel wants Happiness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From Six to Sovereignty: The Girl Who Ruled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eat and Go</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Shall Seal the Heavens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Executed Sage Who Was Reincarnated as a Lich and Started an All-Out War</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demon Instructor's Return</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Archduke's Bride Is a Hell Warrior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo Leveling: Ragnarok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Became a Patron of Villains</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Crow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Marquis Is the Marital Archduke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dukedom's Legendary Prodigy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnated as the Crazed Heir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lord of the Apocalypse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Don't Tell Me You Think Cultivating Immortality Is Difficult?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immortal Fairy, Please Listen to My Explanation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maplestory: The Last Adventurer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Steel Emperor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Luoyang Branch of the Heavenly Demon Cult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spirit Hunter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Player of the Fallen Family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unrivaled Spear Ghost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnation of the Martial God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After Rebirth, I Used Mirror Reversal For Vengeance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Death Attribute Magician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Great Emperor Shinmadae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenger: Apocalypse of Vengeance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hiding Out in an Apocalypse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bad Born Blood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KaguRai: Kagura to Raito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnated as the Lazy and Villainous Noble, I Broke the Scenario and Became the Most Formidable With Extraordinary Magic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Star Armor꞉ I’ll Slaughter Through the Chaos with Star Soul Generals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Demon King Overrun by Heroes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Monkey King’s Journey to the Murim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Sage who returned from another world wants to live quietly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Returned from Another World, Earth Turned Out to Be Quite the Fantasy Too. Also, Losing Heroines, Stop Looking This Way</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embodiment of the Assassin in the Murim World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Märchen - The Embodiment of Tales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sichuan’s Supreme King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Cold-Blooded Warrior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everyone Loves Her</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paper Tiger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Sword-Eating Swordmaster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The World's Best Kunlun Tavern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defense Breaker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worlds Best Assassin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The World's Best Martial Arts Instructor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How a Realist Hero Rebuilt the Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sleepy Princess in the Demon Castle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To Hell With The Status Window</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Becoming a Cheat-Level Skill Thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sichuan's Supreme King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reborn After the Eight Empresses Betrayed Me, Now I’ll Make Them Regret It</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebirth of the Demon Lord: the Slave who Conquered Fate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Strongest Wizard Becomes a Countryside Guard After Taking an Arrow to the Knee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Secret Martial Artist of Demonic Blood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Strongest Hero Who Longs For Revenge Will Peerlessly Annihilate With The Power Of Darkness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Became the Scoundrel of the Cheon Family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supreme Demon of Hyungsan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orc Hero Story - Discovery Chronicles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boukun Meika no Hangyakusha -Aster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jakdu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secretly Cultivating by the Demon Cult Leader's Side</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Old Prisoner Lives in Solitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenge of Young Master Peng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murim’s Dept King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Girlfriend's Friend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teto X Egen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gokusotsu Kraken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Masters of Heaven and Earth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red Storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Dragon Lives in Kunlun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Friend of the Demon King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High Martial Arts: Sweeping Through Three Thousand Emperors with One Hand!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Genius Martial Artist Who Remembers Everything</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Shepherd Wizard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sovereign of a Hundred Blades: Heir to the Strongest Style</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shadow Slave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Tale of Cultivation and Demon Extermination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Former Supreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What a Bountiful Harvest, Demon Lord!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Sword Emperor’s Rise of Namgung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Kidnapped the Youngest Daughter of the Sichuan Tang Clan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">War of Extinction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Divine Demon’s Grand Ascension</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1248,7 +1249,22 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Nimbus Sans"/>
@@ -1297,14 +1313,14 @@
     </fill>
   </fills>
   <borders count="3">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FFD9D9D9"/>
       </left>
@@ -1317,7 +1333,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FFD9D9D9"/>
       </left>
@@ -1333,47 +1349,126 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="5">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF4F81BD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEAF2F8"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1432,74 +1527,57 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:B389" totalsRowShown="0">
-  <autoFilter ref="A1:B389" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:B389" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:B389"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Title"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Episodes"/>
+    <tableColumn id="1" name="Title"/>
+    <tableColumn id="2" name="Episodes"/>
   </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1507,12 +1585,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1541,7 +1619,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1562,7 +1640,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1613,7 +1691,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1631,26 +1709,27 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B392"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B393"/>
+  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="169" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="169"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.43"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1658,3103 +1737,3103 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="4" t="n">
         <v>878</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="6" t="n">
         <v>266</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="6" t="n">
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="4" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="6" t="n">
         <v>135</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="4" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="4" t="n">
         <v>292</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="4" t="n">
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="4" t="n">
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="6" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="4" t="n">
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="6" t="n">
         <v>223</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="4" t="n">
         <v>162</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="6" t="n">
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="4" t="n">
         <v>117</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="6" t="n">
         <v>85</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="4" t="n">
         <v>182</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="6" t="n">
         <v>175</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="4" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="6" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="4" t="n">
         <v>10.1</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="6" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="4" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="6">
+      <c r="B29" s="6" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30" s="4" t="n">
         <v>105</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="6">
+      <c r="B31" s="6" t="n">
         <v>77</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" s="4" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="6">
+      <c r="B33" s="6" t="n">
         <v>88</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34" s="4" t="n">
         <v>99</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="6">
+      <c r="B35" s="6" t="n">
         <v>157</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36" s="4" t="n">
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="6">
+      <c r="B37" s="6" t="n">
         <v>51</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="4">
+      <c r="B38" s="4" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="6">
+      <c r="B39" s="6" t="n">
         <v>58</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="4">
+      <c r="B40" s="4" t="n">
         <v>124</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="6">
+      <c r="B41" s="6" t="n">
         <v>111</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="4">
+      <c r="B42" s="4" t="n">
         <v>63</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="6">
+      <c r="B43" s="6" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B44" s="4">
+      <c r="B44" s="4" t="n">
         <v>162</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B45" s="6">
+      <c r="B45" s="6" t="n">
         <v>64</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B46" s="4">
+      <c r="B46" s="4" t="n">
         <v>140</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="6">
+      <c r="B47" s="6" t="n">
         <v>168</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="4">
+      <c r="B48" s="4" t="n">
         <v>186</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B49" s="6">
+      <c r="B49" s="6" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B50" s="4">
+      <c r="B50" s="4" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B51" s="6">
+      <c r="B51" s="6" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B52" s="4">
+      <c r="B52" s="4" t="n">
         <v>71</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B53" s="6">
+      <c r="B53" s="6" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B54" s="4">
+      <c r="B54" s="4" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B55" s="6">
+      <c r="B55" s="6" t="n">
         <v>156</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B56" s="4">
+      <c r="B56" s="4" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B57" s="6">
+      <c r="B57" s="6" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B58" s="4">
+      <c r="B58" s="4" t="n">
         <v>144</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B59" s="6">
+      <c r="B59" s="6" t="n">
         <v>329</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B60" s="4">
+      <c r="B60" s="4" t="n">
         <v>161</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B61" s="6">
+      <c r="B61" s="6" t="n">
         <v>275</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B62" s="4">
+      <c r="B62" s="4" t="n">
         <v>311</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B63" s="6">
+      <c r="B63" s="6" t="n">
         <v>175</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B64" s="4">
+      <c r="B64" s="4" t="n">
         <v>58</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B65" s="6">
+      <c r="B65" s="6" t="n">
         <v>851</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B66" s="4">
+      <c r="B66" s="4" t="n">
         <v>3644</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B67" s="6">
+      <c r="B67" s="6" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B68" s="4">
+      <c r="B68" s="4" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B69" s="6">
+      <c r="B69" s="6" t="n">
         <v>76</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B70" s="4">
+      <c r="B70" s="4" t="n">
         <v>220</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B71" s="6">
+      <c r="B71" s="6" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B72" s="4">
+      <c r="B72" s="4" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B73" s="6">
+      <c r="B73" s="6" t="n">
         <v>89</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B74" s="4">
+      <c r="B74" s="4" t="n">
         <v>508.1</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B75" s="6">
+      <c r="B75" s="6" t="n">
         <v>43</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B76" s="4">
+      <c r="B76" s="4" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B77" s="6">
+      <c r="B77" s="6" t="n">
         <v>587</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B78" s="4">
+      <c r="B78" s="4" t="n">
         <v>121</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B79" s="6">
+      <c r="B79" s="6" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B80" s="4">
+      <c r="B80" s="4" t="n">
         <v>157</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B81" s="6">
+      <c r="B81" s="6" t="n">
         <v>156</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B82" s="4">
+      <c r="B82" s="4" t="n">
         <v>235</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B83" s="6">
+      <c r="B83" s="6" t="n">
         <v>188</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B84" s="4">
+      <c r="B84" s="4" t="n">
         <v>106</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B85" s="6">
+      <c r="B85" s="6" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B86" s="4">
+      <c r="B86" s="4" t="n">
         <v>33</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B87" s="6">
+      <c r="B87" s="6" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B88" s="4">
+      <c r="B88" s="4" t="n">
         <v>187</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B89" s="6">
+      <c r="B89" s="6" t="n">
         <v>256</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B90" s="4">
+      <c r="B90" s="4" t="n">
         <v>133</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B91" s="6">
+      <c r="B91" s="6" t="n">
         <v>217</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B92" s="4">
+      <c r="B92" s="4" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B93" s="6">
+      <c r="B93" s="6" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B94" s="4">
+      <c r="B94" s="4" t="n">
         <v>65</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B95" s="6">
+      <c r="B95" s="6" t="n">
         <v>56</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B96" s="4">
+      <c r="B96" s="4" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="6">
+      <c r="B97" s="6" t="n">
         <v>52</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B98" s="4">
+      <c r="B98" s="4" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B99" s="6">
+      <c r="B99" s="6" t="n">
         <v>41</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B100" s="4">
+      <c r="B100" s="4" t="n">
         <v>182</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B101" s="6">
+      <c r="B101" s="6" t="n">
         <v>157</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B102" s="4">
+      <c r="B102" s="4" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B103" s="6">
+      <c r="B103" s="6" t="n">
         <v>103</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B104" s="4">
+      <c r="B104" s="4" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B105" s="6">
+      <c r="B105" s="6" t="n">
         <v>94</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B106" s="4">
+      <c r="B106" s="4" t="n">
         <v>221</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B107" s="6">
+      <c r="B107" s="6" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="108" spans="1:2">
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B108" s="4">
+      <c r="B108" s="4" t="n">
         <v>61</v>
       </c>
     </row>
-    <row r="109" spans="1:2">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B109" s="6">
+      <c r="B109" s="6" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:2">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B110" s="4">
+      <c r="B110" s="4" t="n">
         <v>10.1</v>
       </c>
     </row>
-    <row r="111" spans="1:2">
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="B111" s="6">
+      <c r="B111" s="6" t="n">
         <v>79</v>
       </c>
     </row>
-    <row r="112" spans="1:2">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B112" s="4">
+      <c r="B112" s="4" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="113" spans="1:2">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B113" s="6">
+      <c r="B113" s="6" t="n">
         <v>34</v>
       </c>
     </row>
-    <row r="114" spans="1:2">
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B114" s="4">
+      <c r="B114" s="4" t="n">
         <v>38.1</v>
       </c>
     </row>
-    <row r="115" spans="1:2">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B115" s="6">
+      <c r="B115" s="6" t="n">
         <v>63</v>
       </c>
     </row>
-    <row r="116" spans="1:2">
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B116" s="4">
+      <c r="B116" s="4" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="117" spans="1:2">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B117" s="6">
+      <c r="B117" s="6" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="118" spans="1:2">
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B118" s="4">
+      <c r="B118" s="4" t="n">
         <v>49</v>
       </c>
     </row>
-    <row r="119" spans="1:2">
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B119" s="6">
+      <c r="B119" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="120" spans="1:2">
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B120" s="4">
+      <c r="B120" s="4" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="121" spans="1:2">
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B121" s="6">
+      <c r="B121" s="6" t="n">
         <v>43</v>
       </c>
     </row>
-    <row r="122" spans="1:2">
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B122" s="4">
+      <c r="B122" s="4" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="123" spans="1:2">
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B123" s="6">
+      <c r="B123" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="124" spans="1:2">
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B124" s="4">
+      <c r="B124" s="4" t="n">
         <v>33</v>
       </c>
     </row>
-    <row r="125" spans="1:2">
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B125" s="6">
+      <c r="B125" s="6" t="n">
         <v>7.2</v>
       </c>
     </row>
-    <row r="126" spans="1:2">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B126" s="4">
+      <c r="B126" s="4" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="127" spans="1:2">
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B127" s="6">
+      <c r="B127" s="6" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="128" spans="1:2">
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B128" s="4">
+      <c r="B128" s="4" t="n">
         <v>58</v>
       </c>
     </row>
-    <row r="129" spans="1:2">
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="B129" s="6">
+      <c r="B129" s="6" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="130" spans="1:2">
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B130" s="4">
+      <c r="B130" s="4" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="131" spans="1:2">
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B131" s="6">
+      <c r="B131" s="6" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="132" spans="1:2">
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B132" s="4">
+      <c r="B132" s="4" t="n">
         <v>56</v>
       </c>
     </row>
-    <row r="133" spans="1:2">
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B133" s="6">
+      <c r="B133" s="6" t="n">
         <v>12.2</v>
       </c>
     </row>
-    <row r="134" spans="1:2">
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B134" s="4">
+      <c r="B134" s="4" t="n">
         <v>91</v>
       </c>
     </row>
-    <row r="135" spans="1:2">
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B135" s="6">
+      <c r="B135" s="6" t="n">
         <v>165</v>
       </c>
     </row>
-    <row r="136" spans="1:2">
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B136" s="4">
+      <c r="B136" s="4" t="n">
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="1:2">
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="B137" s="6">
+      <c r="B137" s="6" t="n">
         <v>92</v>
       </c>
     </row>
-    <row r="138" spans="1:2">
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B138" s="4">
+      <c r="B138" s="4" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="139" spans="1:2">
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B139" s="6">
+      <c r="B139" s="6" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="140" spans="1:2">
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B140" s="4">
+      <c r="B140" s="4" t="n">
         <v>90</v>
       </c>
     </row>
-    <row r="141" spans="1:2">
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B141" s="6">
+      <c r="B141" s="6" t="n">
         <v>48</v>
       </c>
     </row>
-    <row r="142" spans="1:2">
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B142" s="4">
+      <c r="B142" s="4" t="n">
         <v>39</v>
       </c>
     </row>
-    <row r="143" spans="1:2">
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="B143" s="6">
+      <c r="B143" s="6" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="144" spans="1:2">
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B144" s="4">
+      <c r="B144" s="4" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="145" spans="1:2">
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B145" s="6">
+      <c r="B145" s="6" t="n">
         <v>123</v>
       </c>
     </row>
-    <row r="146" spans="1:2">
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B146" s="4">
+      <c r="B146" s="4" t="n">
         <v>102</v>
       </c>
     </row>
-    <row r="147" spans="1:2">
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B147" s="6">
+      <c r="B147" s="6" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="148" spans="1:2">
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B148" s="4">
+      <c r="B148" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="149" spans="1:2">
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="B149" s="6">
+      <c r="B149" s="6" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="150" spans="1:2">
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B150" s="4">
+      <c r="B150" s="4" t="n">
         <v>73</v>
       </c>
     </row>
-    <row r="151" spans="1:2">
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B151" s="6">
+      <c r="B151" s="6" t="n">
         <v>55</v>
       </c>
     </row>
-    <row r="152" spans="1:2">
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B152" s="4">
+      <c r="B152" s="4" t="n">
         <v>63</v>
       </c>
     </row>
-    <row r="153" spans="1:2">
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B153" s="6">
+      <c r="B153" s="6" t="n">
         <v>83</v>
       </c>
     </row>
-    <row r="154" spans="1:2">
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B154" s="4">
+      <c r="B154" s="4" t="n">
         <v>139</v>
       </c>
     </row>
-    <row r="155" spans="1:2">
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B155" s="6">
+      <c r="B155" s="6" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="156" spans="1:2">
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B156" s="4">
+      <c r="B156" s="4" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="157" spans="1:2">
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B157" s="6">
+      <c r="B157" s="6" t="n">
         <v>76</v>
       </c>
     </row>
-    <row r="158" spans="1:2">
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B158" s="4">
+      <c r="B158" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="159" spans="1:2">
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B159" s="6">
+      <c r="B159" s="6" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="160" spans="1:2">
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B160" s="4">
+      <c r="B160" s="4" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="161" spans="1:2">
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B161" s="6">
+      <c r="B161" s="6" t="n">
         <v>58</v>
       </c>
     </row>
-    <row r="162" spans="1:2">
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B162" s="4">
+      <c r="B162" s="4" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="163" spans="1:2">
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B163" s="6">
+      <c r="B163" s="6" t="n">
         <v>34</v>
       </c>
     </row>
-    <row r="164" spans="1:2">
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B164" s="4">
+      <c r="B164" s="4" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="165" spans="1:2">
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="B165" s="6">
+      <c r="B165" s="6" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="166" spans="1:2">
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B166" s="4">
+      <c r="B166" s="4" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="167" spans="1:2">
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="B167" s="6">
+      <c r="B167" s="6" t="n">
         <v>61</v>
       </c>
     </row>
-    <row r="168" spans="1:2">
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B168" s="4">
+      <c r="B168" s="4" t="n">
         <v>108</v>
       </c>
     </row>
-    <row r="169" spans="1:2">
+    <row r="169" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="B169" s="6">
+      <c r="B169" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="170" spans="1:2">
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B170" s="4">
+      <c r="B170" s="4" t="n">
         <v>49</v>
       </c>
     </row>
-    <row r="171" spans="1:2">
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="B171" s="6">
+      <c r="B171" s="6" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="172" spans="1:2">
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B172" s="4">
+      <c r="B172" s="4" t="n">
         <v>74</v>
       </c>
     </row>
-    <row r="173" spans="1:2">
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="B173" s="6">
+      <c r="B173" s="6" t="n">
         <v>61</v>
       </c>
     </row>
-    <row r="174" spans="1:2">
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B174" s="4">
+      <c r="B174" s="4" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="175" spans="1:2">
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="B175" s="6">
+      <c r="B175" s="6" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="176" spans="1:2">
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B176" s="4">
+      <c r="B176" s="4" t="n">
         <v>104</v>
       </c>
     </row>
-    <row r="177" spans="1:2">
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="B177" s="6">
+      <c r="B177" s="6" t="n">
         <v>76</v>
       </c>
     </row>
-    <row r="178" spans="1:2">
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B178" s="4">
+      <c r="B178" s="4" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="179" spans="1:2">
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="B179" s="6">
+      <c r="B179" s="6" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="180" spans="1:2">
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B180" s="4">
+      <c r="B180" s="4" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="181" spans="1:2">
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="B181" s="6">
+      <c r="B181" s="6" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="182" spans="1:2">
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B182" s="4">
+      <c r="B182" s="4" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="183" spans="1:2">
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="B183" s="6">
+      <c r="B183" s="6" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="184" spans="1:2">
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B184" s="4">
+      <c r="B184" s="4" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="185" spans="1:2">
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="B185" s="6">
+      <c r="B185" s="6" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="186" spans="1:2">
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B186" s="4">
+      <c r="B186" s="4" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="187" spans="1:2">
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="B187" s="6">
+      <c r="B187" s="6" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="188" spans="1:2">
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B188" s="4">
+      <c r="B188" s="4" t="n">
         <v>27</v>
       </c>
     </row>
-    <row r="189" spans="1:2">
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="B189" s="6">
+      <c r="B189" s="6" t="n">
         <v>91</v>
       </c>
     </row>
-    <row r="190" spans="1:2">
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B190" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2">
+      <c r="B190" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="B191" s="6">
+      <c r="B191" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="192" spans="1:2">
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B192" s="4">
+      <c r="B192" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="193" spans="1:2">
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B193" s="6">
+      <c r="B193" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="194" spans="1:2">
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B194" s="4">
+      <c r="B194" s="4" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="195" spans="1:2">
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B195" s="6">
+      <c r="B195" s="6" t="n">
         <v>89</v>
       </c>
     </row>
-    <row r="196" spans="1:2">
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B196" s="4">
+      <c r="B196" s="4" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="197" spans="1:2">
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B197" s="6">
+      <c r="B197" s="6" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="198" spans="1:2">
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B198" s="4">
+      <c r="B198" s="4" t="n">
         <v>59</v>
       </c>
     </row>
-    <row r="199" spans="1:2">
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B199" s="6">
+      <c r="B199" s="6" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="200" spans="1:2">
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B200" s="4">
+      <c r="B200" s="4" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="201" spans="1:2">
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="B201" s="6">
+      <c r="B201" s="6" t="n">
         <v>108</v>
       </c>
     </row>
-    <row r="202" spans="1:2">
+    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B202" s="4">
+      <c r="B202" s="4" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="203" spans="1:2">
+    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="B203" s="6">
+      <c r="B203" s="6" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="204" spans="1:2">
+    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B204" s="4">
+      <c r="B204" s="4" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="205" spans="1:2">
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="B205" s="6">
+      <c r="B205" s="6" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="206" spans="1:2">
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B206" s="4">
+      <c r="B206" s="4" t="n">
         <v>17</v>
       </c>
     </row>
-    <row r="207" spans="1:2">
+    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="B207" s="6">
+      <c r="B207" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="208" spans="1:2">
+    <row r="208" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="B208" s="4">
+      <c r="B208" s="4" t="n">
         <v>220</v>
       </c>
     </row>
-    <row r="209" spans="1:2">
+    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="B209" s="6">
+      <c r="B209" s="6" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="210" spans="1:2">
+    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B210" s="4">
+      <c r="B210" s="4" t="n">
         <v>51</v>
       </c>
     </row>
-    <row r="211" spans="1:2">
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="B211" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2">
+      <c r="B211" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B212" s="4">
+      <c r="B212" s="4" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="213" spans="1:2">
+    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="B213" s="6">
+      <c r="B213" s="6" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="214" spans="1:2">
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B214" s="4">
+      <c r="B214" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="215" spans="1:2">
+    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="B215" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="216" spans="1:2">
+      <c r="B215" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="B216" s="4">
+      <c r="B216" s="4" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="217" spans="1:2">
+    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B217" s="6">
+      <c r="B217" s="6" t="n">
         <v>141</v>
       </c>
     </row>
-    <row r="218" spans="1:2">
+    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B218" s="4">
+      <c r="B218" s="4" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="219" spans="1:2">
+    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="B219" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" spans="1:2">
+      <c r="B219" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="B220" s="4">
+      <c r="B220" s="4" t="n">
         <v>49</v>
       </c>
     </row>
-    <row r="221" spans="1:2">
+    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="B221" s="6">
+      <c r="B221" s="6" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="222" spans="1:2">
+    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B222" s="4">
+      <c r="B222" s="4" t="n">
         <v>23</v>
       </c>
     </row>
-    <row r="223" spans="1:2">
+    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="B223" s="6">
+      <c r="B223" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="224" spans="1:2">
+    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B224" s="4">
+      <c r="B224" s="4" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="225" spans="1:2">
+    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="B225" s="6">
+      <c r="B225" s="6" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="226" spans="1:2">
+    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="B226" s="4">
+      <c r="B226" s="4" t="n">
         <v>36</v>
       </c>
     </row>
-    <row r="227" spans="1:2">
+    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="B227" s="6">
+      <c r="B227" s="6" t="n">
         <v>64</v>
       </c>
     </row>
-    <row r="228" spans="1:2">
+    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="B228" s="4">
+      <c r="B228" s="4" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="229" spans="1:2">
+    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="B229" s="6">
+      <c r="B229" s="6" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="230" spans="1:2">
+    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B230" s="4">
+      <c r="B230" s="4" t="n">
         <v>124</v>
       </c>
     </row>
-    <row r="231" spans="1:2">
+    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="B231" s="6">
+      <c r="B231" s="6" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="232" spans="1:2">
+    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="B232" s="4">
+      <c r="B232" s="4" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="233" spans="1:2">
+    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="B233" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234" spans="1:2">
+      <c r="B233" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="B234" s="4">
+      <c r="B234" s="4" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="235" spans="1:2">
+    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="B235" s="6">
+      <c r="B235" s="6" t="n">
         <v>130</v>
       </c>
     </row>
-    <row r="236" spans="1:2">
+    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="B236" s="4">
+      <c r="B236" s="4" t="n">
         <v>67</v>
       </c>
     </row>
-    <row r="237" spans="1:2">
+    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="B237" s="6">
+      <c r="B237" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="238" spans="1:2">
+    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B238" s="4">
+      <c r="B238" s="4" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="239" spans="1:2">
+    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="B239" s="6">
+      <c r="B239" s="6" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="240" spans="1:2">
+    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B240" s="4">
+      <c r="B240" s="4" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="241" spans="1:2">
+    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="B241" s="6">
+      <c r="B241" s="6" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="242" spans="1:2">
+    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="B242" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243" spans="1:2">
+      <c r="B242" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="B243" s="6">
+      <c r="B243" s="6" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="244" spans="1:2">
+    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B244" s="4">
+      <c r="B244" s="4" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="245" spans="1:2">
+    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="B245" s="6">
+      <c r="B245" s="6" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="246" spans="1:2">
+    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="B246" s="4">
+      <c r="B246" s="4" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="247" spans="1:2">
+    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="B247" s="6">
+      <c r="B247" s="6" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="248" spans="1:2">
+    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="B248" s="4">
+      <c r="B248" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="249" spans="1:2">
+    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="B249" s="6">
+      <c r="B249" s="6" t="n">
         <v>81</v>
       </c>
     </row>
-    <row r="250" spans="1:2">
+    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B250" s="4">
+      <c r="B250" s="4" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="251" spans="1:2">
+    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="B251" s="6">
+      <c r="B251" s="6" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="252" spans="1:2">
+    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="B252" s="4">
+      <c r="B252" s="4" t="n">
         <v>57</v>
       </c>
     </row>
-    <row r="253" spans="1:2">
+    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="B253" s="6">
+      <c r="B253" s="6" t="n">
         <v>112</v>
       </c>
     </row>
-    <row r="254" spans="1:2">
+    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B254" s="4">
+      <c r="B254" s="4" t="n">
         <v>126</v>
       </c>
     </row>
-    <row r="255" spans="1:2">
+    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="B255" s="6">
+      <c r="B255" s="6" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="256" spans="1:2">
+    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="B256" s="4">
+      <c r="B256" s="4" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="257" spans="1:2">
+    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="B257" s="6">
+      <c r="B257" s="6" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="258" spans="1:2">
+    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="B258" s="4">
+      <c r="B258" s="4" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="259" spans="1:2">
+    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="B259" s="6">
+      <c r="B259" s="6" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="260" spans="1:2">
+    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="B260" s="4">
+      <c r="B260" s="4" t="n">
         <v>219</v>
       </c>
     </row>
-    <row r="261" spans="1:2">
+    <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="B261" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262" spans="1:2">
+      <c r="B261" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="B262" s="4">
+      <c r="B262" s="4" t="n">
         <v>55</v>
       </c>
     </row>
-    <row r="263" spans="1:2">
+    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="B263" s="6">
+      <c r="B263" s="6" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:2">
+    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="B264" s="4">
+      <c r="B264" s="4" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="265" spans="1:2">
+    <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="B265" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266" spans="1:2">
+      <c r="B265" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="B266" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="267" spans="1:2">
+      <c r="B266" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="B267" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="268" spans="1:2">
+      <c r="B267" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B268" s="4">
+      <c r="B268" s="4" t="n">
         <v>17</v>
       </c>
     </row>
-    <row r="269" spans="1:2">
+    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="B269" s="6">
+      <c r="B269" s="6" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="270" spans="1:2">
+    <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="B270" s="4">
+      <c r="B270" s="4" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="271" spans="1:2">
+    <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="B271" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="272" spans="1:2">
+      <c r="B271" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="B272" s="4">
+      <c r="B272" s="4" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="273" spans="1:2">
+    <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="B273" s="6">
+      <c r="B273" s="6" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="274" spans="1:2">
+    <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="B274" s="4">
+      <c r="B274" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="275" spans="1:2">
+    <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="B275" s="6">
+      <c r="B275" s="6" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="276" spans="1:2">
+    <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="B276" s="4">
+      <c r="B276" s="4" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="277" spans="1:2">
+    <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="B277" s="6">
+      <c r="B277" s="6" t="n">
         <v>34</v>
       </c>
     </row>
-    <row r="278" spans="1:2">
+    <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="B278" s="4">
+      <c r="B278" s="4" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="279" spans="1:2">
+    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="B279" s="6">
+      <c r="B279" s="6" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="280" spans="1:2">
+    <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B280" s="4">
+      <c r="B280" s="4" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="281" spans="1:2">
+    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="B281" s="6">
+      <c r="B281" s="6" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="282" spans="1:2">
+    <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="B282" s="4">
+      <c r="B282" s="4" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="283" spans="1:2">
+    <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="B283" s="6">
+      <c r="B283" s="6" t="n">
         <v>27</v>
       </c>
     </row>
-    <row r="284" spans="1:2">
+    <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="B284" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285" spans="1:2" ht="15.75">
+      <c r="B284" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="B285" s="6">
+      <c r="B285" s="6" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="286" spans="1:2">
+    <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="B286" s="4">
+      <c r="B286" s="4" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="287" spans="1:2">
+    <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="B287" s="6">
+      <c r="B287" s="6" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="288" spans="1:2">
+    <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="B288" s="4">
+      <c r="B288" s="4" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="289" spans="1:2">
+    <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="B289" s="6">
+      <c r="B289" s="6" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="290" spans="1:2">
+    <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="B290" s="4">
+      <c r="B290" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="291" spans="1:2">
+    <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="B291" s="6">
+      <c r="B291" s="6" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="292" spans="1:2">
+    <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="B292" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="293" spans="1:2">
+      <c r="B292" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="B293" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="294" spans="1:2">
+      <c r="B293" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="B294" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="295" spans="1:2">
+      <c r="B294" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="B295" s="6">
+      <c r="B295" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="296" spans="1:2">
+    <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="B296" s="4">
+      <c r="B296" s="4" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="297" spans="1:2">
+    <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="B297" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="298" spans="1:2">
+      <c r="B297" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="B298" s="4">
+      <c r="B298" s="4" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="299" spans="1:2">
+    <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="B299" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300" spans="1:2">
+      <c r="B299" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="B300" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="301" spans="1:2">
+      <c r="B300" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="B301" s="6">
+      <c r="B301" s="6" t="n">
         <v>56</v>
       </c>
     </row>
-    <row r="302" spans="1:2">
+    <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="B302" s="4">
+      <c r="B302" s="4" t="n">
         <v>41</v>
       </c>
     </row>
-    <row r="303" spans="1:2">
+    <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="B303" s="6">
+      <c r="B303" s="6" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="304" spans="1:2">
+    <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="B304" s="4">
+      <c r="B304" s="4" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="305" spans="1:2">
+    <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="B305" s="6">
+      <c r="B305" s="6" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="306" spans="1:2">
+    <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="B306" s="4">
+      <c r="B306" s="4" t="n">
         <v>27</v>
       </c>
     </row>
-    <row r="307" spans="1:2">
+    <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="B307" s="6">
+      <c r="B307" s="6" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="308" spans="1:2">
+    <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="B308" s="4">
+      <c r="B308" s="4" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="309" spans="1:2">
+    <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="B309" s="6">
+      <c r="B309" s="6" t="n">
         <v>57</v>
       </c>
     </row>
-    <row r="310" spans="1:2">
+    <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="B310" s="4">
+      <c r="B310" s="4" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="311" spans="1:2">
+    <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="B311" s="6">
+      <c r="B311" s="6" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="312" spans="1:2">
+    <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="B312" s="4">
+      <c r="B312" s="4" t="n">
         <v>55</v>
       </c>
     </row>
-    <row r="313" spans="1:2">
+    <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="B313" s="6">
+      <c r="B313" s="6" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="314" spans="1:2">
+    <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="B314" s="4">
+      <c r="B314" s="4" t="n">
         <v>32</v>
       </c>
     </row>
-    <row r="315" spans="1:2">
+    <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="B315" s="6">
+      <c r="B315" s="6" t="n">
         <v>47</v>
       </c>
     </row>
-    <row r="316" spans="1:2">
+    <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="B316" s="4">
+      <c r="B316" s="4" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="317" spans="1:2">
+    <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B317" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="318" spans="1:2">
+      <c r="B317" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="B318" s="4">
+      <c r="B318" s="4" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="319" spans="1:2">
+    <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="B319" s="6">
+      <c r="B319" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="320" spans="1:2">
+    <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="B320" s="4">
+      <c r="B320" s="4" t="n">
         <v>161</v>
       </c>
     </row>
-    <row r="321" spans="1:2">
+    <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="B321" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="322" spans="1:2">
+      <c r="B321" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="B322" s="4">
+      <c r="B322" s="4" t="n">
         <v>34</v>
       </c>
     </row>
-    <row r="323" spans="1:2">
+    <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="B323" s="6">
+      <c r="B323" s="6" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="324" spans="1:2">
+    <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="B324" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="325" spans="1:2">
+      <c r="B324" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="B325" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="326" spans="1:2">
+      <c r="B325" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="B326" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="327" spans="1:2">
+      <c r="B326" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="B327" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="328" spans="1:2">
+      <c r="B327" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="B328" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="329" spans="1:2">
+      <c r="B328" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="B329" s="6">
+      <c r="B329" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="330" spans="1:2">
+    <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="B330" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="331" spans="1:2">
+      <c r="B330" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="B331" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="332" spans="1:2">
+      <c r="B331" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="B332" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="333" spans="1:2">
+      <c r="B332" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="B333" s="6">
+      <c r="B333" s="6" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="334" spans="1:2">
+    <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="B334" s="4">
+      <c r="B334" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="335" spans="1:2">
+    <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="B335" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="336" spans="1:2">
+      <c r="B335" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="B336" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="337" spans="1:2">
+      <c r="B336" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="B337" s="6">
+      <c r="B337" s="6" t="n">
         <v>27</v>
       </c>
     </row>
-    <row r="338" spans="1:2">
+    <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="B338" s="4">
+      <c r="B338" s="4" t="n">
         <v>17</v>
       </c>
     </row>
-    <row r="339" spans="1:2">
+    <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="B339" s="6">
+      <c r="B339" s="6" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="340" spans="1:2">
+    <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="B340" s="4">
+      <c r="B340" s="4" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="341" spans="1:2">
+    <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="B341" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="342" spans="1:2">
+      <c r="B341" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="B342" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="343" spans="1:2">
+      <c r="B342" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="B343" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="344" spans="1:2">
+      <c r="B343" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="B344" s="4">
+      <c r="B344" s="4" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="345" spans="1:2">
+    <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="B345" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="346" spans="1:2">
+      <c r="B345" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="B346" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="347" spans="1:2">
+      <c r="B346" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="B347" s="6">
+      <c r="B347" s="6" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="348" spans="1:2">
+    <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="B348" s="4">
+      <c r="B348" s="4" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="349" spans="1:2">
+    <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="B349" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="350" spans="1:2">
+      <c r="B349" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="B350" s="4">
+      <c r="B350" s="4" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="351" spans="1:2">
+    <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="B351" s="6">
+      <c r="B351" s="6" t="n">
         <v>97</v>
       </c>
     </row>
-    <row r="352" spans="1:2">
+    <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="B352" s="4">
+      <c r="B352" s="4" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="353" spans="1:2">
+    <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="B353" s="6">
+      <c r="B353" s="6" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="354" spans="1:2">
+    <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="B354" s="4">
+      <c r="B354" s="4" t="n">
         <v>52</v>
       </c>
     </row>
-    <row r="355" spans="1:2">
+    <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="B355" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="356" spans="1:2">
+      <c r="B355" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="B356" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="357" spans="1:2">
+      <c r="B356" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="B357" s="6">
+      <c r="B357" s="6" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="358" spans="1:2">
+    <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="B358" s="4">
+      <c r="B358" s="4" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="359" spans="1:2">
+    <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="B359" s="6">
+      <c r="B359" s="6" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="360" spans="1:2">
+    <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="B360" s="4">
+      <c r="B360" s="4" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="361" spans="1:2">
+    <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="B361" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="362" spans="1:2">
+      <c r="B361" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="B362" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="363" spans="1:2">
+      <c r="B362" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="B363" s="4">
+      <c r="B363" s="4" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="364" spans="1:2">
+    <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="B364" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="365" spans="1:2">
+      <c r="B364" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B365" s="4">
+      <c r="B365" s="4" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="366" spans="1:2">
+    <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="B366" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="367" spans="1:2">
+      <c r="B366" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="B367" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="368" spans="1:2">
+      <c r="B367" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="B368" s="6">
+      <c r="B368" s="6" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="369" spans="1:2">
+    <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="B369" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="370" spans="1:2">
+      <c r="B369" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="B370" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="371" spans="1:2">
+      <c r="B370" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="B371" s="4">
+      <c r="B371" s="4" t="n">
         <v>71</v>
       </c>
     </row>
-    <row r="372" spans="1:2">
+    <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="B372" s="6">
+      <c r="B372" s="6" t="n">
         <v>49</v>
       </c>
     </row>
-    <row r="373" spans="1:2">
+    <row r="373" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="B373" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="374" spans="1:2">
+      <c r="B373" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="B374" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="375" spans="1:2">
+      <c r="B374" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="B375" s="1">
+      <c r="B375" s="1" t="n">
         <v>114</v>
       </c>
     </row>
-    <row r="376" spans="1:2">
+    <row r="376" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="B376" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="377" spans="1:2">
+      <c r="B376" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="B377" s="1">
+      <c r="B377" s="1" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="378" spans="1:2">
+    <row r="378" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="B378" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="379" spans="1:2">
+      <c r="B378" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="B379" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="380" spans="1:2">
+      <c r="B379" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="B380" s="1">
+      <c r="B380" s="1" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="381" spans="1:2">
+    <row r="381" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="B381" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="382" spans="1:2">
+      <c r="B381" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="B382" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="383" spans="1:2">
+      <c r="B382" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="B383" s="1">
+      <c r="B383" s="1" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="384" spans="1:2">
+    <row r="384" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="B384" s="9">
+      <c r="B384" s="9" t="n">
         <v>36</v>
       </c>
     </row>
-    <row r="385" spans="1:2">
+    <row r="385" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="B385" s="1">
+      <c r="B385" s="1" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="386" spans="1:2">
-      <c r="A386" t="s">
+    <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A386" s="0" t="s">
         <v>385</v>
       </c>
-      <c r="B386" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="387" spans="1:2">
-      <c r="A387" t="s">
+      <c r="B386" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A387" s="0" t="s">
         <v>386</v>
       </c>
-      <c r="B387" s="1">
+      <c r="B387" s="1" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="388" spans="1:2">
+    <row r="388" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="10" t="s">
         <v>387</v>
       </c>
-      <c r="B388" s="1">
+      <c r="B388" s="1" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="389" spans="1:2">
+    <row r="389" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="7" t="s">
         <v>388</v>
       </c>
@@ -4762,34 +4841,47 @@
         <v>389</v>
       </c>
     </row>
-    <row r="390" spans="1:2">
+    <row r="390" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="7" t="s">
         <v>390</v>
       </c>
-      <c r="B390" s="1">
+      <c r="B390" s="1" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="391" spans="1:2">
+    <row r="391" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="B391" s="1">
+      <c r="B391" s="1" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="392" spans="1:2">
+    <row r="392" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="10" t="s">
         <v>392</v>
       </c>
-      <c r="B392" s="1">
+      <c r="B392" s="1" t="n">
         <v>7</v>
       </c>
     </row>
+    <row r="393" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A393" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="B393" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <tableParts count="1">
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <tableParts>
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>

--- a/Manga.Manhwua/Updated manhwua.xlsx
+++ b/Manga.Manhwua/Updated manhwua.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Manga\Manga.Manhwua\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC1EFBD0-FACA-4B87-8EBC-A7E562723549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -22,511 +27,511 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="394">
   <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Episodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vagabond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My Dragon System</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Knight King Who Returned With A God</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Player Hides His Past</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disastrous Necromancer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Priest of Corruption</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dragon Emperor Martial God</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mookhyang - Dark Lady</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leveling Up By Hoarding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master Of The Martial Arts Library</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Absolute Necromancer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tales Of A Shinning Sword</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyushu Chronicles Of Immortals And Demons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Level 1 Player</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logging 10,000 Years into the Future</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Swordmaster’S Youngest Son</t>
-  </si>
-  <si>
-    <t xml:space="preserve">World’S Greatest Senior Disciple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dragon Master</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Return Of The Disaster-Class Hero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solo Farming In The Tower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chronicles Of The Demon Faction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demonic Master Of Mount Kunlun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Necromancer's Evolutionary Traits</t>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Episodes</t>
+  </si>
+  <si>
+    <t>Kingdom</t>
+  </si>
+  <si>
+    <t>Vagabond</t>
+  </si>
+  <si>
+    <t>My Dragon System</t>
+  </si>
+  <si>
+    <t>The Knight King Who Returned With A God</t>
+  </si>
+  <si>
+    <t>The Player Hides His Past</t>
+  </si>
+  <si>
+    <t>Disastrous Necromancer</t>
+  </si>
+  <si>
+    <t>The Priest of Corruption</t>
+  </si>
+  <si>
+    <t>Dragon Emperor Martial God</t>
+  </si>
+  <si>
+    <t>Mookhyang - Dark Lady</t>
+  </si>
+  <si>
+    <t>Leveling Up By Hoarding</t>
+  </si>
+  <si>
+    <t>Master Of The Martial Arts Library</t>
+  </si>
+  <si>
+    <t>Absolute Necromancer</t>
+  </si>
+  <si>
+    <t>Tales Of A Shinning Sword</t>
+  </si>
+  <si>
+    <t>Kyushu Chronicles Of Immortals And Demons</t>
+  </si>
+  <si>
+    <t>Level 1 Player</t>
+  </si>
+  <si>
+    <t>Logging 10,000 Years into the Future</t>
+  </si>
+  <si>
+    <t>Swordmaster’S Youngest Son</t>
+  </si>
+  <si>
+    <t>World’S Greatest Senior Disciple</t>
+  </si>
+  <si>
+    <t>Dragon Master</t>
+  </si>
+  <si>
+    <t>The Return Of The Disaster-Class Hero</t>
+  </si>
+  <si>
+    <t>Solo Farming In The Tower</t>
+  </si>
+  <si>
+    <t>Chronicles Of The Demon Faction</t>
+  </si>
+  <si>
+    <t>Demonic Master Of Mount Kunlun</t>
+  </si>
+  <si>
+    <t>Necromancer's Evolutionary Traits</t>
   </si>
   <si>
     <t xml:space="preserve">Samurai In Another World </t>
   </si>
   <si>
-    <t xml:space="preserve">Peerless Quest – The Cheat Skill Only I Can Use</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isekai De Haishin Katsudou Wo Shitara Tairyou No Yandere Shinja Wo Umidashite Shimatta Ken</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boundless Necromancer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Academy’S Genius Swordsman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demon Evolution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Iron-Blooded Necromancer Has Returned</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infinite Mage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Star Instructor  Master Baek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Story Of Thorny Spear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blade debt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martial God Regressed To Level 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What, You Dare Pretend In Front Of Me, The Strongest In The Immortal World?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terminally-Ill Genius Dark Knight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heavenly Inquisition Sword</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tsuki Ga Michibiku Isekai Douchuu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Emperor’s Sword</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Constellations Are My Disciples</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenge of the Iron-Blooded Sword Hound</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Zombie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master: This Villainous Disciple Is Not The Holy Child</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solo Max-Level Newbie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Murim Login</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Great Villain Who Threatened to Kill Himself</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon Maker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Reincarnated Assassin is a Genius Swordsman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I was more overpowered than the hero, so I hid my power!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Million Times Attack Speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I am the descendant of the Divine Dragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hero X Demon Queen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Records Of The Demonic Path’S Return</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Five-Dimensional Zone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legendary Youngest Son Of The Marquis House</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I am fated villain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return Of The Mount Hua Sect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beyond Myriad Peoples</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nano Machine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tensei Shitara Dai Nana Ouji Dattanode, Kimamani Majutsu O Kiwamemasu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scoring the Sacred Body of the Ancients from the Get-go</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magic Emperor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martial Peak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Self-Disciplined Me Is Practically Invincible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Power: I Can Control All The Elements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Slayer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightning Degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The World's Best Sect Of Dependency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Return Of Apocalypses Tyrant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What Do You Do When You Suddenly Become An Immortal?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tales Of Demons And Gods</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Kingdoms Of Ruin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Necromancer Academy And The Genius Summoner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yuan Zun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Greatest Estate Designer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conqueror of modern martial arts Kang Haejin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Records Of The Swordsman Scholar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Scholar's Reincarnation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tale of a Scribe Who Retires To The Countryside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return Of The Bachelor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reincarnation Of The Murim Clan's Former Ranker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regressing with the King’s Power</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Last Cultivator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEAVENLY MOON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infinite Leveling: Murim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volcanic Age</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chronicles Of A Returner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Undefeatable Swordsman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Second Life of Dongfang Bubai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Job Change: I Became The Undead Monarch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relife Player</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My Lucky Encounter From The Game Turned Into Reality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Killed an Academy Player</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bloodhound’s Regression Instinct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Raised the Yandere Villain Empress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Max-Level Player’s 100th Regression</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Heavenly Demon Can't Live A Normal Life</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Player That Can't Level Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reborn As The Enemy Prince</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Archmage's Restaurant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Rely on My Invincibility to Deal Tons of Damage Passively!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wild West Murim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster Pet Evolution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Strongest Sect Of All Times</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Youngest Scion Of The Mages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Will Do Whatever I Want In Ten Thousand Years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genkai Level 1 Kara No Nariagari: Saijaku Level No Ore Ga Isekai Saikyou Ni Naru Made</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How to Live at the Max Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The All-Knowing Cultivator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurasu ≪Mushoku≫ No Eiyuu-Tan ~Koushaku-Ka O Tsuihou Sareta Ga, Jitsu Wa Nagutta Dake De Sukiru O Kakutoku Dekiru To Wakari, Tairiku Ichi No Eiyuu Ni Nobori Tsumeru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Villager A Wants To Save The Villainess No Matter What!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Savage Hero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genkai Koe No Tenpu wa, Tensei-sha ni Shika Atsukaenai Overlimit Skill Holders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maken Tsukai No Moto Shounen Hei Wa, Moto Teki Kanbu No Onee-San To Issho Ni Ikitai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mannen D-Rank No Chuunen Boukensha, Yotta Ikioi De Densetsu No Ken Wo Hikkonuku</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dungeon Sherpa: Meikyuu Michisaki Annainin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Sword Master Childhood Friend Power Harassed Me Harshly, So I Broke Off Our Relationship And Made A Fresh Start At The Frontier As A Magic Swordsman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Summoned The Devil To Grant Me A Wish, But I Married Her Instead Since She Was Adorable ~My New Devil Wife~</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Story About A Dragon And The Rising Of An Adventurer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">After Being Called A Hero: The Unrivaled Man Starts A Family</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Warrior Exiled By The Hero And His Lover</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nimotsu Mochi No Nousuji Musou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Strongest Dull Prince’s Secret Battle for the Throne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Sword of Princess Gluttony</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wistoria's Wand And Sword</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Crafty Mage: Frontier Settling Made Easy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delivery Man From Murim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Henkyou Gurashi No Maou, Tensei Shite Saikyou No Majutsushi Ni Naru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Executed Sage Is Reincarnated As A Lich And Starts An All-Out War</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dungeon Ni Hisomu Yandere Na Kanojo Ni Ore Wa Nando Mo Korosareru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Became A Big-Shot On The Heavenly Leaderboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Dark Magician Transmigrates After 66666 Years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reaper Of The Drifting Moon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Unbeatable Dungeon's Lazy Boss Monster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All My Abilities Are Forbidden Spells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How To Survive As A Dragon With Time-Limit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Myst, Might, Mayhem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark And Light Martial Emperor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The doomsday ruthless man: hoarding trillions of supplies at the beginning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Becoming the Swordmaster Rank Young Lord of the Sichuan Tang Family</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This Account Is Ridiculous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Mysterious World’s Greatest Martial Artist Little Prince</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Reborn Young Lord Is An Assassin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">God-Slaying Copycat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Great Mage Of The Hero’S Party Reincarnates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My Brother Is The Chosen One</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Max Level Hero Strikes Back</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overlord of Insects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Game Of Familia: Kazoku Senki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grand General</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Legendary Spearman Returns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ice lord</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My Inventory is Abnormal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Escort Agency Of The Apocalypse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Heavenly Demon Will Give You a Massage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Twin Swords Of The Sima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Versatile Sword Cultivator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magic Academy’s Genius Blinker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Worthless Profession: Dragon Tamer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expelled Hero Is Too Strong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Ten Thousand Clans Invasion: Guardian Of The Rear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My Disciple Became the Great Demon Empress?!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Greatest In The World</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drawing: The Greatest Mangaka Becomes A Skilled “Martial Artist” In Another World</t>
+    <t>Peerless Quest – The Cheat Skill Only I Can Use</t>
+  </si>
+  <si>
+    <t>Isekai De Haishin Katsudou Wo Shitara Tairyou No Yandere Shinja Wo Umidashite Shimatta Ken</t>
+  </si>
+  <si>
+    <t>Boundless Necromancer</t>
+  </si>
+  <si>
+    <t>Academy’S Genius Swordsman</t>
+  </si>
+  <si>
+    <t>Demon Evolution</t>
+  </si>
+  <si>
+    <t>The Iron-Blooded Necromancer Has Returned</t>
+  </si>
+  <si>
+    <t>Infinite Mage</t>
+  </si>
+  <si>
+    <t>Star Instructor  Master Baek</t>
+  </si>
+  <si>
+    <t>The Story Of Thorny Spear</t>
+  </si>
+  <si>
+    <t>Blade debt</t>
+  </si>
+  <si>
+    <t>Martial God Regressed To Level 2</t>
+  </si>
+  <si>
+    <t>What, You Dare Pretend In Front Of Me, The Strongest In The Immortal World?</t>
+  </si>
+  <si>
+    <t>Terminally-Ill Genius Dark Knight</t>
+  </si>
+  <si>
+    <t>Heavenly Inquisition Sword</t>
+  </si>
+  <si>
+    <t>Tsuki Ga Michibiku Isekai Douchuu</t>
+  </si>
+  <si>
+    <t>The Emperor’s Sword</t>
+  </si>
+  <si>
+    <t>The Constellations Are My Disciples</t>
+  </si>
+  <si>
+    <t>Revenge of the Iron-Blooded Sword Hound</t>
+  </si>
+  <si>
+    <t>Mr. Zombie</t>
+  </si>
+  <si>
+    <t>Master: This Villainous Disciple Is Not The Holy Child</t>
+  </si>
+  <si>
+    <t>Solo Max-Level Newbie</t>
+  </si>
+  <si>
+    <t>Murim Login</t>
+  </si>
+  <si>
+    <t>The Great Villain Who Threatened to Kill Himself</t>
+  </si>
+  <si>
+    <t>Weapon Maker</t>
+  </si>
+  <si>
+    <t>The Reincarnated Assassin is a Genius Swordsman</t>
+  </si>
+  <si>
+    <t>I was more overpowered than the hero, so I hid my power!</t>
+  </si>
+  <si>
+    <t>Million Times Attack Speed</t>
+  </si>
+  <si>
+    <t>I am the descendant of the Divine Dragon</t>
+  </si>
+  <si>
+    <t>Hero X Demon Queen</t>
+  </si>
+  <si>
+    <t>Records Of The Demonic Path’S Return</t>
+  </si>
+  <si>
+    <t>Five-Dimensional Zone</t>
+  </si>
+  <si>
+    <t>Legendary Youngest Son Of The Marquis House</t>
+  </si>
+  <si>
+    <t>I am fated villain</t>
+  </si>
+  <si>
+    <t>Return Of The Mount Hua Sect</t>
+  </si>
+  <si>
+    <t>Beyond Myriad Peoples</t>
+  </si>
+  <si>
+    <t>Nano Machine</t>
+  </si>
+  <si>
+    <t>Tensei Shitara Dai Nana Ouji Dattanode, Kimamani Majutsu O Kiwamemasu</t>
+  </si>
+  <si>
+    <t>Scoring the Sacred Body of the Ancients from the Get-go</t>
+  </si>
+  <si>
+    <t>Magic Emperor</t>
+  </si>
+  <si>
+    <t>Martial Peak</t>
+  </si>
+  <si>
+    <t>The Self-Disciplined Me Is Practically Invincible</t>
+  </si>
+  <si>
+    <t>Global Power: I Can Control All The Elements</t>
+  </si>
+  <si>
+    <t>Moon Slayer</t>
+  </si>
+  <si>
+    <t>Lightning Degree</t>
+  </si>
+  <si>
+    <t>The World's Best Sect Of Dependency</t>
+  </si>
+  <si>
+    <t>The Return Of Apocalypses Tyrant</t>
+  </si>
+  <si>
+    <t>What Do You Do When You Suddenly Become An Immortal?</t>
+  </si>
+  <si>
+    <t>Tales Of Demons And Gods</t>
+  </si>
+  <si>
+    <t>The Kingdoms Of Ruin</t>
+  </si>
+  <si>
+    <t>Necromancer Academy And The Genius Summoner</t>
+  </si>
+  <si>
+    <t>Yuan Zun</t>
+  </si>
+  <si>
+    <t>The Greatest Estate Designer</t>
+  </si>
+  <si>
+    <t>Conqueror of modern martial arts Kang Haejin</t>
+  </si>
+  <si>
+    <t>Records Of The Swordsman Scholar</t>
+  </si>
+  <si>
+    <t>The Scholar's Reincarnation</t>
+  </si>
+  <si>
+    <t>Tale of a Scribe Who Retires To The Countryside</t>
+  </si>
+  <si>
+    <t>Return Of The Bachelor</t>
+  </si>
+  <si>
+    <t>Reincarnation Of The Murim Clan's Former Ranker</t>
+  </si>
+  <si>
+    <t>Regressing with the King’s Power</t>
+  </si>
+  <si>
+    <t>The Last Cultivator</t>
+  </si>
+  <si>
+    <t>HEAVENLY MOON</t>
+  </si>
+  <si>
+    <t>Infinite Leveling: Murim</t>
+  </si>
+  <si>
+    <t>Volcanic Age</t>
+  </si>
+  <si>
+    <t>Chronicles Of A Returner</t>
+  </si>
+  <si>
+    <t>The Undefeatable Swordsman</t>
+  </si>
+  <si>
+    <t>Second Life of Dongfang Bubai</t>
+  </si>
+  <si>
+    <t>Job Change: I Became The Undead Monarch</t>
+  </si>
+  <si>
+    <t>Relife Player</t>
+  </si>
+  <si>
+    <t>My Lucky Encounter From The Game Turned Into Reality</t>
+  </si>
+  <si>
+    <t>I Killed an Academy Player</t>
+  </si>
+  <si>
+    <t>Bloodhound’s Regression Instinct</t>
+  </si>
+  <si>
+    <t>I Raised the Yandere Villain Empress</t>
+  </si>
+  <si>
+    <t>The Max-Level Player’s 100th Regression</t>
+  </si>
+  <si>
+    <t>The Heavenly Demon Can't Live A Normal Life</t>
+  </si>
+  <si>
+    <t>The Player That Can't Level Up</t>
+  </si>
+  <si>
+    <t>Reborn As The Enemy Prince</t>
+  </si>
+  <si>
+    <t>The Archmage's Restaurant</t>
+  </si>
+  <si>
+    <t>I Rely on My Invincibility to Deal Tons of Damage Passively!</t>
+  </si>
+  <si>
+    <t>Wild West Murim</t>
+  </si>
+  <si>
+    <t>Monster Pet Evolution</t>
+  </si>
+  <si>
+    <t>The Strongest Sect Of All Times</t>
+  </si>
+  <si>
+    <t>Youngest Scion Of The Mages</t>
+  </si>
+  <si>
+    <t>I Will Do Whatever I Want In Ten Thousand Years</t>
+  </si>
+  <si>
+    <t>Genkai Level 1 Kara No Nariagari: Saijaku Level No Ore Ga Isekai Saikyou Ni Naru Made</t>
+  </si>
+  <si>
+    <t>How to Live at the Max Level</t>
+  </si>
+  <si>
+    <t>The All-Knowing Cultivator</t>
+  </si>
+  <si>
+    <t>Kurasu ≪Mushoku≫ No Eiyuu-Tan ~Koushaku-Ka O Tsuihou Sareta Ga, Jitsu Wa Nagutta Dake De Sukiru O Kakutoku Dekiru To Wakari, Tairiku Ichi No Eiyuu Ni Nobori Tsumeru</t>
+  </si>
+  <si>
+    <t>Villager A Wants To Save The Villainess No Matter What!</t>
+  </si>
+  <si>
+    <t>Savage Hero</t>
+  </si>
+  <si>
+    <t>Genkai Koe No Tenpu wa, Tensei-sha ni Shika Atsukaenai Overlimit Skill Holders</t>
+  </si>
+  <si>
+    <t>Maken Tsukai No Moto Shounen Hei Wa, Moto Teki Kanbu No Onee-San To Issho Ni Ikitai</t>
+  </si>
+  <si>
+    <t>Mannen D-Rank No Chuunen Boukensha, Yotta Ikioi De Densetsu No Ken Wo Hikkonuku</t>
+  </si>
+  <si>
+    <t>Dungeon Sherpa: Meikyuu Michisaki Annainin</t>
+  </si>
+  <si>
+    <t>A Sword Master Childhood Friend Power Harassed Me Harshly, So I Broke Off Our Relationship And Made A Fresh Start At The Frontier As A Magic Swordsman</t>
+  </si>
+  <si>
+    <t>I Summoned The Devil To Grant Me A Wish, But I Married Her Instead Since She Was Adorable ~My New Devil Wife~</t>
+  </si>
+  <si>
+    <t>A Story About A Dragon And The Rising Of An Adventurer</t>
+  </si>
+  <si>
+    <t>After Being Called A Hero: The Unrivaled Man Starts A Family</t>
+  </si>
+  <si>
+    <t>A Warrior Exiled By The Hero And His Lover</t>
+  </si>
+  <si>
+    <t>Nimotsu Mochi No Nousuji Musou</t>
+  </si>
+  <si>
+    <t>The Strongest Dull Prince’s Secret Battle for the Throne</t>
+  </si>
+  <si>
+    <t>The Sword of Princess Gluttony</t>
+  </si>
+  <si>
+    <t>Wistoria's Wand And Sword</t>
+  </si>
+  <si>
+    <t>The Crafty Mage: Frontier Settling Made Easy</t>
+  </si>
+  <si>
+    <t>Delivery Man From Murim</t>
+  </si>
+  <si>
+    <t>Henkyou Gurashi No Maou, Tensei Shite Saikyou No Majutsushi Ni Naru</t>
+  </si>
+  <si>
+    <t>The Executed Sage Is Reincarnated As A Lich And Starts An All-Out War</t>
+  </si>
+  <si>
+    <t>Dungeon Ni Hisomu Yandere Na Kanojo Ni Ore Wa Nando Mo Korosareru</t>
+  </si>
+  <si>
+    <t>I Became A Big-Shot On The Heavenly Leaderboard</t>
+  </si>
+  <si>
+    <t>The Dark Magician Transmigrates After 66666 Years</t>
+  </si>
+  <si>
+    <t>Reaper Of The Drifting Moon</t>
+  </si>
+  <si>
+    <t>The Unbeatable Dungeon's Lazy Boss Monster</t>
+  </si>
+  <si>
+    <t>All My Abilities Are Forbidden Spells</t>
+  </si>
+  <si>
+    <t>How To Survive As A Dragon With Time-Limit</t>
+  </si>
+  <si>
+    <t>Myst, Might, Mayhem</t>
+  </si>
+  <si>
+    <t>Dark And Light Martial Emperor</t>
+  </si>
+  <si>
+    <t>The doomsday ruthless man: hoarding trillions of supplies at the beginning</t>
+  </si>
+  <si>
+    <t>Becoming the Swordmaster Rank Young Lord of the Sichuan Tang Family</t>
+  </si>
+  <si>
+    <t>This Account Is Ridiculous</t>
+  </si>
+  <si>
+    <t>The Mysterious World’s Greatest Martial Artist Little Prince</t>
+  </si>
+  <si>
+    <t>The Reborn Young Lord Is An Assassin</t>
+  </si>
+  <si>
+    <t>God-Slaying Copycat</t>
+  </si>
+  <si>
+    <t>The Great Mage Of The Hero’S Party Reincarnates</t>
+  </si>
+  <si>
+    <t>My Brother Is The Chosen One</t>
+  </si>
+  <si>
+    <t>The Max Level Hero Strikes Back</t>
+  </si>
+  <si>
+    <t>Overlord of Insects</t>
+  </si>
+  <si>
+    <t>Game Of Familia: Kazoku Senki</t>
+  </si>
+  <si>
+    <t>Grand General</t>
+  </si>
+  <si>
+    <t>The Legendary Spearman Returns</t>
+  </si>
+  <si>
+    <t>Ice lord</t>
+  </si>
+  <si>
+    <t>My Inventory is Abnormal</t>
+  </si>
+  <si>
+    <t>Escort Agency Of The Apocalypse</t>
+  </si>
+  <si>
+    <t>The Heavenly Demon Will Give You a Massage</t>
+  </si>
+  <si>
+    <t>The Twin Swords Of The Sima</t>
+  </si>
+  <si>
+    <t>Versatile Sword Cultivator</t>
+  </si>
+  <si>
+    <t>Asura</t>
+  </si>
+  <si>
+    <t>Magic Academy’s Genius Blinker</t>
+  </si>
+  <si>
+    <t>Worthless Profession: Dragon Tamer</t>
+  </si>
+  <si>
+    <t>Expelled Hero Is Too Strong</t>
+  </si>
+  <si>
+    <t>The Ten Thousand Clans Invasion: Guardian Of The Rear</t>
+  </si>
+  <si>
+    <t>My Disciple Became the Great Demon Empress?!</t>
+  </si>
+  <si>
+    <t>The Greatest In The World</t>
+  </si>
+  <si>
+    <t>Drawing: The Greatest Mangaka Becomes A Skilled “Martial Artist” In Another World</t>
   </si>
   <si>
     <r>
@@ -547,7 +552,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">～</t>
+      <t>～</t>
     </r>
     <r>
       <rPr>
@@ -557,690 +562,687 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">I Returned To The Past To Rewrite It As The World's Strongest</t>
+      <t>I Returned To The Past To Rewrite It As The World's Strongest</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Hundreds of Invincible Strikes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">arctic cold war</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apocalyptic Super Farm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sword Sheath's Child</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reincarnator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hunter Academy’S Strongest Battle God</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Childhood Friend of the Zenith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Absolute Regression</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warrior Grandpa And Supreme Granddaughter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Scared the Divine Lord as I Handed over the Ancient Immortal Pill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Become a Legendary Arch Mage by Reading a Book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hiding a logistics center in the apocalypse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Hated Black Mage Returns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Masters Are Subscribing To Me</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Ranker's Guide To The Good Life</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black Serpent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conquering the Academy with Just a Sashimi Knife</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Magic Genius Of The Marquis House</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Reversal Of My Life As A Side Character</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Absolute Dominion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fatal Reset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Necromancer Family’s Young Heir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Starting As A Master Of Female Disciples' Leisure Skills</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Song Baek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surviving as a Genius on Borrowed Time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Regressed Mercenary’s Machinations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Traveling Through Time And Space To Become An Unlucky Npc: I Have A Wife To Protect Me</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cultivation: The Heaven's Fated Useless Genius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Edgeless Sword From The Village</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Levelling Up In An Exclusive Dungeon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reincarnated As A Genius Prodigy Of A Prestigious Family</t>
-  </si>
-  <si>
-    <t xml:space="preserve">From Goblin To Goblin God</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Margrave’S Bastard Son Was The Emperor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Second Eunuch Regains His Manhood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return Of The Runebound Professor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regressing as the Reincarnated Bastard of the Sword Clan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I, The Demon Lord, Am Being Targeted By My Female Disciples!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fated to Be Loved by Villains</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Chaebeol’s Youngest Son</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heavenly Demon Wants To Be A Chef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entomologist In Sichuan Tang Clan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Last Word of the World</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cosmic Heavenly Demon 3077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solo Resurrection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dao of the Bizarre Immortal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tenkaichi: Nihon Saikyou Bugeisha Ketteisen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reincarnation Of The Heavenly Demon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black Corporation: Joseon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perhaps Invincible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The mad gate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surviving the Apocalypse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genius Prismatic Mage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Becoming a God, Starting as water monkey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Became the Successor of the Martial God</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regression of the Yong Clan Heir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chronicles of the Reincarnated Demon God</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenge Of the Bloom Flower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Heavenly Demon Wants a Quiet Life</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster General Recorded Legacy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Using My Cooking Skills in a Murim World</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I’m a Martial Art Villainess, but I’m the Strongest!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metcha Shoukan Sareta Ken</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mount Hua Sect's Genius Phantom Swordsman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I'm going to destroy this country</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The New Beggars' Sect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overgeared</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regressed life of the Sword Clan’s Ignoble Reincarnator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black Fox: Sword Master Of Mount Kunlun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">God-level Assassin, I’m the Shadow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">War Of The Corpses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Illegitimate Who Devours Weapons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Great Sage of the Namgung Clan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limitless Ascension: Strength Amid Adversity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apocalypse: Cockroaches Gives Me Buff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Legendary Hero is an Academy Honors Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Like a Fiery Flame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Magic Tower's Problem Child</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Became the Husband of the Cult Leader of the Demonic Sect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Apocalypse is Here</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If I Don’t Die Soon, I Will Rule The Demon Realm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Will Raise This Family to Greatness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Villain Wants to Live</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genius Archer’s Livestreaming</t>
-  </si>
-  <si>
-    <t xml:space="preserve">After Ten Millennia in Hell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heavenly Grand Archive's Young Master</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Space Cheon-ma 3077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iljin Romance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shut Up, Evil Dragon! I Don't Want to Raise a Child With You Anymore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On the Way to Meet Mom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ultimate Shut-in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The beginning after the end</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reborn in a Cyber Cultivation World, I Fight My Way to the Top</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Level 999 Goblin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dominating the Wasteland: I Control an Immortal Sect in the Apocalypse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Starting As The God Of Wealth, Taming Billions Of Divine Pets!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martial Evolution: Start by Awakening the King of Monsters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Girl from Random Chatting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return of the Legend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elven Queen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emperor of Solo Play</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Fox-Eyed Villain of the Demon Academy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Awakening Contract</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Sword God From a Fallen World</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Awakened to the Ex Skill "Fixed Damage" and Became Invincible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warrior of the Mind Sword</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ninja Reincarnation: Fuuma Kotarou’s Quest to Reclaim His Humanity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empress Maria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reincarnation of the Fist King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">There Are No Bad Warriors in the World</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return From The Depth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return of the Apocalypse-Class Death Knight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oversummoned, Overpowered, and Over It!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Rogue Guard in a Medieval Fantasy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chronicles of the Lazy Sovereign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Was the Final Boss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Tang Clan Chronicles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Demon-Slaying Madman—reborn as a demon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Urek Mazino</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demonic Sect Frontline: Thirteen Flying Dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Goddess of Abundance and the Genius Rogue Apostle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Goguryeo Chronicles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devil Summoner, I am the Abyss Lord</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legend of Dangun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Tale of the Skeleton Messenger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Great Heavenly Demon Sovereign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Regressor's Tale of Cultivation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jade of the Eight Gates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disciple of the Three Kings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">After the School Belle Dumped Me, I Became a Martial Arts God</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dead Mansion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return of the King of Hell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plaything</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Regressor Protects Only Me</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full-Time Awakening</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rebirth of the Divine Demon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return of the First Patriarch: The Strongest Reincarnates into His Descendant 1000 Years Later</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lv. 99 Princess of Black Flame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Battle of the Martial Masters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Yellow-haired Villain in Female Main Character's Novel wants Happiness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">From Six to Sovereignty: The Girl Who Ruled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eat and Go</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Shall Seal the Heavens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Executed Sage Who Was Reincarnated as a Lich and Started an All-Out War</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demon Instructor's Return</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Archduke's Bride Is a Hell Warrior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solo Leveling: Ragnarok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Became a Patron of Villains</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black Crow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Marquis Is the Marital Archduke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dukedom's Legendary Prodigy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reincarnated as the Crazed Heir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lord of the Apocalypse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Don't Tell Me You Think Cultivating Immortality Is Difficult?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immortal Fairy, Please Listen to My Explanation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maplestory: The Last Adventurer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Steel Emperor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Luoyang Branch of the Heavenly Demon Cult</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spirit Hunter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Player of the Fallen Family</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unrivaled Spear Ghost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reincarnation of the Martial God</t>
-  </si>
-  <si>
-    <t xml:space="preserve">After Rebirth, I Used Mirror Reversal For Vengeance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Death Attribute Magician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Great Emperor Shinmadae</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenger: Apocalypse of Vengeance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hiding Out in an Apocalypse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bad Born Blood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KaguRai: Kagura to Raito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reincarnated as the Lazy and Villainous Noble, I Broke the Scenario and Became the Most Formidable With Extraordinary Magic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Star Armor꞉ I’ll Slaughter Through the Chaos with Star Soul Generals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Demon King Overrun by Heroes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Monkey King’s Journey to the Murim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Sage who returned from another world wants to live quietly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Returned from Another World, Earth Turned Out to Be Quite the Fantasy Too. Also, Losing Heroines, Stop Looking This Way</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Embodiment of the Assassin in the Murim World</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Märchen - The Embodiment of Tales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sichuan’s Supreme King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Cold-Blooded Warrior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Everyone Loves Her</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paper Tiger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Sword-Eating Swordmaster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The World's Best Kunlun Tavern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Defense Breaker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Worlds Best Assassin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The World's Best Martial Arts Instructor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How a Realist Hero Rebuilt the Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sleepy Princess in the Demon Castle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To Hell With The Status Window</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Becoming a Cheat-Level Skill Thief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sichuan's Supreme King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reborn After the Eight Empresses Betrayed Me, Now I’ll Make Them Regret It</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rebirth of the Demon Lord: the Slave who Conquered Fate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Strongest Wizard Becomes a Countryside Guard After Taking an Arrow to the Knee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Secret Martial Artist of Demonic Blood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Strongest Hero Who Longs For Revenge Will Peerlessly Annihilate With The Power Of Darkness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Became the Scoundrel of the Cheon Family</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supreme Demon of Hyungsan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orc Hero Story - Discovery Chronicles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boukun Meika no Hangyakusha -Aster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jakdu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secretly Cultivating by the Demon Cult Leader's Side</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Old Prisoner Lives in Solitude</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenge of Young Master Peng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Murim’s Dept King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My Girlfriend's Friend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teto X Egen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gokusotsu Kraken</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Masters of Heaven and Earth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Red Storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Dragon Lives in Kunlun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Friend of the Demon King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High Martial Arts: Sweeping Through Three Thousand Emperors with One Hand!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Genius Martial Artist Who Remembers Everything</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Shepherd Wizard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sovereign of a Hundred Blades: Heir to the Strongest Style</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shadow Slave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Tale of Cultivation and Demon Extermination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Former Supreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What a Bountiful Harvest, Demon Lord!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Sword Emperor’s Rise of Namgung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Kidnapped the Youngest Daughter of the Sichuan Tang Clan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">War of Extinction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Divine Demon’s Grand Ascension</t>
+    <t>Hundreds of Invincible Strikes</t>
+  </si>
+  <si>
+    <t>arctic cold war</t>
+  </si>
+  <si>
+    <t>Apocalyptic Super Farm</t>
+  </si>
+  <si>
+    <t>Sword Sheath's Child</t>
+  </si>
+  <si>
+    <t>Reincarnator</t>
+  </si>
+  <si>
+    <t>Hunter Academy’S Strongest Battle God</t>
+  </si>
+  <si>
+    <t>Childhood Friend of the Zenith</t>
+  </si>
+  <si>
+    <t>Absolute Regression</t>
+  </si>
+  <si>
+    <t>Warrior Grandpa And Supreme Granddaughter</t>
+  </si>
+  <si>
+    <t>I Scared the Divine Lord as I Handed over the Ancient Immortal Pill</t>
+  </si>
+  <si>
+    <t>I Become a Legendary Arch Mage by Reading a Book</t>
+  </si>
+  <si>
+    <t>Hiding a logistics center in the apocalypse</t>
+  </si>
+  <si>
+    <t>The Hated Black Mage Returns</t>
+  </si>
+  <si>
+    <t>The Masters Are Subscribing To Me</t>
+  </si>
+  <si>
+    <t>A Ranker's Guide To The Good Life</t>
+  </si>
+  <si>
+    <t>Black Serpent</t>
+  </si>
+  <si>
+    <t>Conquering the Academy with Just a Sashimi Knife</t>
+  </si>
+  <si>
+    <t>The Magic Genius Of The Marquis House</t>
+  </si>
+  <si>
+    <t>The Reversal Of My Life As A Side Character</t>
+  </si>
+  <si>
+    <t>Absolute Dominion</t>
+  </si>
+  <si>
+    <t>Fatal Reset</t>
+  </si>
+  <si>
+    <t>The Necromancer Family’s Young Heir</t>
+  </si>
+  <si>
+    <t>Starting As A Master Of Female Disciples' Leisure Skills</t>
+  </si>
+  <si>
+    <t>Song Baek</t>
+  </si>
+  <si>
+    <t>Surviving as a Genius on Borrowed Time</t>
+  </si>
+  <si>
+    <t>The Regressed Mercenary’s Machinations</t>
+  </si>
+  <si>
+    <t>Traveling Through Time And Space To Become An Unlucky Npc: I Have A Wife To Protect Me</t>
+  </si>
+  <si>
+    <t>Cultivation: The Heaven's Fated Useless Genius</t>
+  </si>
+  <si>
+    <t>The Edgeless Sword From The Village</t>
+  </si>
+  <si>
+    <t>Levelling Up In An Exclusive Dungeon</t>
+  </si>
+  <si>
+    <t>Reincarnated As A Genius Prodigy Of A Prestigious Family</t>
+  </si>
+  <si>
+    <t>From Goblin To Goblin God</t>
+  </si>
+  <si>
+    <t>Margrave’S Bastard Son Was The Emperor</t>
+  </si>
+  <si>
+    <t>The Second Eunuch Regains His Manhood</t>
+  </si>
+  <si>
+    <t>Return Of The Runebound Professor</t>
+  </si>
+  <si>
+    <t>Regressing as the Reincarnated Bastard of the Sword Clan</t>
+  </si>
+  <si>
+    <t>I, The Demon Lord, Am Being Targeted By My Female Disciples!</t>
+  </si>
+  <si>
+    <t>Fated to Be Loved by Villains</t>
+  </si>
+  <si>
+    <t>The Chaebeol’s Youngest Son</t>
+  </si>
+  <si>
+    <t>Heavenly Demon Wants To Be A Chef</t>
+  </si>
+  <si>
+    <t>Entomologist In Sichuan Tang Clan</t>
+  </si>
+  <si>
+    <t>Last Word of the World</t>
+  </si>
+  <si>
+    <t>Cosmic Heavenly Demon 3077</t>
+  </si>
+  <si>
+    <t>Solo Resurrection</t>
+  </si>
+  <si>
+    <t>Dao of the Bizarre Immortal</t>
+  </si>
+  <si>
+    <t>Tenkaichi: Nihon Saikyou Bugeisha Ketteisen</t>
+  </si>
+  <si>
+    <t>Reincarnation Of The Heavenly Demon</t>
+  </si>
+  <si>
+    <t>Black Corporation: Joseon</t>
+  </si>
+  <si>
+    <t>Perhaps Invincible</t>
+  </si>
+  <si>
+    <t>The mad gate</t>
+  </si>
+  <si>
+    <t>Surviving the Apocalypse</t>
+  </si>
+  <si>
+    <t>Genius Prismatic Mage</t>
+  </si>
+  <si>
+    <t>Becoming a God, Starting as water monkey</t>
+  </si>
+  <si>
+    <t>I Became the Successor of the Martial God</t>
+  </si>
+  <si>
+    <t>Regression of the Yong Clan Heir</t>
+  </si>
+  <si>
+    <t>Chronicles of the Reincarnated Demon God</t>
+  </si>
+  <si>
+    <t>Revenge Of the Bloom Flower</t>
+  </si>
+  <si>
+    <t>The Heavenly Demon Wants a Quiet Life</t>
+  </si>
+  <si>
+    <t>Monster General Recorded Legacy</t>
+  </si>
+  <si>
+    <t>Using My Cooking Skills in a Murim World</t>
+  </si>
+  <si>
+    <t>I’m a Martial Art Villainess, but I’m the Strongest!</t>
+  </si>
+  <si>
+    <t>Metcha Shoukan Sareta Ken</t>
+  </si>
+  <si>
+    <t>Mount Hua Sect's Genius Phantom Swordsman</t>
+  </si>
+  <si>
+    <t>I'm going to destroy this country</t>
+  </si>
+  <si>
+    <t>The New Beggars' Sect</t>
+  </si>
+  <si>
+    <t>Overgeared</t>
+  </si>
+  <si>
+    <t>Regressed life of the Sword Clan’s Ignoble Reincarnator</t>
+  </si>
+  <si>
+    <t>Black Fox: Sword Master Of Mount Kunlun</t>
+  </si>
+  <si>
+    <t>God-level Assassin, I’m the Shadow</t>
+  </si>
+  <si>
+    <t>War Of The Corpses</t>
+  </si>
+  <si>
+    <t>The Illegitimate Who Devours Weapons</t>
+  </si>
+  <si>
+    <t>The Great Sage of the Namgung Clan</t>
+  </si>
+  <si>
+    <t>Limitless Ascension: Strength Amid Adversity</t>
+  </si>
+  <si>
+    <t>Apocalypse: Cockroaches Gives Me Buff</t>
+  </si>
+  <si>
+    <t>The Legendary Hero is an Academy Honors Student</t>
+  </si>
+  <si>
+    <t>Like a Fiery Flame</t>
+  </si>
+  <si>
+    <t>The Magic Tower's Problem Child</t>
+  </si>
+  <si>
+    <t>I Became the Husband of the Cult Leader of the Demonic Sect</t>
+  </si>
+  <si>
+    <t>The Apocalypse is Here</t>
+  </si>
+  <si>
+    <t>If I Don’t Die Soon, I Will Rule The Demon Realm</t>
+  </si>
+  <si>
+    <t>I Will Raise This Family to Greatness</t>
+  </si>
+  <si>
+    <t>The Villain Wants to Live</t>
+  </si>
+  <si>
+    <t>Genius Archer’s Livestreaming</t>
+  </si>
+  <si>
+    <t>After Ten Millennia in Hell</t>
+  </si>
+  <si>
+    <t>Heavenly Grand Archive's Young Master</t>
+  </si>
+  <si>
+    <t>Space Cheon-ma 3077</t>
+  </si>
+  <si>
+    <t>Iljin Romance</t>
+  </si>
+  <si>
+    <t>Shut Up, Evil Dragon! I Don't Want to Raise a Child With You Anymore</t>
+  </si>
+  <si>
+    <t>On the Way to Meet Mom</t>
+  </si>
+  <si>
+    <t>Ultimate Shut-in</t>
+  </si>
+  <si>
+    <t>The beginning after the end</t>
+  </si>
+  <si>
+    <t>Reborn in a Cyber Cultivation World, I Fight My Way to the Top</t>
+  </si>
+  <si>
+    <t>Level 999 Goblin</t>
+  </si>
+  <si>
+    <t>Dominating the Wasteland: I Control an Immortal Sect in the Apocalypse</t>
+  </si>
+  <si>
+    <t>Starting As The God Of Wealth, Taming Billions Of Divine Pets!</t>
+  </si>
+  <si>
+    <t>Martial Evolution: Start by Awakening the King of Monsters</t>
+  </si>
+  <si>
+    <t>The Girl from Random Chatting</t>
+  </si>
+  <si>
+    <t>Return of the Legend</t>
+  </si>
+  <si>
+    <t>Elven Queen</t>
+  </si>
+  <si>
+    <t>Emperor of Solo Play</t>
+  </si>
+  <si>
+    <t>The Fox-Eyed Villain of the Demon Academy</t>
+  </si>
+  <si>
+    <t>The Awakening Contract</t>
+  </si>
+  <si>
+    <t>The Sword God From a Fallen World</t>
+  </si>
+  <si>
+    <t>I Awakened to the Ex Skill "Fixed Damage" and Became Invincible</t>
+  </si>
+  <si>
+    <t>Warrior of the Mind Sword</t>
+  </si>
+  <si>
+    <t>Ninja Reincarnation: Fuuma Kotarou’s Quest to Reclaim His Humanity</t>
+  </si>
+  <si>
+    <t>Empress Maria</t>
+  </si>
+  <si>
+    <t>Reincarnation of the Fist King</t>
+  </si>
+  <si>
+    <t>There Are No Bad Warriors in the World</t>
+  </si>
+  <si>
+    <t>Return From The Depth</t>
+  </si>
+  <si>
+    <t>Return of the Apocalypse-Class Death Knight</t>
+  </si>
+  <si>
+    <t>Oversummoned, Overpowered, and Over It!</t>
+  </si>
+  <si>
+    <t>A Rogue Guard in a Medieval Fantasy</t>
+  </si>
+  <si>
+    <t>Chronicles of the Lazy Sovereign</t>
+  </si>
+  <si>
+    <t>I Was the Final Boss</t>
+  </si>
+  <si>
+    <t>The Tang Clan Chronicles</t>
+  </si>
+  <si>
+    <t>The Demon-Slaying Madman—reborn as a demon</t>
+  </si>
+  <si>
+    <t>Urek Mazino</t>
+  </si>
+  <si>
+    <t>Demonic Sect Frontline: Thirteen Flying Dragons</t>
+  </si>
+  <si>
+    <t>Goddess of Abundance and the Genius Rogue Apostle</t>
+  </si>
+  <si>
+    <t>New Goguryeo Chronicles</t>
+  </si>
+  <si>
+    <t>Devil Summoner, I am the Abyss Lord</t>
+  </si>
+  <si>
+    <t>Legend of Dangun</t>
+  </si>
+  <si>
+    <t>The Tale of the Skeleton Messenger</t>
+  </si>
+  <si>
+    <t>The Great Heavenly Demon Sovereign</t>
+  </si>
+  <si>
+    <t>A Regressor's Tale of Cultivation</t>
+  </si>
+  <si>
+    <t>Jade of the Eight Gates</t>
+  </si>
+  <si>
+    <t>Disciple of the Three Kings</t>
+  </si>
+  <si>
+    <t>After the School Belle Dumped Me, I Became a Martial Arts God</t>
+  </si>
+  <si>
+    <t>Dead Mansion</t>
+  </si>
+  <si>
+    <t>Return of the King of Hell</t>
+  </si>
+  <si>
+    <t>Plaything</t>
+  </si>
+  <si>
+    <t>The Regressor Protects Only Me</t>
+  </si>
+  <si>
+    <t>Full-Time Awakening</t>
+  </si>
+  <si>
+    <t>Rebirth of the Divine Demon</t>
+  </si>
+  <si>
+    <t>Return of the First Patriarch: The Strongest Reincarnates into His Descendant 1000 Years Later</t>
+  </si>
+  <si>
+    <t>Lv. 99 Princess of Black Flame</t>
+  </si>
+  <si>
+    <t>Battle of the Martial Masters</t>
+  </si>
+  <si>
+    <t>The Yellow-haired Villain in Female Main Character's Novel wants Happiness</t>
+  </si>
+  <si>
+    <t>From Six to Sovereignty: The Girl Who Ruled</t>
+  </si>
+  <si>
+    <t>Eat and Go</t>
+  </si>
+  <si>
+    <t>I Shall Seal the Heavens</t>
+  </si>
+  <si>
+    <t>The Executed Sage Who Was Reincarnated as a Lich and Started an All-Out War</t>
+  </si>
+  <si>
+    <t>Demon Instructor's Return</t>
+  </si>
+  <si>
+    <t>The Archduke's Bride Is a Hell Warrior</t>
+  </si>
+  <si>
+    <t>Solo Leveling: Ragnarok</t>
+  </si>
+  <si>
+    <t>I Became a Patron of Villains</t>
+  </si>
+  <si>
+    <t>Black Crow</t>
+  </si>
+  <si>
+    <t>The Marquis Is the Marital Archduke</t>
+  </si>
+  <si>
+    <t>Dukedom's Legendary Prodigy</t>
+  </si>
+  <si>
+    <t>Reincarnated as the Crazed Heir</t>
+  </si>
+  <si>
+    <t>Lord of the Apocalypse</t>
+  </si>
+  <si>
+    <t>Don't Tell Me You Think Cultivating Immortality Is Difficult?</t>
+  </si>
+  <si>
+    <t>Immortal Fairy, Please Listen to My Explanation</t>
+  </si>
+  <si>
+    <t>Maplestory: The Last Adventurer</t>
+  </si>
+  <si>
+    <t>The Steel Emperor</t>
+  </si>
+  <si>
+    <t>The Luoyang Branch of the Heavenly Demon Cult</t>
+  </si>
+  <si>
+    <t>Spirit Hunter</t>
+  </si>
+  <si>
+    <t>Player of the Fallen Family</t>
+  </si>
+  <si>
+    <t>Unrivaled Spear Ghost</t>
+  </si>
+  <si>
+    <t>Reincarnation of the Martial God</t>
+  </si>
+  <si>
+    <t>After Rebirth, I Used Mirror Reversal For Vengeance</t>
+  </si>
+  <si>
+    <t>Death Attribute Magician</t>
+  </si>
+  <si>
+    <t>The Great Emperor Shinmadae</t>
+  </si>
+  <si>
+    <t>Revenger: Apocalypse of Vengeance</t>
+  </si>
+  <si>
+    <t>Hiding Out in an Apocalypse</t>
+  </si>
+  <si>
+    <t>Bad Born Blood</t>
+  </si>
+  <si>
+    <t>KaguRai: Kagura to Raito</t>
+  </si>
+  <si>
+    <t>Reincarnated as the Lazy and Villainous Noble, I Broke the Scenario and Became the Most Formidable With Extraordinary Magic</t>
+  </si>
+  <si>
+    <t>Star Armor꞉ I’ll Slaughter Through the Chaos with Star Soul Generals</t>
+  </si>
+  <si>
+    <t>The Demon King Overrun by Heroes</t>
+  </si>
+  <si>
+    <t>The Monkey King’s Journey to the Murim</t>
+  </si>
+  <si>
+    <t>The Sage who returned from another world wants to live quietly</t>
+  </si>
+  <si>
+    <t>Returned from Another World, Earth Turned Out to Be Quite the Fantasy Too. Also, Losing Heroines, Stop Looking This Way</t>
+  </si>
+  <si>
+    <t>Embodiment of the Assassin in the Murim World</t>
+  </si>
+  <si>
+    <t>Märchen - The Embodiment of Tales</t>
+  </si>
+  <si>
+    <t>Sichuan’s Supreme King</t>
+  </si>
+  <si>
+    <t>The Cold-Blooded Warrior</t>
+  </si>
+  <si>
+    <t>Everyone Loves Her</t>
+  </si>
+  <si>
+    <t>Paper Tiger</t>
+  </si>
+  <si>
+    <t>The Sword-Eating Swordmaster</t>
+  </si>
+  <si>
+    <t>The World's Best Kunlun Tavern</t>
+  </si>
+  <si>
+    <t>Defense Breaker</t>
+  </si>
+  <si>
+    <t>Worlds Best Assassin</t>
+  </si>
+  <si>
+    <t>The World's Best Martial Arts Instructor</t>
+  </si>
+  <si>
+    <t>How a Realist Hero Rebuilt the Kingdom</t>
+  </si>
+  <si>
+    <t>Sleepy Princess in the Demon Castle</t>
+  </si>
+  <si>
+    <t>To Hell With The Status Window</t>
+  </si>
+  <si>
+    <t>Becoming a Cheat-Level Skill Thief</t>
+  </si>
+  <si>
+    <t>Sichuan's Supreme King</t>
+  </si>
+  <si>
+    <t>Reborn After the Eight Empresses Betrayed Me, Now I’ll Make Them Regret It</t>
+  </si>
+  <si>
+    <t>Rebirth of the Demon Lord: the Slave who Conquered Fate</t>
+  </si>
+  <si>
+    <t>The Strongest Wizard Becomes a Countryside Guard After Taking an Arrow to the Knee</t>
+  </si>
+  <si>
+    <t>The Secret Martial Artist of Demonic Blood</t>
+  </si>
+  <si>
+    <t>The Strongest Hero Who Longs For Revenge Will Peerlessly Annihilate With The Power Of Darkness</t>
+  </si>
+  <si>
+    <t>I Became the Scoundrel of the Cheon Family</t>
+  </si>
+  <si>
+    <t>Supreme Demon of Hyungsan</t>
+  </si>
+  <si>
+    <t>Orc Hero Story - Discovery Chronicles</t>
+  </si>
+  <si>
+    <t>Boukun Meika no Hangyakusha -Aster</t>
+  </si>
+  <si>
+    <t>Jakdu</t>
+  </si>
+  <si>
+    <t>Secretly Cultivating by the Demon Cult Leader's Side</t>
+  </si>
+  <si>
+    <t>The Old Prisoner Lives in Solitude</t>
+  </si>
+  <si>
+    <t>Revenge of Young Master Peng</t>
+  </si>
+  <si>
+    <t>Murim’s Dept King</t>
+  </si>
+  <si>
+    <t>My Girlfriend's Friend</t>
+  </si>
+  <si>
+    <t>Teto X Egen</t>
+  </si>
+  <si>
+    <t>Gokusotsu Kraken</t>
+  </si>
+  <si>
+    <t>The Masters of Heaven and Earth</t>
+  </si>
+  <si>
+    <t>Red Storm</t>
+  </si>
+  <si>
+    <t>A Dragon Lives in Kunlun</t>
+  </si>
+  <si>
+    <t>Friend of the Demon King</t>
+  </si>
+  <si>
+    <t>High Martial Arts: Sweeping Through Three Thousand Emperors with One Hand!</t>
+  </si>
+  <si>
+    <t>The Genius Martial Artist Who Remembers Everything</t>
+  </si>
+  <si>
+    <t>The Shepherd Wizard</t>
+  </si>
+  <si>
+    <t>Sovereign of a Hundred Blades: Heir to the Strongest Style</t>
+  </si>
+  <si>
+    <t>Shadow Slave</t>
+  </si>
+  <si>
+    <t>The Tale of Cultivation and Demon Extermination</t>
+  </si>
+  <si>
+    <t>The Former Supreme</t>
+  </si>
+  <si>
+    <t>What a Bountiful Harvest, Demon Lord!</t>
+  </si>
+  <si>
+    <t>sa</t>
+  </si>
+  <si>
+    <t>The Sword Emperor’s Rise of Namgung</t>
+  </si>
+  <si>
+    <t>I Kidnapped the Youngest Daughter of the Sichuan Tang Clan</t>
+  </si>
+  <si>
+    <t>War of Extinction</t>
+  </si>
+  <si>
+    <t>The Divine Demon’s Grand Ascension</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1249,22 +1251,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Nimbus Sans"/>
@@ -1313,14 +1300,14 @@
     </fill>
   </fills>
   <borders count="3">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFD9D9D9"/>
       </left>
@@ -1333,7 +1320,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFD9D9D9"/>
       </left>
@@ -1349,126 +1336,47 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF4F81BD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEAF2F8"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1527,57 +1435,74 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:B389" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:B389"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:B389" totalsRowShown="0">
+  <autoFilter ref="A1:B389" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="2">
-    <tableColumn id="1" name="Title"/>
-    <tableColumn id="2" name="Episodes"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Title"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Episodes"/>
   </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1585,12 +1510,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1619,7 +1544,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1640,7 +1565,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1691,7 +1616,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1709,27 +1634,26 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B393"/>
-  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="169"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.43"/>
+    <col min="1" max="1" width="169" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:2" ht="15.75">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1737,3103 +1661,3103 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="4">
         <v>878</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:2">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="6">
         <v>266</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="4">
         <v>38</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:2">
       <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="6">
         <v>51</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:2">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="4">
         <v>31</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:2">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="6">
         <v>135</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:2">
       <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:2">
       <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:2">
       <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="4">
         <v>292</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:2">
       <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="6">
         <v>25</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:2">
       <c r="A12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="4">
         <v>39</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:2">
       <c r="A13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="6">
         <v>25</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:2">
       <c r="A14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="4">
         <v>116</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:2">
       <c r="A15" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:2">
       <c r="A16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="4">
         <v>73</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:2">
       <c r="A17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="6">
         <v>223</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:2">
       <c r="A18" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="4">
         <v>162</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:2">
       <c r="A19" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="6">
         <v>102</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:2">
       <c r="A20" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" s="4">
         <v>117</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:2">
       <c r="A21" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="6">
         <v>85</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:2">
       <c r="A22" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="4">
         <v>182</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:2">
       <c r="A23" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="6">
         <v>175</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:2">
       <c r="A24" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="4" t="n">
+      <c r="B24" s="4">
         <v>50</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:2">
       <c r="A25" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="6">
         <v>31</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:2">
       <c r="A26" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="4" t="n">
+      <c r="B26" s="4">
         <v>10.1</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:2">
       <c r="A27" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:2">
       <c r="A28" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="4" t="n">
+      <c r="B28" s="4">
         <v>19</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:2">
       <c r="A29" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="6">
         <v>54</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:2">
       <c r="A30" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="4" t="n">
+      <c r="B30" s="4">
         <v>105</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:2">
       <c r="A31" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="6">
         <v>77</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:2">
       <c r="A32" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="4" t="n">
+      <c r="B32" s="4">
         <v>37</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:2">
       <c r="A33" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="6">
         <v>88</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:2">
       <c r="A34" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="4" t="n">
+      <c r="B34" s="4">
         <v>99</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:2">
       <c r="A35" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="6">
         <v>157</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:2">
       <c r="A36" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="4" t="n">
+      <c r="B36" s="4">
         <v>39</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:2">
       <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="6">
         <v>51</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:2">
       <c r="A38" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="4" t="n">
+      <c r="B38" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:2">
       <c r="A39" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:2">
       <c r="A40" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="4" t="n">
+      <c r="B40" s="4">
         <v>124</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:2">
       <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="6">
         <v>111</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:2">
       <c r="A42" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="4" t="n">
+      <c r="B42" s="4">
         <v>63</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:2">
       <c r="A43" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="6">
         <v>45</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:2">
       <c r="A44" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B44" s="4" t="n">
+      <c r="B44" s="4">
         <v>162</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" spans="1:2">
       <c r="A45" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B45" s="6">
         <v>64</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:2">
       <c r="A46" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B46" s="4" t="n">
+      <c r="B46" s="4">
         <v>140</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" spans="1:2">
       <c r="A47" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B47" s="6">
         <v>168</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" spans="1:2">
       <c r="A48" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="4" t="n">
+      <c r="B48" s="4">
         <v>186</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" spans="1:2">
       <c r="A49" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B49" s="6" t="n">
+      <c r="B49" s="6">
         <v>12</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" spans="1:2">
       <c r="A50" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B50" s="4" t="n">
+      <c r="B50" s="4">
         <v>21</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" spans="1:2">
       <c r="A51" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B51" s="6" t="n">
+      <c r="B51" s="6">
         <v>37</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" spans="1:2">
       <c r="A52" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B52" s="4" t="n">
+      <c r="B52" s="4">
         <v>71</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" spans="1:2">
       <c r="A53" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B53" s="6" t="n">
+      <c r="B53" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" spans="1:2">
       <c r="A54" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B54" s="4" t="n">
+      <c r="B54" s="4">
         <v>25</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" spans="1:2">
       <c r="A55" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B55" s="6">
         <v>156</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" spans="1:2">
       <c r="A56" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B56" s="4" t="n">
+      <c r="B56" s="4">
         <v>45</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" spans="1:2">
       <c r="A57" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B57" s="6" t="n">
+      <c r="B57" s="6">
         <v>22</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" spans="1:2">
       <c r="A58" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B58" s="4" t="n">
+      <c r="B58" s="4">
         <v>144</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" spans="1:2">
       <c r="A59" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B59" s="6">
         <v>329</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" spans="1:2">
       <c r="A60" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B60" s="4" t="n">
+      <c r="B60" s="4">
         <v>161</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" spans="1:2">
       <c r="A61" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B61" s="6" t="n">
+      <c r="B61" s="6">
         <v>275</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" spans="1:2">
       <c r="A62" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B62" s="4" t="n">
+      <c r="B62" s="4">
         <v>311</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" spans="1:2">
       <c r="A63" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B63" s="6" t="n">
+      <c r="B63" s="6">
         <v>175</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" spans="1:2">
       <c r="A64" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B64" s="4" t="n">
+      <c r="B64" s="4">
         <v>58</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" spans="1:2">
       <c r="A65" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B65" s="6" t="n">
+      <c r="B65" s="6">
         <v>851</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" spans="1:2">
       <c r="A66" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B66" s="4" t="n">
+      <c r="B66" s="4">
         <v>3644</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" spans="1:2">
       <c r="A67" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B67" s="6" t="n">
+      <c r="B67" s="6">
         <v>46</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" spans="1:2">
       <c r="A68" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B68" s="4" t="n">
+      <c r="B68" s="4">
         <v>44</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" spans="1:2">
       <c r="A69" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B69" s="6" t="n">
+      <c r="B69" s="6">
         <v>76</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" spans="1:2">
       <c r="A70" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B70" s="4" t="n">
+      <c r="B70" s="4">
         <v>220</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" spans="1:2">
       <c r="A71" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B71" s="6" t="n">
+      <c r="B71" s="6">
         <v>29</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" spans="1:2">
       <c r="A72" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B72" s="4" t="n">
+      <c r="B72" s="4">
         <v>25</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" spans="1:2">
       <c r="A73" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B73" s="6" t="n">
+      <c r="B73" s="6">
         <v>89</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" spans="1:2">
       <c r="A74" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B74" s="4" t="n">
+      <c r="B74" s="4">
         <v>508.1</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" spans="1:2">
       <c r="A75" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B75" s="6" t="n">
+      <c r="B75" s="6">
         <v>43</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" spans="1:2">
       <c r="A76" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B76" s="4" t="n">
+      <c r="B76" s="4">
         <v>44</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" spans="1:2">
       <c r="A77" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B77" s="6" t="n">
+      <c r="B77" s="6">
         <v>587</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" spans="1:2">
       <c r="A78" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B78" s="4" t="n">
+      <c r="B78" s="4">
         <v>121</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" spans="1:2">
       <c r="A79" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B79" s="6" t="n">
+      <c r="B79" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" spans="1:2">
       <c r="A80" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B80" s="4" t="n">
+      <c r="B80" s="4">
         <v>157</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" spans="1:2">
       <c r="A81" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B81" s="6" t="n">
+      <c r="B81" s="6">
         <v>156</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" spans="1:2">
       <c r="A82" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B82" s="4" t="n">
+      <c r="B82" s="4">
         <v>235</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" spans="1:2">
       <c r="A83" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B83" s="6" t="n">
+      <c r="B83" s="6">
         <v>188</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" spans="1:2">
       <c r="A84" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B84" s="4" t="n">
+      <c r="B84" s="4">
         <v>106</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" spans="1:2">
       <c r="A85" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B85" s="6" t="n">
+      <c r="B85" s="6">
         <v>46</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" spans="1:2">
       <c r="A86" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B86" s="4" t="n">
+      <c r="B86" s="4">
         <v>33</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" spans="1:2">
       <c r="A87" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B87" s="6" t="n">
+      <c r="B87" s="6">
         <v>15</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" spans="1:2">
       <c r="A88" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B88" s="4" t="n">
+      <c r="B88" s="4">
         <v>187</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" spans="1:2">
       <c r="A89" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B89" s="6" t="n">
+      <c r="B89" s="6">
         <v>256</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" spans="1:2">
       <c r="A90" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B90" s="4" t="n">
+      <c r="B90" s="4">
         <v>133</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" spans="1:2">
       <c r="A91" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B91" s="6" t="n">
+      <c r="B91" s="6">
         <v>217</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" spans="1:2">
       <c r="A92" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B92" s="4" t="n">
+      <c r="B92" s="4">
         <v>20</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" spans="1:2">
       <c r="A93" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B93" s="6" t="n">
+      <c r="B93" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" spans="1:2">
       <c r="A94" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B94" s="4" t="n">
+      <c r="B94" s="4">
         <v>65</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" spans="1:2">
       <c r="A95" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B95" s="6" t="n">
+      <c r="B95" s="6">
         <v>56</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" spans="1:2">
       <c r="A96" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B96" s="4" t="n">
+      <c r="B96" s="4">
         <v>25</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" spans="1:2">
       <c r="A97" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="6" t="n">
+      <c r="B97" s="6">
         <v>52</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" spans="1:2">
       <c r="A98" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B98" s="4" t="n">
+      <c r="B98" s="4">
         <v>15</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" spans="1:2">
       <c r="A99" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B99" s="6" t="n">
+      <c r="B99" s="6">
         <v>41</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" spans="1:2">
       <c r="A100" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B100" s="4" t="n">
+      <c r="B100" s="4">
         <v>182</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" spans="1:2">
       <c r="A101" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B101" s="6" t="n">
+      <c r="B101" s="6">
         <v>157</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" spans="1:2">
       <c r="A102" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B102" s="4" t="n">
+      <c r="B102" s="4">
         <v>31</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" spans="1:2">
       <c r="A103" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B103" s="6" t="n">
+      <c r="B103" s="6">
         <v>103</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" spans="1:2">
       <c r="A104" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B104" s="4" t="n">
+      <c r="B104" s="4">
         <v>15</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" spans="1:2">
       <c r="A105" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B105" s="6" t="n">
+      <c r="B105" s="6">
         <v>94</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" spans="1:2">
       <c r="A106" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B106" s="4" t="n">
+      <c r="B106" s="4">
         <v>221</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" spans="1:2">
       <c r="A107" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B107" s="6" t="n">
+      <c r="B107" s="6">
         <v>50</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" spans="1:2">
       <c r="A108" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B108" s="4" t="n">
+      <c r="B108" s="4">
         <v>61</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" spans="1:2">
       <c r="A109" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B109" s="6" t="n">
+      <c r="B109" s="6">
         <v>7</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" spans="1:2">
       <c r="A110" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B110" s="4" t="n">
+      <c r="B110" s="4">
         <v>10.1</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" spans="1:2">
       <c r="A111" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="B111" s="6" t="n">
+      <c r="B111" s="6">
         <v>79</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" spans="1:2">
       <c r="A112" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B112" s="4" t="n">
+      <c r="B112" s="4">
         <v>46</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" spans="1:2">
       <c r="A113" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B113" s="6" t="n">
+      <c r="B113" s="6">
         <v>34</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" spans="1:2">
       <c r="A114" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B114" s="4" t="n">
+      <c r="B114" s="4">
         <v>38.1</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" spans="1:2">
       <c r="A115" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B115" s="6" t="n">
+      <c r="B115" s="6">
         <v>63</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" spans="1:2">
       <c r="A116" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B116" s="4" t="n">
+      <c r="B116" s="4">
         <v>31</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" spans="1:2">
       <c r="A117" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B117" s="6" t="n">
+      <c r="B117" s="6">
         <v>29</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" spans="1:2">
       <c r="A118" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B118" s="4" t="n">
+      <c r="B118" s="4">
         <v>49</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" spans="1:2">
       <c r="A119" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B119" s="6" t="n">
+      <c r="B119" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" spans="1:2">
       <c r="A120" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B120" s="4" t="n">
+      <c r="B120" s="4">
         <v>20</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" spans="1:2">
       <c r="A121" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B121" s="6" t="n">
+      <c r="B121" s="6">
         <v>43</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" spans="1:2">
       <c r="A122" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B122" s="4" t="n">
+      <c r="B122" s="4">
         <v>19</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" spans="1:2">
       <c r="A123" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B123" s="6" t="n">
+      <c r="B123" s="6">
         <v>25</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" spans="1:2">
       <c r="A124" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B124" s="4" t="n">
+      <c r="B124" s="4">
         <v>33</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" spans="1:2">
       <c r="A125" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B125" s="6" t="n">
+      <c r="B125" s="6">
         <v>7.2</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" spans="1:2">
       <c r="A126" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B126" s="4" t="n">
+      <c r="B126" s="4">
         <v>29</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" spans="1:2">
       <c r="A127" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B127" s="6" t="n">
+      <c r="B127" s="6">
         <v>38</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" spans="1:2">
       <c r="A128" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B128" s="4" t="n">
+      <c r="B128" s="4">
         <v>58</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" spans="1:2">
       <c r="A129" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="B129" s="6" t="n">
+      <c r="B129" s="6">
         <v>18</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" spans="1:2">
       <c r="A130" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B130" s="4" t="n">
+      <c r="B130" s="4">
         <v>54</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" spans="1:2">
       <c r="A131" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B131" s="6" t="n">
+      <c r="B131" s="6">
         <v>37</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" spans="1:2">
       <c r="A132" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B132" s="4" t="n">
+      <c r="B132" s="4">
         <v>56</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" spans="1:2">
       <c r="A133" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B133" s="6" t="n">
+      <c r="B133" s="6">
         <v>12.2</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" spans="1:2">
       <c r="A134" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B134" s="4" t="n">
+      <c r="B134" s="4">
         <v>91</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" spans="1:2">
       <c r="A135" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B135" s="6" t="n">
+      <c r="B135" s="6">
         <v>165</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" spans="1:2">
       <c r="A136" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B136" s="4" t="n">
+      <c r="B136" s="4">
         <v>135</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" spans="1:2">
       <c r="A137" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="B137" s="6" t="n">
+      <c r="B137" s="6">
         <v>92</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" spans="1:2">
       <c r="A138" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B138" s="4" t="n">
+      <c r="B138" s="4">
         <v>14</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" spans="1:2">
       <c r="A139" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B139" s="6" t="n">
+      <c r="B139" s="6">
         <v>31</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" spans="1:2">
       <c r="A140" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B140" s="4" t="n">
+      <c r="B140" s="4">
         <v>90</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" spans="1:2">
       <c r="A141" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B141" s="6" t="n">
+      <c r="B141" s="6">
         <v>48</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" spans="1:2">
       <c r="A142" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B142" s="4" t="n">
+      <c r="B142" s="4">
         <v>39</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" spans="1:2">
       <c r="A143" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="B143" s="6" t="n">
+      <c r="B143" s="6">
         <v>120</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" spans="1:2">
       <c r="A144" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B144" s="4" t="n">
+      <c r="B144" s="4">
         <v>22</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" spans="1:2">
       <c r="A145" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B145" s="6" t="n">
+      <c r="B145" s="6">
         <v>123</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" spans="1:2">
       <c r="A146" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B146" s="4" t="n">
+      <c r="B146" s="4">
         <v>102</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" spans="1:2">
       <c r="A147" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B147" s="6" t="n">
+      <c r="B147" s="6">
         <v>12</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" spans="1:2">
       <c r="A148" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B148" s="4" t="n">
+      <c r="B148" s="4">
         <v>38</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" spans="1:2">
       <c r="A149" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="B149" s="6" t="n">
+      <c r="B149" s="6">
         <v>22</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" spans="1:2">
       <c r="A150" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B150" s="4" t="n">
+      <c r="B150" s="4">
         <v>73</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" spans="1:2">
       <c r="A151" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B151" s="6" t="n">
+      <c r="B151" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" spans="1:2">
       <c r="A152" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B152" s="4" t="n">
+      <c r="B152" s="4">
         <v>63</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" spans="1:2">
       <c r="A153" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B153" s="6" t="n">
+      <c r="B153" s="6">
         <v>83</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" spans="1:2">
       <c r="A154" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B154" s="4" t="n">
+      <c r="B154" s="4">
         <v>139</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" spans="1:2">
       <c r="A155" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B155" s="6" t="n">
+      <c r="B155" s="6">
         <v>15</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" spans="1:2">
       <c r="A156" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B156" s="4" t="n">
+      <c r="B156" s="4">
         <v>24</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" spans="1:2">
       <c r="A157" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B157" s="6" t="n">
+      <c r="B157" s="6">
         <v>76</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" spans="1:2">
       <c r="A158" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B158" s="4" t="n">
+      <c r="B158" s="4">
         <v>38</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" spans="1:2">
       <c r="A159" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B159" s="6" t="n">
+      <c r="B159" s="6">
         <v>44</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" spans="1:2">
       <c r="A160" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B160" s="4" t="n">
+      <c r="B160" s="4">
         <v>26</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" spans="1:2">
       <c r="A161" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B161" s="6" t="n">
+      <c r="B161" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" spans="1:2">
       <c r="A162" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B162" s="4" t="n">
+      <c r="B162" s="4">
         <v>29</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" spans="1:2">
       <c r="A163" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B163" s="6" t="n">
+      <c r="B163" s="6">
         <v>34</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" spans="1:2">
       <c r="A164" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B164" s="4" t="n">
+      <c r="B164" s="4">
         <v>11</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" spans="1:2">
       <c r="A165" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="B165" s="6" t="n">
+      <c r="B165" s="6">
         <v>18</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" spans="1:2">
       <c r="A166" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B166" s="4" t="n">
+      <c r="B166" s="4">
         <v>26</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" spans="1:2">
       <c r="A167" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="B167" s="6" t="n">
+      <c r="B167" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" spans="1:2">
       <c r="A168" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B168" s="4" t="n">
+      <c r="B168" s="4">
         <v>108</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" spans="1:2">
       <c r="A169" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="B169" s="6" t="n">
+      <c r="B169" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" spans="1:2">
       <c r="A170" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B170" s="4" t="n">
+      <c r="B170" s="4">
         <v>49</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" spans="1:2">
       <c r="A171" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="B171" s="6" t="n">
+      <c r="B171" s="6">
         <v>54</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" spans="1:2">
       <c r="A172" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B172" s="4" t="n">
+      <c r="B172" s="4">
         <v>74</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" spans="1:2">
       <c r="A173" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="B173" s="6" t="n">
+      <c r="B173" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" spans="1:2">
       <c r="A174" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B174" s="4" t="n">
+      <c r="B174" s="4">
         <v>37</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" spans="1:2">
       <c r="A175" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="B175" s="6" t="n">
+      <c r="B175" s="6">
         <v>40</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" spans="1:2">
       <c r="A176" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B176" s="4" t="n">
+      <c r="B176" s="4">
         <v>104</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" spans="1:2">
       <c r="A177" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="B177" s="6" t="n">
+      <c r="B177" s="6">
         <v>76</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" spans="1:2">
       <c r="A178" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B178" s="4" t="n">
+      <c r="B178" s="4">
         <v>100</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" spans="1:2">
       <c r="A179" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="B179" s="6" t="n">
+      <c r="B179" s="6">
         <v>50</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" spans="1:2">
       <c r="A180" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B180" s="4" t="n">
+      <c r="B180" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" spans="1:2">
       <c r="A181" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="B181" s="6" t="n">
+      <c r="B181" s="6">
         <v>45</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" spans="1:2">
       <c r="A182" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B182" s="4" t="n">
+      <c r="B182" s="4">
         <v>9</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" spans="1:2">
       <c r="A183" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="B183" s="6" t="n">
+      <c r="B183" s="6">
         <v>15</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" spans="1:2">
       <c r="A184" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B184" s="4" t="n">
+      <c r="B184" s="4">
         <v>37</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" spans="1:2">
       <c r="A185" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="B185" s="6" t="n">
+      <c r="B185" s="6">
         <v>28</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" spans="1:2">
       <c r="A186" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B186" s="4" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B186" s="4">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
       <c r="A187" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="B187" s="6" t="n">
+      <c r="B187" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" spans="1:2">
       <c r="A188" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B188" s="4" t="n">
+      <c r="B188" s="4">
         <v>27</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" spans="1:2">
       <c r="A189" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="B189" s="6" t="n">
+      <c r="B189" s="6">
         <v>91</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" spans="1:2">
       <c r="A190" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B190" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B190" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
       <c r="A191" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="B191" s="6" t="n">
+      <c r="B191" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" spans="1:2">
       <c r="A192" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B192" s="4" t="n">
+      <c r="B192" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" spans="1:2">
       <c r="A193" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B193" s="6" t="n">
+      <c r="B193" s="6">
         <v>25</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" spans="1:2">
       <c r="A194" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B194" s="4" t="n">
+      <c r="B194" s="4">
         <v>54</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" spans="1:2">
       <c r="A195" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B195" s="6" t="n">
+      <c r="B195" s="6">
         <v>89</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" spans="1:2">
       <c r="A196" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B196" s="4" t="n">
+      <c r="B196" s="4">
         <v>54</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" spans="1:2">
       <c r="A197" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B197" s="6" t="n">
+      <c r="B197" s="6">
         <v>29</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" spans="1:2">
       <c r="A198" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B198" s="4" t="n">
+      <c r="B198" s="4">
         <v>59</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" spans="1:2">
       <c r="A199" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B199" s="6" t="n">
+      <c r="B199" s="6">
         <v>26</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" spans="1:2">
       <c r="A200" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B200" s="4" t="n">
+      <c r="B200" s="4">
         <v>26</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" spans="1:2">
       <c r="A201" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="B201" s="6" t="n">
+      <c r="B201" s="6">
         <v>108</v>
       </c>
     </row>
-    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" spans="1:2">
       <c r="A202" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B202" s="4" t="n">
+      <c r="B202" s="4">
         <v>44</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" spans="1:2">
       <c r="A203" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="B203" s="6" t="n">
+      <c r="B203" s="6">
         <v>15</v>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" spans="1:2">
       <c r="A204" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B204" s="4" t="n">
+      <c r="B204" s="4">
         <v>9</v>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" spans="1:2">
       <c r="A205" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="B205" s="6" t="n">
+      <c r="B205" s="6">
         <v>26</v>
       </c>
     </row>
-    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" spans="1:2">
       <c r="A206" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B206" s="4" t="n">
+      <c r="B206" s="4">
         <v>17</v>
       </c>
     </row>
-    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" spans="1:2">
       <c r="A207" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="B207" s="6" t="n">
+      <c r="B207" s="6">
         <v>25</v>
       </c>
     </row>
-    <row r="208" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" spans="1:2">
       <c r="A208" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="B208" s="4" t="n">
+      <c r="B208" s="4">
         <v>220</v>
       </c>
     </row>
-    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" spans="1:2">
       <c r="A209" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="B209" s="6" t="n">
+      <c r="B209" s="6">
         <v>22</v>
       </c>
     </row>
-    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" spans="1:2">
       <c r="A210" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B210" s="4" t="n">
+      <c r="B210" s="4">
         <v>51</v>
       </c>
     </row>
-    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" spans="1:2">
       <c r="A211" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="B211" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B211" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
       <c r="A212" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B212" s="4" t="n">
+      <c r="B212" s="4">
         <v>60</v>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" spans="1:2">
       <c r="A213" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="B213" s="6" t="n">
+      <c r="B213" s="6">
         <v>31</v>
       </c>
     </row>
-    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="214" spans="1:2">
       <c r="A214" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B214" s="4" t="n">
+      <c r="B214" s="4">
         <v>38</v>
       </c>
     </row>
-    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="215" spans="1:2">
       <c r="A215" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="B215" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B215" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
       <c r="A216" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="B216" s="4" t="n">
+      <c r="B216" s="4">
         <v>70</v>
       </c>
     </row>
-    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="217" spans="1:2">
       <c r="A217" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B217" s="6" t="n">
+      <c r="B217" s="6">
         <v>141</v>
       </c>
     </row>
-    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="218" spans="1:2">
       <c r="A218" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B218" s="4" t="n">
+      <c r="B218" s="4">
         <v>31</v>
       </c>
     </row>
-    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="219" spans="1:2">
       <c r="A219" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="B219" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B219" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
       <c r="A220" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="B220" s="4" t="n">
+      <c r="B220" s="4">
         <v>49</v>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" spans="1:2">
       <c r="A221" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="B221" s="6" t="n">
+      <c r="B221" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" spans="1:2">
       <c r="A222" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B222" s="4" t="n">
+      <c r="B222" s="4">
         <v>23</v>
       </c>
     </row>
-    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="223" spans="1:2">
       <c r="A223" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="B223" s="6" t="n">
+      <c r="B223" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="224" spans="1:2">
       <c r="A224" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B224" s="4" t="n">
+      <c r="B224" s="4">
         <v>21</v>
       </c>
     </row>
-    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" spans="1:2">
       <c r="A225" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="B225" s="6" t="n">
+      <c r="B225" s="6">
         <v>26</v>
       </c>
     </row>
-    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" spans="1:2">
       <c r="A226" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="B226" s="4" t="n">
+      <c r="B226" s="4">
         <v>36</v>
       </c>
     </row>
-    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="227" spans="1:2">
       <c r="A227" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="B227" s="6" t="n">
+      <c r="B227" s="6">
         <v>64</v>
       </c>
     </row>
-    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="228" spans="1:2">
       <c r="A228" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="B228" s="4" t="n">
+      <c r="B228" s="4">
         <v>37</v>
       </c>
     </row>
-    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="229" spans="1:2">
       <c r="A229" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="B229" s="6" t="n">
+      <c r="B229" s="6">
         <v>22</v>
       </c>
     </row>
-    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="230" spans="1:2">
       <c r="A230" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B230" s="4" t="n">
+      <c r="B230" s="4">
         <v>124</v>
       </c>
     </row>
-    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="231" spans="1:2">
       <c r="A231" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="B231" s="6" t="n">
+      <c r="B231" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="232" spans="1:2">
       <c r="A232" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="B232" s="4" t="n">
+      <c r="B232" s="4">
         <v>18</v>
       </c>
     </row>
-    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="233" spans="1:2">
       <c r="A233" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="B233" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B233" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
       <c r="A234" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="B234" s="4" t="n">
+      <c r="B234" s="4">
         <v>16</v>
       </c>
     </row>
-    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="235" spans="1:2">
       <c r="A235" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="B235" s="6" t="n">
+      <c r="B235" s="6">
         <v>130</v>
       </c>
     </row>
-    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="236" spans="1:2">
       <c r="A236" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="B236" s="4" t="n">
+      <c r="B236" s="4">
         <v>67</v>
       </c>
     </row>
-    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="237" spans="1:2">
       <c r="A237" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="B237" s="6" t="n">
+      <c r="B237" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="238" spans="1:2">
       <c r="A238" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B238" s="4" t="n">
+      <c r="B238" s="4">
         <v>12</v>
       </c>
     </row>
-    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="239" spans="1:2">
       <c r="A239" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="B239" s="6" t="n">
+      <c r="B239" s="6">
         <v>9</v>
       </c>
     </row>
-    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" spans="1:2">
       <c r="A240" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B240" s="4" t="n">
+      <c r="B240" s="4">
         <v>21</v>
       </c>
     </row>
-    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="241" spans="1:2">
       <c r="A241" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="B241" s="6" t="n">
+      <c r="B241" s="6">
         <v>14</v>
       </c>
     </row>
-    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="242" spans="1:2">
       <c r="A242" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="B242" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B242" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
       <c r="A243" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="B243" s="6" t="n">
+      <c r="B243" s="6">
         <v>12</v>
       </c>
     </row>
-    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="244" spans="1:2">
       <c r="A244" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B244" s="4" t="n">
+      <c r="B244" s="4">
         <v>25</v>
       </c>
     </row>
-    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="245" spans="1:2">
       <c r="A245" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="B245" s="6" t="n">
+      <c r="B245" s="6">
         <v>9</v>
       </c>
     </row>
-    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="246" spans="1:2">
       <c r="A246" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="B246" s="4" t="n">
+      <c r="B246" s="4">
         <v>8</v>
       </c>
     </row>
-    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="247" spans="1:2">
       <c r="A247" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="B247" s="6" t="n">
+      <c r="B247" s="6">
         <v>12</v>
       </c>
     </row>
-    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="248" spans="1:2">
       <c r="A248" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="B248" s="4" t="n">
+      <c r="B248" s="4">
         <v>38</v>
       </c>
     </row>
-    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="249" spans="1:2">
       <c r="A249" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="B249" s="6" t="n">
+      <c r="B249" s="6">
         <v>81</v>
       </c>
     </row>
-    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="250" spans="1:2">
       <c r="A250" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B250" s="4" t="n">
+      <c r="B250" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="251" spans="1:2">
       <c r="A251" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="B251" s="6" t="n">
+      <c r="B251" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="252" spans="1:2">
       <c r="A252" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="B252" s="4" t="n">
+      <c r="B252" s="4">
         <v>57</v>
       </c>
     </row>
-    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="253" spans="1:2">
       <c r="A253" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="B253" s="6" t="n">
+      <c r="B253" s="6">
         <v>112</v>
       </c>
     </row>
-    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="254" spans="1:2">
       <c r="A254" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B254" s="4" t="n">
+      <c r="B254" s="4">
         <v>126</v>
       </c>
     </row>
-    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="255" spans="1:2">
       <c r="A255" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="B255" s="6" t="n">
+      <c r="B255" s="6">
         <v>44</v>
       </c>
     </row>
-    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="256" spans="1:2">
       <c r="A256" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="B256" s="4" t="n">
+      <c r="B256" s="4">
         <v>46</v>
       </c>
     </row>
-    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="257" spans="1:2">
       <c r="A257" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="B257" s="6" t="n">
+      <c r="B257" s="6">
         <v>40</v>
       </c>
     </row>
-    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="258" spans="1:2">
       <c r="A258" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="B258" s="4" t="n">
+      <c r="B258" s="4">
         <v>28</v>
       </c>
     </row>
-    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="259" spans="1:2">
       <c r="A259" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="B259" s="6" t="n">
+      <c r="B259" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="260" spans="1:2">
       <c r="A260" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="B260" s="4" t="n">
+      <c r="B260" s="4">
         <v>219</v>
       </c>
     </row>
-    <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="261" spans="1:2">
       <c r="A261" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="B261" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B261" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
       <c r="A262" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="B262" s="4" t="n">
+      <c r="B262" s="4">
         <v>55</v>
       </c>
     </row>
-    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="263" spans="1:2">
       <c r="A263" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="B263" s="6" t="n">
+      <c r="B263" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="264" spans="1:2">
       <c r="A264" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="B264" s="4" t="n">
+      <c r="B264" s="4">
         <v>22</v>
       </c>
     </row>
-    <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="265" spans="1:2">
       <c r="A265" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="B265" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B265" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
       <c r="A266" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="B266" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B266" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
       <c r="A267" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="B267" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B267" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
       <c r="A268" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B268" s="4" t="n">
+      <c r="B268" s="4">
         <v>17</v>
       </c>
     </row>
-    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="269" spans="1:2">
       <c r="A269" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="B269" s="6" t="n">
+      <c r="B269" s="6">
         <v>18</v>
       </c>
     </row>
-    <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="270" spans="1:2">
       <c r="A270" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="B270" s="4" t="n">
+      <c r="B270" s="4">
         <v>29</v>
       </c>
     </row>
-    <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="271" spans="1:2">
       <c r="A271" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="B271" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B271" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
       <c r="A272" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="B272" s="4" t="n">
+      <c r="B272" s="4">
         <v>22</v>
       </c>
     </row>
-    <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="273" spans="1:2">
       <c r="A273" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="B273" s="6" t="n">
+      <c r="B273" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="274" spans="1:2">
       <c r="A274" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="B274" s="4" t="n">
+      <c r="B274" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="275" spans="1:2">
       <c r="A275" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="B275" s="6" t="n">
+      <c r="B275" s="6">
         <v>45</v>
       </c>
     </row>
-    <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="276" spans="1:2">
       <c r="A276" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="B276" s="4" t="n">
+      <c r="B276" s="4">
         <v>21</v>
       </c>
     </row>
-    <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="277" spans="1:2">
       <c r="A277" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="B277" s="6" t="n">
+      <c r="B277" s="6">
         <v>34</v>
       </c>
     </row>
-    <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="278" spans="1:2">
       <c r="A278" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="B278" s="4" t="n">
+      <c r="B278" s="4">
         <v>40</v>
       </c>
     </row>
-    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="279" spans="1:2">
       <c r="A279" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="B279" s="6" t="n">
+      <c r="B279" s="6">
         <v>22</v>
       </c>
     </row>
-    <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="280" spans="1:2">
       <c r="A280" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B280" s="4" t="n">
+      <c r="B280" s="4">
         <v>25</v>
       </c>
     </row>
-    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="281" spans="1:2">
       <c r="A281" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="B281" s="6" t="n">
+      <c r="B281" s="6">
         <v>45</v>
       </c>
     </row>
-    <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="282" spans="1:2">
       <c r="A282" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="B282" s="4" t="n">
+      <c r="B282" s="4">
         <v>28</v>
       </c>
     </row>
-    <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="283" spans="1:2">
       <c r="A283" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="B283" s="6" t="n">
+      <c r="B283" s="6">
         <v>27</v>
       </c>
     </row>
-    <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="284" spans="1:2">
       <c r="A284" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="B284" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B284" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" ht="15.75">
       <c r="A285" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="B285" s="6" t="n">
+      <c r="B285" s="6">
         <v>16</v>
       </c>
     </row>
-    <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="286" spans="1:2">
       <c r="A286" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="B286" s="4" t="n">
+      <c r="B286" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="287" spans="1:2">
       <c r="A287" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="B287" s="6" t="n">
+      <c r="B287" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="288" spans="1:2">
       <c r="A288" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="B288" s="4" t="n">
+      <c r="B288" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="289" spans="1:2">
       <c r="A289" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="B289" s="6" t="n">
+      <c r="B289" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="290" spans="1:2">
       <c r="A290" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="B290" s="4" t="n">
+      <c r="B290" s="4">
         <v>38</v>
       </c>
     </row>
-    <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="291" spans="1:2">
       <c r="A291" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="B291" s="6" t="n">
+      <c r="B291" s="6">
         <v>31</v>
       </c>
     </row>
-    <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="292" spans="1:2">
       <c r="A292" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="B292" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B292" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
       <c r="A293" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="B293" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B293" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
       <c r="A294" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="B294" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B294" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
       <c r="A295" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="B295" s="6" t="n">
+      <c r="B295" s="6">
         <v>25</v>
       </c>
     </row>
-    <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="296" spans="1:2">
       <c r="A296" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="B296" s="4" t="n">
+      <c r="B296" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="297" spans="1:2">
       <c r="A297" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="B297" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B297" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
       <c r="A298" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="B298" s="4" t="n">
+      <c r="B298" s="4">
         <v>29</v>
       </c>
     </row>
-    <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="299" spans="1:2">
       <c r="A299" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="B299" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B299" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
       <c r="A300" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="B300" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B300" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
       <c r="A301" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="B301" s="6" t="n">
+      <c r="B301" s="6">
         <v>56</v>
       </c>
     </row>
-    <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="302" spans="1:2">
       <c r="A302" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="B302" s="4" t="n">
+      <c r="B302" s="4">
         <v>41</v>
       </c>
     </row>
-    <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="303" spans="1:2">
       <c r="A303" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="B303" s="6" t="n">
+      <c r="B303" s="6">
         <v>21</v>
       </c>
     </row>
-    <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="304" spans="1:2">
       <c r="A304" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="B304" s="4" t="n">
+      <c r="B304" s="4">
         <v>9</v>
       </c>
     </row>
-    <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="305" spans="1:2">
       <c r="A305" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="B305" s="6" t="n">
+      <c r="B305" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="306" spans="1:2">
       <c r="A306" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="B306" s="4" t="n">
+      <c r="B306" s="4">
         <v>27</v>
       </c>
     </row>
-    <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="307" spans="1:2">
       <c r="A307" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="B307" s="6" t="n">
+      <c r="B307" s="6">
         <v>15</v>
       </c>
     </row>
-    <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="308" spans="1:2">
       <c r="A308" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="B308" s="4" t="n">
+      <c r="B308" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="309" spans="1:2">
       <c r="A309" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="B309" s="6" t="n">
+      <c r="B309" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="310" spans="1:2">
       <c r="A310" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="B310" s="4" t="n">
+      <c r="B310" s="4">
         <v>21</v>
       </c>
     </row>
-    <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="311" spans="1:2">
       <c r="A311" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="B311" s="6" t="n">
+      <c r="B311" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="312" spans="1:2">
       <c r="A312" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="B312" s="4" t="n">
+      <c r="B312" s="4">
         <v>55</v>
       </c>
     </row>
-    <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="313" spans="1:2">
       <c r="A313" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="B313" s="6" t="n">
+      <c r="B313" s="6">
         <v>28</v>
       </c>
     </row>
-    <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="314" spans="1:2">
       <c r="A314" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="B314" s="4" t="n">
+      <c r="B314" s="4">
         <v>32</v>
       </c>
     </row>
-    <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="315" spans="1:2">
       <c r="A315" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="B315" s="6" t="n">
+      <c r="B315" s="6">
         <v>47</v>
       </c>
     </row>
-    <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="316" spans="1:2">
       <c r="A316" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="B316" s="4" t="n">
+      <c r="B316" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="317" spans="1:2">
       <c r="A317" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B317" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B317" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
       <c r="A318" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="B318" s="4" t="n">
+      <c r="B318" s="4">
         <v>18</v>
       </c>
     </row>
-    <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="319" spans="1:2">
       <c r="A319" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="B319" s="6" t="n">
+      <c r="B319" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="320" spans="1:2">
       <c r="A320" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="B320" s="4" t="n">
+      <c r="B320" s="4">
         <v>161</v>
       </c>
     </row>
-    <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="321" spans="1:2">
       <c r="A321" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="B321" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B321" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
       <c r="A322" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="B322" s="4" t="n">
+      <c r="B322" s="4">
         <v>34</v>
       </c>
     </row>
-    <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="323" spans="1:2">
       <c r="A323" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="B323" s="6" t="n">
+      <c r="B323" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="324" spans="1:2">
       <c r="A324" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="B324" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B324" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
       <c r="A325" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="B325" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B325" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
       <c r="A326" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="B326" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B326" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
       <c r="A327" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="B327" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B327" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
       <c r="A328" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="B328" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B328" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
       <c r="A329" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="B329" s="6" t="n">
+      <c r="B329" s="6">
         <v>25</v>
       </c>
     </row>
-    <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="330" spans="1:2">
       <c r="A330" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="B330" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B330" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
       <c r="A331" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="B331" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B331" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
       <c r="A332" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="B332" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B332" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
       <c r="A333" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="B333" s="6" t="n">
+      <c r="B333" s="6">
         <v>29</v>
       </c>
     </row>
-    <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="334" spans="1:2">
       <c r="A334" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="B334" s="4" t="n">
+      <c r="B334" s="4">
         <v>38</v>
       </c>
     </row>
-    <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="335" spans="1:2">
       <c r="A335" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="B335" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B335" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
       <c r="A336" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="B336" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B336" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
       <c r="A337" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="B337" s="6" t="n">
+      <c r="B337" s="6">
         <v>27</v>
       </c>
     </row>
-    <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="338" spans="1:2">
       <c r="A338" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="B338" s="4" t="n">
+      <c r="B338" s="4">
         <v>17</v>
       </c>
     </row>
-    <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="339" spans="1:2">
       <c r="A339" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="B339" s="6" t="n">
+      <c r="B339" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="340" spans="1:2">
       <c r="A340" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="B340" s="4" t="n">
+      <c r="B340" s="4">
         <v>8</v>
       </c>
     </row>
-    <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="341" spans="1:2">
       <c r="A341" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="B341" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B341" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
       <c r="A342" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="B342" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B342" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
       <c r="A343" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="B343" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B343" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
       <c r="A344" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="B344" s="4" t="n">
+      <c r="B344" s="4">
         <v>12</v>
       </c>
     </row>
-    <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="345" spans="1:2">
       <c r="A345" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="B345" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B345" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
       <c r="A346" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="B346" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B346" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
       <c r="A347" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="B347" s="6" t="n">
+      <c r="B347" s="6">
         <v>40</v>
       </c>
     </row>
-    <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="348" spans="1:2">
       <c r="A348" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="B348" s="4" t="n">
+      <c r="B348" s="4">
         <v>44</v>
       </c>
     </row>
-    <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="349" spans="1:2">
       <c r="A349" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="B349" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B349" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
       <c r="A350" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="B350" s="4" t="n">
+      <c r="B350" s="4">
         <v>7</v>
       </c>
     </row>
-    <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="351" spans="1:2">
       <c r="A351" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="B351" s="6" t="n">
+      <c r="B351" s="6">
         <v>97</v>
       </c>
     </row>
-    <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="352" spans="1:2">
       <c r="A352" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="B352" s="4" t="n">
+      <c r="B352" s="4">
         <v>29</v>
       </c>
     </row>
-    <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="353" spans="1:2">
       <c r="A353" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="B353" s="6" t="n">
+      <c r="B353" s="6">
         <v>50</v>
       </c>
     </row>
-    <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="354" spans="1:2">
       <c r="A354" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="B354" s="4" t="n">
+      <c r="B354" s="4">
         <v>52</v>
       </c>
     </row>
-    <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="355" spans="1:2">
       <c r="A355" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="B355" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B355" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
       <c r="A356" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="B356" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B356" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
       <c r="A357" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="B357" s="6" t="n">
+      <c r="B357" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="358" spans="1:2">
       <c r="A358" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="B358" s="4" t="n">
+      <c r="B358" s="4">
         <v>15</v>
       </c>
     </row>
-    <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="359" spans="1:2">
       <c r="A359" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="B359" s="6" t="n">
+      <c r="B359" s="6">
         <v>7</v>
       </c>
     </row>
-    <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="360" spans="1:2">
       <c r="A360" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="B360" s="4" t="n">
+      <c r="B360" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="361" spans="1:2">
       <c r="A361" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="B361" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B361" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
       <c r="A362" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="B362" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B362" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
       <c r="A363" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="B363" s="4" t="n">
+      <c r="B363" s="4">
         <v>12</v>
       </c>
     </row>
-    <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="364" spans="1:2">
       <c r="A364" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="B364" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B364" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
       <c r="A365" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B365" s="4" t="n">
+      <c r="B365" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="366" spans="1:2">
       <c r="A366" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="B366" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B366" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
       <c r="A367" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="B367" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B367" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
       <c r="A368" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="B368" s="6" t="n">
+      <c r="B368" s="6">
         <v>9</v>
       </c>
     </row>
-    <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="369" spans="1:2">
       <c r="A369" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="B369" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B369" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
       <c r="A370" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="B370" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B370" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
       <c r="A371" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="B371" s="4" t="n">
+      <c r="B371" s="4">
         <v>71</v>
       </c>
     </row>
-    <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="372" spans="1:2">
       <c r="A372" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="B372" s="6" t="n">
+      <c r="B372" s="6">
         <v>49</v>
       </c>
     </row>
-    <row r="373" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="373" spans="1:2">
       <c r="A373" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="B373" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="374" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B373" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
       <c r="A374" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="B374" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="375" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B374" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
       <c r="A375" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="B375" s="1" t="n">
+      <c r="B375" s="1">
         <v>114</v>
       </c>
     </row>
-    <row r="376" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="376" spans="1:2">
       <c r="A376" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="B376" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="377" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B376" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
       <c r="A377" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="B377" s="1" t="n">
+      <c r="B377" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="378" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="378" spans="1:2">
       <c r="A378" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="B378" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="379" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B378" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
       <c r="A379" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="B379" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="380" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B379" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
       <c r="A380" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="B380" s="1" t="n">
+      <c r="B380" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="381" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="381" spans="1:2">
       <c r="A381" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="B381" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="382" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B381" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
       <c r="A382" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="B382" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="383" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B382" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
       <c r="A383" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="B383" s="1" t="n">
+      <c r="B383" s="1">
         <v>26</v>
       </c>
     </row>
-    <row r="384" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="384" spans="1:2">
       <c r="A384" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="B384" s="9" t="n">
+      <c r="B384" s="9">
         <v>36</v>
       </c>
     </row>
-    <row r="385" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="385" spans="1:2">
       <c r="A385" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="B385" s="1" t="n">
+      <c r="B385" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A386" s="0" t="s">
+    <row r="386" spans="1:2">
+      <c r="A386" t="s">
         <v>385</v>
       </c>
-      <c r="B386" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A387" s="0" t="s">
+      <c r="B386" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387" t="s">
         <v>386</v>
       </c>
-      <c r="B387" s="1" t="n">
+      <c r="B387" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="388" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="388" spans="1:2">
       <c r="A388" s="10" t="s">
         <v>387</v>
       </c>
-      <c r="B388" s="1" t="n">
+      <c r="B388" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="389" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="389" spans="1:2">
       <c r="A389" s="7" t="s">
         <v>388</v>
       </c>
@@ -4841,47 +4765,42 @@
         <v>389</v>
       </c>
     </row>
-    <row r="390" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="390" spans="1:2">
       <c r="A390" s="7" t="s">
         <v>390</v>
       </c>
-      <c r="B390" s="1" t="n">
+      <c r="B390" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="391" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="391" spans="1:2">
       <c r="A391" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="B391" s="1" t="n">
+      <c r="B391" s="1">
         <v>19</v>
       </c>
     </row>
-    <row r="392" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="392" spans="1:2">
       <c r="A392" s="10" t="s">
         <v>392</v>
       </c>
-      <c r="B392" s="1" t="n">
+      <c r="B392" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="393" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="393" spans="1:2">
       <c r="A393" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="B393" s="1" t="n">
+      <c r="B393" s="1">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <tableParts>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>

--- a/Manga.Manhwua/Updated manhwua.xlsx
+++ b/Manga.Manhwua/Updated manhwua.xlsx
@@ -1,21 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Manga\Manga.Manhwua\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEC0FBDA-D4F7-44F3-A141-661DB8B920DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -27,511 +22,511 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="394">
   <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Episodes</t>
-  </si>
-  <si>
-    <t>Kingdom</t>
-  </si>
-  <si>
-    <t>Vagabond</t>
-  </si>
-  <si>
-    <t>My Dragon System</t>
-  </si>
-  <si>
-    <t>The Knight King Who Returned With A God</t>
-  </si>
-  <si>
-    <t>The Player Hides His Past</t>
-  </si>
-  <si>
-    <t>Disastrous Necromancer</t>
-  </si>
-  <si>
-    <t>The Priest of Corruption</t>
-  </si>
-  <si>
-    <t>Dragon Emperor Martial God</t>
-  </si>
-  <si>
-    <t>Mookhyang - Dark Lady</t>
-  </si>
-  <si>
-    <t>Leveling Up By Hoarding</t>
-  </si>
-  <si>
-    <t>Master Of The Martial Arts Library</t>
-  </si>
-  <si>
-    <t>Absolute Necromancer</t>
-  </si>
-  <si>
-    <t>Tales Of A Shinning Sword</t>
-  </si>
-  <si>
-    <t>Kyushu Chronicles Of Immortals And Demons</t>
-  </si>
-  <si>
-    <t>Level 1 Player</t>
-  </si>
-  <si>
-    <t>Logging 10,000 Years into the Future</t>
-  </si>
-  <si>
-    <t>Swordmaster’S Youngest Son</t>
-  </si>
-  <si>
-    <t>World’S Greatest Senior Disciple</t>
-  </si>
-  <si>
-    <t>Dragon Master</t>
-  </si>
-  <si>
-    <t>The Return Of The Disaster-Class Hero</t>
-  </si>
-  <si>
-    <t>Solo Farming In The Tower</t>
-  </si>
-  <si>
-    <t>Chronicles Of The Demon Faction</t>
-  </si>
-  <si>
-    <t>Demonic Master Of Mount Kunlun</t>
-  </si>
-  <si>
-    <t>Necromancer's Evolutionary Traits</t>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Episodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vagabond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Dragon System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Knight King Who Returned With A God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Player Hides His Past</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disastrous Necromancer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Priest of Corruption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragon Emperor Martial God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mookhyang - Dark Lady</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leveling Up By Hoarding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master Of The Martial Arts Library</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Absolute Necromancer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tales Of A Shinning Sword</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyushu Chronicles Of Immortals And Demons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level 1 Player</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logging 10,000 Years into the Future</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swordmaster’S Youngest Son</t>
+  </si>
+  <si>
+    <t xml:space="preserve">World’S Greatest Senior Disciple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragon Master</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Return Of The Disaster-Class Hero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo Farming In The Tower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chronicles Of The Demon Faction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demonic Master Of Mount Kunlun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Necromancer's Evolutionary Traits</t>
   </si>
   <si>
     <t xml:space="preserve">Samurai In Another World </t>
   </si>
   <si>
-    <t>Peerless Quest – The Cheat Skill Only I Can Use</t>
-  </si>
-  <si>
-    <t>Isekai De Haishin Katsudou Wo Shitara Tairyou No Yandere Shinja Wo Umidashite Shimatta Ken</t>
-  </si>
-  <si>
-    <t>Boundless Necromancer</t>
-  </si>
-  <si>
-    <t>Academy’S Genius Swordsman</t>
-  </si>
-  <si>
-    <t>Demon Evolution</t>
-  </si>
-  <si>
-    <t>The Iron-Blooded Necromancer Has Returned</t>
-  </si>
-  <si>
-    <t>Infinite Mage</t>
-  </si>
-  <si>
-    <t>Star Instructor  Master Baek</t>
-  </si>
-  <si>
-    <t>The Story Of Thorny Spear</t>
-  </si>
-  <si>
-    <t>Blade debt</t>
-  </si>
-  <si>
-    <t>Martial God Regressed To Level 2</t>
-  </si>
-  <si>
-    <t>What, You Dare Pretend In Front Of Me, The Strongest In The Immortal World?</t>
-  </si>
-  <si>
-    <t>Terminally-Ill Genius Dark Knight</t>
-  </si>
-  <si>
-    <t>Heavenly Inquisition Sword</t>
-  </si>
-  <si>
-    <t>Tsuki Ga Michibiku Isekai Douchuu</t>
-  </si>
-  <si>
-    <t>The Emperor’s Sword</t>
-  </si>
-  <si>
-    <t>The Constellations Are My Disciples</t>
-  </si>
-  <si>
-    <t>Revenge of the Iron-Blooded Sword Hound</t>
-  </si>
-  <si>
-    <t>Mr. Zombie</t>
-  </si>
-  <si>
-    <t>Master: This Villainous Disciple Is Not The Holy Child</t>
-  </si>
-  <si>
-    <t>Solo Max-Level Newbie</t>
-  </si>
-  <si>
-    <t>Murim Login</t>
-  </si>
-  <si>
-    <t>The Great Villain Who Threatened to Kill Himself</t>
-  </si>
-  <si>
-    <t>Weapon Maker</t>
-  </si>
-  <si>
-    <t>The Reincarnated Assassin is a Genius Swordsman</t>
-  </si>
-  <si>
-    <t>I was more overpowered than the hero, so I hid my power!</t>
-  </si>
-  <si>
-    <t>Million Times Attack Speed</t>
-  </si>
-  <si>
-    <t>I am the descendant of the Divine Dragon</t>
-  </si>
-  <si>
-    <t>Hero X Demon Queen</t>
-  </si>
-  <si>
-    <t>Records Of The Demonic Path’S Return</t>
-  </si>
-  <si>
-    <t>Five-Dimensional Zone</t>
-  </si>
-  <si>
-    <t>Legendary Youngest Son Of The Marquis House</t>
-  </si>
-  <si>
-    <t>I am fated villain</t>
-  </si>
-  <si>
-    <t>Return Of The Mount Hua Sect</t>
-  </si>
-  <si>
-    <t>Beyond Myriad Peoples</t>
-  </si>
-  <si>
-    <t>Nano Machine</t>
-  </si>
-  <si>
-    <t>Tensei Shitara Dai Nana Ouji Dattanode, Kimamani Majutsu O Kiwamemasu</t>
-  </si>
-  <si>
-    <t>Scoring the Sacred Body of the Ancients from the Get-go</t>
-  </si>
-  <si>
-    <t>Magic Emperor</t>
-  </si>
-  <si>
-    <t>Martial Peak</t>
-  </si>
-  <si>
-    <t>The Self-Disciplined Me Is Practically Invincible</t>
-  </si>
-  <si>
-    <t>Global Power: I Can Control All The Elements</t>
-  </si>
-  <si>
-    <t>Moon Slayer</t>
-  </si>
-  <si>
-    <t>Lightning Degree</t>
-  </si>
-  <si>
-    <t>The World's Best Sect Of Dependency</t>
-  </si>
-  <si>
-    <t>The Return Of Apocalypses Tyrant</t>
-  </si>
-  <si>
-    <t>What Do You Do When You Suddenly Become An Immortal?</t>
-  </si>
-  <si>
-    <t>Tales Of Demons And Gods</t>
-  </si>
-  <si>
-    <t>The Kingdoms Of Ruin</t>
-  </si>
-  <si>
-    <t>Necromancer Academy And The Genius Summoner</t>
-  </si>
-  <si>
-    <t>Yuan Zun</t>
-  </si>
-  <si>
-    <t>The Greatest Estate Designer</t>
-  </si>
-  <si>
-    <t>Conqueror of modern martial arts Kang Haejin</t>
-  </si>
-  <si>
-    <t>Records Of The Swordsman Scholar</t>
-  </si>
-  <si>
-    <t>The Scholar's Reincarnation</t>
-  </si>
-  <si>
-    <t>Tale of a Scribe Who Retires To The Countryside</t>
-  </si>
-  <si>
-    <t>Return Of The Bachelor</t>
-  </si>
-  <si>
-    <t>Reincarnation Of The Murim Clan's Former Ranker</t>
-  </si>
-  <si>
-    <t>Regressing with the King’s Power</t>
-  </si>
-  <si>
-    <t>The Last Cultivator</t>
-  </si>
-  <si>
-    <t>HEAVENLY MOON</t>
-  </si>
-  <si>
-    <t>Infinite Leveling: Murim</t>
-  </si>
-  <si>
-    <t>Volcanic Age</t>
-  </si>
-  <si>
-    <t>Chronicles Of A Returner</t>
-  </si>
-  <si>
-    <t>The Undefeatable Swordsman</t>
-  </si>
-  <si>
-    <t>Second Life of Dongfang Bubai</t>
-  </si>
-  <si>
-    <t>Job Change: I Became The Undead Monarch</t>
-  </si>
-  <si>
-    <t>Relife Player</t>
-  </si>
-  <si>
-    <t>My Lucky Encounter From The Game Turned Into Reality</t>
-  </si>
-  <si>
-    <t>I Killed an Academy Player</t>
-  </si>
-  <si>
-    <t>Bloodhound’s Regression Instinct</t>
-  </si>
-  <si>
-    <t>I Raised the Yandere Villain Empress</t>
-  </si>
-  <si>
-    <t>The Max-Level Player’s 100th Regression</t>
-  </si>
-  <si>
-    <t>The Heavenly Demon Can't Live A Normal Life</t>
-  </si>
-  <si>
-    <t>The Player That Can't Level Up</t>
-  </si>
-  <si>
-    <t>Reborn As The Enemy Prince</t>
-  </si>
-  <si>
-    <t>The Archmage's Restaurant</t>
-  </si>
-  <si>
-    <t>I Rely on My Invincibility to Deal Tons of Damage Passively!</t>
-  </si>
-  <si>
-    <t>Wild West Murim</t>
-  </si>
-  <si>
-    <t>Monster Pet Evolution</t>
-  </si>
-  <si>
-    <t>The Strongest Sect Of All Times</t>
-  </si>
-  <si>
-    <t>Youngest Scion Of The Mages</t>
-  </si>
-  <si>
-    <t>I Will Do Whatever I Want In Ten Thousand Years</t>
-  </si>
-  <si>
-    <t>Genkai Level 1 Kara No Nariagari: Saijaku Level No Ore Ga Isekai Saikyou Ni Naru Made</t>
-  </si>
-  <si>
-    <t>How to Live at the Max Level</t>
-  </si>
-  <si>
-    <t>The All-Knowing Cultivator</t>
-  </si>
-  <si>
-    <t>Kurasu ≪Mushoku≫ No Eiyuu-Tan ~Koushaku-Ka O Tsuihou Sareta Ga, Jitsu Wa Nagutta Dake De Sukiru O Kakutoku Dekiru To Wakari, Tairiku Ichi No Eiyuu Ni Nobori Tsumeru</t>
-  </si>
-  <si>
-    <t>Villager A Wants To Save The Villainess No Matter What!</t>
-  </si>
-  <si>
-    <t>Savage Hero</t>
-  </si>
-  <si>
-    <t>Genkai Koe No Tenpu wa, Tensei-sha ni Shika Atsukaenai Overlimit Skill Holders</t>
-  </si>
-  <si>
-    <t>Maken Tsukai No Moto Shounen Hei Wa, Moto Teki Kanbu No Onee-San To Issho Ni Ikitai</t>
-  </si>
-  <si>
-    <t>Mannen D-Rank No Chuunen Boukensha, Yotta Ikioi De Densetsu No Ken Wo Hikkonuku</t>
-  </si>
-  <si>
-    <t>Dungeon Sherpa: Meikyuu Michisaki Annainin</t>
-  </si>
-  <si>
-    <t>A Sword Master Childhood Friend Power Harassed Me Harshly, So I Broke Off Our Relationship And Made A Fresh Start At The Frontier As A Magic Swordsman</t>
-  </si>
-  <si>
-    <t>I Summoned The Devil To Grant Me A Wish, But I Married Her Instead Since She Was Adorable ~My New Devil Wife~</t>
-  </si>
-  <si>
-    <t>A Story About A Dragon And The Rising Of An Adventurer</t>
-  </si>
-  <si>
-    <t>After Being Called A Hero: The Unrivaled Man Starts A Family</t>
-  </si>
-  <si>
-    <t>A Warrior Exiled By The Hero And His Lover</t>
-  </si>
-  <si>
-    <t>Nimotsu Mochi No Nousuji Musou</t>
-  </si>
-  <si>
-    <t>The Strongest Dull Prince’s Secret Battle for the Throne</t>
-  </si>
-  <si>
-    <t>The Sword of Princess Gluttony</t>
-  </si>
-  <si>
-    <t>Wistoria's Wand And Sword</t>
-  </si>
-  <si>
-    <t>The Crafty Mage: Frontier Settling Made Easy</t>
-  </si>
-  <si>
-    <t>Delivery Man From Murim</t>
-  </si>
-  <si>
-    <t>Henkyou Gurashi No Maou, Tensei Shite Saikyou No Majutsushi Ni Naru</t>
-  </si>
-  <si>
-    <t>The Executed Sage Is Reincarnated As A Lich And Starts An All-Out War</t>
-  </si>
-  <si>
-    <t>Dungeon Ni Hisomu Yandere Na Kanojo Ni Ore Wa Nando Mo Korosareru</t>
-  </si>
-  <si>
-    <t>I Became A Big-Shot On The Heavenly Leaderboard</t>
-  </si>
-  <si>
-    <t>The Dark Magician Transmigrates After 66666 Years</t>
-  </si>
-  <si>
-    <t>Reaper Of The Drifting Moon</t>
-  </si>
-  <si>
-    <t>The Unbeatable Dungeon's Lazy Boss Monster</t>
-  </si>
-  <si>
-    <t>All My Abilities Are Forbidden Spells</t>
-  </si>
-  <si>
-    <t>How To Survive As A Dragon With Time-Limit</t>
-  </si>
-  <si>
-    <t>Myst, Might, Mayhem</t>
-  </si>
-  <si>
-    <t>Dark And Light Martial Emperor</t>
-  </si>
-  <si>
-    <t>The doomsday ruthless man: hoarding trillions of supplies at the beginning</t>
-  </si>
-  <si>
-    <t>Becoming the Swordmaster Rank Young Lord of the Sichuan Tang Family</t>
-  </si>
-  <si>
-    <t>This Account Is Ridiculous</t>
-  </si>
-  <si>
-    <t>The Mysterious World’s Greatest Martial Artist Little Prince</t>
-  </si>
-  <si>
-    <t>The Reborn Young Lord Is An Assassin</t>
-  </si>
-  <si>
-    <t>God-Slaying Copycat</t>
-  </si>
-  <si>
-    <t>The Great Mage Of The Hero’S Party Reincarnates</t>
-  </si>
-  <si>
-    <t>My Brother Is The Chosen One</t>
-  </si>
-  <si>
-    <t>The Max Level Hero Strikes Back</t>
-  </si>
-  <si>
-    <t>Overlord of Insects</t>
-  </si>
-  <si>
-    <t>Game Of Familia: Kazoku Senki</t>
-  </si>
-  <si>
-    <t>Grand General</t>
-  </si>
-  <si>
-    <t>The Legendary Spearman Returns</t>
-  </si>
-  <si>
-    <t>Ice lord</t>
-  </si>
-  <si>
-    <t>My Inventory is Abnormal</t>
-  </si>
-  <si>
-    <t>Escort Agency Of The Apocalypse</t>
-  </si>
-  <si>
-    <t>The Heavenly Demon Will Give You a Massage</t>
-  </si>
-  <si>
-    <t>The Twin Swords Of The Sima</t>
-  </si>
-  <si>
-    <t>Versatile Sword Cultivator</t>
-  </si>
-  <si>
-    <t>Asura</t>
-  </si>
-  <si>
-    <t>Magic Academy’s Genius Blinker</t>
-  </si>
-  <si>
-    <t>Worthless Profession: Dragon Tamer</t>
-  </si>
-  <si>
-    <t>Expelled Hero Is Too Strong</t>
-  </si>
-  <si>
-    <t>The Ten Thousand Clans Invasion: Guardian Of The Rear</t>
-  </si>
-  <si>
-    <t>My Disciple Became the Great Demon Empress?!</t>
-  </si>
-  <si>
-    <t>The Greatest In The World</t>
-  </si>
-  <si>
-    <t>Drawing: The Greatest Mangaka Becomes A Skilled “Martial Artist” In Another World</t>
+    <t xml:space="preserve">Peerless Quest – The Cheat Skill Only I Can Use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isekai De Haishin Katsudou Wo Shitara Tairyou No Yandere Shinja Wo Umidashite Shimatta Ken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boundless Necromancer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Academy’S Genius Swordsman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demon Evolution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Iron-Blooded Necromancer Has Returned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infinite Mage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Star Instructor  Master Baek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Story Of Thorny Spear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blade debt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martial God Regressed To Level 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What, You Dare Pretend In Front Of Me, The Strongest In The Immortal World?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminally-Ill Genius Dark Knight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heavenly Inquisition Sword</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tsuki Ga Michibiku Isekai Douchuu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Emperor’s Sword</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Constellations Are My Disciples</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenge of the Iron-Blooded Sword Hound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Zombie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master: This Villainous Disciple Is Not The Holy Child</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo Max-Level Newbie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murim Login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Great Villain Who Threatened to Kill Himself</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon Maker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Reincarnated Assassin is a Genius Swordsman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I was more overpowered than the hero, so I hid my power!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Million Times Attack Speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I am the descendant of the Divine Dragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hero X Demon Queen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Records Of The Demonic Path’S Return</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Five-Dimensional Zone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legendary Youngest Son Of The Marquis House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I am fated villain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return Of The Mount Hua Sect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beyond Myriad Peoples</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nano Machine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tensei Shitara Dai Nana Ouji Dattanode, Kimamani Majutsu O Kiwamemasu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scoring the Sacred Body of the Ancients from the Get-go</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magic Emperor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martial Peak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Self-Disciplined Me Is Practically Invincible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Power: I Can Control All The Elements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Slayer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightning Degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The World's Best Sect Of Dependency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Return Of Apocalypses Tyrant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What Do You Do When You Suddenly Become An Immortal?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tales Of Demons And Gods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Kingdoms Of Ruin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Necromancer Academy And The Genius Summoner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yuan Zun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Greatest Estate Designer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conqueror of modern martial arts Kang Haejin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Records Of The Swordsman Scholar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Scholar's Reincarnation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tale of a Scribe Who Retires To The Countryside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return Of The Bachelor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnation Of The Murim Clan's Former Ranker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regressing with the King’s Power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Last Cultivator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEAVENLY MOON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infinite Leveling: Murim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volcanic Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chronicles Of A Returner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Undefeatable Swordsman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Second Life of Dongfang Bubai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job Change: I Became The Undead Monarch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relife Player</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Lucky Encounter From The Game Turned Into Reality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Killed an Academy Player</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bloodhound’s Regression Instinct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Raised the Yandere Villain Empress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Max-Level Player’s 100th Regression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Heavenly Demon Can't Live A Normal Life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Player That Can't Level Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reborn As The Enemy Prince</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Archmage's Restaurant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Rely on My Invincibility to Deal Tons of Damage Passively!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wild West Murim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster Pet Evolution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Strongest Sect Of All Times</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Youngest Scion Of The Mages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Will Do Whatever I Want In Ten Thousand Years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genkai Level 1 Kara No Nariagari: Saijaku Level No Ore Ga Isekai Saikyou Ni Naru Made</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How to Live at the Max Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The All-Knowing Cultivator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurasu ≪Mushoku≫ No Eiyuu-Tan ~Koushaku-Ka O Tsuihou Sareta Ga, Jitsu Wa Nagutta Dake De Sukiru O Kakutoku Dekiru To Wakari, Tairiku Ichi No Eiyuu Ni Nobori Tsumeru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villager A Wants To Save The Villainess No Matter What!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Savage Hero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genkai Koe No Tenpu wa, Tensei-sha ni Shika Atsukaenai Overlimit Skill Holders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maken Tsukai No Moto Shounen Hei Wa, Moto Teki Kanbu No Onee-San To Issho Ni Ikitai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mannen D-Rank No Chuunen Boukensha, Yotta Ikioi De Densetsu No Ken Wo Hikkonuku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dungeon Sherpa: Meikyuu Michisaki Annainin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Sword Master Childhood Friend Power Harassed Me Harshly, So I Broke Off Our Relationship And Made A Fresh Start At The Frontier As A Magic Swordsman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Summoned The Devil To Grant Me A Wish, But I Married Her Instead Since She Was Adorable ~My New Devil Wife~</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Story About A Dragon And The Rising Of An Adventurer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After Being Called A Hero: The Unrivaled Man Starts A Family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Warrior Exiled By The Hero And His Lover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimotsu Mochi No Nousuji Musou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Strongest Dull Prince’s Secret Battle for the Throne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Sword of Princess Gluttony</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wistoria's Wand And Sword</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Crafty Mage: Frontier Settling Made Easy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delivery Man From Murim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Henkyou Gurashi No Maou, Tensei Shite Saikyou No Majutsushi Ni Naru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Executed Sage Is Reincarnated As A Lich And Starts An All-Out War</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dungeon Ni Hisomu Yandere Na Kanojo Ni Ore Wa Nando Mo Korosareru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Became A Big-Shot On The Heavenly Leaderboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Dark Magician Transmigrates After 66666 Years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reaper Of The Drifting Moon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Unbeatable Dungeon's Lazy Boss Monster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All My Abilities Are Forbidden Spells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How To Survive As A Dragon With Time-Limit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myst, Might, Mayhem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark And Light Martial Emperor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The doomsday ruthless man: hoarding trillions of supplies at the beginning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Becoming the Swordmaster Rank Young Lord of the Sichuan Tang Family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This Account Is Ridiculous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Mysterious World’s Greatest Martial Artist Little Prince</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Reborn Young Lord Is An Assassin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">God-Slaying Copycat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Great Mage Of The Hero’S Party Reincarnates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Brother Is The Chosen One</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Max Level Hero Strikes Back</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overlord of Insects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Game Of Familia: Kazoku Senki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grand General</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Legendary Spearman Returns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ice lord</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Inventory is Abnormal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escort Agency Of The Apocalypse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Heavenly Demon Will Give You a Massage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Twin Swords Of The Sima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Versatile Sword Cultivator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magic Academy’s Genius Blinker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worthless Profession: Dragon Tamer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expelled Hero Is Too Strong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Ten Thousand Clans Invasion: Guardian Of The Rear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Disciple Became the Great Demon Empress?!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Greatest In The World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drawing: The Greatest Mangaka Becomes A Skilled “Martial Artist” In Another World</t>
   </si>
   <si>
     <r>
@@ -552,7 +547,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t>～</t>
+      <t xml:space="preserve">～</t>
     </r>
     <r>
       <rPr>
@@ -562,687 +557,690 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t>I Returned To The Past To Rewrite It As The World's Strongest</t>
+      <t xml:space="preserve">I Returned To The Past To Rewrite It As The World's Strongest</t>
     </r>
   </si>
   <si>
-    <t>Hundreds of Invincible Strikes</t>
-  </si>
-  <si>
-    <t>arctic cold war</t>
-  </si>
-  <si>
-    <t>Apocalyptic Super Farm</t>
-  </si>
-  <si>
-    <t>Sword Sheath's Child</t>
-  </si>
-  <si>
-    <t>Reincarnator</t>
-  </si>
-  <si>
-    <t>Hunter Academy’S Strongest Battle God</t>
-  </si>
-  <si>
-    <t>Childhood Friend of the Zenith</t>
-  </si>
-  <si>
-    <t>Absolute Regression</t>
-  </si>
-  <si>
-    <t>Warrior Grandpa And Supreme Granddaughter</t>
-  </si>
-  <si>
-    <t>I Scared the Divine Lord as I Handed over the Ancient Immortal Pill</t>
-  </si>
-  <si>
-    <t>I Become a Legendary Arch Mage by Reading a Book</t>
-  </si>
-  <si>
-    <t>Hiding a logistics center in the apocalypse</t>
-  </si>
-  <si>
-    <t>The Hated Black Mage Returns</t>
-  </si>
-  <si>
-    <t>The Masters Are Subscribing To Me</t>
-  </si>
-  <si>
-    <t>A Ranker's Guide To The Good Life</t>
-  </si>
-  <si>
-    <t>Black Serpent</t>
-  </si>
-  <si>
-    <t>Conquering the Academy with Just a Sashimi Knife</t>
-  </si>
-  <si>
-    <t>The Magic Genius Of The Marquis House</t>
-  </si>
-  <si>
-    <t>The Reversal Of My Life As A Side Character</t>
-  </si>
-  <si>
-    <t>Absolute Dominion</t>
-  </si>
-  <si>
-    <t>Fatal Reset</t>
-  </si>
-  <si>
-    <t>The Necromancer Family’s Young Heir</t>
-  </si>
-  <si>
-    <t>Starting As A Master Of Female Disciples' Leisure Skills</t>
-  </si>
-  <si>
-    <t>Song Baek</t>
-  </si>
-  <si>
-    <t>Surviving as a Genius on Borrowed Time</t>
-  </si>
-  <si>
-    <t>The Regressed Mercenary’s Machinations</t>
-  </si>
-  <si>
-    <t>Traveling Through Time And Space To Become An Unlucky Npc: I Have A Wife To Protect Me</t>
-  </si>
-  <si>
-    <t>Cultivation: The Heaven's Fated Useless Genius</t>
-  </si>
-  <si>
-    <t>The Edgeless Sword From The Village</t>
-  </si>
-  <si>
-    <t>Levelling Up In An Exclusive Dungeon</t>
-  </si>
-  <si>
-    <t>Reincarnated As A Genius Prodigy Of A Prestigious Family</t>
-  </si>
-  <si>
-    <t>From Goblin To Goblin God</t>
-  </si>
-  <si>
-    <t>Margrave’S Bastard Son Was The Emperor</t>
-  </si>
-  <si>
-    <t>The Second Eunuch Regains His Manhood</t>
-  </si>
-  <si>
-    <t>Return Of The Runebound Professor</t>
-  </si>
-  <si>
-    <t>Regressing as the Reincarnated Bastard of the Sword Clan</t>
-  </si>
-  <si>
-    <t>I, The Demon Lord, Am Being Targeted By My Female Disciples!</t>
-  </si>
-  <si>
-    <t>Fated to Be Loved by Villains</t>
-  </si>
-  <si>
-    <t>The Chaebeol’s Youngest Son</t>
-  </si>
-  <si>
-    <t>Heavenly Demon Wants To Be A Chef</t>
-  </si>
-  <si>
-    <t>Entomologist In Sichuan Tang Clan</t>
-  </si>
-  <si>
-    <t>Last Word of the World</t>
-  </si>
-  <si>
-    <t>Cosmic Heavenly Demon 3077</t>
-  </si>
-  <si>
-    <t>Solo Resurrection</t>
-  </si>
-  <si>
-    <t>Dao of the Bizarre Immortal</t>
-  </si>
-  <si>
-    <t>Tenkaichi: Nihon Saikyou Bugeisha Ketteisen</t>
-  </si>
-  <si>
-    <t>Reincarnation Of The Heavenly Demon</t>
-  </si>
-  <si>
-    <t>Black Corporation: Joseon</t>
-  </si>
-  <si>
-    <t>Perhaps Invincible</t>
-  </si>
-  <si>
-    <t>The mad gate</t>
-  </si>
-  <si>
-    <t>Surviving the Apocalypse</t>
-  </si>
-  <si>
-    <t>Genius Prismatic Mage</t>
-  </si>
-  <si>
-    <t>Becoming a God, Starting as water monkey</t>
-  </si>
-  <si>
-    <t>I Became the Successor of the Martial God</t>
-  </si>
-  <si>
-    <t>Regression of the Yong Clan Heir</t>
-  </si>
-  <si>
-    <t>Chronicles of the Reincarnated Demon God</t>
-  </si>
-  <si>
-    <t>Revenge Of the Bloom Flower</t>
-  </si>
-  <si>
-    <t>The Heavenly Demon Wants a Quiet Life</t>
-  </si>
-  <si>
-    <t>Monster General Recorded Legacy</t>
-  </si>
-  <si>
-    <t>Using My Cooking Skills in a Murim World</t>
-  </si>
-  <si>
-    <t>I’m a Martial Art Villainess, but I’m the Strongest!</t>
-  </si>
-  <si>
-    <t>Metcha Shoukan Sareta Ken</t>
-  </si>
-  <si>
-    <t>Mount Hua Sect's Genius Phantom Swordsman</t>
-  </si>
-  <si>
-    <t>I'm going to destroy this country</t>
-  </si>
-  <si>
-    <t>The New Beggars' Sect</t>
-  </si>
-  <si>
-    <t>Overgeared</t>
-  </si>
-  <si>
-    <t>Regressed life of the Sword Clan’s Ignoble Reincarnator</t>
-  </si>
-  <si>
-    <t>Black Fox: Sword Master Of Mount Kunlun</t>
-  </si>
-  <si>
-    <t>God-level Assassin, I’m the Shadow</t>
-  </si>
-  <si>
-    <t>War Of The Corpses</t>
-  </si>
-  <si>
-    <t>The Illegitimate Who Devours Weapons</t>
-  </si>
-  <si>
-    <t>The Great Sage of the Namgung Clan</t>
-  </si>
-  <si>
-    <t>Limitless Ascension: Strength Amid Adversity</t>
-  </si>
-  <si>
-    <t>Apocalypse: Cockroaches Gives Me Buff</t>
-  </si>
-  <si>
-    <t>The Legendary Hero is an Academy Honors Student</t>
-  </si>
-  <si>
-    <t>Like a Fiery Flame</t>
-  </si>
-  <si>
-    <t>The Magic Tower's Problem Child</t>
-  </si>
-  <si>
-    <t>I Became the Husband of the Cult Leader of the Demonic Sect</t>
-  </si>
-  <si>
-    <t>The Apocalypse is Here</t>
-  </si>
-  <si>
-    <t>If I Don’t Die Soon, I Will Rule The Demon Realm</t>
-  </si>
-  <si>
-    <t>I Will Raise This Family to Greatness</t>
-  </si>
-  <si>
-    <t>The Villain Wants to Live</t>
-  </si>
-  <si>
-    <t>Genius Archer’s Livestreaming</t>
-  </si>
-  <si>
-    <t>After Ten Millennia in Hell</t>
-  </si>
-  <si>
-    <t>Heavenly Grand Archive's Young Master</t>
-  </si>
-  <si>
-    <t>Space Cheon-ma 3077</t>
-  </si>
-  <si>
-    <t>Iljin Romance</t>
-  </si>
-  <si>
-    <t>Shut Up, Evil Dragon! I Don't Want to Raise a Child With You Anymore</t>
-  </si>
-  <si>
-    <t>On the Way to Meet Mom</t>
-  </si>
-  <si>
-    <t>Ultimate Shut-in</t>
-  </si>
-  <si>
-    <t>The beginning after the end</t>
-  </si>
-  <si>
-    <t>Reborn in a Cyber Cultivation World, I Fight My Way to the Top</t>
-  </si>
-  <si>
-    <t>Level 999 Goblin</t>
-  </si>
-  <si>
-    <t>Dominating the Wasteland: I Control an Immortal Sect in the Apocalypse</t>
-  </si>
-  <si>
-    <t>Starting As The God Of Wealth, Taming Billions Of Divine Pets!</t>
-  </si>
-  <si>
-    <t>Martial Evolution: Start by Awakening the King of Monsters</t>
-  </si>
-  <si>
-    <t>The Girl from Random Chatting</t>
-  </si>
-  <si>
-    <t>Return of the Legend</t>
-  </si>
-  <si>
-    <t>Elven Queen</t>
-  </si>
-  <si>
-    <t>Emperor of Solo Play</t>
-  </si>
-  <si>
-    <t>The Fox-Eyed Villain of the Demon Academy</t>
-  </si>
-  <si>
-    <t>The Awakening Contract</t>
-  </si>
-  <si>
-    <t>The Sword God From a Fallen World</t>
-  </si>
-  <si>
-    <t>I Awakened to the Ex Skill "Fixed Damage" and Became Invincible</t>
-  </si>
-  <si>
-    <t>Warrior of the Mind Sword</t>
-  </si>
-  <si>
-    <t>Ninja Reincarnation: Fuuma Kotarou’s Quest to Reclaim His Humanity</t>
-  </si>
-  <si>
-    <t>Empress Maria</t>
-  </si>
-  <si>
-    <t>Reincarnation of the Fist King</t>
-  </si>
-  <si>
-    <t>There Are No Bad Warriors in the World</t>
-  </si>
-  <si>
-    <t>Return From The Depth</t>
-  </si>
-  <si>
-    <t>Return of the Apocalypse-Class Death Knight</t>
-  </si>
-  <si>
-    <t>Oversummoned, Overpowered, and Over It!</t>
-  </si>
-  <si>
-    <t>A Rogue Guard in a Medieval Fantasy</t>
-  </si>
-  <si>
-    <t>Chronicles of the Lazy Sovereign</t>
-  </si>
-  <si>
-    <t>I Was the Final Boss</t>
-  </si>
-  <si>
-    <t>The Tang Clan Chronicles</t>
-  </si>
-  <si>
-    <t>The Demon-Slaying Madman—reborn as a demon</t>
-  </si>
-  <si>
-    <t>Urek Mazino</t>
-  </si>
-  <si>
-    <t>Demonic Sect Frontline: Thirteen Flying Dragons</t>
-  </si>
-  <si>
-    <t>Goddess of Abundance and the Genius Rogue Apostle</t>
-  </si>
-  <si>
-    <t>New Goguryeo Chronicles</t>
-  </si>
-  <si>
-    <t>Devil Summoner, I am the Abyss Lord</t>
-  </si>
-  <si>
-    <t>Legend of Dangun</t>
-  </si>
-  <si>
-    <t>The Tale of the Skeleton Messenger</t>
-  </si>
-  <si>
-    <t>The Great Heavenly Demon Sovereign</t>
-  </si>
-  <si>
-    <t>A Regressor's Tale of Cultivation</t>
-  </si>
-  <si>
-    <t>Jade of the Eight Gates</t>
-  </si>
-  <si>
-    <t>Disciple of the Three Kings</t>
-  </si>
-  <si>
-    <t>After the School Belle Dumped Me, I Became a Martial Arts God</t>
-  </si>
-  <si>
-    <t>Dead Mansion</t>
-  </si>
-  <si>
-    <t>Return of the King of Hell</t>
-  </si>
-  <si>
-    <t>Plaything</t>
-  </si>
-  <si>
-    <t>The Regressor Protects Only Me</t>
-  </si>
-  <si>
-    <t>Full-Time Awakening</t>
-  </si>
-  <si>
-    <t>Rebirth of the Divine Demon</t>
-  </si>
-  <si>
-    <t>Return of the First Patriarch: The Strongest Reincarnates into His Descendant 1000 Years Later</t>
-  </si>
-  <si>
-    <t>Lv. 99 Princess of Black Flame</t>
-  </si>
-  <si>
-    <t>Battle of the Martial Masters</t>
-  </si>
-  <si>
-    <t>The Yellow-haired Villain in Female Main Character's Novel wants Happiness</t>
-  </si>
-  <si>
-    <t>From Six to Sovereignty: The Girl Who Ruled</t>
-  </si>
-  <si>
-    <t>Eat and Go</t>
-  </si>
-  <si>
-    <t>I Shall Seal the Heavens</t>
-  </si>
-  <si>
-    <t>The Executed Sage Who Was Reincarnated as a Lich and Started an All-Out War</t>
-  </si>
-  <si>
-    <t>Demon Instructor's Return</t>
-  </si>
-  <si>
-    <t>The Archduke's Bride Is a Hell Warrior</t>
-  </si>
-  <si>
-    <t>Solo Leveling: Ragnarok</t>
-  </si>
-  <si>
-    <t>I Became a Patron of Villains</t>
-  </si>
-  <si>
-    <t>Black Crow</t>
-  </si>
-  <si>
-    <t>The Marquis Is the Marital Archduke</t>
-  </si>
-  <si>
-    <t>Dukedom's Legendary Prodigy</t>
-  </si>
-  <si>
-    <t>Reincarnated as the Crazed Heir</t>
-  </si>
-  <si>
-    <t>Lord of the Apocalypse</t>
-  </si>
-  <si>
-    <t>Don't Tell Me You Think Cultivating Immortality Is Difficult?</t>
-  </si>
-  <si>
-    <t>Immortal Fairy, Please Listen to My Explanation</t>
-  </si>
-  <si>
-    <t>Maplestory: The Last Adventurer</t>
-  </si>
-  <si>
-    <t>The Steel Emperor</t>
-  </si>
-  <si>
-    <t>The Luoyang Branch of the Heavenly Demon Cult</t>
-  </si>
-  <si>
-    <t>Spirit Hunter</t>
-  </si>
-  <si>
-    <t>Player of the Fallen Family</t>
-  </si>
-  <si>
-    <t>Unrivaled Spear Ghost</t>
-  </si>
-  <si>
-    <t>Reincarnation of the Martial God</t>
-  </si>
-  <si>
-    <t>After Rebirth, I Used Mirror Reversal For Vengeance</t>
-  </si>
-  <si>
-    <t>Death Attribute Magician</t>
-  </si>
-  <si>
-    <t>The Great Emperor Shinmadae</t>
-  </si>
-  <si>
-    <t>Revenger: Apocalypse of Vengeance</t>
-  </si>
-  <si>
-    <t>Hiding Out in an Apocalypse</t>
-  </si>
-  <si>
-    <t>Bad Born Blood</t>
-  </si>
-  <si>
-    <t>KaguRai: Kagura to Raito</t>
-  </si>
-  <si>
-    <t>Reincarnated as the Lazy and Villainous Noble, I Broke the Scenario and Became the Most Formidable With Extraordinary Magic</t>
-  </si>
-  <si>
-    <t>Star Armor꞉ I’ll Slaughter Through the Chaos with Star Soul Generals</t>
-  </si>
-  <si>
-    <t>The Demon King Overrun by Heroes</t>
-  </si>
-  <si>
-    <t>The Monkey King’s Journey to the Murim</t>
-  </si>
-  <si>
-    <t>The Sage who returned from another world wants to live quietly</t>
-  </si>
-  <si>
-    <t>Returned from Another World, Earth Turned Out to Be Quite the Fantasy Too. Also, Losing Heroines, Stop Looking This Way</t>
-  </si>
-  <si>
-    <t>Embodiment of the Assassin in the Murim World</t>
-  </si>
-  <si>
-    <t>Märchen - The Embodiment of Tales</t>
-  </si>
-  <si>
-    <t>Sichuan’s Supreme King</t>
-  </si>
-  <si>
-    <t>The Cold-Blooded Warrior</t>
-  </si>
-  <si>
-    <t>Everyone Loves Her</t>
-  </si>
-  <si>
-    <t>Paper Tiger</t>
-  </si>
-  <si>
-    <t>The Sword-Eating Swordmaster</t>
-  </si>
-  <si>
-    <t>The World's Best Kunlun Tavern</t>
-  </si>
-  <si>
-    <t>Defense Breaker</t>
-  </si>
-  <si>
-    <t>Worlds Best Assassin</t>
-  </si>
-  <si>
-    <t>The World's Best Martial Arts Instructor</t>
-  </si>
-  <si>
-    <t>How a Realist Hero Rebuilt the Kingdom</t>
-  </si>
-  <si>
-    <t>Sleepy Princess in the Demon Castle</t>
-  </si>
-  <si>
-    <t>To Hell With The Status Window</t>
-  </si>
-  <si>
-    <t>Becoming a Cheat-Level Skill Thief</t>
-  </si>
-  <si>
-    <t>Sichuan's Supreme King</t>
-  </si>
-  <si>
-    <t>Reborn After the Eight Empresses Betrayed Me, Now I’ll Make Them Regret It</t>
-  </si>
-  <si>
-    <t>Rebirth of the Demon Lord: the Slave who Conquered Fate</t>
-  </si>
-  <si>
-    <t>The Strongest Wizard Becomes a Countryside Guard After Taking an Arrow to the Knee</t>
-  </si>
-  <si>
-    <t>The Secret Martial Artist of Demonic Blood</t>
-  </si>
-  <si>
-    <t>The Strongest Hero Who Longs For Revenge Will Peerlessly Annihilate With The Power Of Darkness</t>
-  </si>
-  <si>
-    <t>I Became the Scoundrel of the Cheon Family</t>
-  </si>
-  <si>
-    <t>Supreme Demon of Hyungsan</t>
-  </si>
-  <si>
-    <t>Orc Hero Story - Discovery Chronicles</t>
-  </si>
-  <si>
-    <t>Boukun Meika no Hangyakusha -Aster</t>
-  </si>
-  <si>
-    <t>Jakdu</t>
-  </si>
-  <si>
-    <t>Secretly Cultivating by the Demon Cult Leader's Side</t>
-  </si>
-  <si>
-    <t>The Old Prisoner Lives in Solitude</t>
-  </si>
-  <si>
-    <t>Revenge of Young Master Peng</t>
-  </si>
-  <si>
-    <t>Murim’s Dept King</t>
-  </si>
-  <si>
-    <t>My Girlfriend's Friend</t>
-  </si>
-  <si>
-    <t>Teto X Egen</t>
-  </si>
-  <si>
-    <t>Gokusotsu Kraken</t>
-  </si>
-  <si>
-    <t>The Masters of Heaven and Earth</t>
-  </si>
-  <si>
-    <t>Red Storm</t>
-  </si>
-  <si>
-    <t>A Dragon Lives in Kunlun</t>
-  </si>
-  <si>
-    <t>Friend of the Demon King</t>
-  </si>
-  <si>
-    <t>High Martial Arts: Sweeping Through Three Thousand Emperors with One Hand!</t>
-  </si>
-  <si>
-    <t>The Genius Martial Artist Who Remembers Everything</t>
-  </si>
-  <si>
-    <t>The Shepherd Wizard</t>
-  </si>
-  <si>
-    <t>Sovereign of a Hundred Blades: Heir to the Strongest Style</t>
-  </si>
-  <si>
-    <t>Shadow Slave</t>
-  </si>
-  <si>
-    <t>The Tale of Cultivation and Demon Extermination</t>
-  </si>
-  <si>
-    <t>The Former Supreme</t>
-  </si>
-  <si>
-    <t>What a Bountiful Harvest, Demon Lord!</t>
-  </si>
-  <si>
-    <t>sa</t>
-  </si>
-  <si>
-    <t>The Sword Emperor’s Rise of Namgung</t>
-  </si>
-  <si>
-    <t>I Kidnapped the Youngest Daughter of the Sichuan Tang Clan</t>
-  </si>
-  <si>
-    <t>War of Extinction</t>
-  </si>
-  <si>
-    <t>The Divine Demon’s Grand Ascension</t>
+    <t xml:space="preserve">Hundreds of Invincible Strikes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">arctic cold war</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apocalyptic Super Farm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sword Sheath's Child</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunter Academy’S Strongest Battle God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Childhood Friend of the Zenith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Absolute Regression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warrior Grandpa And Supreme Granddaughter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Scared the Divine Lord as I Handed over the Ancient Immortal Pill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Become a Legendary Arch Mage by Reading a Book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hiding a logistics center in the apocalypse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Hated Black Mage Returns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Masters Are Subscribing To Me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Ranker's Guide To The Good Life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Serpent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conquering the Academy with Just a Sashimi Knife</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Magic Genius Of The Marquis House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Reversal Of My Life As A Side Character</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Absolute Dominion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fatal Reset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Necromancer Family’s Young Heir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starting As A Master Of Female Disciples' Leisure Skills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Song Baek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surviving as a Genius on Borrowed Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Regressed Mercenary’s Machinations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traveling Through Time And Space To Become An Unlucky Npc: I Have A Wife To Protect Me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cultivation: The Heaven's Fated Useless Genius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Edgeless Sword From The Village</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Levelling Up In An Exclusive Dungeon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnated As A Genius Prodigy Of A Prestigious Family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From Goblin To Goblin God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margrave’S Bastard Son Was The Emperor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Second Eunuch Regains His Manhood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return Of The Runebound Professor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regressing as the Reincarnated Bastard of the Sword Clan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I, The Demon Lord, Am Being Targeted By My Female Disciples!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fated to Be Loved by Villains</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Chaebeol’s Youngest Son</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heavenly Demon Wants To Be A Chef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entomologist In Sichuan Tang Clan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last Word of the World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cosmic Heavenly Demon 3077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo Resurrection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dao of the Bizarre Immortal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tenkaichi: Nihon Saikyou Bugeisha Ketteisen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnation Of The Heavenly Demon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Corporation: Joseon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perhaps Invincible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The mad gate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surviving the Apocalypse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genius Prismatic Mage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Becoming a God, Starting as water monkey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Became the Successor of the Martial God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regression of the Yong Clan Heir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chronicles of the Reincarnated Demon God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenge Of the Bloom Flower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Heavenly Demon Wants a Quiet Life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster General Recorded Legacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Using My Cooking Skills in a Murim World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I’m a Martial Art Villainess, but I’m the Strongest!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metcha Shoukan Sareta Ken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mount Hua Sect's Genius Phantom Swordsman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I'm going to destroy this country</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The New Beggars' Sect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overgeared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regressed life of the Sword Clan’s Ignoble Reincarnator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Fox: Sword Master Of Mount Kunlun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">God-level Assassin, I’m the Shadow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">War Of The Corpses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Illegitimate Who Devours Weapons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Great Sage of the Namgung Clan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limitless Ascension: Strength Amid Adversity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apocalypse: Cockroaches Gives Me Buff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Legendary Hero is an Academy Honors Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Like a Fiery Flame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Magic Tower's Problem Child</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Became the Husband of the Cult Leader of the Demonic Sect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Apocalypse is Here</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If I Don’t Die Soon, I Will Rule The Demon Realm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Will Raise This Family to Greatness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Villain Wants to Live</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genius Archer’s Livestreaming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After Ten Millennia in Hell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heavenly Grand Archive's Young Master</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Space Cheon-ma 3077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iljin Romance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shut Up, Evil Dragon! I Don't Want to Raise a Child With You Anymore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On the Way to Meet Mom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultimate Shut-in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The beginning after the end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reborn in a Cyber Cultivation World, I Fight My Way to the Top</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level 999 Goblin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominating the Wasteland: I Control an Immortal Sect in the Apocalypse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starting As The God Of Wealth, Taming Billions Of Divine Pets!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martial Evolution: Start by Awakening the King of Monsters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Girl from Random Chatting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return of the Legend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elven Queen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emperor of Solo Play</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Fox-Eyed Villain of the Demon Academy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Awakening Contract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Sword God From a Fallen World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Awakened to the Ex Skill "Fixed Damage" and Became Invincible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warrior of the Mind Sword</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ninja Reincarnation: Fuuma Kotarou’s Quest to Reclaim His Humanity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empress Maria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnation of the Fist King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There Are No Bad Warriors in the World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return From The Depth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return of the Apocalypse-Class Death Knight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oversummoned, Overpowered, and Over It!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Rogue Guard in a Medieval Fantasy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chronicles of the Lazy Sovereign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Was the Final Boss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Tang Clan Chronicles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Demon-Slaying Madman—reborn as a demon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urek Mazino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demonic Sect Frontline: Thirteen Flying Dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goddess of Abundance and the Genius Rogue Apostle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Goguryeo Chronicles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devil Summoner, I am the Abyss Lord</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legend of Dangun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Tale of the Skeleton Messenger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Great Heavenly Demon Sovereign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Regressor's Tale of Cultivation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jade of the Eight Gates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disciple of the Three Kings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After the School Belle Dumped Me, I Became a Martial Arts God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dead Mansion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return of the King of Hell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plaything</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Regressor Protects Only Me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full-Time Awakening</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebirth of the Divine Demon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return of the First Patriarch: The Strongest Reincarnates into His Descendant 1000 Years Later</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lv. 99 Princess of Black Flame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Battle of the Martial Masters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Yellow-haired Villain in Female Main Character's Novel wants Happiness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From Six to Sovereignty: The Girl Who Ruled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eat and Go</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Shall Seal the Heavens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Executed Sage Who Was Reincarnated as a Lich and Started an All-Out War</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demon Instructor's Return</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Archduke's Bride Is a Hell Warrior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo Leveling: Ragnarok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Became a Patron of Villains</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Crow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Marquis Is the Marital Archduke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dukedom's Legendary Prodigy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnated as the Crazed Heir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lord of the Apocalypse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Don't Tell Me You Think Cultivating Immortality Is Difficult?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immortal Fairy, Please Listen to My Explanation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maplestory: The Last Adventurer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Steel Emperor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Luoyang Branch of the Heavenly Demon Cult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spirit Hunter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Player of the Fallen Family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unrivaled Spear Ghost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnation of the Martial God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After Rebirth, I Used Mirror Reversal For Vengeance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Death Attribute Magician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Great Emperor Shinmadae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenger: Apocalypse of Vengeance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hiding Out in an Apocalypse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bad Born Blood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KaguRai: Kagura to Raito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnated as the Lazy and Villainous Noble, I Broke the Scenario and Became the Most Formidable With Extraordinary Magic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Star Armor꞉ I’ll Slaughter Through the Chaos with Star Soul Generals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Demon King Overrun by Heroes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Monkey King’s Journey to the Murim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Sage who returned from another world wants to live quietly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Returned from Another World, Earth Turned Out to Be Quite the Fantasy Too. Also, Losing Heroines, Stop Looking This Way</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embodiment of the Assassin in the Murim World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Märchen - The Embodiment of Tales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sichuan’s Supreme King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Cold-Blooded Warrior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everyone Loves Her</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paper Tiger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Sword-Eating Swordmaster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The World's Best Kunlun Tavern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defense Breaker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worlds Best Assassin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The World's Best Martial Arts Instructor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How a Realist Hero Rebuilt the Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sleepy Princess in the Demon Castle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To Hell With The Status Window</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Becoming a Cheat-Level Skill Thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sichuan's Supreme King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reborn After the Eight Empresses Betrayed Me, Now I’ll Make Them Regret It</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebirth of the Demon Lord: the Slave who Conquered Fate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Strongest Wizard Becomes a Countryside Guard After Taking an Arrow to the Knee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Secret Martial Artist of Demonic Blood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Strongest Hero Who Longs For Revenge Will Peerlessly Annihilate With The Power Of Darkness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Became the Scoundrel of the Cheon Family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supreme Demon of Hyungsan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orc Hero Story - Discovery Chronicles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boukun Meika no Hangyakusha -Aster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jakdu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secretly Cultivating by the Demon Cult Leader's Side</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Old Prisoner Lives in Solitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenge of Young Master Peng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murim’s Dept King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Girlfriend's Friend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teto X Egen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gokusotsu Kraken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Masters of Heaven and Earth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red Storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Dragon Lives in Kunlun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Friend of the Demon King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High Martial Arts: Sweeping Through Three Thousand Emperors with One Hand!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Genius Martial Artist Who Remembers Everything</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Shepherd Wizard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sovereign of a Hundred Blades: Heir to the Strongest Style</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shadow Slave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Tale of Cultivation and Demon Extermination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Former Supreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What a Bountiful Harvest, Demon Lord!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Sword Emperor’s Rise of Namgung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Kidnapped the Youngest Daughter of the Sichuan Tang Clan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">War of Extinction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Divine Demon’s Grand Ascension</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1251,7 +1249,22 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Nimbus Sans"/>
@@ -1300,14 +1313,14 @@
     </fill>
   </fills>
   <borders count="3">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FFD9D9D9"/>
       </left>
@@ -1320,7 +1333,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FFD9D9D9"/>
       </left>
@@ -1336,47 +1349,126 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="5">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF4F81BD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEAF2F8"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1435,74 +1527,57 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:B389" totalsRowShown="0">
-  <autoFilter ref="A1:B389" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:B389" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:B389"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Title"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Episodes"/>
+    <tableColumn id="1" name="Title"/>
+    <tableColumn id="2" name="Episodes"/>
   </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1510,12 +1585,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1544,7 +1619,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1565,7 +1640,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1616,7 +1691,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1634,26 +1709,27 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:B393"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="169" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="169"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.43"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1661,3103 +1737,3103 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="4" t="n">
         <v>878</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="6" t="n">
         <v>266</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="6" t="n">
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="4" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="6" t="n">
         <v>135</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="4" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="4" t="n">
         <v>292</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="4" t="n">
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="4" t="n">
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="6" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="4" t="n">
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="6" t="n">
         <v>223</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="4" t="n">
         <v>162</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="6" t="n">
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="4" t="n">
         <v>117</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="6" t="n">
         <v>85</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="4" t="n">
         <v>182</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="6" t="n">
         <v>175</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="4" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="6" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="4" t="n">
         <v>10.1</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="6" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="4" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="6">
+      <c r="B29" s="6" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30" s="4" t="n">
         <v>105</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="6">
+      <c r="B31" s="6" t="n">
         <v>77</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" s="4" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="6">
+      <c r="B33" s="6" t="n">
         <v>88</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34" s="4" t="n">
         <v>99</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="6">
+      <c r="B35" s="6" t="n">
         <v>157</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36" s="4" t="n">
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="6">
+      <c r="B37" s="6" t="n">
         <v>51</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="4">
+      <c r="B38" s="4" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="6">
+      <c r="B39" s="6" t="n">
         <v>58</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="4">
+      <c r="B40" s="4" t="n">
         <v>124</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="6">
+      <c r="B41" s="6" t="n">
         <v>111</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="4">
+      <c r="B42" s="4" t="n">
         <v>63</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="6">
+      <c r="B43" s="6" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B44" s="4">
+      <c r="B44" s="4" t="n">
         <v>162</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B45" s="6">
+      <c r="B45" s="6" t="n">
         <v>64</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B46" s="4">
+      <c r="B46" s="4" t="n">
         <v>140</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="6">
+      <c r="B47" s="6" t="n">
         <v>168</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="4">
+      <c r="B48" s="4" t="n">
         <v>186</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B49" s="6">
+      <c r="B49" s="6" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B50" s="4">
+      <c r="B50" s="4" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B51" s="6">
+      <c r="B51" s="6" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B52" s="4">
+      <c r="B52" s="4" t="n">
         <v>71</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B53" s="6">
+      <c r="B53" s="6" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B54" s="4">
+      <c r="B54" s="4" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B55" s="6">
+      <c r="B55" s="6" t="n">
         <v>156</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B56" s="4">
+      <c r="B56" s="4" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B57" s="6">
+      <c r="B57" s="6" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B58" s="4">
+      <c r="B58" s="4" t="n">
         <v>144</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B59" s="6">
+      <c r="B59" s="6" t="n">
         <v>329</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B60" s="4">
+      <c r="B60" s="4" t="n">
         <v>161</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B61" s="6">
+      <c r="B61" s="6" t="n">
         <v>275</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B62" s="4">
+      <c r="B62" s="4" t="n">
         <v>311</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B63" s="6">
+      <c r="B63" s="6" t="n">
         <v>175</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B64" s="4">
+      <c r="B64" s="4" t="n">
         <v>58</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B65" s="6">
+      <c r="B65" s="6" t="n">
         <v>851</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B66" s="4">
+      <c r="B66" s="4" t="n">
         <v>3644</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B67" s="6">
+      <c r="B67" s="6" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B68" s="4">
+      <c r="B68" s="4" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B69" s="6">
+      <c r="B69" s="6" t="n">
         <v>76</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B70" s="4">
+      <c r="B70" s="4" t="n">
         <v>220</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B71" s="6">
+      <c r="B71" s="6" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B72" s="4">
+      <c r="B72" s="4" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B73" s="6">
+      <c r="B73" s="6" t="n">
         <v>89</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B74" s="4">
+      <c r="B74" s="4" t="n">
         <v>508.1</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B75" s="6">
+      <c r="B75" s="6" t="n">
         <v>43</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B76" s="4">
+      <c r="B76" s="4" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B77" s="6">
+      <c r="B77" s="6" t="n">
         <v>587</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B78" s="4">
+      <c r="B78" s="4" t="n">
         <v>121</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B79" s="6">
+      <c r="B79" s="6" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B80" s="4">
+      <c r="B80" s="4" t="n">
         <v>157</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B81" s="6">
+      <c r="B81" s="6" t="n">
         <v>156</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B82" s="4">
+      <c r="B82" s="4" t="n">
         <v>235</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B83" s="6">
+      <c r="B83" s="6" t="n">
         <v>188</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B84" s="4">
+      <c r="B84" s="4" t="n">
         <v>106</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B85" s="6">
+      <c r="B85" s="6" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B86" s="4">
+      <c r="B86" s="4" t="n">
         <v>33</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B87" s="6">
+      <c r="B87" s="6" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B88" s="4">
+      <c r="B88" s="4" t="n">
         <v>187</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B89" s="6">
+      <c r="B89" s="6" t="n">
         <v>256</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B90" s="4">
+      <c r="B90" s="4" t="n">
         <v>133</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B91" s="6">
+      <c r="B91" s="6" t="n">
         <v>217</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B92" s="4">
+      <c r="B92" s="4" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B93" s="6">
+      <c r="B93" s="6" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B94" s="4">
+      <c r="B94" s="4" t="n">
         <v>65</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B95" s="6">
+      <c r="B95" s="6" t="n">
         <v>56</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B96" s="4">
+      <c r="B96" s="4" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="6">
+      <c r="B97" s="6" t="n">
         <v>52</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B98" s="4">
+      <c r="B98" s="4" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B99" s="6">
+      <c r="B99" s="6" t="n">
         <v>41</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B100" s="4">
+      <c r="B100" s="4" t="n">
         <v>182</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B101" s="6">
+      <c r="B101" s="6" t="n">
         <v>157</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B102" s="4">
+      <c r="B102" s="4" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B103" s="6">
+      <c r="B103" s="6" t="n">
         <v>103</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B104" s="4">
+      <c r="B104" s="4" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B105" s="6">
+      <c r="B105" s="6" t="n">
         <v>94</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B106" s="4">
+      <c r="B106" s="4" t="n">
         <v>221</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B107" s="6">
+      <c r="B107" s="6" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="108" spans="1:2">
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B108" s="4">
+      <c r="B108" s="4" t="n">
         <v>61</v>
       </c>
     </row>
-    <row r="109" spans="1:2">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B109" s="6">
+      <c r="B109" s="6" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:2">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B110" s="4">
+      <c r="B110" s="4" t="n">
         <v>10.1</v>
       </c>
     </row>
-    <row r="111" spans="1:2">
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="B111" s="6">
+      <c r="B111" s="6" t="n">
         <v>79</v>
       </c>
     </row>
-    <row r="112" spans="1:2">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B112" s="4">
+      <c r="B112" s="4" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="113" spans="1:2">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B113" s="6">
+      <c r="B113" s="6" t="n">
         <v>34</v>
       </c>
     </row>
-    <row r="114" spans="1:2">
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B114" s="4">
+      <c r="B114" s="4" t="n">
         <v>38.1</v>
       </c>
     </row>
-    <row r="115" spans="1:2">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B115" s="6">
+      <c r="B115" s="6" t="n">
         <v>63</v>
       </c>
     </row>
-    <row r="116" spans="1:2">
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B116" s="4">
+      <c r="B116" s="4" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="117" spans="1:2">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B117" s="6">
+      <c r="B117" s="6" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="118" spans="1:2">
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B118" s="4">
+      <c r="B118" s="4" t="n">
         <v>49</v>
       </c>
     </row>
-    <row r="119" spans="1:2">
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B119" s="6">
+      <c r="B119" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="120" spans="1:2">
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B120" s="4">
+      <c r="B120" s="4" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="121" spans="1:2">
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B121" s="6">
+      <c r="B121" s="6" t="n">
         <v>43</v>
       </c>
     </row>
-    <row r="122" spans="1:2">
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B122" s="4">
+      <c r="B122" s="4" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="123" spans="1:2">
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B123" s="6">
+      <c r="B123" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="124" spans="1:2">
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B124" s="4">
+      <c r="B124" s="4" t="n">
         <v>33</v>
       </c>
     </row>
-    <row r="125" spans="1:2">
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B125" s="6">
+      <c r="B125" s="6" t="n">
         <v>7.2</v>
       </c>
     </row>
-    <row r="126" spans="1:2">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B126" s="4">
+      <c r="B126" s="4" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="127" spans="1:2">
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B127" s="6">
+      <c r="B127" s="6" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="128" spans="1:2">
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B128" s="4">
+      <c r="B128" s="4" t="n">
         <v>58</v>
       </c>
     </row>
-    <row r="129" spans="1:2">
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="B129" s="6">
+      <c r="B129" s="6" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="130" spans="1:2">
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B130" s="4">
+      <c r="B130" s="4" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="131" spans="1:2">
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B131" s="6">
+      <c r="B131" s="6" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="132" spans="1:2">
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B132" s="4">
+      <c r="B132" s="4" t="n">
         <v>56</v>
       </c>
     </row>
-    <row r="133" spans="1:2">
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B133" s="6">
+      <c r="B133" s="6" t="n">
         <v>12.2</v>
       </c>
     </row>
-    <row r="134" spans="1:2">
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B134" s="4">
+      <c r="B134" s="4" t="n">
         <v>91</v>
       </c>
     </row>
-    <row r="135" spans="1:2">
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B135" s="6">
+      <c r="B135" s="6" t="n">
         <v>165</v>
       </c>
     </row>
-    <row r="136" spans="1:2">
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B136" s="4">
+      <c r="B136" s="4" t="n">
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="1:2">
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="B137" s="6">
+      <c r="B137" s="6" t="n">
         <v>92</v>
       </c>
     </row>
-    <row r="138" spans="1:2">
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B138" s="4">
+      <c r="B138" s="4" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="139" spans="1:2">
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B139" s="6">
+      <c r="B139" s="6" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="140" spans="1:2">
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B140" s="4">
+      <c r="B140" s="4" t="n">
         <v>90</v>
       </c>
     </row>
-    <row r="141" spans="1:2">
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B141" s="6">
+      <c r="B141" s="6" t="n">
         <v>48</v>
       </c>
     </row>
-    <row r="142" spans="1:2">
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B142" s="4">
+      <c r="B142" s="4" t="n">
         <v>39</v>
       </c>
     </row>
-    <row r="143" spans="1:2">
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="B143" s="6">
+      <c r="B143" s="6" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="144" spans="1:2">
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B144" s="4">
+      <c r="B144" s="4" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="145" spans="1:2">
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B145" s="6">
+      <c r="B145" s="6" t="n">
         <v>123</v>
       </c>
     </row>
-    <row r="146" spans="1:2">
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B146" s="4">
+      <c r="B146" s="4" t="n">
         <v>102</v>
       </c>
     </row>
-    <row r="147" spans="1:2">
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B147" s="6">
+      <c r="B147" s="6" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="148" spans="1:2">
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B148" s="4">
+      <c r="B148" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="149" spans="1:2">
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="B149" s="6">
+      <c r="B149" s="6" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="150" spans="1:2">
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B150" s="4">
+      <c r="B150" s="4" t="n">
         <v>73</v>
       </c>
     </row>
-    <row r="151" spans="1:2">
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B151" s="6">
+      <c r="B151" s="6" t="n">
         <v>55</v>
       </c>
     </row>
-    <row r="152" spans="1:2">
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B152" s="4">
+      <c r="B152" s="4" t="n">
         <v>63</v>
       </c>
     </row>
-    <row r="153" spans="1:2">
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B153" s="6">
+      <c r="B153" s="6" t="n">
         <v>83</v>
       </c>
     </row>
-    <row r="154" spans="1:2">
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B154" s="4">
+      <c r="B154" s="4" t="n">
         <v>139</v>
       </c>
     </row>
-    <row r="155" spans="1:2">
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B155" s="6">
+      <c r="B155" s="6" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="156" spans="1:2">
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B156" s="4">
+      <c r="B156" s="4" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="157" spans="1:2">
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B157" s="6">
+      <c r="B157" s="6" t="n">
         <v>76</v>
       </c>
     </row>
-    <row r="158" spans="1:2">
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B158" s="4">
+      <c r="B158" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="159" spans="1:2">
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B159" s="6">
+      <c r="B159" s="6" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="160" spans="1:2">
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B160" s="4">
+      <c r="B160" s="4" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="161" spans="1:2">
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B161" s="6">
+      <c r="B161" s="6" t="n">
         <v>58</v>
       </c>
     </row>
-    <row r="162" spans="1:2">
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B162" s="4">
+      <c r="B162" s="4" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="163" spans="1:2">
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B163" s="6">
+      <c r="B163" s="6" t="n">
         <v>34</v>
       </c>
     </row>
-    <row r="164" spans="1:2">
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B164" s="4">
+      <c r="B164" s="4" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="165" spans="1:2">
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="B165" s="6">
+      <c r="B165" s="6" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="166" spans="1:2">
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B166" s="4">
+      <c r="B166" s="4" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="167" spans="1:2">
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="B167" s="6">
+      <c r="B167" s="6" t="n">
         <v>61</v>
       </c>
     </row>
-    <row r="168" spans="1:2">
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B168" s="4">
+      <c r="B168" s="4" t="n">
         <v>108</v>
       </c>
     </row>
-    <row r="169" spans="1:2">
+    <row r="169" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="B169" s="6">
+      <c r="B169" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="170" spans="1:2">
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B170" s="4">
+      <c r="B170" s="4" t="n">
         <v>49</v>
       </c>
     </row>
-    <row r="171" spans="1:2">
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="B171" s="6">
+      <c r="B171" s="6" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="172" spans="1:2">
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B172" s="4">
+      <c r="B172" s="4" t="n">
         <v>74</v>
       </c>
     </row>
-    <row r="173" spans="1:2">
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="B173" s="6">
+      <c r="B173" s="6" t="n">
         <v>61</v>
       </c>
     </row>
-    <row r="174" spans="1:2">
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B174" s="4">
+      <c r="B174" s="4" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="175" spans="1:2">
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="B175" s="6">
+      <c r="B175" s="6" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="176" spans="1:2">
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B176" s="4">
+      <c r="B176" s="4" t="n">
         <v>104</v>
       </c>
     </row>
-    <row r="177" spans="1:2">
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="B177" s="6">
+      <c r="B177" s="6" t="n">
         <v>76</v>
       </c>
     </row>
-    <row r="178" spans="1:2">
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B178" s="4">
+      <c r="B178" s="4" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="179" spans="1:2">
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="B179" s="6">
+      <c r="B179" s="6" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="180" spans="1:2">
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B180" s="4">
+      <c r="B180" s="4" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="181" spans="1:2">
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="B181" s="6">
+      <c r="B181" s="6" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="182" spans="1:2">
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B182" s="4">
+      <c r="B182" s="4" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="183" spans="1:2">
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="B183" s="6">
+      <c r="B183" s="6" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="184" spans="1:2">
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B184" s="4">
+      <c r="B184" s="4" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="185" spans="1:2">
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="B185" s="6">
+      <c r="B185" s="6" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="186" spans="1:2">
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B186" s="4">
+      <c r="B186" s="4" t="n">
         <v>95</v>
       </c>
     </row>
-    <row r="187" spans="1:2">
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="B187" s="6">
+      <c r="B187" s="6" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="188" spans="1:2">
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B188" s="4">
+      <c r="B188" s="4" t="n">
         <v>27</v>
       </c>
     </row>
-    <row r="189" spans="1:2">
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="B189" s="6">
+      <c r="B189" s="6" t="n">
         <v>91</v>
       </c>
     </row>
-    <row r="190" spans="1:2">
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B190" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2">
+      <c r="B190" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="B191" s="6">
+      <c r="B191" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="192" spans="1:2">
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B192" s="4">
+      <c r="B192" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="193" spans="1:2">
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B193" s="6">
+      <c r="B193" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="194" spans="1:2">
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B194" s="4">
+      <c r="B194" s="4" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="195" spans="1:2">
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B195" s="6">
+      <c r="B195" s="6" t="n">
         <v>89</v>
       </c>
     </row>
-    <row r="196" spans="1:2">
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B196" s="4">
+      <c r="B196" s="4" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="197" spans="1:2">
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B197" s="6">
+      <c r="B197" s="6" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="198" spans="1:2">
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B198" s="4">
+      <c r="B198" s="4" t="n">
         <v>59</v>
       </c>
     </row>
-    <row r="199" spans="1:2">
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B199" s="6">
+      <c r="B199" s="6" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="200" spans="1:2">
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B200" s="4">
+      <c r="B200" s="4" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="201" spans="1:2">
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="B201" s="6">
+      <c r="B201" s="6" t="n">
         <v>108</v>
       </c>
     </row>
-    <row r="202" spans="1:2">
+    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B202" s="4">
+      <c r="B202" s="4" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="203" spans="1:2">
+    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="B203" s="6">
+      <c r="B203" s="6" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="204" spans="1:2">
+    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B204" s="4">
+      <c r="B204" s="4" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="205" spans="1:2">
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="B205" s="6">
+      <c r="B205" s="6" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="206" spans="1:2">
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B206" s="4">
+      <c r="B206" s="4" t="n">
         <v>17</v>
       </c>
     </row>
-    <row r="207" spans="1:2">
+    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="B207" s="6">
+      <c r="B207" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="208" spans="1:2">
+    <row r="208" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="B208" s="4">
+      <c r="B208" s="4" t="n">
         <v>220</v>
       </c>
     </row>
-    <row r="209" spans="1:2">
+    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="B209" s="6">
+      <c r="B209" s="6" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="210" spans="1:2">
+    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B210" s="4">
+      <c r="B210" s="4" t="n">
         <v>51</v>
       </c>
     </row>
-    <row r="211" spans="1:2">
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="B211" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2">
+      <c r="B211" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B212" s="4">
+      <c r="B212" s="4" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="213" spans="1:2">
+    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="B213" s="6">
+      <c r="B213" s="6" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="214" spans="1:2">
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B214" s="4">
+      <c r="B214" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="215" spans="1:2">
+    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="B215" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="216" spans="1:2">
+      <c r="B215" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="B216" s="4">
+      <c r="B216" s="4" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="217" spans="1:2">
+    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B217" s="6">
+      <c r="B217" s="6" t="n">
         <v>141</v>
       </c>
     </row>
-    <row r="218" spans="1:2">
+    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B218" s="4">
+      <c r="B218" s="4" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="219" spans="1:2">
+    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="B219" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" spans="1:2">
+      <c r="B219" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="B220" s="4">
+      <c r="B220" s="4" t="n">
         <v>49</v>
       </c>
     </row>
-    <row r="221" spans="1:2">
+    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="B221" s="6">
+      <c r="B221" s="6" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="222" spans="1:2">
+    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B222" s="4">
+      <c r="B222" s="4" t="n">
         <v>23</v>
       </c>
     </row>
-    <row r="223" spans="1:2">
+    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="B223" s="6">
+      <c r="B223" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="224" spans="1:2">
+    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B224" s="4">
+      <c r="B224" s="4" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="225" spans="1:2">
+    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="B225" s="6">
+      <c r="B225" s="6" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="226" spans="1:2">
+    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="B226" s="4">
+      <c r="B226" s="4" t="n">
         <v>36</v>
       </c>
     </row>
-    <row r="227" spans="1:2">
+    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="B227" s="6">
+      <c r="B227" s="6" t="n">
         <v>64</v>
       </c>
     </row>
-    <row r="228" spans="1:2">
+    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="B228" s="4">
+      <c r="B228" s="4" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="229" spans="1:2">
+    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="B229" s="6">
+      <c r="B229" s="6" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="230" spans="1:2">
+    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B230" s="4">
+      <c r="B230" s="4" t="n">
         <v>124</v>
       </c>
     </row>
-    <row r="231" spans="1:2">
+    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="B231" s="6">
+      <c r="B231" s="6" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="232" spans="1:2">
+    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="B232" s="4">
+      <c r="B232" s="4" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="233" spans="1:2">
+    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="B233" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234" spans="1:2">
+      <c r="B233" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="B234" s="4">
+      <c r="B234" s="4" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="235" spans="1:2">
+    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="B235" s="6">
+      <c r="B235" s="6" t="n">
         <v>130</v>
       </c>
     </row>
-    <row r="236" spans="1:2">
+    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="B236" s="4">
+      <c r="B236" s="4" t="n">
         <v>67</v>
       </c>
     </row>
-    <row r="237" spans="1:2">
+    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="B237" s="6">
+      <c r="B237" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="238" spans="1:2">
+    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B238" s="4">
+      <c r="B238" s="4" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="239" spans="1:2">
+    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="B239" s="6">
+      <c r="B239" s="6" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="240" spans="1:2">
+    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B240" s="4">
+      <c r="B240" s="4" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="241" spans="1:2">
+    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="B241" s="6">
+      <c r="B241" s="6" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="242" spans="1:2">
+    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="B242" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243" spans="1:2">
+      <c r="B242" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="B243" s="6">
+      <c r="B243" s="6" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="244" spans="1:2">
+    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B244" s="4">
+      <c r="B244" s="4" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="245" spans="1:2">
+    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="B245" s="6">
+      <c r="B245" s="6" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="246" spans="1:2">
+    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="B246" s="4">
+      <c r="B246" s="4" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="247" spans="1:2">
+    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="B247" s="6">
+      <c r="B247" s="6" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="248" spans="1:2">
+    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="B248" s="4">
+      <c r="B248" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="249" spans="1:2">
+    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="B249" s="6">
+      <c r="B249" s="6" t="n">
         <v>81</v>
       </c>
     </row>
-    <row r="250" spans="1:2">
+    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B250" s="4">
+      <c r="B250" s="4" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="251" spans="1:2">
+    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="B251" s="6">
+      <c r="B251" s="6" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="252" spans="1:2">
+    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="B252" s="4">
+      <c r="B252" s="4" t="n">
         <v>57</v>
       </c>
     </row>
-    <row r="253" spans="1:2">
+    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="B253" s="6">
+      <c r="B253" s="6" t="n">
         <v>112</v>
       </c>
     </row>
-    <row r="254" spans="1:2">
+    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B254" s="4">
+      <c r="B254" s="4" t="n">
         <v>126</v>
       </c>
     </row>
-    <row r="255" spans="1:2">
+    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="B255" s="6">
+      <c r="B255" s="6" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="256" spans="1:2">
+    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="B256" s="4">
+      <c r="B256" s="4" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="257" spans="1:2">
+    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="B257" s="6">
+      <c r="B257" s="6" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="258" spans="1:2">
+    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="B258" s="4">
+      <c r="B258" s="4" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="259" spans="1:2">
+    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="B259" s="6">
+      <c r="B259" s="6" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="260" spans="1:2">
+    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="B260" s="4">
+      <c r="B260" s="4" t="n">
         <v>219</v>
       </c>
     </row>
-    <row r="261" spans="1:2">
+    <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="B261" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262" spans="1:2">
+      <c r="B261" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="B262" s="4">
+      <c r="B262" s="4" t="n">
         <v>55</v>
       </c>
     </row>
-    <row r="263" spans="1:2">
+    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="B263" s="6">
+      <c r="B263" s="6" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:2">
+    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="B264" s="4">
+      <c r="B264" s="4" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="265" spans="1:2">
+    <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="B265" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266" spans="1:2">
+      <c r="B265" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="B266" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="267" spans="1:2">
+      <c r="B266" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="B267" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="268" spans="1:2">
+      <c r="B267" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B268" s="4">
+      <c r="B268" s="4" t="n">
         <v>17</v>
       </c>
     </row>
-    <row r="269" spans="1:2">
+    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="B269" s="6">
+      <c r="B269" s="6" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="270" spans="1:2">
+    <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="B270" s="4">
+      <c r="B270" s="4" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="271" spans="1:2">
+    <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="B271" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="272" spans="1:2">
+      <c r="B271" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="B272" s="4">
+      <c r="B272" s="4" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="273" spans="1:2">
+    <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="B273" s="6">
+      <c r="B273" s="6" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="274" spans="1:2">
+    <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="B274" s="4">
+      <c r="B274" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="275" spans="1:2">
+    <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="B275" s="6">
+      <c r="B275" s="6" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="276" spans="1:2">
+    <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="B276" s="4">
+      <c r="B276" s="4" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="277" spans="1:2">
+    <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="B277" s="6">
+      <c r="B277" s="6" t="n">
         <v>34</v>
       </c>
     </row>
-    <row r="278" spans="1:2">
+    <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="B278" s="4">
+      <c r="B278" s="4" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="279" spans="1:2">
+    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="B279" s="6">
+      <c r="B279" s="6" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="280" spans="1:2">
+    <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B280" s="4">
+      <c r="B280" s="4" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="281" spans="1:2">
+    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="B281" s="6">
+      <c r="B281" s="6" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="282" spans="1:2">
+    <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="B282" s="4">
+      <c r="B282" s="4" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="283" spans="1:2">
+    <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="B283" s="6">
+      <c r="B283" s="6" t="n">
         <v>27</v>
       </c>
     </row>
-    <row r="284" spans="1:2">
+    <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="B284" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285" spans="1:2" ht="15.75">
+      <c r="B284" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="B285" s="6">
+      <c r="B285" s="6" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="286" spans="1:2">
+    <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="B286" s="4">
+      <c r="B286" s="4" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="287" spans="1:2">
+    <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="B287" s="6">
+      <c r="B287" s="6" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="288" spans="1:2">
+    <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="B288" s="4">
+      <c r="B288" s="4" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="289" spans="1:2">
+    <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="B289" s="6">
+      <c r="B289" s="6" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="290" spans="1:2">
+    <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="B290" s="4">
+      <c r="B290" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="291" spans="1:2">
+    <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="B291" s="6">
+      <c r="B291" s="6" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="292" spans="1:2">
+    <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="B292" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="293" spans="1:2">
+      <c r="B292" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="B293" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="294" spans="1:2">
+      <c r="B293" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="B294" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="295" spans="1:2">
+      <c r="B294" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="B295" s="6">
+      <c r="B295" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="296" spans="1:2">
+    <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="B296" s="4">
+      <c r="B296" s="4" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="297" spans="1:2">
+    <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="B297" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="298" spans="1:2">
+      <c r="B297" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="B298" s="4">
+      <c r="B298" s="4" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="299" spans="1:2">
+    <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="B299" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300" spans="1:2">
+      <c r="B299" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="B300" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="301" spans="1:2">
+      <c r="B300" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="B301" s="6">
+      <c r="B301" s="6" t="n">
         <v>56</v>
       </c>
     </row>
-    <row r="302" spans="1:2">
+    <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="B302" s="4">
+      <c r="B302" s="4" t="n">
         <v>41</v>
       </c>
     </row>
-    <row r="303" spans="1:2">
+    <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="B303" s="6">
+      <c r="B303" s="6" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="304" spans="1:2">
+    <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="B304" s="4">
+      <c r="B304" s="4" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="305" spans="1:2">
+    <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="B305" s="6">
+      <c r="B305" s="6" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="306" spans="1:2">
+    <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="B306" s="4">
+      <c r="B306" s="4" t="n">
         <v>27</v>
       </c>
     </row>
-    <row r="307" spans="1:2">
+    <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="B307" s="6">
+      <c r="B307" s="6" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="308" spans="1:2">
+    <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="B308" s="4">
+      <c r="B308" s="4" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="309" spans="1:2">
+    <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="B309" s="6">
+      <c r="B309" s="6" t="n">
         <v>57</v>
       </c>
     </row>
-    <row r="310" spans="1:2">
+    <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="B310" s="4">
+      <c r="B310" s="4" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="311" spans="1:2">
+    <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="B311" s="6">
+      <c r="B311" s="6" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="312" spans="1:2">
+    <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="B312" s="4">
+      <c r="B312" s="4" t="n">
         <v>55</v>
       </c>
     </row>
-    <row r="313" spans="1:2">
+    <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="B313" s="6">
+      <c r="B313" s="6" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="314" spans="1:2">
+    <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="B314" s="4">
+      <c r="B314" s="4" t="n">
         <v>32</v>
       </c>
     </row>
-    <row r="315" spans="1:2">
+    <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="B315" s="6">
+      <c r="B315" s="6" t="n">
         <v>47</v>
       </c>
     </row>
-    <row r="316" spans="1:2">
+    <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="B316" s="4">
+      <c r="B316" s="4" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="317" spans="1:2">
+    <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B317" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="318" spans="1:2">
+      <c r="B317" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="B318" s="4">
+      <c r="B318" s="4" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="319" spans="1:2">
+    <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="B319" s="6">
+      <c r="B319" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="320" spans="1:2">
+    <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="B320" s="4">
+      <c r="B320" s="4" t="n">
         <v>161</v>
       </c>
     </row>
-    <row r="321" spans="1:2">
+    <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="B321" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="322" spans="1:2">
+      <c r="B321" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="B322" s="4">
+      <c r="B322" s="4" t="n">
         <v>34</v>
       </c>
     </row>
-    <row r="323" spans="1:2">
+    <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="B323" s="6">
+      <c r="B323" s="6" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="324" spans="1:2">
+    <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="B324" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="325" spans="1:2">
+      <c r="B324" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="B325" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="326" spans="1:2">
+      <c r="B325" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="B326" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="327" spans="1:2">
+      <c r="B326" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="B327" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="328" spans="1:2">
+      <c r="B327" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="B328" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="329" spans="1:2">
+      <c r="B328" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="B329" s="6">
+      <c r="B329" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="330" spans="1:2">
+    <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="B330" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="331" spans="1:2">
+      <c r="B330" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="B331" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="332" spans="1:2">
+      <c r="B331" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="B332" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="333" spans="1:2">
+      <c r="B332" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="B333" s="6">
+      <c r="B333" s="6" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="334" spans="1:2">
+    <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="B334" s="4">
+      <c r="B334" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="335" spans="1:2">
+    <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="B335" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="336" spans="1:2">
+      <c r="B335" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="B336" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="337" spans="1:2">
+      <c r="B336" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="B337" s="6">
+      <c r="B337" s="6" t="n">
         <v>27</v>
       </c>
     </row>
-    <row r="338" spans="1:2">
+    <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="B338" s="4">
+      <c r="B338" s="4" t="n">
         <v>17</v>
       </c>
     </row>
-    <row r="339" spans="1:2">
+    <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="B339" s="6">
+      <c r="B339" s="6" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="340" spans="1:2">
+    <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="B340" s="4">
+      <c r="B340" s="4" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="341" spans="1:2">
+    <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="B341" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="342" spans="1:2">
+      <c r="B341" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="B342" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="343" spans="1:2">
+      <c r="B342" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="B343" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="344" spans="1:2">
+      <c r="B343" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="B344" s="4">
+      <c r="B344" s="4" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="345" spans="1:2">
+    <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="B345" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="346" spans="1:2">
+      <c r="B345" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="B346" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="347" spans="1:2">
+      <c r="B346" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="B347" s="6">
+      <c r="B347" s="6" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="348" spans="1:2">
+    <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="B348" s="4">
+      <c r="B348" s="4" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="349" spans="1:2">
+    <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="B349" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="350" spans="1:2">
+      <c r="B349" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="B350" s="4">
+      <c r="B350" s="4" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="351" spans="1:2">
+    <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="B351" s="6">
+      <c r="B351" s="6" t="n">
         <v>97</v>
       </c>
     </row>
-    <row r="352" spans="1:2">
+    <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="B352" s="4">
+      <c r="B352" s="4" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="353" spans="1:2">
+    <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="B353" s="6">
+      <c r="B353" s="6" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="354" spans="1:2">
+    <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="B354" s="4">
+      <c r="B354" s="4" t="n">
         <v>52</v>
       </c>
     </row>
-    <row r="355" spans="1:2">
+    <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="B355" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="356" spans="1:2">
+      <c r="B355" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="B356" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="357" spans="1:2">
+      <c r="B356" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="B357" s="6">
+      <c r="B357" s="6" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="358" spans="1:2">
+    <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="B358" s="4">
+      <c r="B358" s="4" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="359" spans="1:2">
+    <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="B359" s="6">
+      <c r="B359" s="6" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="360" spans="1:2">
+    <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="B360" s="4">
+      <c r="B360" s="4" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="361" spans="1:2">
+    <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="B361" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="362" spans="1:2">
+      <c r="B361" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="B362" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="363" spans="1:2">
+      <c r="B362" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="B363" s="4">
+      <c r="B363" s="4" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="364" spans="1:2">
+    <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="B364" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="365" spans="1:2">
+      <c r="B364" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B365" s="4">
+      <c r="B365" s="4" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="366" spans="1:2">
+    <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="B366" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="367" spans="1:2">
+      <c r="B366" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="B367" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="368" spans="1:2">
+      <c r="B367" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="B368" s="6">
+      <c r="B368" s="6" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="369" spans="1:2">
+    <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="B369" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="370" spans="1:2">
+      <c r="B369" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="B370" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="371" spans="1:2">
+      <c r="B370" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="B371" s="4">
+      <c r="B371" s="4" t="n">
         <v>71</v>
       </c>
     </row>
-    <row r="372" spans="1:2">
+    <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="B372" s="6">
+      <c r="B372" s="6" t="n">
         <v>49</v>
       </c>
     </row>
-    <row r="373" spans="1:2">
+    <row r="373" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="B373" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="374" spans="1:2">
+      <c r="B373" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="B374" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="375" spans="1:2">
+      <c r="B374" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="B375" s="1">
+      <c r="B375" s="1" t="n">
         <v>114</v>
       </c>
     </row>
-    <row r="376" spans="1:2">
+    <row r="376" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="B376" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="377" spans="1:2">
+      <c r="B376" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="B377" s="1">
+      <c r="B377" s="1" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="378" spans="1:2">
+    <row r="378" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="B378" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="379" spans="1:2">
+      <c r="B378" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="B379" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="380" spans="1:2">
+      <c r="B379" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="B380" s="1">
+      <c r="B380" s="1" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="381" spans="1:2">
+    <row r="381" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="B381" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="382" spans="1:2">
+      <c r="B381" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="B382" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="383" spans="1:2">
+      <c r="B382" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="B383" s="1">
+      <c r="B383" s="1" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="384" spans="1:2">
+    <row r="384" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="B384" s="9">
+      <c r="B384" s="9" t="n">
         <v>36</v>
       </c>
     </row>
-    <row r="385" spans="1:2">
+    <row r="385" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="B385" s="1">
+      <c r="B385" s="1" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="386" spans="1:2">
-      <c r="A386" t="s">
+    <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A386" s="0" t="s">
         <v>385</v>
       </c>
-      <c r="B386" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="387" spans="1:2">
-      <c r="A387" t="s">
+      <c r="B386" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A387" s="0" t="s">
         <v>386</v>
       </c>
-      <c r="B387" s="1">
+      <c r="B387" s="1" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="388" spans="1:2">
+    <row r="388" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="10" t="s">
         <v>387</v>
       </c>
-      <c r="B388" s="1">
+      <c r="B388" s="1" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="389" spans="1:2">
+    <row r="389" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="7" t="s">
         <v>388</v>
       </c>
@@ -4765,42 +4841,47 @@
         <v>389</v>
       </c>
     </row>
-    <row r="390" spans="1:2">
+    <row r="390" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="7" t="s">
         <v>390</v>
       </c>
-      <c r="B390" s="1">
+      <c r="B390" s="1" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="391" spans="1:2">
+    <row r="391" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="B391" s="1">
+      <c r="B391" s="1" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="392" spans="1:2">
+    <row r="392" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="10" t="s">
         <v>392</v>
       </c>
-      <c r="B392" s="1">
+      <c r="B392" s="1" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="393" spans="1:2">
+    <row r="393" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="B393" s="1">
-        <v>23</v>
+      <c r="B393" s="1" t="n">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <tableParts count="1">
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <tableParts>
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>

--- a/Manga.Manhwua/Updated manhwua.xlsx
+++ b/Manga.Manhwua/Updated manhwua.xlsx
@@ -1,21 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Manga\Manga.Manhwua\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E160DCA0-3FBD-467C-A9D5-69CA89779C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -27,511 +22,511 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="394">
   <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Episodes</t>
-  </si>
-  <si>
-    <t>Kingdom</t>
-  </si>
-  <si>
-    <t>Vagabond</t>
-  </si>
-  <si>
-    <t>My Dragon System</t>
-  </si>
-  <si>
-    <t>The Knight King Who Returned With A God</t>
-  </si>
-  <si>
-    <t>The Player Hides His Past</t>
-  </si>
-  <si>
-    <t>Disastrous Necromancer</t>
-  </si>
-  <si>
-    <t>The Priest of Corruption</t>
-  </si>
-  <si>
-    <t>Dragon Emperor Martial God</t>
-  </si>
-  <si>
-    <t>Mookhyang - Dark Lady</t>
-  </si>
-  <si>
-    <t>Leveling Up By Hoarding</t>
-  </si>
-  <si>
-    <t>Master Of The Martial Arts Library</t>
-  </si>
-  <si>
-    <t>Absolute Necromancer</t>
-  </si>
-  <si>
-    <t>Tales Of A Shinning Sword</t>
-  </si>
-  <si>
-    <t>Kyushu Chronicles Of Immortals And Demons</t>
-  </si>
-  <si>
-    <t>Level 1 Player</t>
-  </si>
-  <si>
-    <t>Logging 10,000 Years into the Future</t>
-  </si>
-  <si>
-    <t>Swordmaster’S Youngest Son</t>
-  </si>
-  <si>
-    <t>World’S Greatest Senior Disciple</t>
-  </si>
-  <si>
-    <t>Dragon Master</t>
-  </si>
-  <si>
-    <t>The Return Of The Disaster-Class Hero</t>
-  </si>
-  <si>
-    <t>Solo Farming In The Tower</t>
-  </si>
-  <si>
-    <t>Chronicles Of The Demon Faction</t>
-  </si>
-  <si>
-    <t>Demonic Master Of Mount Kunlun</t>
-  </si>
-  <si>
-    <t>Necromancer's Evolutionary Traits</t>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Episodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vagabond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Dragon System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Knight King Who Returned With A God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Player Hides His Past</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disastrous Necromancer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Priest of Corruption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragon Emperor Martial God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mookhyang - Dark Lady</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leveling Up By Hoarding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master Of The Martial Arts Library</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Absolute Necromancer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tales Of A Shinning Sword</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyushu Chronicles Of Immortals And Demons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level 1 Player</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logging 10,000 Years into the Future</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swordmaster’S Youngest Son</t>
+  </si>
+  <si>
+    <t xml:space="preserve">World’S Greatest Senior Disciple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragon Master</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Return Of The Disaster-Class Hero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo Farming In The Tower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chronicles Of The Demon Faction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demonic Master Of Mount Kunlun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Necromancer's Evolutionary Traits</t>
   </si>
   <si>
     <t xml:space="preserve">Samurai In Another World </t>
   </si>
   <si>
-    <t>Peerless Quest – The Cheat Skill Only I Can Use</t>
-  </si>
-  <si>
-    <t>Isekai De Haishin Katsudou Wo Shitara Tairyou No Yandere Shinja Wo Umidashite Shimatta Ken</t>
-  </si>
-  <si>
-    <t>Boundless Necromancer</t>
-  </si>
-  <si>
-    <t>Academy’S Genius Swordsman</t>
-  </si>
-  <si>
-    <t>Demon Evolution</t>
-  </si>
-  <si>
-    <t>The Iron-Blooded Necromancer Has Returned</t>
-  </si>
-  <si>
-    <t>Infinite Mage</t>
-  </si>
-  <si>
-    <t>Star Instructor  Master Baek</t>
-  </si>
-  <si>
-    <t>The Story Of Thorny Spear</t>
-  </si>
-  <si>
-    <t>Blade debt</t>
-  </si>
-  <si>
-    <t>Martial God Regressed To Level 2</t>
-  </si>
-  <si>
-    <t>What, You Dare Pretend In Front Of Me, The Strongest In The Immortal World?</t>
-  </si>
-  <si>
-    <t>Terminally-Ill Genius Dark Knight</t>
-  </si>
-  <si>
-    <t>Heavenly Inquisition Sword</t>
-  </si>
-  <si>
-    <t>Tsuki Ga Michibiku Isekai Douchuu</t>
-  </si>
-  <si>
-    <t>The Emperor’s Sword</t>
-  </si>
-  <si>
-    <t>The Constellations Are My Disciples</t>
-  </si>
-  <si>
-    <t>Revenge of the Iron-Blooded Sword Hound</t>
-  </si>
-  <si>
-    <t>Mr. Zombie</t>
-  </si>
-  <si>
-    <t>Master: This Villainous Disciple Is Not The Holy Child</t>
-  </si>
-  <si>
-    <t>Solo Max-Level Newbie</t>
-  </si>
-  <si>
-    <t>Murim Login</t>
-  </si>
-  <si>
-    <t>The Great Villain Who Threatened to Kill Himself</t>
-  </si>
-  <si>
-    <t>Weapon Maker</t>
-  </si>
-  <si>
-    <t>The Reincarnated Assassin is a Genius Swordsman</t>
-  </si>
-  <si>
-    <t>I was more overpowered than the hero, so I hid my power!</t>
-  </si>
-  <si>
-    <t>Million Times Attack Speed</t>
-  </si>
-  <si>
-    <t>I am the descendant of the Divine Dragon</t>
-  </si>
-  <si>
-    <t>Hero X Demon Queen</t>
-  </si>
-  <si>
-    <t>Records Of The Demonic Path’S Return</t>
-  </si>
-  <si>
-    <t>Five-Dimensional Zone</t>
-  </si>
-  <si>
-    <t>Legendary Youngest Son Of The Marquis House</t>
-  </si>
-  <si>
-    <t>I am fated villain</t>
-  </si>
-  <si>
-    <t>Return Of The Mount Hua Sect</t>
-  </si>
-  <si>
-    <t>Beyond Myriad Peoples</t>
-  </si>
-  <si>
-    <t>Nano Machine</t>
-  </si>
-  <si>
-    <t>Tensei Shitara Dai Nana Ouji Dattanode, Kimamani Majutsu O Kiwamemasu</t>
-  </si>
-  <si>
-    <t>Scoring the Sacred Body of the Ancients from the Get-go</t>
-  </si>
-  <si>
-    <t>Magic Emperor</t>
-  </si>
-  <si>
-    <t>Martial Peak</t>
-  </si>
-  <si>
-    <t>The Self-Disciplined Me Is Practically Invincible</t>
-  </si>
-  <si>
-    <t>Global Power: I Can Control All The Elements</t>
-  </si>
-  <si>
-    <t>Moon Slayer</t>
-  </si>
-  <si>
-    <t>Lightning Degree</t>
-  </si>
-  <si>
-    <t>The World's Best Sect Of Dependency</t>
-  </si>
-  <si>
-    <t>The Return Of Apocalypses Tyrant</t>
-  </si>
-  <si>
-    <t>What Do You Do When You Suddenly Become An Immortal?</t>
-  </si>
-  <si>
-    <t>Tales Of Demons And Gods</t>
-  </si>
-  <si>
-    <t>The Kingdoms Of Ruin</t>
-  </si>
-  <si>
-    <t>Necromancer Academy And The Genius Summoner</t>
-  </si>
-  <si>
-    <t>Yuan Zun</t>
-  </si>
-  <si>
-    <t>The Greatest Estate Designer</t>
-  </si>
-  <si>
-    <t>Conqueror of modern martial arts Kang Haejin</t>
-  </si>
-  <si>
-    <t>Records Of The Swordsman Scholar</t>
-  </si>
-  <si>
-    <t>The Scholar's Reincarnation</t>
-  </si>
-  <si>
-    <t>Tale of a Scribe Who Retires To The Countryside</t>
-  </si>
-  <si>
-    <t>Return Of The Bachelor</t>
-  </si>
-  <si>
-    <t>Reincarnation Of The Murim Clan's Former Ranker</t>
-  </si>
-  <si>
-    <t>Regressing with the King’s Power</t>
-  </si>
-  <si>
-    <t>The Last Cultivator</t>
-  </si>
-  <si>
-    <t>HEAVENLY MOON</t>
-  </si>
-  <si>
-    <t>Infinite Leveling: Murim</t>
-  </si>
-  <si>
-    <t>Volcanic Age</t>
-  </si>
-  <si>
-    <t>Chronicles Of A Returner</t>
-  </si>
-  <si>
-    <t>The Undefeatable Swordsman</t>
-  </si>
-  <si>
-    <t>Second Life of Dongfang Bubai</t>
-  </si>
-  <si>
-    <t>Job Change: I Became The Undead Monarch</t>
-  </si>
-  <si>
-    <t>Relife Player</t>
-  </si>
-  <si>
-    <t>My Lucky Encounter From The Game Turned Into Reality</t>
-  </si>
-  <si>
-    <t>I Killed an Academy Player</t>
-  </si>
-  <si>
-    <t>Bloodhound’s Regression Instinct</t>
-  </si>
-  <si>
-    <t>I Raised the Yandere Villain Empress</t>
-  </si>
-  <si>
-    <t>The Max-Level Player’s 100th Regression</t>
-  </si>
-  <si>
-    <t>The Heavenly Demon Can't Live A Normal Life</t>
-  </si>
-  <si>
-    <t>The Player That Can't Level Up</t>
-  </si>
-  <si>
-    <t>Reborn As The Enemy Prince</t>
-  </si>
-  <si>
-    <t>The Archmage's Restaurant</t>
-  </si>
-  <si>
-    <t>I Rely on My Invincibility to Deal Tons of Damage Passively!</t>
-  </si>
-  <si>
-    <t>Wild West Murim</t>
-  </si>
-  <si>
-    <t>Monster Pet Evolution</t>
-  </si>
-  <si>
-    <t>The Strongest Sect Of All Times</t>
-  </si>
-  <si>
-    <t>Youngest Scion Of The Mages</t>
-  </si>
-  <si>
-    <t>I Will Do Whatever I Want In Ten Thousand Years</t>
-  </si>
-  <si>
-    <t>Genkai Level 1 Kara No Nariagari: Saijaku Level No Ore Ga Isekai Saikyou Ni Naru Made</t>
-  </si>
-  <si>
-    <t>How to Live at the Max Level</t>
-  </si>
-  <si>
-    <t>The All-Knowing Cultivator</t>
-  </si>
-  <si>
-    <t>Kurasu ≪Mushoku≫ No Eiyuu-Tan ~Koushaku-Ka O Tsuihou Sareta Ga, Jitsu Wa Nagutta Dake De Sukiru O Kakutoku Dekiru To Wakari, Tairiku Ichi No Eiyuu Ni Nobori Tsumeru</t>
-  </si>
-  <si>
-    <t>Villager A Wants To Save The Villainess No Matter What!</t>
-  </si>
-  <si>
-    <t>Savage Hero</t>
-  </si>
-  <si>
-    <t>Genkai Koe No Tenpu wa, Tensei-sha ni Shika Atsukaenai Overlimit Skill Holders</t>
-  </si>
-  <si>
-    <t>Maken Tsukai No Moto Shounen Hei Wa, Moto Teki Kanbu No Onee-San To Issho Ni Ikitai</t>
-  </si>
-  <si>
-    <t>Mannen D-Rank No Chuunen Boukensha, Yotta Ikioi De Densetsu No Ken Wo Hikkonuku</t>
-  </si>
-  <si>
-    <t>Dungeon Sherpa: Meikyuu Michisaki Annainin</t>
-  </si>
-  <si>
-    <t>A Sword Master Childhood Friend Power Harassed Me Harshly, So I Broke Off Our Relationship And Made A Fresh Start At The Frontier As A Magic Swordsman</t>
-  </si>
-  <si>
-    <t>I Summoned The Devil To Grant Me A Wish, But I Married Her Instead Since She Was Adorable ~My New Devil Wife~</t>
-  </si>
-  <si>
-    <t>A Story About A Dragon And The Rising Of An Adventurer</t>
-  </si>
-  <si>
-    <t>After Being Called A Hero: The Unrivaled Man Starts A Family</t>
-  </si>
-  <si>
-    <t>A Warrior Exiled By The Hero And His Lover</t>
-  </si>
-  <si>
-    <t>Nimotsu Mochi No Nousuji Musou</t>
-  </si>
-  <si>
-    <t>The Strongest Dull Prince’s Secret Battle for the Throne</t>
-  </si>
-  <si>
-    <t>The Sword of Princess Gluttony</t>
-  </si>
-  <si>
-    <t>Wistoria's Wand And Sword</t>
-  </si>
-  <si>
-    <t>The Crafty Mage: Frontier Settling Made Easy</t>
-  </si>
-  <si>
-    <t>Delivery Man From Murim</t>
-  </si>
-  <si>
-    <t>Henkyou Gurashi No Maou, Tensei Shite Saikyou No Majutsushi Ni Naru</t>
-  </si>
-  <si>
-    <t>The Executed Sage Is Reincarnated As A Lich And Starts An All-Out War</t>
-  </si>
-  <si>
-    <t>Dungeon Ni Hisomu Yandere Na Kanojo Ni Ore Wa Nando Mo Korosareru</t>
-  </si>
-  <si>
-    <t>I Became A Big-Shot On The Heavenly Leaderboard</t>
-  </si>
-  <si>
-    <t>The Dark Magician Transmigrates After 66666 Years</t>
-  </si>
-  <si>
-    <t>Reaper Of The Drifting Moon</t>
-  </si>
-  <si>
-    <t>The Unbeatable Dungeon's Lazy Boss Monster</t>
-  </si>
-  <si>
-    <t>All My Abilities Are Forbidden Spells</t>
-  </si>
-  <si>
-    <t>How To Survive As A Dragon With Time-Limit</t>
-  </si>
-  <si>
-    <t>Myst, Might, Mayhem</t>
-  </si>
-  <si>
-    <t>Dark And Light Martial Emperor</t>
-  </si>
-  <si>
-    <t>The doomsday ruthless man: hoarding trillions of supplies at the beginning</t>
-  </si>
-  <si>
-    <t>Becoming the Swordmaster Rank Young Lord of the Sichuan Tang Family</t>
-  </si>
-  <si>
-    <t>This Account Is Ridiculous</t>
-  </si>
-  <si>
-    <t>The Mysterious World’s Greatest Martial Artist Little Prince</t>
-  </si>
-  <si>
-    <t>The Reborn Young Lord Is An Assassin</t>
-  </si>
-  <si>
-    <t>God-Slaying Copycat</t>
-  </si>
-  <si>
-    <t>The Great Mage Of The Hero’S Party Reincarnates</t>
-  </si>
-  <si>
-    <t>My Brother Is The Chosen One</t>
-  </si>
-  <si>
-    <t>The Max Level Hero Strikes Back</t>
-  </si>
-  <si>
-    <t>Overlord of Insects</t>
-  </si>
-  <si>
-    <t>Game Of Familia: Kazoku Senki</t>
-  </si>
-  <si>
-    <t>Grand General</t>
-  </si>
-  <si>
-    <t>The Legendary Spearman Returns</t>
-  </si>
-  <si>
-    <t>Ice lord</t>
-  </si>
-  <si>
-    <t>My Inventory is Abnormal</t>
-  </si>
-  <si>
-    <t>Escort Agency Of The Apocalypse</t>
-  </si>
-  <si>
-    <t>The Heavenly Demon Will Give You a Massage</t>
-  </si>
-  <si>
-    <t>The Twin Swords Of The Sima</t>
-  </si>
-  <si>
-    <t>Versatile Sword Cultivator</t>
-  </si>
-  <si>
-    <t>Asura</t>
-  </si>
-  <si>
-    <t>Magic Academy’s Genius Blinker</t>
-  </si>
-  <si>
-    <t>Worthless Profession: Dragon Tamer</t>
-  </si>
-  <si>
-    <t>Expelled Hero Is Too Strong</t>
-  </si>
-  <si>
-    <t>The Ten Thousand Clans Invasion: Guardian Of The Rear</t>
-  </si>
-  <si>
-    <t>My Disciple Became the Great Demon Empress?!</t>
-  </si>
-  <si>
-    <t>The Greatest In The World</t>
-  </si>
-  <si>
-    <t>Drawing: The Greatest Mangaka Becomes A Skilled “Martial Artist” In Another World</t>
+    <t xml:space="preserve">Peerless Quest – The Cheat Skill Only I Can Use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isekai De Haishin Katsudou Wo Shitara Tairyou No Yandere Shinja Wo Umidashite Shimatta Ken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boundless Necromancer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Academy’S Genius Swordsman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demon Evolution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Iron-Blooded Necromancer Has Returned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infinite Mage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Star Instructor  Master Baek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Story Of Thorny Spear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blade debt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martial God Regressed To Level 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What, You Dare Pretend In Front Of Me, The Strongest In The Immortal World?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminally-Ill Genius Dark Knight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heavenly Inquisition Sword</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tsuki Ga Michibiku Isekai Douchuu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Emperor’s Sword</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Constellations Are My Disciples</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenge of the Iron-Blooded Sword Hound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Zombie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master: This Villainous Disciple Is Not The Holy Child</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo Max-Level Newbie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murim Login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Great Villain Who Threatened to Kill Himself</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon Maker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Reincarnated Assassin is a Genius Swordsman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I was more overpowered than the hero, so I hid my power!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Million Times Attack Speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I am the descendant of the Divine Dragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hero X Demon Queen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Records Of The Demonic Path’S Return</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Five-Dimensional Zone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legendary Youngest Son Of The Marquis House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I am fated villain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return Of The Mount Hua Sect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beyond Myriad Peoples</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nano Machine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tensei Shitara Dai Nana Ouji Dattanode, Kimamani Majutsu O Kiwamemasu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scoring the Sacred Body of the Ancients from the Get-go</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magic Emperor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martial Peak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Self-Disciplined Me Is Practically Invincible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Power: I Can Control All The Elements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Slayer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightning Degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The World's Best Sect Of Dependency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Return Of Apocalypses Tyrant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What Do You Do When You Suddenly Become An Immortal?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tales Of Demons And Gods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Kingdoms Of Ruin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Necromancer Academy And The Genius Summoner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yuan Zun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Greatest Estate Designer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conqueror of modern martial arts Kang Haejin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Records Of The Swordsman Scholar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Scholar's Reincarnation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tale of a Scribe Who Retires To The Countryside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return Of The Bachelor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnation Of The Murim Clan's Former Ranker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regressing with the King’s Power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Last Cultivator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEAVENLY MOON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infinite Leveling: Murim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volcanic Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chronicles Of A Returner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Undefeatable Swordsman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Second Life of Dongfang Bubai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job Change: I Became The Undead Monarch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relife Player</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Lucky Encounter From The Game Turned Into Reality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Killed an Academy Player</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bloodhound’s Regression Instinct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Raised the Yandere Villain Empress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Max-Level Player’s 100th Regression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Heavenly Demon Can't Live A Normal Life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Player That Can't Level Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reborn As The Enemy Prince</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Archmage's Restaurant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Rely on My Invincibility to Deal Tons of Damage Passively!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wild West Murim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster Pet Evolution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Strongest Sect Of All Times</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Youngest Scion Of The Mages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Will Do Whatever I Want In Ten Thousand Years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genkai Level 1 Kara No Nariagari: Saijaku Level No Ore Ga Isekai Saikyou Ni Naru Made</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How to Live at the Max Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The All-Knowing Cultivator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurasu ≪Mushoku≫ No Eiyuu-Tan ~Koushaku-Ka O Tsuihou Sareta Ga, Jitsu Wa Nagutta Dake De Sukiru O Kakutoku Dekiru To Wakari, Tairiku Ichi No Eiyuu Ni Nobori Tsumeru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villager A Wants To Save The Villainess No Matter What!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Savage Hero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genkai Koe No Tenpu wa, Tensei-sha ni Shika Atsukaenai Overlimit Skill Holders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maken Tsukai No Moto Shounen Hei Wa, Moto Teki Kanbu No Onee-San To Issho Ni Ikitai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mannen D-Rank No Chuunen Boukensha, Yotta Ikioi De Densetsu No Ken Wo Hikkonuku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dungeon Sherpa: Meikyuu Michisaki Annainin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Sword Master Childhood Friend Power Harassed Me Harshly, So I Broke Off Our Relationship And Made A Fresh Start At The Frontier As A Magic Swordsman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Summoned The Devil To Grant Me A Wish, But I Married Her Instead Since She Was Adorable ~My New Devil Wife~</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Story About A Dragon And The Rising Of An Adventurer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After Being Called A Hero: The Unrivaled Man Starts A Family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Warrior Exiled By The Hero And His Lover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimotsu Mochi No Nousuji Musou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Strongest Dull Prince’s Secret Battle for the Throne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Sword of Princess Gluttony</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wistoria's Wand And Sword</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Crafty Mage: Frontier Settling Made Easy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delivery Man From Murim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Henkyou Gurashi No Maou, Tensei Shite Saikyou No Majutsushi Ni Naru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Executed Sage Is Reincarnated As A Lich And Starts An All-Out War</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dungeon Ni Hisomu Yandere Na Kanojo Ni Ore Wa Nando Mo Korosareru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Became A Big-Shot On The Heavenly Leaderboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Dark Magician Transmigrates After 66666 Years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reaper Of The Drifting Moon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Unbeatable Dungeon's Lazy Boss Monster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All My Abilities Are Forbidden Spells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How To Survive As A Dragon With Time-Limit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myst, Might, Mayhem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark And Light Martial Emperor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The doomsday ruthless man: hoarding trillions of supplies at the beginning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Becoming the Swordmaster Rank Young Lord of the Sichuan Tang Family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This Account Is Ridiculous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Mysterious World’s Greatest Martial Artist Little Prince</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Reborn Young Lord Is An Assassin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">God-Slaying Copycat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Great Mage Of The Hero’S Party Reincarnates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Brother Is The Chosen One</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Max Level Hero Strikes Back</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overlord of Insects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Game Of Familia: Kazoku Senki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grand General</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Legendary Spearman Returns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ice lord</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Inventory is Abnormal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escort Agency Of The Apocalypse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Heavenly Demon Will Give You a Massage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Twin Swords Of The Sima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Versatile Sword Cultivator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magic Academy’s Genius Blinker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worthless Profession: Dragon Tamer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expelled Hero Is Too Strong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Ten Thousand Clans Invasion: Guardian Of The Rear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Disciple Became the Great Demon Empress?!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Greatest In The World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drawing: The Greatest Mangaka Becomes A Skilled “Martial Artist” In Another World</t>
   </si>
   <si>
     <r>
@@ -552,7 +547,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t>～</t>
+      <t xml:space="preserve">～</t>
     </r>
     <r>
       <rPr>
@@ -562,687 +557,690 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t>I Returned To The Past To Rewrite It As The World's Strongest</t>
+      <t xml:space="preserve">I Returned To The Past To Rewrite It As The World's Strongest</t>
     </r>
   </si>
   <si>
-    <t>Hundreds of Invincible Strikes</t>
-  </si>
-  <si>
-    <t>arctic cold war</t>
-  </si>
-  <si>
-    <t>Apocalyptic Super Farm</t>
-  </si>
-  <si>
-    <t>Sword Sheath's Child</t>
-  </si>
-  <si>
-    <t>Reincarnator</t>
-  </si>
-  <si>
-    <t>Hunter Academy’S Strongest Battle God</t>
-  </si>
-  <si>
-    <t>Childhood Friend of the Zenith</t>
-  </si>
-  <si>
-    <t>Absolute Regression</t>
-  </si>
-  <si>
-    <t>Warrior Grandpa And Supreme Granddaughter</t>
-  </si>
-  <si>
-    <t>I Scared the Divine Lord as I Handed over the Ancient Immortal Pill</t>
-  </si>
-  <si>
-    <t>I Become a Legendary Arch Mage by Reading a Book</t>
-  </si>
-  <si>
-    <t>Hiding a logistics center in the apocalypse</t>
-  </si>
-  <si>
-    <t>The Hated Black Mage Returns</t>
-  </si>
-  <si>
-    <t>The Masters Are Subscribing To Me</t>
-  </si>
-  <si>
-    <t>A Ranker's Guide To The Good Life</t>
-  </si>
-  <si>
-    <t>Black Serpent</t>
-  </si>
-  <si>
-    <t>Conquering the Academy with Just a Sashimi Knife</t>
-  </si>
-  <si>
-    <t>The Magic Genius Of The Marquis House</t>
-  </si>
-  <si>
-    <t>The Reversal Of My Life As A Side Character</t>
-  </si>
-  <si>
-    <t>Absolute Dominion</t>
-  </si>
-  <si>
-    <t>Fatal Reset</t>
-  </si>
-  <si>
-    <t>The Necromancer Family’s Young Heir</t>
-  </si>
-  <si>
-    <t>Starting As A Master Of Female Disciples' Leisure Skills</t>
-  </si>
-  <si>
-    <t>Song Baek</t>
-  </si>
-  <si>
-    <t>Surviving as a Genius on Borrowed Time</t>
-  </si>
-  <si>
-    <t>The Regressed Mercenary’s Machinations</t>
-  </si>
-  <si>
-    <t>Traveling Through Time And Space To Become An Unlucky Npc: I Have A Wife To Protect Me</t>
-  </si>
-  <si>
-    <t>Cultivation: The Heaven's Fated Useless Genius</t>
-  </si>
-  <si>
-    <t>The Edgeless Sword From The Village</t>
-  </si>
-  <si>
-    <t>Levelling Up In An Exclusive Dungeon</t>
-  </si>
-  <si>
-    <t>Reincarnated As A Genius Prodigy Of A Prestigious Family</t>
-  </si>
-  <si>
-    <t>From Goblin To Goblin God</t>
-  </si>
-  <si>
-    <t>Margrave’S Bastard Son Was The Emperor</t>
-  </si>
-  <si>
-    <t>The Second Eunuch Regains His Manhood</t>
-  </si>
-  <si>
-    <t>Return Of The Runebound Professor</t>
-  </si>
-  <si>
-    <t>Regressing as the Reincarnated Bastard of the Sword Clan</t>
-  </si>
-  <si>
-    <t>I, The Demon Lord, Am Being Targeted By My Female Disciples!</t>
-  </si>
-  <si>
-    <t>Fated to Be Loved by Villains</t>
-  </si>
-  <si>
-    <t>The Chaebeol’s Youngest Son</t>
-  </si>
-  <si>
-    <t>Heavenly Demon Wants To Be A Chef</t>
-  </si>
-  <si>
-    <t>Entomologist In Sichuan Tang Clan</t>
-  </si>
-  <si>
-    <t>Last Word of the World</t>
-  </si>
-  <si>
-    <t>Cosmic Heavenly Demon 3077</t>
-  </si>
-  <si>
-    <t>Solo Resurrection</t>
-  </si>
-  <si>
-    <t>Dao of the Bizarre Immortal</t>
-  </si>
-  <si>
-    <t>Tenkaichi: Nihon Saikyou Bugeisha Ketteisen</t>
-  </si>
-  <si>
-    <t>Reincarnation Of The Heavenly Demon</t>
-  </si>
-  <si>
-    <t>Black Corporation: Joseon</t>
-  </si>
-  <si>
-    <t>Perhaps Invincible</t>
-  </si>
-  <si>
-    <t>The mad gate</t>
-  </si>
-  <si>
-    <t>Surviving the Apocalypse</t>
-  </si>
-  <si>
-    <t>Genius Prismatic Mage</t>
-  </si>
-  <si>
-    <t>Becoming a God, Starting as water monkey</t>
-  </si>
-  <si>
-    <t>I Became the Successor of the Martial God</t>
-  </si>
-  <si>
-    <t>Regression of the Yong Clan Heir</t>
-  </si>
-  <si>
-    <t>Chronicles of the Reincarnated Demon God</t>
-  </si>
-  <si>
-    <t>Revenge Of the Bloom Flower</t>
-  </si>
-  <si>
-    <t>The Heavenly Demon Wants a Quiet Life</t>
-  </si>
-  <si>
-    <t>Monster General Recorded Legacy</t>
-  </si>
-  <si>
-    <t>Using My Cooking Skills in a Murim World</t>
-  </si>
-  <si>
-    <t>I’m a Martial Art Villainess, but I’m the Strongest!</t>
-  </si>
-  <si>
-    <t>Metcha Shoukan Sareta Ken</t>
-  </si>
-  <si>
-    <t>Mount Hua Sect's Genius Phantom Swordsman</t>
-  </si>
-  <si>
-    <t>I'm going to destroy this country</t>
-  </si>
-  <si>
-    <t>The New Beggars' Sect</t>
-  </si>
-  <si>
-    <t>Overgeared</t>
-  </si>
-  <si>
-    <t>Regressed life of the Sword Clan’s Ignoble Reincarnator</t>
-  </si>
-  <si>
-    <t>Black Fox: Sword Master Of Mount Kunlun</t>
-  </si>
-  <si>
-    <t>God-level Assassin, I’m the Shadow</t>
-  </si>
-  <si>
-    <t>War Of The Corpses</t>
-  </si>
-  <si>
-    <t>The Illegitimate Who Devours Weapons</t>
-  </si>
-  <si>
-    <t>The Great Sage of the Namgung Clan</t>
-  </si>
-  <si>
-    <t>Limitless Ascension: Strength Amid Adversity</t>
-  </si>
-  <si>
-    <t>Apocalypse: Cockroaches Gives Me Buff</t>
-  </si>
-  <si>
-    <t>The Legendary Hero is an Academy Honors Student</t>
-  </si>
-  <si>
-    <t>Like a Fiery Flame</t>
-  </si>
-  <si>
-    <t>The Magic Tower's Problem Child</t>
-  </si>
-  <si>
-    <t>I Became the Husband of the Cult Leader of the Demonic Sect</t>
-  </si>
-  <si>
-    <t>The Apocalypse is Here</t>
-  </si>
-  <si>
-    <t>If I Don’t Die Soon, I Will Rule The Demon Realm</t>
-  </si>
-  <si>
-    <t>I Will Raise This Family to Greatness</t>
-  </si>
-  <si>
-    <t>The Villain Wants to Live</t>
-  </si>
-  <si>
-    <t>Genius Archer’s Livestreaming</t>
-  </si>
-  <si>
-    <t>After Ten Millennia in Hell</t>
-  </si>
-  <si>
-    <t>Heavenly Grand Archive's Young Master</t>
-  </si>
-  <si>
-    <t>Space Cheon-ma 3077</t>
-  </si>
-  <si>
-    <t>Iljin Romance</t>
-  </si>
-  <si>
-    <t>Shut Up, Evil Dragon! I Don't Want to Raise a Child With You Anymore</t>
-  </si>
-  <si>
-    <t>On the Way to Meet Mom</t>
-  </si>
-  <si>
-    <t>Ultimate Shut-in</t>
-  </si>
-  <si>
-    <t>The beginning after the end</t>
-  </si>
-  <si>
-    <t>Reborn in a Cyber Cultivation World, I Fight My Way to the Top</t>
-  </si>
-  <si>
-    <t>Level 999 Goblin</t>
-  </si>
-  <si>
-    <t>Dominating the Wasteland: I Control an Immortal Sect in the Apocalypse</t>
-  </si>
-  <si>
-    <t>Starting As The God Of Wealth, Taming Billions Of Divine Pets!</t>
-  </si>
-  <si>
-    <t>Martial Evolution: Start by Awakening the King of Monsters</t>
-  </si>
-  <si>
-    <t>The Girl from Random Chatting</t>
-  </si>
-  <si>
-    <t>Return of the Legend</t>
-  </si>
-  <si>
-    <t>Elven Queen</t>
-  </si>
-  <si>
-    <t>Emperor of Solo Play</t>
-  </si>
-  <si>
-    <t>The Fox-Eyed Villain of the Demon Academy</t>
-  </si>
-  <si>
-    <t>The Awakening Contract</t>
-  </si>
-  <si>
-    <t>The Sword God From a Fallen World</t>
-  </si>
-  <si>
-    <t>I Awakened to the Ex Skill "Fixed Damage" and Became Invincible</t>
-  </si>
-  <si>
-    <t>Warrior of the Mind Sword</t>
-  </si>
-  <si>
-    <t>Ninja Reincarnation: Fuuma Kotarou’s Quest to Reclaim His Humanity</t>
-  </si>
-  <si>
-    <t>Empress Maria</t>
-  </si>
-  <si>
-    <t>Reincarnation of the Fist King</t>
-  </si>
-  <si>
-    <t>There Are No Bad Warriors in the World</t>
-  </si>
-  <si>
-    <t>Return From The Depth</t>
-  </si>
-  <si>
-    <t>Return of the Apocalypse-Class Death Knight</t>
-  </si>
-  <si>
-    <t>Oversummoned, Overpowered, and Over It!</t>
-  </si>
-  <si>
-    <t>A Rogue Guard in a Medieval Fantasy</t>
-  </si>
-  <si>
-    <t>Chronicles of the Lazy Sovereign</t>
-  </si>
-  <si>
-    <t>I Was the Final Boss</t>
-  </si>
-  <si>
-    <t>The Tang Clan Chronicles</t>
-  </si>
-  <si>
-    <t>The Demon-Slaying Madman—reborn as a demon</t>
-  </si>
-  <si>
-    <t>Urek Mazino</t>
-  </si>
-  <si>
-    <t>Demonic Sect Frontline: Thirteen Flying Dragons</t>
-  </si>
-  <si>
-    <t>Goddess of Abundance and the Genius Rogue Apostle</t>
-  </si>
-  <si>
-    <t>New Goguryeo Chronicles</t>
-  </si>
-  <si>
-    <t>Devil Summoner, I am the Abyss Lord</t>
-  </si>
-  <si>
-    <t>Legend of Dangun</t>
-  </si>
-  <si>
-    <t>The Tale of the Skeleton Messenger</t>
-  </si>
-  <si>
-    <t>The Great Heavenly Demon Sovereign</t>
-  </si>
-  <si>
-    <t>A Regressor's Tale of Cultivation</t>
-  </si>
-  <si>
-    <t>Jade of the Eight Gates</t>
-  </si>
-  <si>
-    <t>Disciple of the Three Kings</t>
-  </si>
-  <si>
-    <t>After the School Belle Dumped Me, I Became a Martial Arts God</t>
-  </si>
-  <si>
-    <t>Dead Mansion</t>
-  </si>
-  <si>
-    <t>Return of the King of Hell</t>
-  </si>
-  <si>
-    <t>Plaything</t>
-  </si>
-  <si>
-    <t>The Regressor Protects Only Me</t>
-  </si>
-  <si>
-    <t>Full-Time Awakening</t>
-  </si>
-  <si>
-    <t>Rebirth of the Divine Demon</t>
-  </si>
-  <si>
-    <t>Return of the First Patriarch: The Strongest Reincarnates into His Descendant 1000 Years Later</t>
-  </si>
-  <si>
-    <t>Lv. 99 Princess of Black Flame</t>
-  </si>
-  <si>
-    <t>Battle of the Martial Masters</t>
-  </si>
-  <si>
-    <t>The Yellow-haired Villain in Female Main Character's Novel wants Happiness</t>
-  </si>
-  <si>
-    <t>From Six to Sovereignty: The Girl Who Ruled</t>
-  </si>
-  <si>
-    <t>Eat and Go</t>
-  </si>
-  <si>
-    <t>I Shall Seal the Heavens</t>
-  </si>
-  <si>
-    <t>The Executed Sage Who Was Reincarnated as a Lich and Started an All-Out War</t>
-  </si>
-  <si>
-    <t>Demon Instructor's Return</t>
-  </si>
-  <si>
-    <t>The Archduke's Bride Is a Hell Warrior</t>
-  </si>
-  <si>
-    <t>Solo Leveling: Ragnarok</t>
-  </si>
-  <si>
-    <t>I Became a Patron of Villains</t>
-  </si>
-  <si>
-    <t>Black Crow</t>
-  </si>
-  <si>
-    <t>The Marquis Is the Marital Archduke</t>
-  </si>
-  <si>
-    <t>Dukedom's Legendary Prodigy</t>
-  </si>
-  <si>
-    <t>Reincarnated as the Crazed Heir</t>
-  </si>
-  <si>
-    <t>Lord of the Apocalypse</t>
-  </si>
-  <si>
-    <t>Don't Tell Me You Think Cultivating Immortality Is Difficult?</t>
-  </si>
-  <si>
-    <t>Immortal Fairy, Please Listen to My Explanation</t>
-  </si>
-  <si>
-    <t>Maplestory: The Last Adventurer</t>
-  </si>
-  <si>
-    <t>The Steel Emperor</t>
-  </si>
-  <si>
-    <t>The Luoyang Branch of the Heavenly Demon Cult</t>
-  </si>
-  <si>
-    <t>Spirit Hunter</t>
-  </si>
-  <si>
-    <t>Player of the Fallen Family</t>
-  </si>
-  <si>
-    <t>Unrivaled Spear Ghost</t>
-  </si>
-  <si>
-    <t>Reincarnation of the Martial God</t>
-  </si>
-  <si>
-    <t>After Rebirth, I Used Mirror Reversal For Vengeance</t>
-  </si>
-  <si>
-    <t>Death Attribute Magician</t>
-  </si>
-  <si>
-    <t>The Great Emperor Shinmadae</t>
-  </si>
-  <si>
-    <t>Revenger: Apocalypse of Vengeance</t>
-  </si>
-  <si>
-    <t>Hiding Out in an Apocalypse</t>
-  </si>
-  <si>
-    <t>Bad Born Blood</t>
-  </si>
-  <si>
-    <t>KaguRai: Kagura to Raito</t>
-  </si>
-  <si>
-    <t>Reincarnated as the Lazy and Villainous Noble, I Broke the Scenario and Became the Most Formidable With Extraordinary Magic</t>
-  </si>
-  <si>
-    <t>Star Armor꞉ I’ll Slaughter Through the Chaos with Star Soul Generals</t>
-  </si>
-  <si>
-    <t>The Demon King Overrun by Heroes</t>
-  </si>
-  <si>
-    <t>The Monkey King’s Journey to the Murim</t>
-  </si>
-  <si>
-    <t>The Sage who returned from another world wants to live quietly</t>
-  </si>
-  <si>
-    <t>Returned from Another World, Earth Turned Out to Be Quite the Fantasy Too. Also, Losing Heroines, Stop Looking This Way</t>
-  </si>
-  <si>
-    <t>Embodiment of the Assassin in the Murim World</t>
-  </si>
-  <si>
-    <t>Märchen - The Embodiment of Tales</t>
-  </si>
-  <si>
-    <t>Sichuan’s Supreme King</t>
-  </si>
-  <si>
-    <t>The Cold-Blooded Warrior</t>
-  </si>
-  <si>
-    <t>Everyone Loves Her</t>
-  </si>
-  <si>
-    <t>Paper Tiger</t>
-  </si>
-  <si>
-    <t>The Sword-Eating Swordmaster</t>
-  </si>
-  <si>
-    <t>The World's Best Kunlun Tavern</t>
-  </si>
-  <si>
-    <t>Defense Breaker</t>
-  </si>
-  <si>
-    <t>Worlds Best Assassin</t>
-  </si>
-  <si>
-    <t>The World's Best Martial Arts Instructor</t>
-  </si>
-  <si>
-    <t>How a Realist Hero Rebuilt the Kingdom</t>
-  </si>
-  <si>
-    <t>Sleepy Princess in the Demon Castle</t>
-  </si>
-  <si>
-    <t>To Hell With The Status Window</t>
-  </si>
-  <si>
-    <t>Becoming a Cheat-Level Skill Thief</t>
-  </si>
-  <si>
-    <t>Sichuan's Supreme King</t>
-  </si>
-  <si>
-    <t>Reborn After the Eight Empresses Betrayed Me, Now I’ll Make Them Regret It</t>
-  </si>
-  <si>
-    <t>Rebirth of the Demon Lord: the Slave who Conquered Fate</t>
-  </si>
-  <si>
-    <t>The Strongest Wizard Becomes a Countryside Guard After Taking an Arrow to the Knee</t>
-  </si>
-  <si>
-    <t>The Secret Martial Artist of Demonic Blood</t>
-  </si>
-  <si>
-    <t>The Strongest Hero Who Longs For Revenge Will Peerlessly Annihilate With The Power Of Darkness</t>
-  </si>
-  <si>
-    <t>I Became the Scoundrel of the Cheon Family</t>
-  </si>
-  <si>
-    <t>Supreme Demon of Hyungsan</t>
-  </si>
-  <si>
-    <t>Orc Hero Story - Discovery Chronicles</t>
-  </si>
-  <si>
-    <t>Boukun Meika no Hangyakusha -Aster</t>
-  </si>
-  <si>
-    <t>Jakdu</t>
-  </si>
-  <si>
-    <t>Secretly Cultivating by the Demon Cult Leader's Side</t>
-  </si>
-  <si>
-    <t>The Old Prisoner Lives in Solitude</t>
-  </si>
-  <si>
-    <t>Revenge of Young Master Peng</t>
-  </si>
-  <si>
-    <t>Murim’s Dept King</t>
-  </si>
-  <si>
-    <t>My Girlfriend's Friend</t>
-  </si>
-  <si>
-    <t>Teto X Egen</t>
-  </si>
-  <si>
-    <t>Gokusotsu Kraken</t>
-  </si>
-  <si>
-    <t>The Masters of Heaven and Earth</t>
-  </si>
-  <si>
-    <t>Red Storm</t>
-  </si>
-  <si>
-    <t>A Dragon Lives in Kunlun</t>
-  </si>
-  <si>
-    <t>Friend of the Demon King</t>
-  </si>
-  <si>
-    <t>High Martial Arts: Sweeping Through Three Thousand Emperors with One Hand!</t>
-  </si>
-  <si>
-    <t>The Genius Martial Artist Who Remembers Everything</t>
-  </si>
-  <si>
-    <t>The Shepherd Wizard</t>
-  </si>
-  <si>
-    <t>Sovereign of a Hundred Blades: Heir to the Strongest Style</t>
-  </si>
-  <si>
-    <t>Shadow Slave</t>
-  </si>
-  <si>
-    <t>The Tale of Cultivation and Demon Extermination</t>
-  </si>
-  <si>
-    <t>The Former Supreme</t>
-  </si>
-  <si>
-    <t>What a Bountiful Harvest, Demon Lord!</t>
-  </si>
-  <si>
-    <t>The Sword Emperor’s Rise of Namgung</t>
-  </si>
-  <si>
-    <t>I Kidnapped the Youngest Daughter of the Sichuan Tang Clan</t>
-  </si>
-  <si>
-    <t>War of Extinction</t>
-  </si>
-  <si>
-    <t>The Divine Demon’s Grand Ascension</t>
-  </si>
-  <si>
-    <t>All the Heroes Are My Enemies: The ‘Useless’ Class Dropout Overpowers Everyone With His Barrier Skill and Takes Revenge</t>
+    <t xml:space="preserve">Hundreds of Invincible Strikes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">arctic cold war</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apocalyptic Super Farm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sword Sheath's Child</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunter Academy’S Strongest Battle God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Childhood Friend of the Zenith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Absolute Regression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warrior Grandpa And Supreme Granddaughter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Scared the Divine Lord as I Handed over the Ancient Immortal Pill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Become a Legendary Arch Mage by Reading a Book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hiding a logistics center in the apocalypse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Hated Black Mage Returns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Masters Are Subscribing To Me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Ranker's Guide To The Good Life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Serpent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conquering the Academy with Just a Sashimi Knife</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Magic Genius Of The Marquis House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Reversal Of My Life As A Side Character</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Absolute Dominion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fatal Reset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Necromancer Family’s Young Heir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starting As A Master Of Female Disciples' Leisure Skills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Song Baek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surviving as a Genius on Borrowed Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Regressed Mercenary’s Machinations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traveling Through Time And Space To Become An Unlucky Npc: I Have A Wife To Protect Me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cultivation: The Heaven's Fated Useless Genius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Edgeless Sword From The Village</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Levelling Up In An Exclusive Dungeon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnated As A Genius Prodigy Of A Prestigious Family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From Goblin To Goblin God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margrave’S Bastard Son Was The Emperor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Second Eunuch Regains His Manhood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return Of The Runebound Professor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regressing as the Reincarnated Bastard of the Sword Clan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I, The Demon Lord, Am Being Targeted By My Female Disciples!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fated to Be Loved by Villains</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Chaebeol’s Youngest Son</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heavenly Demon Wants To Be A Chef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entomologist In Sichuan Tang Clan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last Word of the World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cosmic Heavenly Demon 3077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo Resurrection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dao of the Bizarre Immortal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tenkaichi: Nihon Saikyou Bugeisha Ketteisen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnation Of The Heavenly Demon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Corporation: Joseon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perhaps Invincible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The mad gate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surviving the Apocalypse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genius Prismatic Mage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Becoming a God, Starting as water monkey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Became the Successor of the Martial God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regression of the Yong Clan Heir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chronicles of the Reincarnated Demon God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenge Of the Bloom Flower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Heavenly Demon Wants a Quiet Life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster General Recorded Legacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Using My Cooking Skills in a Murim World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I’m a Martial Art Villainess, but I’m the Strongest!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metcha Shoukan Sareta Ken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mount Hua Sect's Genius Phantom Swordsman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I'm going to destroy this country</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The New Beggars' Sect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overgeared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regressed life of the Sword Clan’s Ignoble Reincarnator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Fox: Sword Master Of Mount Kunlun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">God-level Assassin, I’m the Shadow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">War Of The Corpses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Illegitimate Who Devours Weapons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Great Sage of the Namgung Clan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limitless Ascension: Strength Amid Adversity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apocalypse: Cockroaches Gives Me Buff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Legendary Hero is an Academy Honors Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Like a Fiery Flame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Magic Tower's Problem Child</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Became the Husband of the Cult Leader of the Demonic Sect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Apocalypse is Here</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If I Don’t Die Soon, I Will Rule The Demon Realm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Will Raise This Family to Greatness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Villain Wants to Live</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genius Archer’s Livestreaming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After Ten Millennia in Hell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heavenly Grand Archive's Young Master</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Space Cheon-ma 3077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iljin Romance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shut Up, Evil Dragon! I Don't Want to Raise a Child With You Anymore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On the Way to Meet Mom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultimate Shut-in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The beginning after the end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reborn in a Cyber Cultivation World, I Fight My Way to the Top</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level 999 Goblin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominating the Wasteland: I Control an Immortal Sect in the Apocalypse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starting As The God Of Wealth, Taming Billions Of Divine Pets!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martial Evolution: Start by Awakening the King of Monsters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Girl from Random Chatting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return of the Legend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elven Queen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emperor of Solo Play</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Fox-Eyed Villain of the Demon Academy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Awakening Contract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Sword God From a Fallen World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Awakened to the Ex Skill "Fixed Damage" and Became Invincible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warrior of the Mind Sword</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ninja Reincarnation: Fuuma Kotarou’s Quest to Reclaim His Humanity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empress Maria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnation of the Fist King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There Are No Bad Warriors in the World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return From The Depth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return of the Apocalypse-Class Death Knight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oversummoned, Overpowered, and Over It!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Rogue Guard in a Medieval Fantasy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chronicles of the Lazy Sovereign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Was the Final Boss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Tang Clan Chronicles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Demon-Slaying Madman—reborn as a demon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urek Mazino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demonic Sect Frontline: Thirteen Flying Dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goddess of Abundance and the Genius Rogue Apostle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Goguryeo Chronicles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devil Summoner, I am the Abyss Lord</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legend of Dangun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Tale of the Skeleton Messenger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Great Heavenly Demon Sovereign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Regressor's Tale of Cultivation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jade of the Eight Gates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disciple of the Three Kings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After the School Belle Dumped Me, I Became a Martial Arts God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dead Mansion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return of the King of Hell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plaything</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Regressor Protects Only Me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full-Time Awakening</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebirth of the Divine Demon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return of the First Patriarch: The Strongest Reincarnates into His Descendant 1000 Years Later</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lv. 99 Princess of Black Flame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Battle of the Martial Masters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Yellow-haired Villain in Female Main Character's Novel wants Happiness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From Six to Sovereignty: The Girl Who Ruled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eat and Go</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Shall Seal the Heavens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Executed Sage Who Was Reincarnated as a Lich and Started an All-Out War</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demon Instructor's Return</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Archduke's Bride Is a Hell Warrior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo Leveling: Ragnarok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Became a Patron of Villains</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Crow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Marquis Is the Marital Archduke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dukedom's Legendary Prodigy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnated as the Crazed Heir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lord of the Apocalypse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Don't Tell Me You Think Cultivating Immortality Is Difficult?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immortal Fairy, Please Listen to My Explanation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maplestory: The Last Adventurer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Steel Emperor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Luoyang Branch of the Heavenly Demon Cult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spirit Hunter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Player of the Fallen Family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unrivaled Spear Ghost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnation of the Martial God</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After Rebirth, I Used Mirror Reversal For Vengeance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Death Attribute Magician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Great Emperor Shinmadae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenger: Apocalypse of Vengeance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hiding Out in an Apocalypse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bad Born Blood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KaguRai: Kagura to Raito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnated as the Lazy and Villainous Noble, I Broke the Scenario and Became the Most Formidable With Extraordinary Magic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Star Armor꞉ I’ll Slaughter Through the Chaos with Star Soul Generals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Demon King Overrun by Heroes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Monkey King’s Journey to the Murim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Sage who returned from another world wants to live quietly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Returned from Another World, Earth Turned Out to Be Quite the Fantasy Too. Also, Losing Heroines, Stop Looking This Way</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embodiment of the Assassin in the Murim World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Märchen - The Embodiment of Tales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sichuan’s Supreme King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Cold-Blooded Warrior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everyone Loves Her</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paper Tiger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Sword-Eating Swordmaster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The World's Best Kunlun Tavern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defense Breaker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worlds Best Assassin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The World's Best Martial Arts Instructor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How a Realist Hero Rebuilt the Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sleepy Princess in the Demon Castle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To Hell With The Status Window</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Becoming a Cheat-Level Skill Thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sichuan's Supreme King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reborn After the Eight Empresses Betrayed Me, Now I’ll Make Them Regret It</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebirth of the Demon Lord: the Slave who Conquered Fate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Strongest Wizard Becomes a Countryside Guard After Taking an Arrow to the Knee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Secret Martial Artist of Demonic Blood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Strongest Hero Who Longs For Revenge Will Peerlessly Annihilate With The Power Of Darkness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Became the Scoundrel of the Cheon Family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supreme Demon of Hyungsan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orc Hero Story - Discovery Chronicles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boukun Meika no Hangyakusha -Aster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jakdu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secretly Cultivating by the Demon Cult Leader's Side</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Old Prisoner Lives in Solitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenge of Young Master Peng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murim’s Dept King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Girlfriend's Friend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teto X Egen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gokusotsu Kraken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Masters of Heaven and Earth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red Storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Dragon Lives in Kunlun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Friend of the Demon King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High Martial Arts: Sweeping Through Three Thousand Emperors with One Hand!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Genius Martial Artist Who Remembers Everything</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Shepherd Wizard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sovereign of a Hundred Blades: Heir to the Strongest Style</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shadow Slave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Tale of Cultivation and Demon Extermination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Former Supreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What a Bountiful Harvest, Demon Lord!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Sword Emperor’s Rise of Namgung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Kidnapped the Youngest Daughter of the Sichuan Tang Clan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">War of Extinction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Divine Demon’s Grand Ascension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All the Heroes Are My Enemies: The ‘Useless’ Class Dropout Overpowers Everyone With His Barrier Skill and Takes Revenge</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1251,14 +1249,22 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Nimbus Sans"/>
@@ -1301,14 +1307,14 @@
     </fill>
   </fills>
   <borders count="3">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FFD9D9D9"/>
       </left>
@@ -1321,7 +1327,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FFD9D9D9"/>
       </left>
@@ -1337,48 +1343,122 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF4F81BD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1437,74 +1517,57 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:B401" totalsRowShown="0">
-  <autoFilter ref="A1:B401" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:B401" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:B401"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Title"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Episodes"/>
+    <tableColumn id="1" name="Title"/>
+    <tableColumn id="2" name="Episodes"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1512,12 +1575,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1546,7 +1609,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1567,7 +1630,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1618,7 +1681,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1636,26 +1699,27 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:B394"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="169" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="169"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.43"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1663,3154 +1727,3159 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="4" t="n">
         <v>878</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="4" t="n">
         <v>266</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="4" t="n">
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="4" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="4" t="n">
         <v>135</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="4" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="4" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="4" t="n">
         <v>292</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="4" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="4" t="n">
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="4" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="4" t="n">
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="4" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="4" t="n">
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="4" t="n">
         <v>223</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="4" t="n">
         <v>162</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="4" t="n">
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="4" t="n">
         <v>117</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="4" t="n">
         <v>85</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="4" t="n">
         <v>182</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="4" t="n">
         <v>175</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="4" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="4" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="4" t="n">
         <v>10.1</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="4" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="4" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30" s="4" t="n">
         <v>105</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31" s="4" t="n">
         <v>77</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" s="4" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B33" s="4" t="n">
         <v>88</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34" s="4" t="n">
         <v>99</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B35" s="4" t="n">
         <v>157</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36" s="4" t="n">
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="4">
+      <c r="B37" s="4" t="n">
         <v>51</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="4">
+      <c r="B38" s="4" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="4">
+      <c r="B39" s="4" t="n">
         <v>58</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="4">
+      <c r="B40" s="4" t="n">
         <v>124</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="4">
+      <c r="B41" s="4" t="n">
         <v>111</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="4">
+      <c r="B42" s="4" t="n">
         <v>63</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="4">
+      <c r="B43" s="4" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B44" s="4">
+      <c r="B44" s="4" t="n">
         <v>162</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B45" s="4">
+      <c r="B45" s="4" t="n">
         <v>64</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B46" s="4">
+      <c r="B46" s="4" t="n">
         <v>140</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="4">
+      <c r="B47" s="4" t="n">
         <v>168</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="4">
+      <c r="B48" s="4" t="n">
         <v>186</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B49" s="4">
+      <c r="B49" s="4" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B50" s="4">
+      <c r="B50" s="4" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B51" s="4">
+      <c r="B51" s="4" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B52" s="4">
+      <c r="B52" s="4" t="n">
         <v>71</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B53" s="4">
+      <c r="B53" s="4" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B54" s="4">
+      <c r="B54" s="4" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B55" s="4">
+      <c r="B55" s="4" t="n">
         <v>156</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B56" s="4">
+      <c r="B56" s="4" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B57" s="4">
+      <c r="B57" s="4" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B58" s="4">
+      <c r="B58" s="4" t="n">
         <v>144</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B59" s="4">
+      <c r="B59" s="4" t="n">
         <v>329</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B60" s="4">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
+      <c r="B60" s="4" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B61" s="4">
+      <c r="B61" s="4" t="n">
         <v>275</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B62" s="4">
+      <c r="B62" s="4" t="n">
         <v>311</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B63" s="4">
+      <c r="B63" s="4" t="n">
         <v>175</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B64" s="4">
+      <c r="B64" s="4" t="n">
         <v>58</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B65" s="4">
+      <c r="B65" s="4" t="n">
         <v>851</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B66" s="4">
+      <c r="B66" s="4" t="n">
         <v>3644</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B67" s="4">
+      <c r="B67" s="4" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B68" s="4">
+      <c r="B68" s="4" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B69" s="4">
+      <c r="B69" s="4" t="n">
         <v>76</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B70" s="4">
+      <c r="B70" s="4" t="n">
         <v>220</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B71" s="4">
+      <c r="B71" s="4" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B72" s="4">
+      <c r="B72" s="4" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B73" s="4">
+      <c r="B73" s="4" t="n">
         <v>89</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B74" s="4">
+      <c r="B74" s="4" t="n">
         <v>508.1</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B75" s="4">
+      <c r="B75" s="4" t="n">
         <v>43</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B76" s="4">
+      <c r="B76" s="4" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B77" s="4">
+      <c r="B77" s="4" t="n">
         <v>587</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B78" s="4">
+      <c r="B78" s="4" t="n">
         <v>121</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B79" s="4">
+      <c r="B79" s="4" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B80" s="4">
+      <c r="B80" s="4" t="n">
         <v>157</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B81" s="4">
+      <c r="B81" s="4" t="n">
         <v>156</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B82" s="4">
+      <c r="B82" s="4" t="n">
         <v>235</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B83" s="4">
+      <c r="B83" s="4" t="n">
         <v>188</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B84" s="4">
+      <c r="B84" s="4" t="n">
         <v>106</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B85" s="4">
+      <c r="B85" s="4" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B86" s="4">
+      <c r="B86" s="4" t="n">
         <v>33</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B87" s="4">
+      <c r="B87" s="4" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B88" s="4">
+      <c r="B88" s="4" t="n">
         <v>187</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B89" s="4">
+      <c r="B89" s="4" t="n">
         <v>256</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B90" s="4">
+      <c r="B90" s="4" t="n">
         <v>133</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B91" s="4">
+      <c r="B91" s="4" t="n">
         <v>217</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B92" s="4">
+      <c r="B92" s="4" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B93" s="4">
+      <c r="B93" s="4" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B94" s="4">
+      <c r="B94" s="4" t="n">
         <v>65</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B95" s="4">
+      <c r="B95" s="4" t="n">
         <v>56</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B96" s="4">
+      <c r="B96" s="4" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="4">
+      <c r="B97" s="4" t="n">
         <v>52</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B98" s="4">
+      <c r="B98" s="4" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B99" s="4">
+      <c r="B99" s="4" t="n">
         <v>41</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B100" s="4">
+      <c r="B100" s="4" t="n">
         <v>182</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B101" s="4">
+      <c r="B101" s="4" t="n">
         <v>157</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B102" s="4">
+      <c r="B102" s="4" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B103" s="4">
+      <c r="B103" s="4" t="n">
         <v>103</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B104" s="4">
+      <c r="B104" s="4" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B105" s="4">
+      <c r="B105" s="4" t="n">
         <v>94</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B106" s="4">
+      <c r="B106" s="4" t="n">
         <v>221</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B107" s="4">
+      <c r="B107" s="4" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="108" spans="1:2">
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B108" s="4">
+      <c r="B108" s="4" t="n">
         <v>61</v>
       </c>
     </row>
-    <row r="109" spans="1:2">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B109" s="4">
+      <c r="B109" s="4" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:2">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B110" s="4">
+      <c r="B110" s="4" t="n">
         <v>10.1</v>
       </c>
     </row>
-    <row r="111" spans="1:2">
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B111" s="4">
+      <c r="B111" s="4" t="n">
         <v>79</v>
       </c>
     </row>
-    <row r="112" spans="1:2">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B112" s="4">
+      <c r="B112" s="4" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="113" spans="1:2">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B113" s="4">
+      <c r="B113" s="4" t="n">
         <v>34</v>
       </c>
     </row>
-    <row r="114" spans="1:2">
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B114" s="4">
+      <c r="B114" s="4" t="n">
         <v>38.1</v>
       </c>
     </row>
-    <row r="115" spans="1:2">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B115" s="4">
+      <c r="B115" s="4" t="n">
         <v>63</v>
       </c>
     </row>
-    <row r="116" spans="1:2">
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B116" s="4">
+      <c r="B116" s="4" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="117" spans="1:2">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B117" s="4">
+      <c r="B117" s="4" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="118" spans="1:2">
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B118" s="4">
+      <c r="B118" s="4" t="n">
         <v>49</v>
       </c>
     </row>
-    <row r="119" spans="1:2">
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B119" s="4">
+      <c r="B119" s="4" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="120" spans="1:2">
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B120" s="4">
+      <c r="B120" s="4" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="121" spans="1:2">
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B121" s="4">
+      <c r="B121" s="4" t="n">
         <v>43</v>
       </c>
     </row>
-    <row r="122" spans="1:2">
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B122" s="4">
+      <c r="B122" s="4" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="123" spans="1:2">
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B123" s="4">
+      <c r="B123" s="4" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="124" spans="1:2">
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B124" s="4">
+      <c r="B124" s="4" t="n">
         <v>33</v>
       </c>
     </row>
-    <row r="125" spans="1:2">
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B125" s="4">
+      <c r="B125" s="4" t="n">
         <v>7.2</v>
       </c>
     </row>
-    <row r="126" spans="1:2">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B126" s="4">
+      <c r="B126" s="4" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="127" spans="1:2">
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B127" s="4">
+      <c r="B127" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="128" spans="1:2">
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B128" s="4">
+      <c r="B128" s="4" t="n">
         <v>58</v>
       </c>
     </row>
-    <row r="129" spans="1:2">
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B129" s="4">
+      <c r="B129" s="4" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="130" spans="1:2">
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B130" s="4">
+      <c r="B130" s="4" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="131" spans="1:2">
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B131" s="4">
+      <c r="B131" s="4" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="132" spans="1:2">
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B132" s="4">
+      <c r="B132" s="4" t="n">
         <v>56</v>
       </c>
     </row>
-    <row r="133" spans="1:2">
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B133" s="4">
+      <c r="B133" s="4" t="n">
         <v>12.2</v>
       </c>
     </row>
-    <row r="134" spans="1:2">
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B134" s="4">
+      <c r="B134" s="4" t="n">
         <v>91</v>
       </c>
     </row>
-    <row r="135" spans="1:2">
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B135" s="4">
+      <c r="B135" s="4" t="n">
         <v>165</v>
       </c>
     </row>
-    <row r="136" spans="1:2">
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B136" s="4">
+      <c r="B136" s="4" t="n">
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="1:2">
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B137" s="4">
+      <c r="B137" s="4" t="n">
         <v>92</v>
       </c>
     </row>
-    <row r="138" spans="1:2">
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B138" s="4">
+      <c r="B138" s="4" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="139" spans="1:2">
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B139" s="4">
+      <c r="B139" s="4" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="140" spans="1:2">
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B140" s="4">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2">
+      <c r="B140" s="4" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B141" s="4">
+      <c r="B141" s="4" t="n">
         <v>48</v>
       </c>
     </row>
-    <row r="142" spans="1:2">
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B142" s="4">
+      <c r="B142" s="4" t="n">
         <v>39</v>
       </c>
     </row>
-    <row r="143" spans="1:2">
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B143" s="4">
+      <c r="B143" s="4" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="144" spans="1:2">
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B144" s="4">
+      <c r="B144" s="4" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="145" spans="1:2">
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B145" s="4">
+      <c r="B145" s="4" t="n">
         <v>123</v>
       </c>
     </row>
-    <row r="146" spans="1:2">
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B146" s="4">
+      <c r="B146" s="4" t="n">
         <v>102</v>
       </c>
     </row>
-    <row r="147" spans="1:2">
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B147" s="4">
+      <c r="B147" s="4" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="148" spans="1:2">
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B148" s="4">
+      <c r="B148" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="149" spans="1:2">
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B149" s="4">
+      <c r="B149" s="4" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="150" spans="1:2">
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B150" s="4">
+      <c r="B150" s="4" t="n">
         <v>73</v>
       </c>
     </row>
-    <row r="151" spans="1:2">
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B151" s="4">
+      <c r="B151" s="4" t="n">
         <v>55</v>
       </c>
     </row>
-    <row r="152" spans="1:2">
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B152" s="4">
+      <c r="B152" s="4" t="n">
         <v>63</v>
       </c>
     </row>
-    <row r="153" spans="1:2">
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B153" s="4">
+      <c r="B153" s="4" t="n">
         <v>83</v>
       </c>
     </row>
-    <row r="154" spans="1:2">
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B154" s="4">
+      <c r="B154" s="4" t="n">
         <v>139</v>
       </c>
     </row>
-    <row r="155" spans="1:2">
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B155" s="4">
+      <c r="B155" s="4" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="156" spans="1:2">
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B156" s="4">
+      <c r="B156" s="4" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="157" spans="1:2">
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B157" s="4">
+      <c r="B157" s="4" t="n">
         <v>76</v>
       </c>
     </row>
-    <row r="158" spans="1:2">
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B158" s="4">
+      <c r="B158" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="159" spans="1:2">
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B159" s="4">
+      <c r="B159" s="4" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="160" spans="1:2">
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B160" s="4">
+      <c r="B160" s="4" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="161" spans="1:2">
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B161" s="4">
+      <c r="B161" s="4" t="n">
         <v>58</v>
       </c>
     </row>
-    <row r="162" spans="1:2">
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B162" s="4">
+      <c r="B162" s="4" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="163" spans="1:2">
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B163" s="4">
+      <c r="B163" s="4" t="n">
         <v>34</v>
       </c>
     </row>
-    <row r="164" spans="1:2">
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B164" s="4">
+      <c r="B164" s="4" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="165" spans="1:2">
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B165" s="4">
+      <c r="B165" s="4" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="166" spans="1:2">
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B166" s="4">
+      <c r="B166" s="4" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="167" spans="1:2">
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B167" s="4">
+      <c r="B167" s="4" t="n">
         <v>61</v>
       </c>
     </row>
-    <row r="168" spans="1:2">
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B168" s="4">
+      <c r="B168" s="4" t="n">
         <v>108</v>
       </c>
     </row>
-    <row r="169" spans="1:2">
+    <row r="169" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B169" s="4">
+      <c r="B169" s="4" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="170" spans="1:2">
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B170" s="4">
+      <c r="B170" s="4" t="n">
         <v>49</v>
       </c>
     </row>
-    <row r="171" spans="1:2">
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B171" s="4">
+      <c r="B171" s="4" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="172" spans="1:2">
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B172" s="4">
+      <c r="B172" s="4" t="n">
         <v>74</v>
       </c>
     </row>
-    <row r="173" spans="1:2">
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B173" s="4">
+      <c r="B173" s="4" t="n">
         <v>61</v>
       </c>
     </row>
-    <row r="174" spans="1:2">
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B174" s="4">
+      <c r="B174" s="4" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="175" spans="1:2">
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B175" s="4">
+      <c r="B175" s="4" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="176" spans="1:2">
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B176" s="4">
+      <c r="B176" s="4" t="n">
         <v>104</v>
       </c>
     </row>
-    <row r="177" spans="1:2">
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B177" s="4">
+      <c r="B177" s="4" t="n">
         <v>76</v>
       </c>
     </row>
-    <row r="178" spans="1:2">
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B178" s="4">
+      <c r="B178" s="4" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="179" spans="1:2">
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B179" s="4">
+      <c r="B179" s="4" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="180" spans="1:2">
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B180" s="4">
+      <c r="B180" s="4" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="181" spans="1:2">
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B181" s="4">
+      <c r="B181" s="4" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="182" spans="1:2">
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B182" s="4">
+      <c r="B182" s="4" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="183" spans="1:2">
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B183" s="4">
+      <c r="B183" s="4" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="184" spans="1:2">
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B184" s="4">
+      <c r="B184" s="4" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="185" spans="1:2">
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B185" s="4">
+      <c r="B185" s="4" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="186" spans="1:2">
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B186" s="4">
+      <c r="B186" s="4" t="n">
         <v>95</v>
       </c>
     </row>
-    <row r="187" spans="1:2">
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B187" s="4">
+      <c r="B187" s="4" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="188" spans="1:2">
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B188" s="4">
+      <c r="B188" s="4" t="n">
         <v>27</v>
       </c>
     </row>
-    <row r="189" spans="1:2">
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B189" s="4">
+      <c r="B189" s="4" t="n">
         <v>91</v>
       </c>
     </row>
-    <row r="190" spans="1:2">
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B190" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2">
+      <c r="B190" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="B191" s="4">
+      <c r="B191" s="4" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="192" spans="1:2">
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B192" s="4">
+      <c r="B192" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="193" spans="1:2">
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B193" s="4">
+      <c r="B193" s="4" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="194" spans="1:2">
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B194" s="4">
+      <c r="B194" s="4" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="195" spans="1:2">
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B195" s="4">
+      <c r="B195" s="4" t="n">
         <v>89</v>
       </c>
     </row>
-    <row r="196" spans="1:2">
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B196" s="4">
+      <c r="B196" s="4" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="197" spans="1:2">
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="B197" s="4">
+      <c r="B197" s="4" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="198" spans="1:2">
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B198" s="4">
+      <c r="B198" s="4" t="n">
         <v>59</v>
       </c>
     </row>
-    <row r="199" spans="1:2">
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B199" s="4">
+      <c r="B199" s="4" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="200" spans="1:2">
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B200" s="4">
+      <c r="B200" s="4" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="201" spans="1:2">
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="B201" s="4">
+      <c r="B201" s="4" t="n">
         <v>108</v>
       </c>
     </row>
-    <row r="202" spans="1:2">
+    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B202" s="4">
+      <c r="B202" s="4" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="203" spans="1:2">
+    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B203" s="4">
+      <c r="B203" s="4" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="204" spans="1:2">
+    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B204" s="4">
+      <c r="B204" s="4" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="205" spans="1:2">
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B205" s="4">
+      <c r="B205" s="4" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="206" spans="1:2">
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B206" s="4">
+      <c r="B206" s="4" t="n">
         <v>17</v>
       </c>
     </row>
-    <row r="207" spans="1:2">
+    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="B207" s="4">
+      <c r="B207" s="4" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="208" spans="1:2">
+    <row r="208" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B208" s="4">
+      <c r="B208" s="4" t="n">
         <v>220</v>
       </c>
     </row>
-    <row r="209" spans="1:2">
+    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B209" s="4">
+      <c r="B209" s="4" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="210" spans="1:2">
+    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B210" s="4">
+      <c r="B210" s="4" t="n">
         <v>51</v>
       </c>
     </row>
-    <row r="211" spans="1:2">
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B211" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2">
+      <c r="B211" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B212" s="4">
+      <c r="B212" s="4" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="213" spans="1:2">
+    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="B213" s="4">
+      <c r="B213" s="4" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="214" spans="1:2">
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B214" s="4">
+      <c r="B214" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="215" spans="1:2">
+    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="B215" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="216" spans="1:2">
+      <c r="B215" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="B216" s="4">
+      <c r="B216" s="4" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="217" spans="1:2">
+    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="B217" s="4">
+      <c r="B217" s="4" t="n">
         <v>141</v>
       </c>
     </row>
-    <row r="218" spans="1:2">
+    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B218" s="4">
+      <c r="B218" s="4" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="219" spans="1:2">
+    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B219" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" spans="1:2">
+      <c r="B219" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="B220" s="4">
+      <c r="B220" s="4" t="n">
         <v>49</v>
       </c>
     </row>
-    <row r="221" spans="1:2">
+    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="B221" s="4">
+      <c r="B221" s="4" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="222" spans="1:2">
+    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B222" s="4">
+      <c r="B222" s="4" t="n">
         <v>23</v>
       </c>
     </row>
-    <row r="223" spans="1:2">
+    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="B223" s="4">
+      <c r="B223" s="4" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="224" spans="1:2">
+    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B224" s="4">
+      <c r="B224" s="4" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="225" spans="1:2">
+    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="B225" s="4">
+      <c r="B225" s="4" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="226" spans="1:2">
+    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="B226" s="4">
+      <c r="B226" s="4" t="n">
         <v>36</v>
       </c>
     </row>
-    <row r="227" spans="1:2">
+    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="B227" s="4">
+      <c r="B227" s="4" t="n">
         <v>64</v>
       </c>
     </row>
-    <row r="228" spans="1:2">
+    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="B228" s="4">
+      <c r="B228" s="4" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="229" spans="1:2">
+    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B229" s="4">
+      <c r="B229" s="4" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="230" spans="1:2">
+    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B230" s="4">
+      <c r="B230" s="4" t="n">
         <v>124</v>
       </c>
     </row>
-    <row r="231" spans="1:2">
+    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="B231" s="4">
+      <c r="B231" s="4" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="232" spans="1:2">
+    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="B232" s="4">
+      <c r="B232" s="4" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="233" spans="1:2">
+    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B233" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234" spans="1:2">
+      <c r="B233" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="B234" s="4">
+      <c r="B234" s="4" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="235" spans="1:2">
+    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="B235" s="4">
+      <c r="B235" s="4" t="n">
         <v>130</v>
       </c>
     </row>
-    <row r="236" spans="1:2">
+    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="B236" s="4">
+      <c r="B236" s="4" t="n">
         <v>67</v>
       </c>
     </row>
-    <row r="237" spans="1:2">
+    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B237" s="4">
+      <c r="B237" s="4" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="238" spans="1:2">
+    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B238" s="4">
+      <c r="B238" s="4" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="239" spans="1:2">
+    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B239" s="4">
+      <c r="B239" s="4" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="240" spans="1:2">
+    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B240" s="4">
+      <c r="B240" s="4" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="241" spans="1:2">
+    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="B241" s="4">
+      <c r="B241" s="4" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="242" spans="1:2">
+    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="B242" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243" spans="1:2">
+      <c r="B242" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="B243" s="4">
+      <c r="B243" s="4" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="244" spans="1:2">
+    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B244" s="4">
+      <c r="B244" s="4" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="245" spans="1:2">
+    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="B245" s="4">
+      <c r="B245" s="4" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="246" spans="1:2">
+    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="B246" s="4">
+      <c r="B246" s="4" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="247" spans="1:2">
+    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="B247" s="4">
+      <c r="B247" s="4" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="248" spans="1:2">
+    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="B248" s="4">
+      <c r="B248" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="249" spans="1:2">
+    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="B249" s="4">
+      <c r="B249" s="4" t="n">
         <v>81</v>
       </c>
     </row>
-    <row r="250" spans="1:2">
+    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B250" s="4">
+      <c r="B250" s="4" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="251" spans="1:2">
+    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="B251" s="4">
+      <c r="B251" s="4" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="252" spans="1:2">
+    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="B252" s="4">
+      <c r="B252" s="4" t="n">
         <v>57</v>
       </c>
     </row>
-    <row r="253" spans="1:2">
+    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B253" s="4">
+      <c r="B253" s="4" t="n">
         <v>112</v>
       </c>
     </row>
-    <row r="254" spans="1:2">
+    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B254" s="4">
+      <c r="B254" s="4" t="n">
         <v>126</v>
       </c>
     </row>
-    <row r="255" spans="1:2">
+    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="B255" s="4">
+      <c r="B255" s="4" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="256" spans="1:2">
+    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="B256" s="4">
+      <c r="B256" s="4" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="257" spans="1:2">
+    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="B257" s="4">
+      <c r="B257" s="4" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="258" spans="1:2">
+    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="B258" s="4">
+      <c r="B258" s="4" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="259" spans="1:2">
+    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B259" s="4">
+      <c r="B259" s="4" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="260" spans="1:2">
+    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="B260" s="4">
+      <c r="B260" s="4" t="n">
         <v>219</v>
       </c>
     </row>
-    <row r="261" spans="1:2">
+    <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="B261" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262" spans="1:2">
+      <c r="B261" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="B262" s="4">
+      <c r="B262" s="4" t="n">
         <v>55</v>
       </c>
     </row>
-    <row r="263" spans="1:2">
+    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="B263" s="4">
+      <c r="B263" s="4" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:2">
+    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="B264" s="4">
+      <c r="B264" s="4" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="265" spans="1:2">
+    <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="B265" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266" spans="1:2">
+      <c r="B265" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="B266" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="267" spans="1:2">
+      <c r="B266" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="B267" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="268" spans="1:2">
+      <c r="B267" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B268" s="4">
+      <c r="B268" s="4" t="n">
         <v>17</v>
       </c>
     </row>
-    <row r="269" spans="1:2">
+    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="B269" s="4">
+      <c r="B269" s="4" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="270" spans="1:2">
+    <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="B270" s="4">
+      <c r="B270" s="4" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="271" spans="1:2">
+    <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="B271" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="272" spans="1:2">
+      <c r="B271" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="B272" s="4">
+      <c r="B272" s="4" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="273" spans="1:2">
+    <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="B273" s="4">
+      <c r="B273" s="4" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="274" spans="1:2">
+    <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="B274" s="4">
+      <c r="B274" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="275" spans="1:2">
+    <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="B275" s="4">
+      <c r="B275" s="4" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="276" spans="1:2">
+    <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="B276" s="4">
+      <c r="B276" s="4" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="277" spans="1:2">
+    <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="B277" s="4">
+      <c r="B277" s="4" t="n">
         <v>34</v>
       </c>
     </row>
-    <row r="278" spans="1:2">
+    <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="B278" s="4">
+      <c r="B278" s="4" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="279" spans="1:2">
+    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="B279" s="4">
+      <c r="B279" s="4" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="280" spans="1:2">
+    <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B280" s="4">
+      <c r="B280" s="4" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="281" spans="1:2">
+    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="B281" s="4">
+      <c r="B281" s="4" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="282" spans="1:2">
+    <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="B282" s="4">
+      <c r="B282" s="4" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="283" spans="1:2">
+    <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="B283" s="4">
+      <c r="B283" s="4" t="n">
         <v>27</v>
       </c>
     </row>
-    <row r="284" spans="1:2">
+    <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="B284" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285" spans="1:2" ht="15.75">
+      <c r="B284" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="B285" s="4">
+      <c r="B285" s="4" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="286" spans="1:2">
+    <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="B286" s="4">
+      <c r="B286" s="4" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="287" spans="1:2">
+    <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="B287" s="4">
+      <c r="B287" s="4" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="288" spans="1:2">
+    <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="B288" s="4">
+      <c r="B288" s="4" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="289" spans="1:2">
+    <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="B289" s="4">
+      <c r="B289" s="4" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="290" spans="1:2">
+    <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="B290" s="4">
+      <c r="B290" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="291" spans="1:2">
+    <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="B291" s="4">
+      <c r="B291" s="4" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="292" spans="1:2">
+    <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="B292" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="293" spans="1:2">
+      <c r="B292" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="B293" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="294" spans="1:2">
+      <c r="B293" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="B294" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="295" spans="1:2">
+      <c r="B294" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="B295" s="4">
+      <c r="B295" s="4" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="296" spans="1:2">
+    <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="B296" s="4">
+      <c r="B296" s="4" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="297" spans="1:2">
+    <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="B297" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="298" spans="1:2">
+      <c r="B297" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="B298" s="4">
+      <c r="B298" s="4" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="299" spans="1:2">
+    <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="B299" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300" spans="1:2">
+      <c r="B299" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="B300" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="301" spans="1:2">
+      <c r="B300" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="B301" s="4">
+      <c r="B301" s="4" t="n">
         <v>56</v>
       </c>
     </row>
-    <row r="302" spans="1:2">
+    <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="B302" s="4">
+      <c r="B302" s="4" t="n">
         <v>41</v>
       </c>
     </row>
-    <row r="303" spans="1:2">
+    <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="B303" s="4">
+      <c r="B303" s="4" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="304" spans="1:2">
+    <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="B304" s="4">
+      <c r="B304" s="4" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="305" spans="1:2">
+    <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="B305" s="4">
+      <c r="B305" s="4" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="306" spans="1:2">
+    <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="B306" s="4">
+      <c r="B306" s="4" t="n">
         <v>27</v>
       </c>
     </row>
-    <row r="307" spans="1:2">
+    <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="B307" s="4">
+      <c r="B307" s="4" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="308" spans="1:2">
+    <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="B308" s="4">
+      <c r="B308" s="4" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="309" spans="1:2">
+    <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="B309" s="4">
+      <c r="B309" s="4" t="n">
         <v>57</v>
       </c>
     </row>
-    <row r="310" spans="1:2">
+    <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="B310" s="4">
+      <c r="B310" s="4" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="311" spans="1:2">
+    <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="B311" s="4">
+      <c r="B311" s="4" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="312" spans="1:2">
+    <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="B312" s="4">
+      <c r="B312" s="4" t="n">
         <v>55</v>
       </c>
     </row>
-    <row r="313" spans="1:2">
+    <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="B313" s="4">
+      <c r="B313" s="4" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="314" spans="1:2">
+    <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="B314" s="4">
+      <c r="B314" s="4" t="n">
         <v>32</v>
       </c>
     </row>
-    <row r="315" spans="1:2">
+    <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="B315" s="4">
+      <c r="B315" s="4" t="n">
         <v>47</v>
       </c>
     </row>
-    <row r="316" spans="1:2">
+    <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="B316" s="4">
+      <c r="B316" s="4" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="317" spans="1:2">
+    <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="B317" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="318" spans="1:2">
+      <c r="B317" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="B318" s="4">
+      <c r="B318" s="4" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="319" spans="1:2">
+    <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="B319" s="4">
+      <c r="B319" s="4" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="320" spans="1:2">
+    <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="B320" s="4">
+      <c r="B320" s="4" t="n">
         <v>161</v>
       </c>
     </row>
-    <row r="321" spans="1:2">
+    <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="B321" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="322" spans="1:2">
+      <c r="B321" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="B322" s="4">
+      <c r="B322" s="4" t="n">
         <v>34</v>
       </c>
     </row>
-    <row r="323" spans="1:2">
+    <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="B323" s="4">
+      <c r="B323" s="4" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="324" spans="1:2">
+    <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="B324" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="325" spans="1:2">
+      <c r="B324" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="B325" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="326" spans="1:2">
+      <c r="B325" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="B326" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="327" spans="1:2">
+      <c r="B326" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="B327" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="328" spans="1:2">
+      <c r="B327" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="B328" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="329" spans="1:2">
+      <c r="B328" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="B329" s="4">
+      <c r="B329" s="4" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="330" spans="1:2">
+    <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="B330" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="331" spans="1:2">
+      <c r="B330" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="B331" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="332" spans="1:2">
+      <c r="B331" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="B332" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="333" spans="1:2">
+      <c r="B332" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="B333" s="4">
+      <c r="B333" s="4" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="334" spans="1:2">
+    <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="B334" s="4">
+      <c r="B334" s="4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="335" spans="1:2">
+    <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="B335" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="336" spans="1:2">
+      <c r="B335" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="B336" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="337" spans="1:2">
+      <c r="B336" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="B337" s="4">
+      <c r="B337" s="4" t="n">
         <v>27</v>
       </c>
     </row>
-    <row r="338" spans="1:2">
+    <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="B338" s="4">
+      <c r="B338" s="4" t="n">
         <v>17</v>
       </c>
     </row>
-    <row r="339" spans="1:2">
+    <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="B339" s="4">
+      <c r="B339" s="4" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="340" spans="1:2">
+    <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="B340" s="4">
+      <c r="B340" s="4" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="341" spans="1:2">
+    <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="B341" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="342" spans="1:2">
+      <c r="B341" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="B342" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="343" spans="1:2">
+      <c r="B342" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="B343" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="344" spans="1:2">
+      <c r="B343" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="B344" s="4">
+      <c r="B344" s="4" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="345" spans="1:2">
+    <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="B345" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="346" spans="1:2">
+      <c r="B345" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="B346" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="347" spans="1:2">
+      <c r="B346" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="B347" s="4">
+      <c r="B347" s="4" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="348" spans="1:2">
+    <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="B348" s="4">
+      <c r="B348" s="4" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="349" spans="1:2">
+    <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="B349" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="350" spans="1:2">
+      <c r="B349" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="B350" s="4">
+      <c r="B350" s="4" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="351" spans="1:2">
+    <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="B351" s="4">
+      <c r="B351" s="4" t="n">
         <v>97</v>
       </c>
     </row>
-    <row r="352" spans="1:2">
+    <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="B352" s="4">
+      <c r="B352" s="4" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="353" spans="1:2">
+    <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="B353" s="4">
+      <c r="B353" s="4" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="354" spans="1:2">
+    <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="B354" s="4">
+      <c r="B354" s="4" t="n">
         <v>52</v>
       </c>
     </row>
-    <row r="355" spans="1:2">
+    <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="B355" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="356" spans="1:2">
+      <c r="B355" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="B356" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="357" spans="1:2">
+      <c r="B356" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="B357" s="4">
+      <c r="B357" s="4" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="358" spans="1:2">
+    <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="B358" s="4">
+      <c r="B358" s="4" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="359" spans="1:2">
+    <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="B359" s="4">
+      <c r="B359" s="4" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="360" spans="1:2">
+    <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="B360" s="4">
+      <c r="B360" s="4" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="361" spans="1:2">
+    <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="B361" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="362" spans="1:2">
+      <c r="B361" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="B362" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="363" spans="1:2">
+      <c r="B362" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="B363" s="4">
+      <c r="B363" s="4" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="364" spans="1:2">
+    <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="B364" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="365" spans="1:2">
+      <c r="B364" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B365" s="4">
+      <c r="B365" s="4" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="366" spans="1:2">
+    <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="B366" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="367" spans="1:2">
+      <c r="B366" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="B367" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="368" spans="1:2">
+      <c r="B367" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="B368" s="4">
+      <c r="B368" s="4" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="369" spans="1:2">
+    <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="B369" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="370" spans="1:2">
+      <c r="B369" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="B370" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="371" spans="1:2">
+      <c r="B370" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="B371" s="4">
+      <c r="B371" s="4" t="n">
         <v>71</v>
       </c>
     </row>
-    <row r="372" spans="1:2">
+    <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="7" t="s">
         <v>371</v>
       </c>
-      <c r="B372" s="8">
+      <c r="B372" s="8" t="n">
         <v>49</v>
       </c>
     </row>
-    <row r="373" spans="1:2">
+    <row r="373" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="B373" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="374" spans="1:2">
+      <c r="B373" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="5" t="s">
         <v>373</v>
       </c>
-      <c r="B374" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="375" spans="1:2">
+      <c r="B374" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="B375" s="1">
+      <c r="B375" s="1" t="n">
         <v>114</v>
       </c>
     </row>
-    <row r="376" spans="1:2">
+    <row r="376" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="B376" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="377" spans="1:2">
+      <c r="B376" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="B377" s="1">
+      <c r="B377" s="1" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="378" spans="1:2">
+    <row r="378" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="5" t="s">
         <v>377</v>
       </c>
-      <c r="B378" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="379" spans="1:2">
+      <c r="B378" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="B379" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="380" spans="1:2">
+      <c r="B379" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="5" t="s">
         <v>379</v>
       </c>
-      <c r="B380" s="1">
+      <c r="B380" s="1" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="381" spans="1:2">
+    <row r="381" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="B381" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="382" spans="1:2">
+      <c r="B381" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="B382" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="383" spans="1:2">
+      <c r="B382" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="B383" s="1">
+      <c r="B383" s="1" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="384" spans="1:2">
+    <row r="384" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="B384" s="9">
+      <c r="B384" s="9" t="n">
         <v>36</v>
       </c>
     </row>
-    <row r="385" spans="1:2">
+    <row r="385" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="B385" s="1">
+      <c r="B385" s="1" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="386" spans="1:2">
-      <c r="A386" t="s">
+    <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A386" s="0" t="s">
         <v>385</v>
       </c>
-      <c r="B386" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="387" spans="1:2">
-      <c r="A387" t="s">
+      <c r="B386" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A387" s="0" t="s">
         <v>386</v>
       </c>
-      <c r="B387" s="1">
+      <c r="B387" s="1" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="388" spans="1:2">
+    <row r="388" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="10" t="s">
         <v>387</v>
       </c>
-      <c r="B388" s="1">
+      <c r="B388" s="1" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="389" spans="1:2">
+    <row r="389" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="5" t="s">
         <v>388</v>
       </c>
-      <c r="B389" s="9">
+      <c r="B389" s="9" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="390" spans="1:2">
+    <row r="390" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="5" t="s">
         <v>389</v>
       </c>
-      <c r="B390" s="1">
+      <c r="B390" s="1" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="391" spans="1:2">
+    <row r="391" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="10" t="s">
         <v>390</v>
       </c>
-      <c r="B391" s="1">
+      <c r="B391" s="1" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="392" spans="1:2">
+    <row r="392" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="B392" s="1">
+      <c r="B392" s="1" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="393" spans="1:2">
+    <row r="393" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="B393" s="1">
+      <c r="B393" s="1" t="n">
         <v>66</v>
       </c>
     </row>
-    <row r="394" spans="1:2">
+    <row r="394" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A394" s="11" t="s">
         <v>393</v>
       </c>
-      <c r="B394" s="1">
+      <c r="B394" s="1" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <tableParts count="1">
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <tableParts>
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>

--- a/Manga.Manhwua/Updated manhwua.xlsx
+++ b/Manga.Manhwua/Updated manhwua.xlsx
@@ -1368,52 +1368,56 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1715,3159 +1719,3159 @@
   <dimension ref="A1:B394"/>
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="169"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="169"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="13.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="5" t="n">
         <v>878</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="5" t="n">
         <v>266</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="5" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="5" t="n">
         <v>51</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="5" t="n">
         <v>31</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="5" t="n">
         <v>135</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="5" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="5" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="5" t="n">
         <v>292</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="5" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="5" t="n">
         <v>39</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="5" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="5" t="n">
         <v>116</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="5" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="5" t="n">
         <v>73</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="5" t="n">
         <v>223</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="5" t="n">
         <v>162</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="5" t="n">
         <v>102</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" s="5" t="n">
         <v>117</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="5" t="n">
         <v>85</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="5" t="n">
         <v>182</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="4" t="n">
+      <c r="B23" s="5" t="n">
         <v>175</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="4" t="n">
+      <c r="B24" s="5" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="4" t="n">
+      <c r="B25" s="5" t="n">
         <v>31</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="4" t="n">
+      <c r="B26" s="5" t="n">
         <v>10.1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="4" t="n">
+      <c r="B27" s="5" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="4" t="n">
+      <c r="B28" s="5" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="4" t="n">
+      <c r="B29" s="5" t="n">
         <v>54</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="4" t="n">
+      <c r="B30" s="5" t="n">
         <v>105</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="4" t="n">
+      <c r="B31" s="5" t="n">
         <v>77</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="4" t="n">
+      <c r="B32" s="5" t="n">
         <v>37</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="4" t="n">
+      <c r="B33" s="5" t="n">
         <v>88</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="4" t="n">
+      <c r="B34" s="5" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="4" t="n">
+      <c r="B35" s="5" t="n">
         <v>157</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="4" t="n">
+      <c r="B36" s="5" t="n">
         <v>39</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="4" t="n">
+      <c r="B37" s="5" t="n">
         <v>51</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="4" t="n">
+      <c r="B38" s="5" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="4" t="n">
+      <c r="B39" s="5" t="n">
         <v>58</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="4" t="n">
+      <c r="B40" s="5" t="n">
         <v>124</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="4" t="n">
+      <c r="B41" s="5" t="n">
         <v>111</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="4" t="n">
+      <c r="B42" s="5" t="n">
         <v>63</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="4" t="n">
+      <c r="B43" s="5" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B44" s="4" t="n">
+      <c r="B44" s="5" t="n">
         <v>162</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B45" s="4" t="n">
+      <c r="B45" s="5" t="n">
         <v>64</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B46" s="4" t="n">
+      <c r="B46" s="5" t="n">
         <v>140</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="4" t="n">
+      <c r="B47" s="5" t="n">
         <v>168</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="4" t="n">
+      <c r="B48" s="5" t="n">
         <v>186</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B49" s="4" t="n">
+      <c r="B49" s="5" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B50" s="4" t="n">
+      <c r="B50" s="5" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B51" s="4" t="n">
+      <c r="B51" s="5" t="n">
         <v>37</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B52" s="4" t="n">
+      <c r="B52" s="5" t="n">
         <v>71</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="3" t="s">
+      <c r="A53" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B53" s="4" t="n">
+      <c r="B53" s="5" t="n">
         <v>70</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="3" t="s">
+      <c r="A54" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B54" s="4" t="n">
+      <c r="B54" s="5" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B55" s="4" t="n">
+      <c r="B55" s="5" t="n">
         <v>156</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="3" t="s">
+      <c r="A56" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B56" s="4" t="n">
+      <c r="B56" s="5" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="3" t="s">
+      <c r="A57" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B57" s="4" t="n">
+      <c r="B57" s="5" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="3" t="s">
+      <c r="A58" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B58" s="4" t="n">
+      <c r="B58" s="5" t="n">
         <v>144</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B59" s="4" t="n">
+      <c r="B59" s="5" t="n">
         <v>329</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="3" t="s">
+      <c r="A60" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B60" s="4" t="n">
+      <c r="B60" s="5" t="n">
         <v>181</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="3" t="s">
+      <c r="A61" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B61" s="4" t="n">
+      <c r="B61" s="5" t="n">
         <v>275</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="3" t="s">
+      <c r="A62" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B62" s="4" t="n">
+      <c r="B62" s="5" t="n">
         <v>311</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="3" t="s">
+      <c r="A63" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B63" s="4" t="n">
+      <c r="B63" s="5" t="n">
         <v>175</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="3" t="s">
+      <c r="A64" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B64" s="4" t="n">
+      <c r="B64" s="5" t="n">
         <v>58</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="3" t="s">
+      <c r="A65" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B65" s="4" t="n">
+      <c r="B65" s="5" t="n">
         <v>851</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="3" t="s">
+      <c r="A66" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B66" s="4" t="n">
+      <c r="B66" s="5" t="n">
         <v>3644</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="3" t="s">
+      <c r="A67" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B67" s="4" t="n">
+      <c r="B67" s="5" t="n">
         <v>46</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="3" t="s">
+      <c r="A68" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B68" s="4" t="n">
+      <c r="B68" s="5" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="3" t="s">
+      <c r="A69" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B69" s="4" t="n">
+      <c r="B69" s="5" t="n">
         <v>76</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="3" t="s">
+      <c r="A70" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B70" s="4" t="n">
+      <c r="B70" s="5" t="n">
         <v>220</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="3" t="s">
+      <c r="A71" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B71" s="4" t="n">
+      <c r="B71" s="5" t="n">
         <v>29</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="3" t="s">
+      <c r="A72" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B72" s="4" t="n">
+      <c r="B72" s="5" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="3" t="s">
+      <c r="A73" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B73" s="4" t="n">
+      <c r="B73" s="5" t="n">
         <v>89</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="3" t="s">
+      <c r="A74" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B74" s="4" t="n">
+      <c r="B74" s="5" t="n">
         <v>508.1</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="3" t="s">
+      <c r="A75" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B75" s="4" t="n">
+      <c r="B75" s="5" t="n">
         <v>43</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="3" t="s">
+      <c r="A76" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B76" s="4" t="n">
+      <c r="B76" s="5" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="3" t="s">
+      <c r="A77" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B77" s="4" t="n">
+      <c r="B77" s="5" t="n">
         <v>587</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="3" t="s">
+      <c r="A78" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B78" s="4" t="n">
+      <c r="B78" s="5" t="n">
         <v>121</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="3" t="s">
+      <c r="A79" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B79" s="4" t="n">
+      <c r="B79" s="5" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="3" t="s">
+      <c r="A80" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B80" s="4" t="n">
+      <c r="B80" s="5" t="n">
         <v>157</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="3" t="s">
+      <c r="A81" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B81" s="4" t="n">
+      <c r="B81" s="5" t="n">
         <v>156</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="3" t="s">
+      <c r="A82" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B82" s="4" t="n">
+      <c r="B82" s="5" t="n">
         <v>235</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="3" t="s">
+      <c r="A83" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B83" s="4" t="n">
+      <c r="B83" s="5" t="n">
         <v>188</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="3" t="s">
+      <c r="A84" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B84" s="4" t="n">
+      <c r="B84" s="5" t="n">
         <v>106</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="3" t="s">
+      <c r="A85" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B85" s="4" t="n">
+      <c r="B85" s="5" t="n">
         <v>46</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="3" t="s">
+      <c r="A86" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B86" s="4" t="n">
+      <c r="B86" s="5" t="n">
         <v>33</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="3" t="s">
+      <c r="A87" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B87" s="4" t="n">
+      <c r="B87" s="5" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="3" t="s">
+      <c r="A88" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B88" s="4" t="n">
+      <c r="B88" s="5" t="n">
         <v>187</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="3" t="s">
+      <c r="A89" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B89" s="4" t="n">
+      <c r="B89" s="5" t="n">
         <v>256</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="3" t="s">
+      <c r="A90" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B90" s="4" t="n">
+      <c r="B90" s="5" t="n">
         <v>133</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="3" t="s">
+      <c r="A91" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B91" s="4" t="n">
+      <c r="B91" s="5" t="n">
         <v>217</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="3" t="s">
+      <c r="A92" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B92" s="4" t="n">
+      <c r="B92" s="5" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="3" t="s">
+      <c r="A93" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B93" s="4" t="n">
+      <c r="B93" s="5" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="3" t="s">
+      <c r="A94" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B94" s="4" t="n">
+      <c r="B94" s="5" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="3" t="s">
+      <c r="A95" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B95" s="4" t="n">
+      <c r="B95" s="5" t="n">
         <v>56</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="3" t="s">
+      <c r="A96" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B96" s="4" t="n">
+      <c r="B96" s="5" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="3" t="s">
+      <c r="A97" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B97" s="5" t="n">
         <v>52</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="3" t="s">
+      <c r="A98" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B98" s="4" t="n">
+      <c r="B98" s="5" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="3" t="s">
+      <c r="A99" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B99" s="4" t="n">
+      <c r="B99" s="5" t="n">
         <v>41</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="3" t="s">
+      <c r="A100" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B100" s="4" t="n">
+      <c r="B100" s="5" t="n">
         <v>182</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="3" t="s">
+      <c r="A101" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B101" s="4" t="n">
+      <c r="B101" s="5" t="n">
         <v>157</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="3" t="s">
+      <c r="A102" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B102" s="4" t="n">
+      <c r="B102" s="5" t="n">
         <v>31</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="3" t="s">
+      <c r="A103" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B103" s="4" t="n">
+      <c r="B103" s="5" t="n">
         <v>103</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="3" t="s">
+      <c r="A104" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B104" s="4" t="n">
+      <c r="B104" s="5" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="3" t="s">
+      <c r="A105" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B105" s="4" t="n">
+      <c r="B105" s="5" t="n">
         <v>94</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="3" t="s">
+      <c r="A106" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B106" s="4" t="n">
+      <c r="B106" s="5" t="n">
         <v>221</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="3" t="s">
+      <c r="A107" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B107" s="4" t="n">
+      <c r="B107" s="5" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="3" t="s">
+      <c r="A108" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B108" s="4" t="n">
+      <c r="B108" s="5" t="n">
         <v>61</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="3" t="s">
+      <c r="A109" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B109" s="4" t="n">
+      <c r="B109" s="5" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="3" t="s">
+      <c r="A110" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B110" s="4" t="n">
+      <c r="B110" s="5" t="n">
         <v>10.1</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="3" t="s">
+      <c r="A111" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B111" s="4" t="n">
+      <c r="B111" s="5" t="n">
         <v>79</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="3" t="s">
+      <c r="A112" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="B112" s="4" t="n">
+      <c r="B112" s="5" t="n">
         <v>46</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="3" t="s">
+      <c r="A113" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B113" s="4" t="n">
+      <c r="B113" s="5" t="n">
         <v>34</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="3" t="s">
+      <c r="A114" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B114" s="4" t="n">
+      <c r="B114" s="5" t="n">
         <v>38.1</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="3" t="s">
+      <c r="A115" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B115" s="4" t="n">
+      <c r="B115" s="5" t="n">
         <v>63</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="3" t="s">
+      <c r="A116" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B116" s="4" t="n">
+      <c r="B116" s="5" t="n">
         <v>31</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="3" t="s">
+      <c r="A117" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B117" s="4" t="n">
+      <c r="B117" s="5" t="n">
         <v>29</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="3" t="s">
+      <c r="A118" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B118" s="4" t="n">
+      <c r="B118" s="5" t="n">
         <v>49</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="3" t="s">
+      <c r="A119" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B119" s="4" t="n">
+      <c r="B119" s="5" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="3" t="s">
+      <c r="A120" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B120" s="4" t="n">
+      <c r="B120" s="5" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="3" t="s">
+      <c r="A121" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B121" s="4" t="n">
+      <c r="B121" s="5" t="n">
         <v>43</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="3" t="s">
+      <c r="A122" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B122" s="4" t="n">
+      <c r="B122" s="5" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="3" t="s">
+      <c r="A123" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B123" s="4" t="n">
+      <c r="B123" s="5" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="3" t="s">
+      <c r="A124" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="B124" s="4" t="n">
+      <c r="B124" s="5" t="n">
         <v>33</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="3" t="s">
+      <c r="A125" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B125" s="4" t="n">
+      <c r="B125" s="5" t="n">
         <v>7.2</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="3" t="s">
+      <c r="A126" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B126" s="4" t="n">
+      <c r="B126" s="5" t="n">
         <v>29</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="3" t="s">
+      <c r="A127" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B127" s="4" t="n">
+      <c r="B127" s="5" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="3" t="s">
+      <c r="A128" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B128" s="4" t="n">
+      <c r="B128" s="5" t="n">
         <v>58</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="3" t="s">
+      <c r="A129" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B129" s="4" t="n">
+      <c r="B129" s="5" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="3" t="s">
+      <c r="A130" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B130" s="4" t="n">
+      <c r="B130" s="5" t="n">
         <v>54</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="3" t="s">
+      <c r="A131" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B131" s="4" t="n">
+      <c r="B131" s="5" t="n">
         <v>37</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="3" t="s">
+      <c r="A132" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B132" s="4" t="n">
+      <c r="B132" s="5" t="n">
         <v>56</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="3" t="s">
+      <c r="A133" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B133" s="4" t="n">
+      <c r="B133" s="5" t="n">
         <v>12.2</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="3" t="s">
+      <c r="A134" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B134" s="4" t="n">
+      <c r="B134" s="5" t="n">
         <v>91</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="3" t="s">
+      <c r="A135" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B135" s="4" t="n">
+      <c r="B135" s="5" t="n">
         <v>165</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="3" t="s">
+      <c r="A136" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B136" s="4" t="n">
+      <c r="B136" s="5" t="n">
         <v>135</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="3" t="s">
+      <c r="A137" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B137" s="4" t="n">
+      <c r="B137" s="5" t="n">
         <v>92</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="3" t="s">
+      <c r="A138" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B138" s="4" t="n">
+      <c r="B138" s="5" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="3" t="s">
+      <c r="A139" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="B139" s="4" t="n">
+      <c r="B139" s="5" t="n">
         <v>31</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="3" t="s">
+      <c r="A140" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B140" s="4" t="n">
+      <c r="B140" s="5" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B141" s="5" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B142" s="5" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B143" s="5" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B144" s="5" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B145" s="5" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B146" s="5" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B147" s="5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B148" s="5" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B149" s="5" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B150" s="5" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B151" s="5" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B152" s="5" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B153" s="5" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B154" s="5" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B155" s="5" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B156" s="5" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B157" s="5" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B158" s="5" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B159" s="5" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B160" s="5" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B161" s="5" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B162" s="5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B163" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B164" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B165" s="5" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B166" s="5" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B167" s="5" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B168" s="5" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B169" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B170" s="5" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B171" s="5" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B172" s="5" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B173" s="5" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B174" s="5" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B175" s="5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B176" s="5" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B177" s="5" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B178" s="5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B179" s="5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B180" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B181" s="5" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B182" s="5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B183" s="5" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B184" s="5" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B185" s="5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B186" s="5" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B187" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B188" s="5" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B189" s="5" t="n">
         <v>91</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="3" t="s">
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B190" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B191" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B192" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B193" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B194" s="5" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B195" s="5" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B196" s="5" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B197" s="5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B198" s="5" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B199" s="5" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B200" s="5" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B201" s="5" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B202" s="5" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B203" s="5" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B204" s="5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B205" s="5" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B206" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B207" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B208" s="5" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B209" s="5" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B210" s="5" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B211" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B212" s="5" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B213" s="5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B214" s="5" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B215" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B216" s="5" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B217" s="5" t="n">
         <v>141</v>
       </c>
-      <c r="B141" s="4" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B142" s="4" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="B143" s="4" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="B144" s="4" t="n">
+    </row>
+    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B218" s="5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B219" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A220" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B220" s="5" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B221" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A222" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B222" s="5" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A223" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B223" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A224" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B224" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A225" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B225" s="5" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A226" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B226" s="5" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A227" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B227" s="5" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A228" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B228" s="5" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A229" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B229" s="5" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B145" s="4" t="n">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="B146" s="4" t="n">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="B147" s="4" t="n">
+    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A230" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B230" s="5" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A231" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B231" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B232" s="5" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A233" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="B233" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A234" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B234" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A235" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B235" s="5" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A236" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B236" s="5" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B237" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A238" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B238" s="5" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B148" s="4" t="n">
+    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A239" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B239" s="5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A240" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B240" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A241" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B241" s="5" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A242" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B242" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A243" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B243" s="5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A244" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B244" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A245" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B245" s="5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A246" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B246" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A247" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B247" s="5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A248" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B248" s="5" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B149" s="4" t="n">
+    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A249" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B249" s="5" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A250" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="B250" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A251" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B251" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A252" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B252" s="5" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A253" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B253" s="5" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A254" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B254" s="5" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A255" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B255" s="5" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A256" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B256" s="5" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A257" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B257" s="5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A258" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B258" s="5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A259" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B259" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A260" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B260" s="5" t="n">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A261" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B261" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A262" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="B262" s="5" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A263" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B263" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A264" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B264" s="5" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="B150" s="4" t="n">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B151" s="4" t="n">
+    <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A265" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B265" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A266" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B266" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A267" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B267" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A268" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="B268" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A269" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B269" s="5" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A270" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B270" s="5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A271" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B271" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A272" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B272" s="5" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A273" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="B273" s="5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A274" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B274" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A275" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="B275" s="5" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A276" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B276" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A277" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="B277" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A278" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B278" s="5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A279" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="B279" s="5" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A280" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B280" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A281" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B281" s="5" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A282" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B282" s="5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A283" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="B283" s="5" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A284" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B284" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A285" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="B285" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A286" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B286" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A287" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="B287" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A288" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="B288" s="5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A289" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B289" s="5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A290" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B290" s="5" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A291" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="B291" s="5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A292" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B292" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A293" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="B293" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A294" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B294" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A295" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="B295" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A296" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="B296" s="5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A297" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B297" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A298" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="B298" s="5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A299" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B299" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A300" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="B300" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A301" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="B301" s="5" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A302" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="B302" s="5" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A303" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B303" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A304" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="B304" s="5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A305" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="B305" s="5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A306" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="B306" s="5" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A307" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="B307" s="5" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A308" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="B308" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A309" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="B309" s="5" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A310" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="B310" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A311" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="B311" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A312" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="B312" s="5" t="n">
         <v>55</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B152" s="4" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B153" s="4" t="n">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="B154" s="4" t="n">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="B155" s="4" t="n">
+    <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A313" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="B313" s="5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A314" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="B314" s="5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A315" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="B315" s="5" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A316" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="B316" s="5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A317" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="B317" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A318" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="B318" s="5" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A319" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B319" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A320" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B320" s="5" t="n">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A321" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="B321" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A322" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="B322" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A323" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="B323" s="5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A324" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B324" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A325" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="B325" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A326" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="B326" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A327" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="B327" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A328" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="B328" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A329" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="B329" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A330" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B330" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A331" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="B331" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A332" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="B332" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A333" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="B333" s="5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A334" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="B334" s="5" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A335" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="B335" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A336" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="B336" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A337" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="B337" s="5" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A338" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="B338" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A339" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="B339" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A340" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="B340" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A341" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="B341" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A342" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="B342" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A343" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="B343" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A344" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="B344" s="5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A345" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="B345" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A346" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B346" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A347" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="B347" s="5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A348" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="B348" s="5" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A349" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="B349" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A350" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="B350" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A351" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="B351" s="5" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A352" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="B352" s="5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A353" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="B353" s="5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A354" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="B354" s="5" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A355" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="B355" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A356" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="B356" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A357" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="B357" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A358" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="B358" s="5" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B156" s="4" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B157" s="4" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="B158" s="4" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B159" s="4" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B160" s="4" t="n">
+    <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A359" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="B359" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A360" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B360" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A361" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="B361" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A362" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="B362" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A363" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="B363" s="5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A364" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="B364" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A365" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="B365" s="5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A366" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="B366" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A367" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B367" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A368" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="B368" s="5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A369" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="B369" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A370" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="B370" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A371" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="B371" s="5" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A372" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="B372" s="9" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="373" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A373" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="B373" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A374" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="B374" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A375" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="B375" s="2" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="376" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A376" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="B376" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A377" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="B377" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="378" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A378" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="B378" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A379" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="B379" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A380" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="B380" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="381" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A381" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="B381" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A382" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="B382" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A383" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="B383" s="2" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B161" s="4" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="B162" s="4" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B163" s="4" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B164" s="4" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="B165" s="4" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="B166" s="4" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="B167" s="4" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B168" s="4" t="n">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="169" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="B169" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B170" s="4" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="B171" s="4" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B172" s="4" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B173" s="4" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B174" s="4" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="B175" s="4" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="B176" s="4" t="n">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="B177" s="4" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B178" s="4" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="B179" s="4" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="B180" s="4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B181" s="4" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B182" s="4" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="B183" s="4" t="n">
+    <row r="384" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A384" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="B384" s="10" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="385" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A385" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="B385" s="2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A386" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B386" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A387" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B387" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="388" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A388" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="B388" s="2" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="389" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A389" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="B389" s="10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="390" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A390" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="B390" s="2" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B184" s="4" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="B185" s="4" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="B186" s="4" t="n">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B187" s="4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B188" s="4" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="B189" s="4" t="n">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B190" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B191" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B192" s="4" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B193" s="4" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B194" s="4" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="B195" s="4" t="n">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="B196" s="4" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="B197" s="4" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="B198" s="4" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B199" s="4" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="B200" s="4" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="B201" s="4" t="n">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="B202" s="4" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="B203" s="4" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="B204" s="4" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="B205" s="4" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B206" s="4" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B207" s="4" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="208" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="B208" s="4" t="n">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="B209" s="4" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B210" s="4" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="B211" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B212" s="4" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="B213" s="4" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B214" s="4" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B215" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="B216" s="4" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B217" s="4" t="n">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B218" s="4" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B219" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B220" s="4" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B221" s="4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B222" s="4" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B223" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B224" s="4" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B225" s="4" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="B226" s="4" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="B227" s="4" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B228" s="4" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="B229" s="4" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="B230" s="4" t="n">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B231" s="4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="B232" s="4" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="B233" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="B234" s="4" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="B235" s="4" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="B236" s="4" t="n">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="B237" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="B238" s="4" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="B239" s="4" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="B240" s="4" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="B241" s="4" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="B242" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="B243" s="4" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="B244" s="4" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="B245" s="4" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="B246" s="4" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="B247" s="4" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="B248" s="4" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="B249" s="4" t="n">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B250" s="4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="B251" s="4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="B252" s="4" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="B253" s="4" t="n">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="B254" s="4" t="n">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="B255" s="4" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="B256" s="4" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A257" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="B257" s="4" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="B258" s="4" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="B259" s="4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A260" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="B260" s="4" t="n">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="B261" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A262" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="B262" s="4" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A263" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="B263" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A264" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="B264" s="4" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A265" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="B265" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A266" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="B266" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A267" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="B267" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A268" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="B268" s="4" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A269" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="B269" s="4" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A270" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="B270" s="4" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A271" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="B271" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A272" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="B272" s="4" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A273" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="B273" s="4" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A274" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B274" s="4" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A275" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="B275" s="4" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A276" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="B276" s="4" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A277" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="B277" s="4" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A278" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="B278" s="4" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A279" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="B279" s="4" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A280" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="B280" s="4" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A281" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="B281" s="4" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A282" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="B282" s="4" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A283" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="B283" s="4" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A284" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="B284" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A285" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="B285" s="4" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A286" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="B286" s="4" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A287" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="B287" s="4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A288" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="B288" s="4" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A289" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="B289" s="4" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A290" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="B290" s="4" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A291" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="B291" s="4" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A292" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="B292" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A293" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="B293" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A294" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="B294" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A295" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="B295" s="4" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A296" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="B296" s="4" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A297" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="B297" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A298" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="B298" s="4" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A299" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="B299" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A300" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="B300" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A301" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="B301" s="4" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A302" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="B302" s="4" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A303" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="B303" s="4" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A304" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="B304" s="4" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A305" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="B305" s="4" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A306" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="B306" s="4" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A307" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="B307" s="4" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A308" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="B308" s="4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A309" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="B309" s="4" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A310" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="B310" s="4" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A311" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="B311" s="4" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A312" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="B312" s="4" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A313" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="B313" s="4" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A314" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="B314" s="4" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A315" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="B315" s="4" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A316" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="B316" s="4" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A317" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="B317" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A318" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="B318" s="4" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A319" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="B319" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A320" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="B320" s="4" t="n">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A321" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="B321" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A322" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="B322" s="4" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A323" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="B323" s="4" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A324" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="B324" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A325" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="B325" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A326" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B326" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A327" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="B327" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A328" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="B328" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A329" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="B329" s="4" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A330" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="B330" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A331" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="B331" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A332" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="B332" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A333" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="B333" s="4" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A334" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="B334" s="4" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A335" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="B335" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A336" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="B336" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A337" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="B337" s="4" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A338" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="B338" s="4" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A339" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="B339" s="4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A340" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="B340" s="4" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A341" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="B341" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A342" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="B342" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A343" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="B343" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A344" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="B344" s="4" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A345" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="B345" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A346" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="B346" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A347" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="B347" s="4" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A348" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="B348" s="4" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A349" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="B349" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A350" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="B350" s="4" t="n">
+    <row r="391" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A391" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="B391" s="2" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="392" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A392" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="B392" s="2" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A351" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="B351" s="4" t="n">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A352" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="B352" s="4" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A353" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="B353" s="4" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A354" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="B354" s="4" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A355" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="B355" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A356" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="B356" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A357" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="B357" s="4" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A358" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="B358" s="4" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A359" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="B359" s="4" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A360" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="B360" s="4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A361" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="B361" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A362" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="B362" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A363" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="B363" s="4" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A364" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="B364" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A365" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="B365" s="4" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A366" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="B366" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A367" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="B367" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A368" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="B368" s="4" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A369" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="B369" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A370" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="B370" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A371" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="B371" s="4" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A372" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="B372" s="8" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="373" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A373" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="B373" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="374" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A374" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="B374" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="375" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A375" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="B375" s="1" t="n">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="376" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A376" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="B376" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="377" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A377" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="B377" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="378" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A378" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="B378" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="379" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A379" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="B379" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="380" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A380" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="B380" s="1" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="381" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A381" s="5" t="s">
-        <v>380</v>
-      </c>
-      <c r="B381" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="382" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A382" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="B382" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="383" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A383" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="B383" s="1" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="384" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A384" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="B384" s="9" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="385" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A385" s="10" t="s">
-        <v>384</v>
-      </c>
-      <c r="B385" s="1" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A386" s="0" t="s">
-        <v>385</v>
-      </c>
-      <c r="B386" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A387" s="0" t="s">
-        <v>386</v>
-      </c>
-      <c r="B387" s="1" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="388" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A388" s="10" t="s">
-        <v>387</v>
-      </c>
-      <c r="B388" s="1" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="389" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A389" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="B389" s="9" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="390" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A390" s="5" t="s">
-        <v>389</v>
-      </c>
-      <c r="B390" s="1" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="391" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A391" s="10" t="s">
-        <v>390</v>
-      </c>
-      <c r="B391" s="1" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="392" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A392" s="10" t="s">
-        <v>391</v>
-      </c>
-      <c r="B392" s="1" t="n">
-        <v>7</v>
-      </c>
-    </row>
     <row r="393" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A393" s="5" t="s">
+      <c r="A393" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="B393" s="1" t="n">
+      <c r="B393" s="2" t="n">
         <v>66</v>
       </c>
     </row>
     <row r="394" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A394" s="11" t="s">
+      <c r="A394" s="12" t="s">
         <v>393</v>
       </c>
-      <c r="B394" s="1" t="n">
+      <c r="B394" s="2" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Manga.Manhwua/Updated manhwua.xlsx
+++ b/Manga.Manhwua/Updated manhwua.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Manga\Manga.Manhwua\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{562F531B-0038-49BA-9E18-8CCFF62E4DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{238DD9A1-4B2E-4D0B-B477-FDCABFAAB1BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="400">
   <si>
     <t>Title</t>
   </si>
@@ -830,9 +830,6 @@
     <t>Shut Up, Evil Dragon! I Don't Want to Raise a Child With You Anymore</t>
   </si>
   <si>
-    <t>On the Way to Meet Mom</t>
-  </si>
-  <si>
     <t>Ultimate Shut-in</t>
   </si>
   <si>
@@ -1236,19 +1233,54 @@
   </si>
   <si>
     <t>All the Heroes Are My Enemies: The ‘Useless’ Class Dropout Overpowers Everyone With His Barrier Skill and Takes Revenge</t>
+  </si>
+  <si>
+    <t>Whispers of a Scheming Demon</t>
+  </si>
+  <si>
+    <t>The Old Man Vows Revenge Against His Demon Wife</t>
+  </si>
+  <si>
+    <t>On My Way To See My Mom</t>
+  </si>
+  <si>
+    <t>Hand Jumper</t>
+  </si>
+  <si>
+    <t>Resurrection Boy</t>
+  </si>
+  <si>
+    <t>Unholy Blood</t>
+  </si>
+  <si>
+    <t>I'm Gonna Annihilate This Land</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1333,12 +1365,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1350,7 +1382,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1363,6 +1395,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1451,8 +1492,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:B401" totalsRowShown="0">
-  <autoFilter ref="A1:B401" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:B417" totalsRowShown="0">
+  <autoFilter ref="A1:B417" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Title"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Episodes"/>
@@ -1640,7 +1681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B394"/>
+  <dimension ref="A1:B400"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="169" customWidth="1"/>
@@ -1828,7 +1869,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="4">
-        <v>175</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2764,7 +2805,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="4">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -3704,8 +3745,8 @@
       </c>
     </row>
     <row r="258" spans="1:2">
-      <c r="A258" s="3" t="s">
-        <v>258</v>
+      <c r="A258" s="13" t="s">
+        <v>395</v>
       </c>
       <c r="B258" s="4">
         <v>28</v>
@@ -3713,7 +3754,7 @@
     </row>
     <row r="259" spans="1:2">
       <c r="A259" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B259" s="4">
         <v>30</v>
@@ -3721,7 +3762,7 @@
     </row>
     <row r="260" spans="1:2">
       <c r="A260" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B260" s="4">
         <v>219</v>
@@ -3729,7 +3770,7 @@
     </row>
     <row r="261" spans="1:2">
       <c r="A261" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B261" s="4">
         <v>0</v>
@@ -3737,7 +3778,7 @@
     </row>
     <row r="262" spans="1:2">
       <c r="A262" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B262" s="4">
         <v>55</v>
@@ -3745,7 +3786,7 @@
     </row>
     <row r="263" spans="1:2">
       <c r="A263" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B263" s="4">
         <v>1</v>
@@ -3753,7 +3794,7 @@
     </row>
     <row r="264" spans="1:2">
       <c r="A264" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B264" s="4">
         <v>22</v>
@@ -3761,7 +3802,7 @@
     </row>
     <row r="265" spans="1:2">
       <c r="A265" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B265" s="4">
         <v>0</v>
@@ -3769,7 +3810,7 @@
     </row>
     <row r="266" spans="1:2">
       <c r="A266" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B266" s="4">
         <v>0</v>
@@ -3777,7 +3818,7 @@
     </row>
     <row r="267" spans="1:2">
       <c r="A267" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B267" s="4">
         <v>0</v>
@@ -3785,7 +3826,7 @@
     </row>
     <row r="268" spans="1:2">
       <c r="A268" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B268" s="4">
         <v>17</v>
@@ -3793,7 +3834,7 @@
     </row>
     <row r="269" spans="1:2">
       <c r="A269" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B269" s="4">
         <v>18</v>
@@ -3801,7 +3842,7 @@
     </row>
     <row r="270" spans="1:2">
       <c r="A270" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B270" s="4">
         <v>29</v>
@@ -3809,7 +3850,7 @@
     </row>
     <row r="271" spans="1:2">
       <c r="A271" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B271" s="4">
         <v>0</v>
@@ -3817,7 +3858,7 @@
     </row>
     <row r="272" spans="1:2">
       <c r="A272" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B272" s="4">
         <v>22</v>
@@ -3825,7 +3866,7 @@
     </row>
     <row r="273" spans="1:2">
       <c r="A273" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B273" s="4">
         <v>6</v>
@@ -3833,7 +3874,7 @@
     </row>
     <row r="274" spans="1:2">
       <c r="A274" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B274" s="4">
         <v>3</v>
@@ -3841,7 +3882,7 @@
     </row>
     <row r="275" spans="1:2">
       <c r="A275" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B275" s="4">
         <v>45</v>
@@ -3849,7 +3890,7 @@
     </row>
     <row r="276" spans="1:2">
       <c r="A276" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B276" s="4">
         <v>21</v>
@@ -3857,7 +3898,7 @@
     </row>
     <row r="277" spans="1:2">
       <c r="A277" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B277" s="4">
         <v>34</v>
@@ -3865,7 +3906,7 @@
     </row>
     <row r="278" spans="1:2">
       <c r="A278" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B278" s="4">
         <v>40</v>
@@ -3873,7 +3914,7 @@
     </row>
     <row r="279" spans="1:2">
       <c r="A279" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B279" s="4">
         <v>22</v>
@@ -3881,7 +3922,7 @@
     </row>
     <row r="280" spans="1:2">
       <c r="A280" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B280" s="4">
         <v>25</v>
@@ -3889,7 +3930,7 @@
     </row>
     <row r="281" spans="1:2">
       <c r="A281" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B281" s="4">
         <v>45</v>
@@ -3897,7 +3938,7 @@
     </row>
     <row r="282" spans="1:2">
       <c r="A282" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B282" s="4">
         <v>28</v>
@@ -3905,7 +3946,7 @@
     </row>
     <row r="283" spans="1:2">
       <c r="A283" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B283" s="4">
         <v>27</v>
@@ -3913,7 +3954,7 @@
     </row>
     <row r="284" spans="1:2">
       <c r="A284" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B284" s="4">
         <v>0</v>
@@ -3921,7 +3962,7 @@
     </row>
     <row r="285" spans="1:2" ht="15.75">
       <c r="A285" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B285" s="4">
         <v>16</v>
@@ -3929,7 +3970,7 @@
     </row>
     <row r="286" spans="1:2">
       <c r="A286" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B286" s="4">
         <v>4</v>
@@ -3937,7 +3978,7 @@
     </row>
     <row r="287" spans="1:2">
       <c r="A287" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B287" s="4">
         <v>30</v>
@@ -3945,7 +3986,7 @@
     </row>
     <row r="288" spans="1:2">
       <c r="A288" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B288" s="4">
         <v>6</v>
@@ -3953,7 +3994,7 @@
     </row>
     <row r="289" spans="1:2">
       <c r="A289" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B289" s="4">
         <v>6</v>
@@ -3961,7 +4002,7 @@
     </row>
     <row r="290" spans="1:2">
       <c r="A290" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B290" s="4">
         <v>38</v>
@@ -3969,7 +4010,7 @@
     </row>
     <row r="291" spans="1:2">
       <c r="A291" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B291" s="4">
         <v>31</v>
@@ -3977,7 +4018,7 @@
     </row>
     <row r="292" spans="1:2">
       <c r="A292" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B292" s="4">
         <v>0</v>
@@ -3985,7 +4026,7 @@
     </row>
     <row r="293" spans="1:2">
       <c r="A293" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B293" s="4">
         <v>0</v>
@@ -3993,7 +4034,7 @@
     </row>
     <row r="294" spans="1:2">
       <c r="A294" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B294" s="4">
         <v>0</v>
@@ -4001,7 +4042,7 @@
     </row>
     <row r="295" spans="1:2">
       <c r="A295" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B295" s="4">
         <v>25</v>
@@ -4009,7 +4050,7 @@
     </row>
     <row r="296" spans="1:2">
       <c r="A296" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B296" s="4">
         <v>6</v>
@@ -4017,7 +4058,7 @@
     </row>
     <row r="297" spans="1:2">
       <c r="A297" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B297" s="4">
         <v>0</v>
@@ -4025,7 +4066,7 @@
     </row>
     <row r="298" spans="1:2">
       <c r="A298" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B298" s="4">
         <v>29</v>
@@ -4033,7 +4074,7 @@
     </row>
     <row r="299" spans="1:2">
       <c r="A299" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B299" s="4">
         <v>0</v>
@@ -4041,7 +4082,7 @@
     </row>
     <row r="300" spans="1:2">
       <c r="A300" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B300" s="4">
         <v>0</v>
@@ -4049,7 +4090,7 @@
     </row>
     <row r="301" spans="1:2">
       <c r="A301" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B301" s="4">
         <v>56</v>
@@ -4057,7 +4098,7 @@
     </row>
     <row r="302" spans="1:2">
       <c r="A302" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B302" s="4">
         <v>41</v>
@@ -4065,7 +4106,7 @@
     </row>
     <row r="303" spans="1:2">
       <c r="A303" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B303" s="4">
         <v>21</v>
@@ -4073,7 +4114,7 @@
     </row>
     <row r="304" spans="1:2">
       <c r="A304" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B304" s="4">
         <v>9</v>
@@ -4081,7 +4122,7 @@
     </row>
     <row r="305" spans="1:2">
       <c r="A305" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B305" s="4">
         <v>6</v>
@@ -4089,7 +4130,7 @@
     </row>
     <row r="306" spans="1:2">
       <c r="A306" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B306" s="4">
         <v>27</v>
@@ -4097,7 +4138,7 @@
     </row>
     <row r="307" spans="1:2">
       <c r="A307" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B307" s="4">
         <v>15</v>
@@ -4105,7 +4146,7 @@
     </row>
     <row r="308" spans="1:2">
       <c r="A308" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B308" s="4">
         <v>30</v>
@@ -4113,7 +4154,7 @@
     </row>
     <row r="309" spans="1:2">
       <c r="A309" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B309" s="4">
         <v>57</v>
@@ -4121,7 +4162,7 @@
     </row>
     <row r="310" spans="1:2">
       <c r="A310" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B310" s="4">
         <v>21</v>
@@ -4129,7 +4170,7 @@
     </row>
     <row r="311" spans="1:2">
       <c r="A311" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B311" s="4">
         <v>8</v>
@@ -4137,7 +4178,7 @@
     </row>
     <row r="312" spans="1:2">
       <c r="A312" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B312" s="4">
         <v>55</v>
@@ -4145,7 +4186,7 @@
     </row>
     <row r="313" spans="1:2">
       <c r="A313" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B313" s="4">
         <v>28</v>
@@ -4153,7 +4194,7 @@
     </row>
     <row r="314" spans="1:2">
       <c r="A314" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B314" s="4">
         <v>32</v>
@@ -4161,7 +4202,7 @@
     </row>
     <row r="315" spans="1:2">
       <c r="A315" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B315" s="4">
         <v>47</v>
@@ -4169,7 +4210,7 @@
     </row>
     <row r="316" spans="1:2">
       <c r="A316" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B316" s="4">
         <v>6</v>
@@ -4177,7 +4218,7 @@
     </row>
     <row r="317" spans="1:2">
       <c r="A317" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B317" s="4">
         <v>0</v>
@@ -4185,7 +4226,7 @@
     </row>
     <row r="318" spans="1:2">
       <c r="A318" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B318" s="4">
         <v>18</v>
@@ -4193,7 +4234,7 @@
     </row>
     <row r="319" spans="1:2">
       <c r="A319" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B319" s="4">
         <v>20</v>
@@ -4201,7 +4242,7 @@
     </row>
     <row r="320" spans="1:2">
       <c r="A320" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B320" s="4">
         <v>161</v>
@@ -4209,7 +4250,7 @@
     </row>
     <row r="321" spans="1:2">
       <c r="A321" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B321" s="4">
         <v>0</v>
@@ -4217,7 +4258,7 @@
     </row>
     <row r="322" spans="1:2">
       <c r="A322" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B322" s="4">
         <v>34</v>
@@ -4225,7 +4266,7 @@
     </row>
     <row r="323" spans="1:2">
       <c r="A323" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B323" s="4">
         <v>10</v>
@@ -4233,7 +4274,7 @@
     </row>
     <row r="324" spans="1:2">
       <c r="A324" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B324" s="4">
         <v>0</v>
@@ -4241,7 +4282,7 @@
     </row>
     <row r="325" spans="1:2">
       <c r="A325" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B325" s="4">
         <v>0</v>
@@ -4249,7 +4290,7 @@
     </row>
     <row r="326" spans="1:2">
       <c r="A326" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B326" s="4">
         <v>0</v>
@@ -4257,7 +4298,7 @@
     </row>
     <row r="327" spans="1:2">
       <c r="A327" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B327" s="4">
         <v>0</v>
@@ -4265,7 +4306,7 @@
     </row>
     <row r="328" spans="1:2">
       <c r="A328" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B328" s="4">
         <v>0</v>
@@ -4273,7 +4314,7 @@
     </row>
     <row r="329" spans="1:2">
       <c r="A329" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B329" s="4">
         <v>25</v>
@@ -4281,7 +4322,7 @@
     </row>
     <row r="330" spans="1:2">
       <c r="A330" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B330" s="4">
         <v>0</v>
@@ -4289,7 +4330,7 @@
     </row>
     <row r="331" spans="1:2">
       <c r="A331" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B331" s="4">
         <v>0</v>
@@ -4297,7 +4338,7 @@
     </row>
     <row r="332" spans="1:2">
       <c r="A332" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B332" s="4">
         <v>0</v>
@@ -4305,7 +4346,7 @@
     </row>
     <row r="333" spans="1:2">
       <c r="A333" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B333" s="4">
         <v>29</v>
@@ -4313,7 +4354,7 @@
     </row>
     <row r="334" spans="1:2">
       <c r="A334" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B334" s="4">
         <v>38</v>
@@ -4321,7 +4362,7 @@
     </row>
     <row r="335" spans="1:2">
       <c r="A335" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B335" s="4">
         <v>0</v>
@@ -4329,7 +4370,7 @@
     </row>
     <row r="336" spans="1:2">
       <c r="A336" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B336" s="4">
         <v>0</v>
@@ -4337,7 +4378,7 @@
     </row>
     <row r="337" spans="1:2">
       <c r="A337" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B337" s="4">
         <v>27</v>
@@ -4345,7 +4386,7 @@
     </row>
     <row r="338" spans="1:2">
       <c r="A338" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B338" s="4">
         <v>17</v>
@@ -4353,7 +4394,7 @@
     </row>
     <row r="339" spans="1:2">
       <c r="A339" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B339" s="4">
         <v>5</v>
@@ -4361,7 +4402,7 @@
     </row>
     <row r="340" spans="1:2">
       <c r="A340" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B340" s="4">
         <v>8</v>
@@ -4369,7 +4410,7 @@
     </row>
     <row r="341" spans="1:2">
       <c r="A341" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B341" s="4">
         <v>0</v>
@@ -4377,7 +4418,7 @@
     </row>
     <row r="342" spans="1:2">
       <c r="A342" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B342" s="4">
         <v>0</v>
@@ -4385,7 +4426,7 @@
     </row>
     <row r="343" spans="1:2">
       <c r="A343" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B343" s="4">
         <v>0</v>
@@ -4393,7 +4434,7 @@
     </row>
     <row r="344" spans="1:2">
       <c r="A344" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B344" s="4">
         <v>12</v>
@@ -4401,7 +4442,7 @@
     </row>
     <row r="345" spans="1:2">
       <c r="A345" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B345" s="4">
         <v>0</v>
@@ -4409,7 +4450,7 @@
     </row>
     <row r="346" spans="1:2">
       <c r="A346" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B346" s="4">
         <v>0</v>
@@ -4417,7 +4458,7 @@
     </row>
     <row r="347" spans="1:2">
       <c r="A347" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B347" s="4">
         <v>40</v>
@@ -4425,7 +4466,7 @@
     </row>
     <row r="348" spans="1:2">
       <c r="A348" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B348" s="4">
         <v>44</v>
@@ -4433,7 +4474,7 @@
     </row>
     <row r="349" spans="1:2">
       <c r="A349" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B349" s="4">
         <v>0</v>
@@ -4441,7 +4482,7 @@
     </row>
     <row r="350" spans="1:2">
       <c r="A350" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B350" s="4">
         <v>7</v>
@@ -4449,7 +4490,7 @@
     </row>
     <row r="351" spans="1:2">
       <c r="A351" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B351" s="4">
         <v>97</v>
@@ -4457,7 +4498,7 @@
     </row>
     <row r="352" spans="1:2">
       <c r="A352" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B352" s="4">
         <v>29</v>
@@ -4465,7 +4506,7 @@
     </row>
     <row r="353" spans="1:2">
       <c r="A353" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B353" s="4">
         <v>50</v>
@@ -4473,7 +4514,7 @@
     </row>
     <row r="354" spans="1:2">
       <c r="A354" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B354" s="4">
         <v>52</v>
@@ -4481,7 +4522,7 @@
     </row>
     <row r="355" spans="1:2">
       <c r="A355" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B355" s="4">
         <v>0</v>
@@ -4489,7 +4530,7 @@
     </row>
     <row r="356" spans="1:2">
       <c r="A356" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B356" s="4">
         <v>0</v>
@@ -4497,7 +4538,7 @@
     </row>
     <row r="357" spans="1:2">
       <c r="A357" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B357" s="4">
         <v>4</v>
@@ -4505,7 +4546,7 @@
     </row>
     <row r="358" spans="1:2">
       <c r="A358" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B358" s="4">
         <v>15</v>
@@ -4513,7 +4554,7 @@
     </row>
     <row r="359" spans="1:2">
       <c r="A359" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B359" s="4">
         <v>7</v>
@@ -4521,7 +4562,7 @@
     </row>
     <row r="360" spans="1:2">
       <c r="A360" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B360" s="4">
         <v>5</v>
@@ -4529,7 +4570,7 @@
     </row>
     <row r="361" spans="1:2">
       <c r="A361" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B361" s="4">
         <v>0</v>
@@ -4537,7 +4578,7 @@
     </row>
     <row r="362" spans="1:2">
       <c r="A362" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B362" s="4">
         <v>0</v>
@@ -4545,7 +4586,7 @@
     </row>
     <row r="363" spans="1:2">
       <c r="A363" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B363" s="4">
         <v>12</v>
@@ -4553,7 +4594,7 @@
     </row>
     <row r="364" spans="1:2">
       <c r="A364" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B364" s="4">
         <v>0</v>
@@ -4561,7 +4602,7 @@
     </row>
     <row r="365" spans="1:2">
       <c r="A365" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B365" s="4">
         <v>6</v>
@@ -4569,7 +4610,7 @@
     </row>
     <row r="366" spans="1:2">
       <c r="A366" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B366" s="4">
         <v>0</v>
@@ -4577,7 +4618,7 @@
     </row>
     <row r="367" spans="1:2">
       <c r="A367" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B367" s="4">
         <v>0</v>
@@ -4585,7 +4626,7 @@
     </row>
     <row r="368" spans="1:2">
       <c r="A368" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B368" s="4">
         <v>9</v>
@@ -4593,7 +4634,7 @@
     </row>
     <row r="369" spans="1:2">
       <c r="A369" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B369" s="4">
         <v>0</v>
@@ -4601,7 +4642,7 @@
     </row>
     <row r="370" spans="1:2">
       <c r="A370" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B370" s="4">
         <v>0</v>
@@ -4609,7 +4650,7 @@
     </row>
     <row r="371" spans="1:2">
       <c r="A371" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B371" s="4">
         <v>71</v>
@@ -4617,7 +4658,7 @@
     </row>
     <row r="372" spans="1:2">
       <c r="A372" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B372" s="8">
         <v>49</v>
@@ -4625,7 +4666,7 @@
     </row>
     <row r="373" spans="1:2">
       <c r="A373" s="5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B373" s="1">
         <v>0</v>
@@ -4633,7 +4674,7 @@
     </row>
     <row r="374" spans="1:2">
       <c r="A374" s="5" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B374" s="1">
         <v>0</v>
@@ -4641,7 +4682,7 @@
     </row>
     <row r="375" spans="1:2">
       <c r="A375" s="5" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B375" s="1">
         <v>114</v>
@@ -4649,7 +4690,7 @@
     </row>
     <row r="376" spans="1:2">
       <c r="A376" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B376" s="1">
         <v>0</v>
@@ -4657,7 +4698,7 @@
     </row>
     <row r="377" spans="1:2">
       <c r="A377" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B377" s="1">
         <v>3</v>
@@ -4665,7 +4706,7 @@
     </row>
     <row r="378" spans="1:2">
       <c r="A378" s="5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B378" s="1">
         <v>0</v>
@@ -4673,7 +4714,7 @@
     </row>
     <row r="379" spans="1:2">
       <c r="A379" s="5" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B379" s="1">
         <v>0</v>
@@ -4681,7 +4722,7 @@
     </row>
     <row r="380" spans="1:2">
       <c r="A380" s="5" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B380" s="1">
         <v>8</v>
@@ -4689,7 +4730,7 @@
     </row>
     <row r="381" spans="1:2">
       <c r="A381" s="5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B381" s="1">
         <v>0</v>
@@ -4697,7 +4738,7 @@
     </row>
     <row r="382" spans="1:2">
       <c r="A382" s="5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B382" s="1">
         <v>0</v>
@@ -4705,7 +4746,7 @@
     </row>
     <row r="383" spans="1:2">
       <c r="A383" s="5" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B383" s="1">
         <v>26</v>
@@ -4713,7 +4754,7 @@
     </row>
     <row r="384" spans="1:2">
       <c r="A384" s="5" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B384" s="9">
         <v>36</v>
@@ -4721,7 +4762,7 @@
     </row>
     <row r="385" spans="1:2">
       <c r="A385" s="10" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B385" s="1">
         <v>6</v>
@@ -4729,7 +4770,7 @@
     </row>
     <row r="386" spans="1:2">
       <c r="A386" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B386" s="1">
         <v>0</v>
@@ -4737,7 +4778,7 @@
     </row>
     <row r="387" spans="1:2">
       <c r="A387" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B387" s="1">
         <v>8</v>
@@ -4745,7 +4786,7 @@
     </row>
     <row r="388" spans="1:2">
       <c r="A388" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B388" s="1">
         <v>16</v>
@@ -4753,7 +4794,7 @@
     </row>
     <row r="389" spans="1:2">
       <c r="A389" s="5" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B389" s="9">
         <v>5</v>
@@ -4761,7 +4802,7 @@
     </row>
     <row r="390" spans="1:2">
       <c r="A390" s="5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B390" s="1">
         <v>15</v>
@@ -4769,7 +4810,7 @@
     </row>
     <row r="391" spans="1:2">
       <c r="A391" s="10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B391" s="1">
         <v>19</v>
@@ -4777,7 +4818,7 @@
     </row>
     <row r="392" spans="1:2">
       <c r="A392" s="10" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B392" s="1">
         <v>7</v>
@@ -4785,7 +4826,7 @@
     </row>
     <row r="393" spans="1:2">
       <c r="A393" s="5" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B393" s="1">
         <v>66</v>
@@ -4793,17 +4834,65 @@
     </row>
     <row r="394" spans="1:2">
       <c r="A394" t="s">
+        <v>392</v>
+      </c>
+      <c r="B394" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395" s="11" t="s">
         <v>393</v>
       </c>
-      <c r="B394" s="1">
+      <c r="B395" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="B396" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397" t="s">
+        <v>396</v>
+      </c>
+      <c r="B397" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="B398" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399" t="s">
+        <v>398</v>
+      </c>
+      <c r="B399" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="B400" s="1">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Manga.Manhwua/Updated manhwua.xlsx
+++ b/Manga.Manhwua/Updated manhwua.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Manga\Manga.Manhwua\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{238DD9A1-4B2E-4D0B-B477-FDCABFAAB1BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FDD11CB-F123-4334-B3DB-042EC3D32BE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="398">
   <si>
     <t>Title</t>
   </si>
@@ -94,9 +94,6 @@
   </si>
   <si>
     <t>Solo Farming In The Tower</t>
-  </si>
-  <si>
-    <t>Chronicles Of The Demon Faction</t>
   </si>
   <si>
     <t>Demonic Master Of Mount Kunlun</t>
@@ -755,9 +752,6 @@
     <t>Mount Hua Sect's Genius Phantom Swordsman</t>
   </si>
   <si>
-    <t>I'm going to destroy this country</t>
-  </si>
-  <si>
     <t>The New Beggars' Sect</t>
   </si>
   <si>
@@ -1260,13 +1254,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1365,12 +1366,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1382,7 +1383,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1397,11 +1398,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1865,16 +1869,14 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="A23" s="3"/>
       <c r="B23" s="4">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" s="4">
         <v>50</v>
@@ -1882,7 +1884,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" s="4">
         <v>31</v>
@@ -1890,7 +1892,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" s="4">
         <v>10.1</v>
@@ -1898,7 +1900,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" s="4">
         <v>3</v>
@@ -1906,7 +1908,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28" s="4">
         <v>19</v>
@@ -1914,7 +1916,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29" s="4">
         <v>54</v>
@@ -1922,7 +1924,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30" s="4">
         <v>105</v>
@@ -1930,7 +1932,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B31" s="4">
         <v>77</v>
@@ -1938,7 +1940,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B32" s="4">
         <v>37</v>
@@ -1946,7 +1948,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33" s="4">
         <v>88</v>
@@ -1954,7 +1956,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B34" s="4">
         <v>99</v>
@@ -1962,7 +1964,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B35" s="4">
         <v>157</v>
@@ -1970,7 +1972,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B36" s="4">
         <v>39</v>
@@ -1978,7 +1980,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B37" s="4">
         <v>51</v>
@@ -1986,7 +1988,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38" s="4">
         <v>5</v>
@@ -1994,7 +1996,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B39" s="4">
         <v>58</v>
@@ -2002,7 +2004,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40" s="4">
         <v>124</v>
@@ -2010,7 +2012,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" s="4">
         <v>111</v>
@@ -2018,7 +2020,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B42" s="4">
         <v>63</v>
@@ -2026,7 +2028,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B43" s="4">
         <v>45</v>
@@ -2034,7 +2036,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B44" s="4">
         <v>162</v>
@@ -2042,7 +2044,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B45" s="4">
         <v>64</v>
@@ -2050,7 +2052,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B46" s="4">
         <v>140</v>
@@ -2058,7 +2060,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" s="4">
         <v>168</v>
@@ -2066,7 +2068,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B48" s="4">
         <v>186</v>
@@ -2074,7 +2076,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B49" s="4">
         <v>12</v>
@@ -2082,7 +2084,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B50" s="4">
         <v>21</v>
@@ -2090,7 +2092,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B51" s="4">
         <v>37</v>
@@ -2098,7 +2100,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B52" s="4">
         <v>71</v>
@@ -2106,7 +2108,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B53" s="4">
         <v>70</v>
@@ -2114,7 +2116,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B54" s="4">
         <v>25</v>
@@ -2122,7 +2124,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B55" s="4">
         <v>156</v>
@@ -2130,7 +2132,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B56" s="4">
         <v>45</v>
@@ -2138,7 +2140,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B57" s="4">
         <v>22</v>
@@ -2146,7 +2148,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B58" s="4">
         <v>144</v>
@@ -2154,7 +2156,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B59" s="4">
         <v>329</v>
@@ -2162,7 +2164,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B60" s="4">
         <v>181</v>
@@ -2170,7 +2172,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B61" s="4">
         <v>275</v>
@@ -2178,7 +2180,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B62" s="4">
         <v>311</v>
@@ -2186,7 +2188,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B63" s="4">
         <v>175</v>
@@ -2194,7 +2196,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B64" s="4">
         <v>58</v>
@@ -2202,7 +2204,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B65" s="4">
         <v>851</v>
@@ -2210,7 +2212,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B66" s="4">
         <v>3644</v>
@@ -2218,7 +2220,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B67" s="4">
         <v>46</v>
@@ -2226,7 +2228,7 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B68" s="4">
         <v>44</v>
@@ -2234,7 +2236,7 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B69" s="4">
         <v>76</v>
@@ -2242,7 +2244,7 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B70" s="4">
         <v>220</v>
@@ -2250,7 +2252,7 @@
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B71" s="4">
         <v>29</v>
@@ -2258,7 +2260,7 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B72" s="4">
         <v>25</v>
@@ -2266,7 +2268,7 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B73" s="4">
         <v>89</v>
@@ -2274,7 +2276,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B74" s="4">
         <v>508.1</v>
@@ -2282,7 +2284,7 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B75" s="4">
         <v>43</v>
@@ -2290,7 +2292,7 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B76" s="4">
         <v>44</v>
@@ -2298,7 +2300,7 @@
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B77" s="4">
         <v>587</v>
@@ -2306,7 +2308,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B78" s="4">
         <v>121</v>
@@ -2314,7 +2316,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B79" s="4">
         <v>8</v>
@@ -2322,7 +2324,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B80" s="4">
         <v>157</v>
@@ -2330,7 +2332,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B81" s="4">
         <v>156</v>
@@ -2338,7 +2340,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B82" s="4">
         <v>235</v>
@@ -2346,7 +2348,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B83" s="4">
         <v>188</v>
@@ -2354,7 +2356,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B84" s="4">
         <v>106</v>
@@ -2362,7 +2364,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B85" s="4">
         <v>46</v>
@@ -2370,7 +2372,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B86" s="4">
         <v>33</v>
@@ -2378,7 +2380,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B87" s="4">
         <v>15</v>
@@ -2386,7 +2388,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B88" s="4">
         <v>187</v>
@@ -2394,7 +2396,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B89" s="4">
         <v>256</v>
@@ -2402,7 +2404,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B90" s="4">
         <v>133</v>
@@ -2410,7 +2412,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B91" s="4">
         <v>217</v>
@@ -2418,7 +2420,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B92" s="4">
         <v>20</v>
@@ -2426,7 +2428,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B93" s="4">
         <v>11</v>
@@ -2434,7 +2436,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B94" s="4">
         <v>65</v>
@@ -2442,7 +2444,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B95" s="4">
         <v>56</v>
@@ -2450,7 +2452,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B96" s="4">
         <v>25</v>
@@ -2458,7 +2460,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B97" s="4">
         <v>52</v>
@@ -2466,7 +2468,7 @@
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B98" s="4">
         <v>15</v>
@@ -2474,7 +2476,7 @@
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B99" s="4">
         <v>41</v>
@@ -2482,7 +2484,7 @@
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B100" s="4">
         <v>182</v>
@@ -2490,7 +2492,7 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B101" s="4">
         <v>157</v>
@@ -2498,7 +2500,7 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B102" s="4">
         <v>31</v>
@@ -2506,7 +2508,7 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B103" s="4">
         <v>103</v>
@@ -2514,7 +2516,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B104" s="4">
         <v>15</v>
@@ -2522,7 +2524,7 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B105" s="4">
         <v>94</v>
@@ -2530,7 +2532,7 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B106" s="4">
         <v>221</v>
@@ -2538,7 +2540,7 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B107" s="4">
         <v>50</v>
@@ -2546,7 +2548,7 @@
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B108" s="4">
         <v>61</v>
@@ -2554,7 +2556,7 @@
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B109" s="4">
         <v>7</v>
@@ -2562,7 +2564,7 @@
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B110" s="4">
         <v>10.1</v>
@@ -2570,7 +2572,7 @@
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B111" s="4">
         <v>79</v>
@@ -2578,7 +2580,7 @@
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B112" s="4">
         <v>46</v>
@@ -2586,7 +2588,7 @@
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B113" s="4">
         <v>34</v>
@@ -2594,7 +2596,7 @@
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B114" s="4">
         <v>38.1</v>
@@ -2602,7 +2604,7 @@
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B115" s="4">
         <v>63</v>
@@ -2610,7 +2612,7 @@
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B116" s="4">
         <v>31</v>
@@ -2618,7 +2620,7 @@
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B117" s="4">
         <v>29</v>
@@ -2626,7 +2628,7 @@
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B118" s="4">
         <v>49</v>
@@ -2634,7 +2636,7 @@
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B119" s="4">
         <v>20</v>
@@ -2642,7 +2644,7 @@
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B120" s="4">
         <v>20</v>
@@ -2650,7 +2652,7 @@
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B121" s="4">
         <v>43</v>
@@ -2658,7 +2660,7 @@
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B122" s="4">
         <v>19</v>
@@ -2666,7 +2668,7 @@
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B123" s="4">
         <v>25</v>
@@ -2674,7 +2676,7 @@
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B124" s="4">
         <v>33</v>
@@ -2682,7 +2684,7 @@
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B125" s="4">
         <v>7.2</v>
@@ -2690,7 +2692,7 @@
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B126" s="4">
         <v>29</v>
@@ -2698,7 +2700,7 @@
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B127" s="4">
         <v>38</v>
@@ -2706,7 +2708,7 @@
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B128" s="4">
         <v>58</v>
@@ -2714,7 +2716,7 @@
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B129" s="4">
         <v>18</v>
@@ -2722,7 +2724,7 @@
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B130" s="4">
         <v>54</v>
@@ -2730,7 +2732,7 @@
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B131" s="4">
         <v>37</v>
@@ -2738,7 +2740,7 @@
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B132" s="4">
         <v>56</v>
@@ -2746,7 +2748,7 @@
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B133" s="4">
         <v>12.2</v>
@@ -2754,7 +2756,7 @@
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B134" s="4">
         <v>91</v>
@@ -2762,7 +2764,7 @@
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B135" s="4">
         <v>165</v>
@@ -2770,7 +2772,7 @@
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B136" s="4">
         <v>135</v>
@@ -2778,7 +2780,7 @@
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B137" s="4">
         <v>92</v>
@@ -2786,7 +2788,7 @@
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B138" s="4">
         <v>14</v>
@@ -2794,7 +2796,7 @@
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B139" s="4">
         <v>31</v>
@@ -2802,7 +2804,7 @@
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B140" s="4">
         <v>117</v>
@@ -2810,7 +2812,7 @@
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B141" s="4">
         <v>48</v>
@@ -2818,7 +2820,7 @@
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B142" s="4">
         <v>39</v>
@@ -2826,7 +2828,7 @@
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B143" s="4">
         <v>120</v>
@@ -2834,7 +2836,7 @@
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B144" s="4">
         <v>22</v>
@@ -2842,7 +2844,7 @@
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B145" s="4">
         <v>123</v>
@@ -2850,7 +2852,7 @@
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B146" s="4">
         <v>102</v>
@@ -2858,7 +2860,7 @@
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B147" s="4">
         <v>12</v>
@@ -2866,7 +2868,7 @@
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B148" s="4">
         <v>38</v>
@@ -2874,7 +2876,7 @@
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B149" s="4">
         <v>22</v>
@@ -2882,7 +2884,7 @@
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B150" s="4">
         <v>73</v>
@@ -2890,7 +2892,7 @@
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B151" s="4">
         <v>55</v>
@@ -2898,7 +2900,7 @@
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B152" s="4">
         <v>63</v>
@@ -2906,7 +2908,7 @@
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B153" s="4">
         <v>83</v>
@@ -2914,7 +2916,7 @@
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B154" s="4">
         <v>139</v>
@@ -2922,7 +2924,7 @@
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B155" s="4">
         <v>15</v>
@@ -2930,7 +2932,7 @@
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B156" s="4">
         <v>24</v>
@@ -2938,7 +2940,7 @@
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B157" s="4">
         <v>76</v>
@@ -2946,7 +2948,7 @@
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B158" s="4">
         <v>38</v>
@@ -2954,7 +2956,7 @@
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B159" s="4">
         <v>44</v>
@@ -2962,7 +2964,7 @@
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B160" s="4">
         <v>26</v>
@@ -2970,7 +2972,7 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B161" s="4">
         <v>58</v>
@@ -2978,7 +2980,7 @@
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B162" s="4">
         <v>29</v>
@@ -2986,7 +2988,7 @@
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B163" s="4">
         <v>34</v>
@@ -2994,7 +2996,7 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B164" s="4">
         <v>11</v>
@@ -3002,7 +3004,7 @@
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B165" s="4">
         <v>18</v>
@@ -3010,7 +3012,7 @@
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B166" s="4">
         <v>26</v>
@@ -3018,7 +3020,7 @@
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B167" s="4">
         <v>61</v>
@@ -3026,7 +3028,7 @@
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B168" s="4">
         <v>108</v>
@@ -3034,7 +3036,7 @@
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B169" s="4">
         <v>20</v>
@@ -3042,7 +3044,7 @@
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B170" s="4">
         <v>49</v>
@@ -3050,7 +3052,7 @@
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B171" s="4">
         <v>54</v>
@@ -3058,7 +3060,7 @@
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B172" s="4">
         <v>74</v>
@@ -3066,7 +3068,7 @@
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B173" s="4">
         <v>61</v>
@@ -3074,7 +3076,7 @@
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B174" s="4">
         <v>37</v>
@@ -3082,7 +3084,7 @@
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B175" s="4">
         <v>40</v>
@@ -3090,7 +3092,7 @@
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B176" s="4">
         <v>104</v>
@@ -3098,7 +3100,7 @@
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B177" s="4">
         <v>76</v>
@@ -3106,7 +3108,7 @@
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B178" s="4">
         <v>100</v>
@@ -3114,7 +3116,7 @@
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B179" s="4">
         <v>50</v>
@@ -3122,7 +3124,7 @@
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B180" s="4">
         <v>30</v>
@@ -3130,7 +3132,7 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B181" s="4">
         <v>45</v>
@@ -3138,7 +3140,7 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B182" s="4">
         <v>9</v>
@@ -3146,7 +3148,7 @@
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B183" s="4">
         <v>15</v>
@@ -3154,7 +3156,7 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B184" s="4">
         <v>37</v>
@@ -3162,7 +3164,7 @@
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B185" s="4">
         <v>28</v>
@@ -3170,7 +3172,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B186" s="4">
         <v>95</v>
@@ -3178,7 +3180,7 @@
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B187" s="4">
         <v>30</v>
@@ -3186,7 +3188,7 @@
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B188" s="4">
         <v>27</v>
@@ -3194,15 +3196,15 @@
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B189" s="4">
-        <v>91</v>
+        <v>110</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B190" s="4">
         <v>0</v>
@@ -3210,7 +3212,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B191" s="4">
         <v>20</v>
@@ -3218,7 +3220,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B192" s="4">
         <v>3</v>
@@ -3226,7 +3228,7 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B193" s="4">
         <v>25</v>
@@ -3234,7 +3236,7 @@
     </row>
     <row r="194" spans="1:2">
       <c r="A194" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B194" s="4">
         <v>54</v>
@@ -3242,7 +3244,7 @@
     </row>
     <row r="195" spans="1:2">
       <c r="A195" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B195" s="4">
         <v>89</v>
@@ -3250,7 +3252,7 @@
     </row>
     <row r="196" spans="1:2">
       <c r="A196" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B196" s="4">
         <v>54</v>
@@ -3258,7 +3260,7 @@
     </row>
     <row r="197" spans="1:2">
       <c r="A197" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B197" s="4">
         <v>29</v>
@@ -3266,7 +3268,7 @@
     </row>
     <row r="198" spans="1:2">
       <c r="A198" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B198" s="4">
         <v>59</v>
@@ -3274,7 +3276,7 @@
     </row>
     <row r="199" spans="1:2">
       <c r="A199" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B199" s="4">
         <v>26</v>
@@ -3282,7 +3284,7 @@
     </row>
     <row r="200" spans="1:2">
       <c r="A200" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B200" s="4">
         <v>26</v>
@@ -3290,7 +3292,7 @@
     </row>
     <row r="201" spans="1:2">
       <c r="A201" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B201" s="4">
         <v>108</v>
@@ -3298,7 +3300,7 @@
     </row>
     <row r="202" spans="1:2">
       <c r="A202" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B202" s="4">
         <v>44</v>
@@ -3306,7 +3308,7 @@
     </row>
     <row r="203" spans="1:2">
       <c r="A203" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B203" s="4">
         <v>15</v>
@@ -3314,7 +3316,7 @@
     </row>
     <row r="204" spans="1:2">
       <c r="A204" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B204" s="4">
         <v>9</v>
@@ -3322,7 +3324,7 @@
     </row>
     <row r="205" spans="1:2">
       <c r="A205" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B205" s="4">
         <v>26</v>
@@ -3330,7 +3332,7 @@
     </row>
     <row r="206" spans="1:2">
       <c r="A206" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B206" s="4">
         <v>17</v>
@@ -3338,7 +3340,7 @@
     </row>
     <row r="207" spans="1:2">
       <c r="A207" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B207" s="4">
         <v>25</v>
@@ -3346,7 +3348,7 @@
     </row>
     <row r="208" spans="1:2">
       <c r="A208" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B208" s="4">
         <v>220</v>
@@ -3354,7 +3356,7 @@
     </row>
     <row r="209" spans="1:2">
       <c r="A209" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B209" s="4">
         <v>22</v>
@@ -3362,7 +3364,7 @@
     </row>
     <row r="210" spans="1:2">
       <c r="A210" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B210" s="4">
         <v>51</v>
@@ -3370,7 +3372,7 @@
     </row>
     <row r="211" spans="1:2">
       <c r="A211" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B211" s="4">
         <v>0</v>
@@ -3378,7 +3380,7 @@
     </row>
     <row r="212" spans="1:2">
       <c r="A212" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B212" s="4">
         <v>60</v>
@@ -3386,7 +3388,7 @@
     </row>
     <row r="213" spans="1:2">
       <c r="A213" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B213" s="4">
         <v>31</v>
@@ -3394,7 +3396,7 @@
     </row>
     <row r="214" spans="1:2">
       <c r="A214" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B214" s="4">
         <v>38</v>
@@ -3402,7 +3404,7 @@
     </row>
     <row r="215" spans="1:2">
       <c r="A215" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B215" s="4">
         <v>0</v>
@@ -3410,7 +3412,7 @@
     </row>
     <row r="216" spans="1:2">
       <c r="A216" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B216" s="4">
         <v>70</v>
@@ -3418,7 +3420,7 @@
     </row>
     <row r="217" spans="1:2">
       <c r="A217" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B217" s="4">
         <v>141</v>
@@ -3426,7 +3428,7 @@
     </row>
     <row r="218" spans="1:2">
       <c r="A218" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B218" s="4">
         <v>31</v>
@@ -3434,7 +3436,7 @@
     </row>
     <row r="219" spans="1:2">
       <c r="A219" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B219" s="4">
         <v>0</v>
@@ -3442,7 +3444,7 @@
     </row>
     <row r="220" spans="1:2">
       <c r="A220" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B220" s="4">
         <v>49</v>
@@ -3450,7 +3452,7 @@
     </row>
     <row r="221" spans="1:2">
       <c r="A221" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B221" s="4">
         <v>30</v>
@@ -3458,7 +3460,7 @@
     </row>
     <row r="222" spans="1:2">
       <c r="A222" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B222" s="4">
         <v>23</v>
@@ -3466,7 +3468,7 @@
     </row>
     <row r="223" spans="1:2">
       <c r="A223" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B223" s="4">
         <v>20</v>
@@ -3474,7 +3476,7 @@
     </row>
     <row r="224" spans="1:2">
       <c r="A224" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B224" s="4">
         <v>21</v>
@@ -3482,7 +3484,7 @@
     </row>
     <row r="225" spans="1:2">
       <c r="A225" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B225" s="4">
         <v>26</v>
@@ -3490,7 +3492,7 @@
     </row>
     <row r="226" spans="1:2">
       <c r="A226" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B226" s="4">
         <v>36</v>
@@ -3498,7 +3500,7 @@
     </row>
     <row r="227" spans="1:2">
       <c r="A227" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B227" s="4">
         <v>64</v>
@@ -3506,7 +3508,7 @@
     </row>
     <row r="228" spans="1:2">
       <c r="A228" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B228" s="4">
         <v>37</v>
@@ -3514,7 +3516,7 @@
     </row>
     <row r="229" spans="1:2">
       <c r="A229" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B229" s="4">
         <v>22</v>
@@ -3522,7 +3524,7 @@
     </row>
     <row r="230" spans="1:2">
       <c r="A230" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B230" s="4">
         <v>124</v>
@@ -3530,7 +3532,7 @@
     </row>
     <row r="231" spans="1:2">
       <c r="A231" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B231" s="4">
         <v>30</v>
@@ -3538,15 +3540,15 @@
     </row>
     <row r="232" spans="1:2">
       <c r="A232" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B232" s="4">
         <v>18</v>
       </c>
     </row>
     <row r="233" spans="1:2">
-      <c r="A233" s="3" t="s">
-        <v>233</v>
+      <c r="A233" s="14" t="s">
+        <v>397</v>
       </c>
       <c r="B233" s="4">
         <v>0</v>
@@ -3554,7 +3556,7 @@
     </row>
     <row r="234" spans="1:2">
       <c r="A234" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B234" s="4">
         <v>16</v>
@@ -3562,7 +3564,7 @@
     </row>
     <row r="235" spans="1:2">
       <c r="A235" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B235" s="4">
         <v>130</v>
@@ -3570,7 +3572,7 @@
     </row>
     <row r="236" spans="1:2">
       <c r="A236" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B236" s="4">
         <v>67</v>
@@ -3578,7 +3580,7 @@
     </row>
     <row r="237" spans="1:2">
       <c r="A237" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B237" s="4">
         <v>20</v>
@@ -3586,7 +3588,7 @@
     </row>
     <row r="238" spans="1:2">
       <c r="A238" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B238" s="4">
         <v>12</v>
@@ -3594,7 +3596,7 @@
     </row>
     <row r="239" spans="1:2">
       <c r="A239" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B239" s="4">
         <v>9</v>
@@ -3602,7 +3604,7 @@
     </row>
     <row r="240" spans="1:2">
       <c r="A240" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B240" s="4">
         <v>21</v>
@@ -3610,7 +3612,7 @@
     </row>
     <row r="241" spans="1:2">
       <c r="A241" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B241" s="4">
         <v>14</v>
@@ -3618,7 +3620,7 @@
     </row>
     <row r="242" spans="1:2">
       <c r="A242" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B242" s="4">
         <v>0</v>
@@ -3626,7 +3628,7 @@
     </row>
     <row r="243" spans="1:2">
       <c r="A243" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B243" s="4">
         <v>12</v>
@@ -3634,7 +3636,7 @@
     </row>
     <row r="244" spans="1:2">
       <c r="A244" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B244" s="4">
         <v>25</v>
@@ -3642,7 +3644,7 @@
     </row>
     <row r="245" spans="1:2">
       <c r="A245" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B245" s="4">
         <v>9</v>
@@ -3650,7 +3652,7 @@
     </row>
     <row r="246" spans="1:2">
       <c r="A246" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B246" s="4">
         <v>8</v>
@@ -3658,7 +3660,7 @@
     </row>
     <row r="247" spans="1:2">
       <c r="A247" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B247" s="4">
         <v>12</v>
@@ -3666,7 +3668,7 @@
     </row>
     <row r="248" spans="1:2">
       <c r="A248" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B248" s="4">
         <v>38</v>
@@ -3674,7 +3676,7 @@
     </row>
     <row r="249" spans="1:2">
       <c r="A249" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B249" s="4">
         <v>81</v>
@@ -3682,7 +3684,7 @@
     </row>
     <row r="250" spans="1:2">
       <c r="A250" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B250" s="4">
         <v>30</v>
@@ -3690,7 +3692,7 @@
     </row>
     <row r="251" spans="1:2">
       <c r="A251" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B251" s="4">
         <v>30</v>
@@ -3698,7 +3700,7 @@
     </row>
     <row r="252" spans="1:2">
       <c r="A252" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B252" s="4">
         <v>57</v>
@@ -3706,7 +3708,7 @@
     </row>
     <row r="253" spans="1:2">
       <c r="A253" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B253" s="4">
         <v>112</v>
@@ -3714,7 +3716,7 @@
     </row>
     <row r="254" spans="1:2">
       <c r="A254" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B254" s="4">
         <v>126</v>
@@ -3722,7 +3724,7 @@
     </row>
     <row r="255" spans="1:2">
       <c r="A255" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B255" s="4">
         <v>44</v>
@@ -3730,7 +3732,7 @@
     </row>
     <row r="256" spans="1:2">
       <c r="A256" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B256" s="4">
         <v>46</v>
@@ -3738,7 +3740,7 @@
     </row>
     <row r="257" spans="1:2">
       <c r="A257" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B257" s="4">
         <v>40</v>
@@ -3746,7 +3748,7 @@
     </row>
     <row r="258" spans="1:2">
       <c r="A258" s="13" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B258" s="4">
         <v>28</v>
@@ -3754,7 +3756,7 @@
     </row>
     <row r="259" spans="1:2">
       <c r="A259" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B259" s="4">
         <v>30</v>
@@ -3762,7 +3764,7 @@
     </row>
     <row r="260" spans="1:2">
       <c r="A260" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B260" s="4">
         <v>219</v>
@@ -3770,7 +3772,7 @@
     </row>
     <row r="261" spans="1:2">
       <c r="A261" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B261" s="4">
         <v>0</v>
@@ -3778,7 +3780,7 @@
     </row>
     <row r="262" spans="1:2">
       <c r="A262" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B262" s="4">
         <v>55</v>
@@ -3786,7 +3788,7 @@
     </row>
     <row r="263" spans="1:2">
       <c r="A263" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B263" s="4">
         <v>1</v>
@@ -3794,7 +3796,7 @@
     </row>
     <row r="264" spans="1:2">
       <c r="A264" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B264" s="4">
         <v>22</v>
@@ -3802,7 +3804,7 @@
     </row>
     <row r="265" spans="1:2">
       <c r="A265" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B265" s="4">
         <v>0</v>
@@ -3810,7 +3812,7 @@
     </row>
     <row r="266" spans="1:2">
       <c r="A266" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B266" s="4">
         <v>0</v>
@@ -3818,7 +3820,7 @@
     </row>
     <row r="267" spans="1:2">
       <c r="A267" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B267" s="4">
         <v>0</v>
@@ -3826,7 +3828,7 @@
     </row>
     <row r="268" spans="1:2">
       <c r="A268" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B268" s="4">
         <v>17</v>
@@ -3834,7 +3836,7 @@
     </row>
     <row r="269" spans="1:2">
       <c r="A269" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B269" s="4">
         <v>18</v>
@@ -3842,7 +3844,7 @@
     </row>
     <row r="270" spans="1:2">
       <c r="A270" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B270" s="4">
         <v>29</v>
@@ -3850,7 +3852,7 @@
     </row>
     <row r="271" spans="1:2">
       <c r="A271" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B271" s="4">
         <v>0</v>
@@ -3858,7 +3860,7 @@
     </row>
     <row r="272" spans="1:2">
       <c r="A272" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B272" s="4">
         <v>22</v>
@@ -3866,7 +3868,7 @@
     </row>
     <row r="273" spans="1:2">
       <c r="A273" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B273" s="4">
         <v>6</v>
@@ -3874,7 +3876,7 @@
     </row>
     <row r="274" spans="1:2">
       <c r="A274" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B274" s="4">
         <v>3</v>
@@ -3882,7 +3884,7 @@
     </row>
     <row r="275" spans="1:2">
       <c r="A275" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B275" s="4">
         <v>45</v>
@@ -3890,7 +3892,7 @@
     </row>
     <row r="276" spans="1:2">
       <c r="A276" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B276" s="4">
         <v>21</v>
@@ -3898,7 +3900,7 @@
     </row>
     <row r="277" spans="1:2">
       <c r="A277" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B277" s="4">
         <v>34</v>
@@ -3906,7 +3908,7 @@
     </row>
     <row r="278" spans="1:2">
       <c r="A278" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B278" s="4">
         <v>40</v>
@@ -3914,7 +3916,7 @@
     </row>
     <row r="279" spans="1:2">
       <c r="A279" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B279" s="4">
         <v>22</v>
@@ -3922,7 +3924,7 @@
     </row>
     <row r="280" spans="1:2">
       <c r="A280" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B280" s="4">
         <v>25</v>
@@ -3930,7 +3932,7 @@
     </row>
     <row r="281" spans="1:2">
       <c r="A281" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B281" s="4">
         <v>45</v>
@@ -3938,7 +3940,7 @@
     </row>
     <row r="282" spans="1:2">
       <c r="A282" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B282" s="4">
         <v>28</v>
@@ -3946,7 +3948,7 @@
     </row>
     <row r="283" spans="1:2">
       <c r="A283" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B283" s="4">
         <v>27</v>
@@ -3954,7 +3956,7 @@
     </row>
     <row r="284" spans="1:2">
       <c r="A284" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B284" s="4">
         <v>0</v>
@@ -3962,7 +3964,7 @@
     </row>
     <row r="285" spans="1:2" ht="15.75">
       <c r="A285" s="6" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B285" s="4">
         <v>16</v>
@@ -3970,7 +3972,7 @@
     </row>
     <row r="286" spans="1:2">
       <c r="A286" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B286" s="4">
         <v>4</v>
@@ -3978,7 +3980,7 @@
     </row>
     <row r="287" spans="1:2">
       <c r="A287" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B287" s="4">
         <v>30</v>
@@ -3986,7 +3988,7 @@
     </row>
     <row r="288" spans="1:2">
       <c r="A288" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B288" s="4">
         <v>6</v>
@@ -3994,7 +3996,7 @@
     </row>
     <row r="289" spans="1:2">
       <c r="A289" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B289" s="4">
         <v>6</v>
@@ -4002,7 +4004,7 @@
     </row>
     <row r="290" spans="1:2">
       <c r="A290" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B290" s="4">
         <v>38</v>
@@ -4010,7 +4012,7 @@
     </row>
     <row r="291" spans="1:2">
       <c r="A291" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B291" s="4">
         <v>31</v>
@@ -4018,7 +4020,7 @@
     </row>
     <row r="292" spans="1:2">
       <c r="A292" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B292" s="4">
         <v>0</v>
@@ -4026,7 +4028,7 @@
     </row>
     <row r="293" spans="1:2">
       <c r="A293" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B293" s="4">
         <v>0</v>
@@ -4034,7 +4036,7 @@
     </row>
     <row r="294" spans="1:2">
       <c r="A294" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B294" s="4">
         <v>0</v>
@@ -4042,7 +4044,7 @@
     </row>
     <row r="295" spans="1:2">
       <c r="A295" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B295" s="4">
         <v>25</v>
@@ -4050,7 +4052,7 @@
     </row>
     <row r="296" spans="1:2">
       <c r="A296" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B296" s="4">
         <v>6</v>
@@ -4058,7 +4060,7 @@
     </row>
     <row r="297" spans="1:2">
       <c r="A297" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B297" s="4">
         <v>0</v>
@@ -4066,7 +4068,7 @@
     </row>
     <row r="298" spans="1:2">
       <c r="A298" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B298" s="4">
         <v>29</v>
@@ -4074,7 +4076,7 @@
     </row>
     <row r="299" spans="1:2">
       <c r="A299" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B299" s="4">
         <v>0</v>
@@ -4082,7 +4084,7 @@
     </row>
     <row r="300" spans="1:2">
       <c r="A300" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B300" s="4">
         <v>0</v>
@@ -4090,7 +4092,7 @@
     </row>
     <row r="301" spans="1:2">
       <c r="A301" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B301" s="4">
         <v>56</v>
@@ -4098,7 +4100,7 @@
     </row>
     <row r="302" spans="1:2">
       <c r="A302" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B302" s="4">
         <v>41</v>
@@ -4106,7 +4108,7 @@
     </row>
     <row r="303" spans="1:2">
       <c r="A303" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B303" s="4">
         <v>21</v>
@@ -4114,7 +4116,7 @@
     </row>
     <row r="304" spans="1:2">
       <c r="A304" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B304" s="4">
         <v>9</v>
@@ -4122,7 +4124,7 @@
     </row>
     <row r="305" spans="1:2">
       <c r="A305" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B305" s="4">
         <v>6</v>
@@ -4130,7 +4132,7 @@
     </row>
     <row r="306" spans="1:2">
       <c r="A306" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B306" s="4">
         <v>27</v>
@@ -4138,7 +4140,7 @@
     </row>
     <row r="307" spans="1:2">
       <c r="A307" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B307" s="4">
         <v>15</v>
@@ -4146,7 +4148,7 @@
     </row>
     <row r="308" spans="1:2">
       <c r="A308" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B308" s="4">
         <v>30</v>
@@ -4154,7 +4156,7 @@
     </row>
     <row r="309" spans="1:2">
       <c r="A309" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B309" s="4">
         <v>57</v>
@@ -4162,7 +4164,7 @@
     </row>
     <row r="310" spans="1:2">
       <c r="A310" s="3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B310" s="4">
         <v>21</v>
@@ -4170,7 +4172,7 @@
     </row>
     <row r="311" spans="1:2">
       <c r="A311" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B311" s="4">
         <v>8</v>
@@ -4178,7 +4180,7 @@
     </row>
     <row r="312" spans="1:2">
       <c r="A312" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B312" s="4">
         <v>55</v>
@@ -4186,7 +4188,7 @@
     </row>
     <row r="313" spans="1:2">
       <c r="A313" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B313" s="4">
         <v>28</v>
@@ -4194,7 +4196,7 @@
     </row>
     <row r="314" spans="1:2">
       <c r="A314" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B314" s="4">
         <v>32</v>
@@ -4202,7 +4204,7 @@
     </row>
     <row r="315" spans="1:2">
       <c r="A315" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B315" s="4">
         <v>47</v>
@@ -4210,7 +4212,7 @@
     </row>
     <row r="316" spans="1:2">
       <c r="A316" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B316" s="4">
         <v>6</v>
@@ -4218,7 +4220,7 @@
     </row>
     <row r="317" spans="1:2">
       <c r="A317" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B317" s="4">
         <v>0</v>
@@ -4226,7 +4228,7 @@
     </row>
     <row r="318" spans="1:2">
       <c r="A318" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B318" s="4">
         <v>18</v>
@@ -4234,7 +4236,7 @@
     </row>
     <row r="319" spans="1:2">
       <c r="A319" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B319" s="4">
         <v>20</v>
@@ -4242,7 +4244,7 @@
     </row>
     <row r="320" spans="1:2">
       <c r="A320" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B320" s="4">
         <v>161</v>
@@ -4250,7 +4252,7 @@
     </row>
     <row r="321" spans="1:2">
       <c r="A321" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B321" s="4">
         <v>0</v>
@@ -4258,7 +4260,7 @@
     </row>
     <row r="322" spans="1:2">
       <c r="A322" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B322" s="4">
         <v>34</v>
@@ -4266,7 +4268,7 @@
     </row>
     <row r="323" spans="1:2">
       <c r="A323" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B323" s="4">
         <v>10</v>
@@ -4274,7 +4276,7 @@
     </row>
     <row r="324" spans="1:2">
       <c r="A324" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B324" s="4">
         <v>0</v>
@@ -4282,7 +4284,7 @@
     </row>
     <row r="325" spans="1:2">
       <c r="A325" s="3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B325" s="4">
         <v>0</v>
@@ -4290,7 +4292,7 @@
     </row>
     <row r="326" spans="1:2">
       <c r="A326" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B326" s="4">
         <v>0</v>
@@ -4298,7 +4300,7 @@
     </row>
     <row r="327" spans="1:2">
       <c r="A327" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B327" s="4">
         <v>0</v>
@@ -4306,7 +4308,7 @@
     </row>
     <row r="328" spans="1:2">
       <c r="A328" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B328" s="4">
         <v>0</v>
@@ -4314,7 +4316,7 @@
     </row>
     <row r="329" spans="1:2">
       <c r="A329" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B329" s="4">
         <v>25</v>
@@ -4322,7 +4324,7 @@
     </row>
     <row r="330" spans="1:2">
       <c r="A330" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B330" s="4">
         <v>0</v>
@@ -4330,7 +4332,7 @@
     </row>
     <row r="331" spans="1:2">
       <c r="A331" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B331" s="4">
         <v>0</v>
@@ -4338,7 +4340,7 @@
     </row>
     <row r="332" spans="1:2">
       <c r="A332" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B332" s="4">
         <v>0</v>
@@ -4346,7 +4348,7 @@
     </row>
     <row r="333" spans="1:2">
       <c r="A333" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B333" s="4">
         <v>29</v>
@@ -4354,7 +4356,7 @@
     </row>
     <row r="334" spans="1:2">
       <c r="A334" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B334" s="4">
         <v>38</v>
@@ -4362,7 +4364,7 @@
     </row>
     <row r="335" spans="1:2">
       <c r="A335" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B335" s="4">
         <v>0</v>
@@ -4370,7 +4372,7 @@
     </row>
     <row r="336" spans="1:2">
       <c r="A336" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B336" s="4">
         <v>0</v>
@@ -4378,7 +4380,7 @@
     </row>
     <row r="337" spans="1:2">
       <c r="A337" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B337" s="4">
         <v>27</v>
@@ -4386,7 +4388,7 @@
     </row>
     <row r="338" spans="1:2">
       <c r="A338" s="3" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B338" s="4">
         <v>17</v>
@@ -4394,7 +4396,7 @@
     </row>
     <row r="339" spans="1:2">
       <c r="A339" s="3" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B339" s="4">
         <v>5</v>
@@ -4402,7 +4404,7 @@
     </row>
     <row r="340" spans="1:2">
       <c r="A340" s="3" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B340" s="4">
         <v>8</v>
@@ -4410,7 +4412,7 @@
     </row>
     <row r="341" spans="1:2">
       <c r="A341" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B341" s="4">
         <v>0</v>
@@ -4418,7 +4420,7 @@
     </row>
     <row r="342" spans="1:2">
       <c r="A342" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B342" s="4">
         <v>0</v>
@@ -4426,7 +4428,7 @@
     </row>
     <row r="343" spans="1:2">
       <c r="A343" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B343" s="4">
         <v>0</v>
@@ -4434,7 +4436,7 @@
     </row>
     <row r="344" spans="1:2">
       <c r="A344" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B344" s="4">
         <v>12</v>
@@ -4442,7 +4444,7 @@
     </row>
     <row r="345" spans="1:2">
       <c r="A345" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B345" s="4">
         <v>0</v>
@@ -4450,7 +4452,7 @@
     </row>
     <row r="346" spans="1:2">
       <c r="A346" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B346" s="4">
         <v>0</v>
@@ -4458,7 +4460,7 @@
     </row>
     <row r="347" spans="1:2">
       <c r="A347" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B347" s="4">
         <v>40</v>
@@ -4466,7 +4468,7 @@
     </row>
     <row r="348" spans="1:2">
       <c r="A348" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B348" s="4">
         <v>44</v>
@@ -4474,7 +4476,7 @@
     </row>
     <row r="349" spans="1:2">
       <c r="A349" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B349" s="4">
         <v>0</v>
@@ -4482,7 +4484,7 @@
     </row>
     <row r="350" spans="1:2">
       <c r="A350" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B350" s="4">
         <v>7</v>
@@ -4490,7 +4492,7 @@
     </row>
     <row r="351" spans="1:2">
       <c r="A351" s="3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B351" s="4">
         <v>97</v>
@@ -4498,7 +4500,7 @@
     </row>
     <row r="352" spans="1:2">
       <c r="A352" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B352" s="4">
         <v>29</v>
@@ -4506,7 +4508,7 @@
     </row>
     <row r="353" spans="1:2">
       <c r="A353" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B353" s="4">
         <v>50</v>
@@ -4514,7 +4516,7 @@
     </row>
     <row r="354" spans="1:2">
       <c r="A354" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B354" s="4">
         <v>52</v>
@@ -4522,7 +4524,7 @@
     </row>
     <row r="355" spans="1:2">
       <c r="A355" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B355" s="4">
         <v>0</v>
@@ -4530,7 +4532,7 @@
     </row>
     <row r="356" spans="1:2">
       <c r="A356" s="3" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B356" s="4">
         <v>0</v>
@@ -4538,7 +4540,7 @@
     </row>
     <row r="357" spans="1:2">
       <c r="A357" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B357" s="4">
         <v>4</v>
@@ -4546,7 +4548,7 @@
     </row>
     <row r="358" spans="1:2">
       <c r="A358" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B358" s="4">
         <v>15</v>
@@ -4554,7 +4556,7 @@
     </row>
     <row r="359" spans="1:2">
       <c r="A359" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B359" s="4">
         <v>7</v>
@@ -4562,7 +4564,7 @@
     </row>
     <row r="360" spans="1:2">
       <c r="A360" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B360" s="4">
         <v>5</v>
@@ -4570,7 +4572,7 @@
     </row>
     <row r="361" spans="1:2">
       <c r="A361" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B361" s="4">
         <v>0</v>
@@ -4578,7 +4580,7 @@
     </row>
     <row r="362" spans="1:2">
       <c r="A362" s="3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B362" s="4">
         <v>0</v>
@@ -4586,7 +4588,7 @@
     </row>
     <row r="363" spans="1:2">
       <c r="A363" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B363" s="4">
         <v>12</v>
@@ -4594,7 +4596,7 @@
     </row>
     <row r="364" spans="1:2">
       <c r="A364" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B364" s="4">
         <v>0</v>
@@ -4602,7 +4604,7 @@
     </row>
     <row r="365" spans="1:2">
       <c r="A365" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B365" s="4">
         <v>6</v>
@@ -4610,7 +4612,7 @@
     </row>
     <row r="366" spans="1:2">
       <c r="A366" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B366" s="4">
         <v>0</v>
@@ -4618,7 +4620,7 @@
     </row>
     <row r="367" spans="1:2">
       <c r="A367" s="3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B367" s="4">
         <v>0</v>
@@ -4626,7 +4628,7 @@
     </row>
     <row r="368" spans="1:2">
       <c r="A368" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B368" s="4">
         <v>9</v>
@@ -4634,7 +4636,7 @@
     </row>
     <row r="369" spans="1:2">
       <c r="A369" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B369" s="4">
         <v>0</v>
@@ -4642,7 +4644,7 @@
     </row>
     <row r="370" spans="1:2">
       <c r="A370" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B370" s="4">
         <v>0</v>
@@ -4650,7 +4652,7 @@
     </row>
     <row r="371" spans="1:2">
       <c r="A371" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B371" s="4">
         <v>71</v>
@@ -4658,7 +4660,7 @@
     </row>
     <row r="372" spans="1:2">
       <c r="A372" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B372" s="8">
         <v>49</v>
@@ -4666,7 +4668,7 @@
     </row>
     <row r="373" spans="1:2">
       <c r="A373" s="5" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B373" s="1">
         <v>0</v>
@@ -4674,7 +4676,7 @@
     </row>
     <row r="374" spans="1:2">
       <c r="A374" s="5" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B374" s="1">
         <v>0</v>
@@ -4682,7 +4684,7 @@
     </row>
     <row r="375" spans="1:2">
       <c r="A375" s="5" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B375" s="1">
         <v>114</v>
@@ -4690,7 +4692,7 @@
     </row>
     <row r="376" spans="1:2">
       <c r="A376" s="5" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B376" s="1">
         <v>0</v>
@@ -4698,7 +4700,7 @@
     </row>
     <row r="377" spans="1:2">
       <c r="A377" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B377" s="1">
         <v>3</v>
@@ -4706,7 +4708,7 @@
     </row>
     <row r="378" spans="1:2">
       <c r="A378" s="5" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B378" s="1">
         <v>0</v>
@@ -4714,7 +4716,7 @@
     </row>
     <row r="379" spans="1:2">
       <c r="A379" s="5" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B379" s="1">
         <v>0</v>
@@ -4722,7 +4724,7 @@
     </row>
     <row r="380" spans="1:2">
       <c r="A380" s="5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B380" s="1">
         <v>8</v>
@@ -4730,7 +4732,7 @@
     </row>
     <row r="381" spans="1:2">
       <c r="A381" s="5" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B381" s="1">
         <v>0</v>
@@ -4738,7 +4740,7 @@
     </row>
     <row r="382" spans="1:2">
       <c r="A382" s="5" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B382" s="1">
         <v>0</v>
@@ -4746,7 +4748,7 @@
     </row>
     <row r="383" spans="1:2">
       <c r="A383" s="5" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B383" s="1">
         <v>26</v>
@@ -4754,7 +4756,7 @@
     </row>
     <row r="384" spans="1:2">
       <c r="A384" s="5" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B384" s="9">
         <v>36</v>
@@ -4762,7 +4764,7 @@
     </row>
     <row r="385" spans="1:2">
       <c r="A385" s="10" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B385" s="1">
         <v>6</v>
@@ -4770,7 +4772,7 @@
     </row>
     <row r="386" spans="1:2">
       <c r="A386" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B386" s="1">
         <v>0</v>
@@ -4778,7 +4780,7 @@
     </row>
     <row r="387" spans="1:2">
       <c r="A387" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B387" s="1">
         <v>8</v>
@@ -4786,7 +4788,7 @@
     </row>
     <row r="388" spans="1:2">
       <c r="A388" s="10" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B388" s="1">
         <v>16</v>
@@ -4794,7 +4796,7 @@
     </row>
     <row r="389" spans="1:2">
       <c r="A389" s="5" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B389" s="9">
         <v>5</v>
@@ -4802,7 +4804,7 @@
     </row>
     <row r="390" spans="1:2">
       <c r="A390" s="5" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B390" s="1">
         <v>15</v>
@@ -4810,7 +4812,7 @@
     </row>
     <row r="391" spans="1:2">
       <c r="A391" s="10" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B391" s="1">
         <v>19</v>
@@ -4818,7 +4820,7 @@
     </row>
     <row r="392" spans="1:2">
       <c r="A392" s="10" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B392" s="1">
         <v>7</v>
@@ -4826,7 +4828,7 @@
     </row>
     <row r="393" spans="1:2">
       <c r="A393" s="5" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B393" s="1">
         <v>66</v>
@@ -4834,7 +4836,7 @@
     </row>
     <row r="394" spans="1:2">
       <c r="A394" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B394" s="1">
         <v>0</v>
@@ -4842,7 +4844,7 @@
     </row>
     <row r="395" spans="1:2">
       <c r="A395" s="11" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B395" s="1">
         <v>8</v>
@@ -4850,7 +4852,7 @@
     </row>
     <row r="396" spans="1:2">
       <c r="A396" s="12" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B396" s="1">
         <v>0</v>
@@ -4858,7 +4860,7 @@
     </row>
     <row r="397" spans="1:2">
       <c r="A397" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B397" s="1">
         <v>0</v>
@@ -4866,7 +4868,7 @@
     </row>
     <row r="398" spans="1:2">
       <c r="A398" s="13" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B398" s="1">
         <v>0</v>
@@ -4874,19 +4876,14 @@
     </row>
     <row r="399" spans="1:2">
       <c r="A399" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B399" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="400" spans="1:2">
-      <c r="A400" s="13" t="s">
-        <v>399</v>
-      </c>
-      <c r="B400" s="1">
-        <v>0</v>
-      </c>
+      <c r="A400" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Manga.Manhwua/Updated manhwua.xlsx
+++ b/Manga.Manhwua/Updated manhwua.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Manga\Manga.Manhwua\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FDD11CB-F123-4334-B3DB-042EC3D32BE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB67A93-03CB-4509-B9D6-B88FB8642132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="399">
   <si>
     <t>Title</t>
   </si>
@@ -1249,18 +1249,28 @@
   <si>
     <t>I'm Gonna Annihilate This Land</t>
   </si>
+  <si>
+    <t>The Wandering Knight’s Survival Manual</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1366,12 +1376,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1383,7 +1393,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1398,11 +1408,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3551,7 +3564,7 @@
         <v>397</v>
       </c>
       <c r="B233" s="4">
-        <v>0</v>
+        <v>53</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4883,7 +4896,12 @@
       </c>
     </row>
     <row r="400" spans="1:2">
-      <c r="A400" s="13"/>
+      <c r="A400" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="B400" s="1">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
